--- a/results/job_matches_2026-05-06.xlsx
+++ b/results/job_matches_2026-05-06.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G130"/>
+  <dimension ref="A1:G168"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -853,17 +853,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Software Engineer - DevOps and MLOps</t>
+          <t>Junior DevOps Engineer (GCP)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>San Francisco Bay Area, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Kafka, PostgreSQL, MongoDB, Cassandra</t>
+          <t>AWS, SQS, SNS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2fcad788d48ba696</t>
+          <t>https://www.indeed.com/viewjob?jk=56a30f4a788f09b2</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Junior DevOps Engineer (GCP)</t>
+          <t>Software Engineer, Cloud Infrastructure (Multiple Seniority Levels)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>San Carlos, CA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka</t>
+          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, SQS, ECS, IAM, RDS</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,14 +916,14 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56a30f4a788f09b2</t>
+          <t>https://www.indeed.com/viewjob?jk=07cee960b10bf15e</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Software Engineer, Cloud Infrastructure (Multiple Seniority Levels)</t>
+          <t>Software Engineer - DevOps and MLOps</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>San Carlos, CA, US USA</t>
+          <t>San Francisco Bay Area, CA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, SQS, ECS, IAM, RDS</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Kafka, PostgreSQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07cee960b10bf15e</t>
+          <t>https://www.indeed.com/viewjob?jk=2fcad788d48ba696</t>
         </is>
       </c>
     </row>
@@ -1133,17 +1133,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Sr Data Engineer, Python + Spark (Data Federation skillset - Data Lakehouse - Eg: Starburst) - New York</t>
+          <t>Sr Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Photon</t>
+          <t>Commence</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Leesburg, VA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,34 +1151,34 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, S3, Azure, Databricks, Medallion Architecture, GCP, Spark, PySpark</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, NoSQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7767a92d7d08a3b</t>
+          <t>https://www.indeed.com/viewjob?jk=9093ede7f2269db2</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - ETL, Java</t>
+          <t>Sr Data Engineer, Python + Spark (Data Federation skillset - Data Lakehouse - Eg: Starburst) - New York</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>RevSpring, Inc</t>
+          <t>Photon</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Redshift, S3, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop, Scala</t>
+          <t>AWS, Glue, EMR, S3, Azure, Databricks, Medallion Architecture, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a9c009a05948507</t>
+          <t>https://www.indeed.com/viewjob?jk=f7767a92d7d08a3b</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba5ba3f3a840901f</t>
+          <t>https://www.indeed.com/viewjob?jk=4a9c009a05948507</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec9899d266d7f4ea</t>
+          <t>https://www.indeed.com/viewjob?jk=ba5ba3f3a840901f</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>DevOps Engineer (GCP)</t>
+          <t>Senior Software Engineer - ETL, Java</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>RevSpring, Inc</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark</t>
+          <t>Redshift, S3, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop, Scala</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,14 +1301,14 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d617836814bb437</t>
+          <t>https://www.indeed.com/viewjob?jk=ec9899d266d7f4ea</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Junior GCP Cloud Engineer</t>
+          <t>DevOps Engineer (GCP)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Data Modeling, Kimball</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11aa4a83b27dbdc6</t>
+          <t>https://www.indeed.com/viewjob?jk=9d617836814bb437</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Azure, Google Cloud Platform, GCP, Kafka, NoSQL, Data Modeling, ETL, Talend, Tableau, Splunk</t>
+          <t>IAM, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Data Modeling, Kimball</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3e7636193fed6ce</t>
+          <t>https://www.indeed.com/viewjob?jk=11aa4a83b27dbdc6</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Junior GCP Cloud Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Verisk</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, S3, RDS, Spark, Scala, PostgreSQL, Data Modeling</t>
+          <t>Azure, Google Cloud Platform, GCP, Kafka, NoSQL, Data Modeling, ETL, Talend, Tableau, Splunk</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb57edcbdb36ad26</t>
+          <t>https://www.indeed.com/viewjob?jk=b3e7636193fed6ce</t>
         </is>
       </c>
     </row>
@@ -1483,17 +1483,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>DevOps/AI Ops Administrator</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Verisk</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Event Hubs, Dataflow, Scala, Snowflake, PostgreSQL, Power BI, CI/CD</t>
+          <t>AWS, Glue, Lambda, Athena, S3, RDS, Spark, Scala, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8de348813177f92b</t>
+          <t>https://www.indeed.com/viewjob?jk=cb57edcbdb36ad26</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>DevOps/AI Ops Administrator</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Metropolis</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Glue, SNS, RDS, Spark, PySpark, Scala, Snowflake, SQL Server, MySQL</t>
+          <t>RDS, Azure, Databricks, Event Hubs, Dataflow, Scala, Snowflake, PostgreSQL, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9fd5c209c01d504</t>
+          <t>https://www.indeed.com/viewjob?jk=8de348813177f92b</t>
         </is>
       </c>
     </row>
@@ -1558,12 +1558,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>metropolis</t>
+          <t>Metropolis</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d51453a1afa374b4</t>
+          <t>https://www.indeed.com/viewjob?jk=b9fd5c209c01d504</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Cloud Migration Engineer (GCP)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>metropolis</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, Snowflake, SQL Server</t>
+          <t>AWS, Glue, SNS, RDS, Spark, PySpark, Scala, Snowflake, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb7efc81616340cd</t>
+          <t>https://www.indeed.com/viewjob?jk=d51453a1afa374b4</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Databricks)</t>
+          <t>Software Engineer – ETL, Java</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Infinitive Inc</t>
+          <t>RevSpring, Inc</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,17 +1641,17 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, S3, Azure, Databricks, Unity Catalog, GCP</t>
+          <t>Redshift, S3, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop, Scala</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aee5e62267dbbb6c</t>
+          <t>https://www.indeed.com/viewjob?jk=3ebdf3dd92985403</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ebdf3dd92985403</t>
+          <t>https://www.indeed.com/viewjob?jk=5c4b1e40555df27f</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c4b1e40555df27f</t>
+          <t>https://www.indeed.com/viewjob?jk=9d1957e3729d8614</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Software Engineer – ETL, Java</t>
+          <t>Cloud Migration Engineer (GCP)</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>RevSpring, Inc</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Redshift, S3, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop, Scala</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d1957e3729d8614</t>
+          <t>https://www.indeed.com/viewjob?jk=fb7efc81616340cd</t>
         </is>
       </c>
     </row>
@@ -1833,17 +1833,17 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Computing Architect 4 (contract)</t>
+          <t>Senior Data Engineer (Databricks)</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Boeing</t>
+          <t>Infinitive Inc</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Ashburn, VA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,34 +1851,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Scala, Kafka, Data Modeling, ELT</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, S3, Azure, Databricks, Unity Catalog, GCP</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83fa749fc70ff9b5</t>
+          <t>https://www.indeed.com/viewjob?jk=aee5e62267dbbb6c</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Terraform MLOps Engineer</t>
+          <t>Computing Architect 4 (contract)</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Boeing</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Vertex AI, Scala, Kafka, NoSQL, MLOps</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Scala, Kafka, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1c091b77ba59917</t>
+          <t>https://www.indeed.com/viewjob?jk=83fa749fc70ff9b5</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Software Developer II</t>
+          <t>Terraform MLOps Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Floor &amp; Decor</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL, Splunk, CI/CD</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Vertex AI, Scala, Kafka, NoSQL, MLOps</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,32 +1931,32 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e331a6c4c6f76859</t>
+          <t>https://www.indeed.com/viewjob?jk=b1c091b77ba59917</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Sr. Streaming Engineer</t>
+          <t>Software Developer II</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Ness Digital Engineering</t>
+          <t>Floor &amp; Decor</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, IAM, RDS, Spark, Scala, Kafka, NoSQL, Splunk</t>
+          <t>RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f90fa0ab3164dcd1</t>
+          <t>https://www.indeed.com/viewjob?jk=e331a6c4c6f76859</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer - Cloud Dev</t>
+          <t>Sr. Streaming Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Transmedics</t>
+          <t>Ness Digital Engineering</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Andover, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, Redshift, Step Functions, S3, SQS, SNS, API Gateway, IAM</t>
+          <t>AWS, Kinesis, S3, IAM, RDS, Spark, Scala, Kafka, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2efe7bed588da272</t>
+          <t>https://www.indeed.com/viewjob?jk=f90fa0ab3164dcd1</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Cloud Service Desk Analyst</t>
+          <t>Senior Software Development Engineer - Cloud Dev</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Transmedics</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Andover, MA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, Azure, Scala, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, Lambda, Kinesis, Redshift, Step Functions, S3, SQS, SNS, API Gateway, IAM</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e883ce8f9ac322fb</t>
+          <t>https://www.indeed.com/viewjob?jk=2efe7bed588da272</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Sr MERN engineer</t>
+          <t>Cloud Service Desk Analyst</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Purple Squirrels Software LLC</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Newark, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, Lambda, S3, ECS, IAM, Azure, Scala, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=edf2effb08935b9f</t>
+          <t>https://www.indeed.com/viewjob?jk=e883ce8f9ac322fb</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>MLOps Engineer</t>
+          <t>Sr MERN engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Purple Squirrels Software LLC</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Newark, CA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,34 +2096,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, S3, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56f1aa48ba26ae3c</t>
+          <t>https://www.indeed.com/viewjob?jk=edf2effb08935b9f</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Junior Cloud Security Analyst</t>
+          <t>MLOps Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,34 +2131,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Databricks, Blob Storage, Unity Catalog, Google Cloud Platform, Spark</t>
+          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb95dfff70e6d2a4</t>
+          <t>https://www.indeed.com/viewjob?jk=56f1aa48ba26ae3c</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Business Intelligence Developer (Healthcare Data, EDI, ETL)</t>
+          <t>Junior Cloud Security Analyst</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>MicroHealth LLC</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Vienna, VA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Scala, Snowflake, SQL Server, PostgreSQL, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, S3, IAM, RDS, Azure, Databricks, Blob Storage, Unity Catalog, Google Cloud Platform, Spark</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ba3d7e28ab6494c</t>
+          <t>https://www.indeed.com/viewjob?jk=cb95dfff70e6d2a4</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Databricks Developer</t>
+          <t>Business Intelligence Developer (Healthcare Data, EDI, ETL)</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Sloan</t>
+          <t>MicroHealth LLC</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Franklin Park, IL, US USA</t>
+          <t>Vienna, VA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, EMR, RDS, Scala, Snowflake, SQL Server, PostgreSQL, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9921503eb16c8225</t>
+          <t>https://www.indeed.com/viewjob?jk=3ba3d7e28ab6494c</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Software Engineer - Specialist</t>
+          <t>Databricks Developer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Sloan</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Franklin Park, IL, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, SQL Server, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=932c71a7f13aa9a1</t>
+          <t>https://www.indeed.com/viewjob?jk=9921503eb16c8225</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>GCP ETL Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Kroll Inc.</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Hadoop, Spark, Kafka, Snowflake, Dimensional Modeling, ETL, Talend</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Scala, Polars, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,14 +2281,14 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5268867584b4379</t>
+          <t>https://www.indeed.com/viewjob?jk=d56048c057634cd1</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>GCP Support Associate</t>
+          <t>GCP ETL Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, MySQL, Splunk, CI/CD</t>
+          <t>AWS, Azure, GCP, Hadoop, Spark, Kafka, Snowflake, Dimensional Modeling, ETL, Talend</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,32 +2316,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29c27657463cb6ea</t>
+          <t>https://www.indeed.com/viewjob?jk=d5268867584b4379</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Software Engineer - Specialist</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Paramount</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Fort Lauderdale, FL, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Dataflow, Scala, MongoDB, NoSQL, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, SQL Server, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,32 +2351,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a12925c69dfc7bed</t>
+          <t>https://www.indeed.com/viewjob?jk=932c71a7f13aa9a1</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>AI Agent Engineer</t>
+          <t>GCP Support Associate</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Momentive Software</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Athena, SQS, SNS, API Gateway, ECS, RDS, Azure, GCP</t>
+          <t>IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, MySQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ac9574b3f75cc2c</t>
+          <t>https://www.indeed.com/viewjob?jk=29c27657463cb6ea</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Cloud Database Engineer (Hybrid - Seattle, WA)</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Moore</t>
+          <t>Nordstrom</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Westminster, CO, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT, dbt</t>
+          <t>AWS, Glue, Kinesis, Redshift, Athena, S3, RDS, Kafka, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8c5af154805cd95</t>
+          <t>https://www.indeed.com/viewjob?jk=1666a61865ef57aa</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Data Engineer (ETL / Python Developer)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>CSpring</t>
+          <t>Moore</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Springfield, IL, US USA</t>
+          <t>Westminster, CO, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b861e2c1a0a03133</t>
+          <t>https://www.indeed.com/viewjob?jk=b8c5af154805cd95</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Imprint</t>
+          <t>Paramount</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Fort Lauderdale, FL, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Kinesis, S3, RDS, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, RDS, GCP, BigQuery, Dataflow, Scala, MongoDB, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e35bafcce4ab1000</t>
+          <t>https://www.indeed.com/viewjob?jk=a12925c69dfc7bed</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer (ETL / Python Developer)</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Imprint</t>
+          <t>CSpring</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Springfield, IL, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Kinesis, S3, RDS, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=baaf38c4500e2b06</t>
+          <t>https://www.indeed.com/viewjob?jk=b861e2c1a0a03133</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior AI Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Velvetech</t>
+          <t>Imprint</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Vertex AI, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD</t>
+          <t>Kinesis, S3, RDS, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2bec7882b34f08c9</t>
+          <t>https://www.indeed.com/viewjob?jk=e35bafcce4ab1000</t>
         </is>
       </c>
     </row>
@@ -2573,12 +2573,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Imprint</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Westminster, CO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT, dbt</t>
+          <t>Kinesis, S3, RDS, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d49164a52434e329</t>
+          <t>https://www.indeed.com/viewjob?jk=baaf38c4500e2b06</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>AWS Data Engineer - Databricks</t>
+          <t>Senior AI Data Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>RadCube</t>
+          <t>Velvetech</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Databricks, Scala, Databricks Lakehouse, Data Modeling</t>
+          <t>AWS, IAM, Azure, GCP, Vertex AI, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2dcfccb6b6d90b1</t>
+          <t>https://www.indeed.com/viewjob?jk=2bec7882b34f08c9</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Software Engineer - Cloud</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Carnegie Robotics LLC</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Westminster, CO, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, PostgreSQL, MongoDB, DynamoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2f5b0b9c556cdca</t>
+          <t>https://www.indeed.com/viewjob?jk=d49164a52434e329</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Python/PySpark/AWS)</t>
+          <t>AWS Data Engineer - Databricks</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Infinitive Inc</t>
+          <t>RadCube</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Azure, Spark, PySpark, Scala, Spark Streaming, Data Modeling, ETL, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Databricks, Scala, Databricks Lakehouse, Data Modeling</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2025-02-18</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45083db400feff94</t>
+          <t>https://www.indeed.com/viewjob?jk=d2dcfccb6b6d90b1</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Data Engineer (Python/PySpark/AWS)</t>
+          <t>Software Engineer - Cloud</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Infinitive Inc</t>
+          <t>Carnegie Robotics LLC</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Azure, Spark, PySpark, Scala, Spark Streaming, Data Modeling, ETL, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, PostgreSQL, MongoDB, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2025-01-27</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e742c4bedd2037b</t>
+          <t>https://www.indeed.com/viewjob?jk=e2f5b0b9c556cdca</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Full Stack Engineer, Experienced</t>
+          <t>Senior Data Engineer (Python/PySpark/AWS)</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Blue Shield of California</t>
+          <t>Infinitive Inc</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Ashburn, VA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, NoSQL, CI/CD, Terraform</t>
+          <t>AWS, Azure, Spark, PySpark, Scala, Spark Streaming, Data Modeling, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2025-02-18</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93fe5a9749607800</t>
+          <t>https://www.indeed.com/viewjob?jk=45083db400feff94</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Full Stack Engineer, Senior</t>
+          <t>Data Engineer (Python/PySpark/AWS)</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Blue Shield of California</t>
+          <t>Infinitive Inc</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Ashburn, VA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, NoSQL, CI/CD, Terraform</t>
+          <t>AWS, Azure, Spark, PySpark, Scala, Spark Streaming, Data Modeling, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2025-01-27</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bcc6fa1baccf83e5</t>
+          <t>https://www.indeed.com/viewjob?jk=5e742c4bedd2037b</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Full Stack Engineer, Consultant</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Blue Shield of California</t>
+          <t>Miami Marlins</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, NoSQL, CI/CD, Terraform</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, GCP, Scala, Snowflake, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3a7d3c5d7336760</t>
+          <t>https://www.indeed.com/viewjob?jk=ff87deef607d5450</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Summer Intern, Platform Engineering</t>
+          <t>AI Agent Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Outfront Media</t>
+          <t>Momentive Software</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD, Docker</t>
+          <t>AWS, Lambda, Athena, SQS, SNS, API Gateway, ECS, RDS, Azure, GCP</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2aa35bb9483f10ad</t>
+          <t>https://www.indeed.com/viewjob?jk=6ac9574b3f75cc2c</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Java Software Engineer</t>
+          <t>Full Stack Engineer, Experienced</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Blue Shield of California</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=257d265c3f7e2882</t>
+          <t>https://www.indeed.com/viewjob?jk=93fe5a9749607800</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Docker MLOps Engineer</t>
+          <t>Full Stack Engineer, Senior</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Blue Shield of California</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, Kafka, Snowflake, Data Modeling, MLOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3cd445b405cda13</t>
+          <t>https://www.indeed.com/viewjob?jk=bcc6fa1baccf83e5</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Salesforce Data Cloud Architect</t>
+          <t>Full Stack Engineer, Consultant</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Skechers</t>
+          <t>Blue Shield of California</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Manhattan Beach, CA, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ETL, ELT, MLflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebe8dee39468099e</t>
+          <t>https://www.indeed.com/viewjob?jk=a3a7d3c5d7336760</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Customer Centric Engineer</t>
+          <t>Summer Intern, Platform Engineering</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Outfront Media</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Scala, Snowflake, ELT, dbt, Tableau, Docker</t>
+          <t>AWS, Lambda, S3, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,32 +3016,32 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29a2186b968dd17c</t>
+          <t>https://www.indeed.com/viewjob?jk=2aa35bb9483f10ad</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Java Software Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Versant</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, GCP, Spark, NoSQL, ETL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,32 +3051,32 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fbef82ce93a90ed</t>
+          <t>https://www.indeed.com/viewjob?jk=257d265c3f7e2882</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>AI/ML Engineer</t>
+          <t>Docker MLOps Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Redapt inc</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Woodinville, WA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, GCP, Vertex AI, Spark, Snowflake, Data Modeling, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, Kafka, Snowflake, Data Modeling, MLOps</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,14 +3086,14 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9c94059f3dd29b3</t>
+          <t>https://www.indeed.com/viewjob?jk=e3cd445b405cda13</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer - News</t>
+          <t>Customer Centric Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3103,15 +3103,15 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Step Functions, SQS, SNS, RDS, Databricks, Spark</t>
+          <t>AWS, Azure, GCP, BigQuery, Scala, Snowflake, ELT, dbt, Tableau, Docker</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,59 +3121,59 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c5ae4f292525796</t>
+          <t>https://www.indeed.com/viewjob?jk=29a2186b968dd17c</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Data Engineering - E&amp;A - Data Engineer I</t>
+          <t>Salesforce Data Cloud Architect</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Genesis Global Group</t>
+          <t>Skechers</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Myrtle Point, OR, US USA</t>
+          <t>Manhattan Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ETL, ELT, MLflow</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2526bf14df16c3e8</t>
+          <t>https://www.indeed.com/viewjob?jk=ebe8dee39468099e</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior, Data Engineer</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Carrington Mortgage Services, LLC</t>
+          <t>Clayco</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, ETL, Microsoft SSIS</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfdf1b9d489fb8ec</t>
+          <t>https://www.indeed.com/viewjob?jk=61cc49187bd6e01d</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>GCP Support Associate</t>
+          <t>Data Engineering - E&amp;A - Data Engineer I</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Genesis Global Group</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Myrtle Point, OR, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>ECS, IAM, Google Cloud Platform, GCP, Dataflow, Cloud Storage, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9acaddb632586c1</t>
+          <t>https://www.indeed.com/viewjob?jk=2526bf14df16c3e8</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Analytics Engineer (Tableau / Python)</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>CSpring</t>
+          <t>Versant</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Springfield, IL, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Tableau</t>
+          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, GCP, Spark, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a0afa4d54ffc362</t>
+          <t>https://www.indeed.com/viewjob?jk=1fbef82ce93a90ed</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Data Systems Engineer</t>
+          <t>Senior, Data Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Central Health</t>
+          <t>Carrington Mortgage Services, LLC</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,34 +3286,34 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, ETL, Microsoft SSIS</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41eed22913274d81</t>
+          <t>https://www.indeed.com/viewjob?jk=dfdf1b9d489fb8ec</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>GCP Support Associate</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>mSupply</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,34 +3321,34 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Medallion Architecture, Dataflow, Scala, Data Modeling, ETL, ELT</t>
+          <t>ECS, IAM, Google Cloud Platform, GCP, Dataflow, Cloud Storage, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=faaa8b1f4d565bbd</t>
+          <t>https://www.indeed.com/viewjob?jk=a9acaddb632586c1</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Systems Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Victory Live</t>
+          <t>Central Health</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,34 +3356,34 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Snowflake, SQL Server, DynamoDB, ELT, dbt, Terraform</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1c259f0b00d1299</t>
+          <t>https://www.indeed.com/viewjob?jk=41eed22913274d81</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>AI Senior Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Wood Mackenzie</t>
+          <t>mSupply</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,34 +3391,34 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, ECS, Azure, Scala, DynamoDB, ETL, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Medallion Architecture, Dataflow, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69e1b61070a9b37b</t>
+          <t>https://www.indeed.com/viewjob?jk=faaa8b1f4d565bbd</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>AI/ML Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Redapt inc</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Woodinville, WA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,34 +3426,34 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Redshift, Azure, Databricks, GCP, Vertex AI, Spark, Snowflake, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fab02a342213956</t>
+          <t>https://www.indeed.com/viewjob?jk=b9c94059f3dd29b3</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>AI Systems Administrator</t>
+          <t>Senior Machine Learning Engineer - News</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>ECS, RDS, Azure, Databricks, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Glue, Lambda, Kinesis, Step Functions, SQS, SNS, RDS, Databricks, Spark</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a338fa1fa96ea390</t>
+          <t>https://www.indeed.com/viewjob?jk=6c5ae4f292525796</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Sr. ML Engineer – ML &amp; Applied AI</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Gap Inc.</t>
+          <t>Victory Live</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,34 +3496,34 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Snowflake, SQL Server, DynamoDB, ELT, dbt, Terraform</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9323c5e89dc8edb</t>
+          <t>https://www.indeed.com/viewjob?jk=a1c259f0b00d1299</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Sr. ML Engineer – ML &amp; Applied AI</t>
+          <t>AI Senior Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Gap Inc.</t>
+          <t>Wood Mackenzie</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Pleasanton, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,42 +3531,42 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MLOps, CI/CD</t>
+          <t>AWS, Lambda, Redshift, S3, ECS, Azure, Scala, DynamoDB, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7aa4ac97e72f7a6d</t>
+          <t>https://www.indeed.com/viewjob?jk=69e1b61070a9b37b</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI Systems Administrator</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Vertex AI, Scala, Data Modeling, Jenkins, Terraform, Jenkins</t>
+          <t>ECS, RDS, Azure, Databricks, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,94 +3576,94 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bbf23a169f18dbc</t>
+          <t>https://www.indeed.com/viewjob?jk=a338fa1fa96ea390</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. ML Engineer – ML &amp; Applied AI</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Gap Inc.</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Vertex AI, Scala, Data Modeling, Jenkins, Terraform, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b05514433681d42</t>
+          <t>https://www.indeed.com/viewjob?jk=d9323c5e89dc8edb</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. ML Engineer – ML &amp; Applied AI</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Clark Construction</t>
+          <t>Gap Inc.</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Pleasanton, CA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, dbt</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f199bfc2e975b58</t>
+          <t>https://www.indeed.com/viewjob?jk=7aa4ac97e72f7a6d</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Junior GCP Cloud Engineer</t>
+          <t>Snowflake Platform Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, Dataflow, Cloud Storage, Scala, Oracle, ETL, ELT, dbt</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Scala, Snowflake, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=817a2d7d06f177a9</t>
+          <t>https://www.indeed.com/viewjob?jk=ecb6b777a849d07c</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Sr. Professional, Software Engineering (Python)</t>
+          <t>Snowflake Platform Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Cotality</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, Tableau, CI/CD, Terraform</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Scala, Snowflake, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83e013cc49a29087</t>
+          <t>https://www.indeed.com/viewjob?jk=136f0d6f19e6f0c6</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Senior Platform/DevOps Engineer (Kubernetes-Linux)</t>
+          <t>Sr. Professional, Software Engineering (Python)</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>ARMADA</t>
+          <t>Cotality</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, Tableau, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b0e9b75e0f5558d</t>
+          <t>https://www.indeed.com/viewjob?jk=83e013cc49a29087</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Senior Platform/DevOps Engineer (Kubernetes-Linux)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>ARMADA</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Sammamish, WA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>RDS, GCP, BigQuery, Dataflow, Vertex AI, Scala, Data Modeling, Jenkins, Terraform, Jenkins</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=efa4e4e3099a0ae2</t>
+          <t>https://www.indeed.com/viewjob?jk=4bbf23a169f18dbc</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Senior Platform/DevOps Engineer (Kubernetes-Linux)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>ARMADA</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Kirkland, WA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>RDS, GCP, BigQuery, Dataflow, Vertex AI, Scala, Data Modeling, Jenkins, Terraform, Jenkins</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,24 +3821,24 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33ae1f1f9d08c546</t>
+          <t>https://www.indeed.com/viewjob?jk=4b05514433681d42</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Senior Platform/DevOps Engineer (Kubernetes-Linux)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>ARMADA</t>
+          <t>Clark Construction</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Renton, WA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Azure, GCP, Spark, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, dbt</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d25130b996402485</t>
+          <t>https://www.indeed.com/viewjob?jk=6f199bfc2e975b58</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Bothell, WA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6f9224460f3210c</t>
+          <t>https://www.indeed.com/viewjob?jk=7b0e9b75e0f5558d</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Redmond, WA, US USA</t>
+          <t>Sammamish, WA, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b86c940f686047d8</t>
+          <t>https://www.indeed.com/viewjob?jk=efa4e4e3099a0ae2</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Platform/DevOps Engineer (Kubernetes-Linux)</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ARMADA</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Somerville, MA, US USA</t>
+          <t>Kirkland, WA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Scala, Snowflake, ETL, ELT, dbt, Tableau, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75339d7552c524c1</t>
+          <t>https://www.indeed.com/viewjob?jk=33ae1f1f9d08c546</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Sr. Site Reliability Engineer</t>
+          <t>Senior Platform/DevOps Engineer (Kubernetes-Linux)</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>PitchBook</t>
+          <t>ARMADA</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Renton, WA, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, SQL Server, PostgreSQL, MySQL, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=181ce2100b853c3a</t>
+          <t>https://www.indeed.com/viewjob?jk=d25130b996402485</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Senior Data Engineer / Data Architect</t>
+          <t>Senior Platform/DevOps Engineer (Kubernetes-Linux)</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>ARMADA</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Bothell, WA, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e83d1768e75b1203</t>
+          <t>https://www.indeed.com/viewjob?jk=b6f9224460f3210c</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Snowflake Data Movement Engineer</t>
+          <t>Senior Platform/DevOps Engineer (Kubernetes-Linux)</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Smart Tech Skills LLC</t>
+          <t>ARMADA</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Redmond, WA, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, ETL, CI/CD, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,24 +4066,24 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12ef21c70e148f1d</t>
+          <t>https://www.indeed.com/viewjob?jk=b86c940f686047d8</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Site Reliability / Infrastructure Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>General Intuition &amp; Medal</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Somerville, MA, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Scala, MySQL, CI/CD, GitHub Actions, Terraform</t>
+          <t>Redshift, RDS, Azure, Scala, Snowflake, ETL, ELT, dbt, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,24 +4101,24 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a84d1c588e106220</t>
+          <t>https://www.indeed.com/viewjob?jk=75339d7552c524c1</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Kubernetes MLOps Engineer</t>
+          <t>Sr. Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>PitchBook</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, Scala, MLOps, CI/CD</t>
+          <t>AWS, RDS, GCP, Scala, SQL Server, PostgreSQL, MySQL, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,24 +4136,24 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82d92ef7ef6e6f18</t>
+          <t>https://www.indeed.com/viewjob?jk=181ce2100b853c3a</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Full Stack Product Engineer (Java)</t>
+          <t>Junior GCP Cloud Engineer</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Allstate Insurance</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, ELT, CI/CD, Git</t>
+          <t>RDS, Google Cloud Platform, GCP, Dataflow, Cloud Storage, Scala, Oracle, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,24 +4171,24 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d15adff582efc740</t>
+          <t>https://www.indeed.com/viewjob?jk=817a2d7d06f177a9</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>DevOps &amp; Infrastructure Engineer - Level I</t>
+          <t>Senior Data Engineer / Data Architect</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>SPRING ARBOR UNIVERSITY</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Spring Arbor, MI, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Oracle, CI/CD, Jenkins, GitHub Actions, Docker, Jenkins</t>
+          <t>AWS, Kinesis, Redshift, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,24 +4206,24 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0b216de71eb3804</t>
+          <t>https://www.indeed.com/viewjob?jk=e83d1768e75b1203</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Senior GCP Kubernetes Engineer</t>
+          <t>Snowflake Data Movement Engineer</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Smart Tech Skills LLC</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Kafka, Oracle, PostgreSQL, CI/CD, Jenkins, Maven</t>
+          <t>RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, ETL, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,24 +4241,24 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a77679969db6e94b</t>
+          <t>https://www.indeed.com/viewjob?jk=12ef21c70e148f1d</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer, Enterprise Technology</t>
+          <t>Site Reliability / Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Rivian</t>
+          <t>General Intuition &amp; Medal</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,24 +4266,24 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MySQL, NoSQL, Splunk, Docker, Kubernetes</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Scala, MySQL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fab081dda06a1ba5</t>
+          <t>https://www.indeed.com/viewjob?jk=a84d1c588e106220</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Senior GCP IAM Engineer</t>
+          <t>Kubernetes MLOps Engineer</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -4293,7 +4293,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Kafka, Snowflake</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, Scala, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,24 +4311,24 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e01ee86f0306e6c</t>
+          <t>https://www.indeed.com/viewjob?jk=82d92ef7ef6e6f18</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>QA Analyst / ETL Tester</t>
+          <t>Sr. Data Architect Specialist</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>CSpring</t>
+          <t>SAMYANG AMERICA INC</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Springfield, IL, US USA</t>
+          <t>Brea, CA, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>RDS, Azure, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Data Modeling, Snowflake Schema, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,32 +4346,32 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ebf7b3987a302e8</t>
+          <t>https://www.indeed.com/viewjob?jk=f2086e3e44cfc021</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Engineer II-Software Development</t>
+          <t>Full Stack Product Engineer (Java)</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Microchip Technology</t>
+          <t>Allstate Insurance</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, ELT, CI/CD, Git</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,32 +4381,32 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3013681a0e1c4f81</t>
+          <t>https://www.indeed.com/viewjob?jk=d15adff582efc740</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Engineer II-Software Development</t>
+          <t>DevOps &amp; Infrastructure Engineer - Level I</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Microchip Technology</t>
+          <t>SPRING ARBOR UNIVERSITY</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Spring Arbor, MI, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLOps, CI/CD</t>
+          <t>AWS, Azure, GCP, Scala, Oracle, CI/CD, Jenkins, GitHub Actions, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,32 +4416,32 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2649d75a044fe7bd</t>
+          <t>https://www.indeed.com/viewjob?jk=b0b216de71eb3804</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - VAULT</t>
+          <t>Senior GCP Kubernetes Engineer</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Bloomberg</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Hive, Spark, Scala, Kafka, Cassandra</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, Oracle, PostgreSQL, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,49 +4451,49 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d744cfcd1fce896</t>
+          <t>https://www.indeed.com/viewjob?jk=a77679969db6e94b</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>BigData ,Python and Py Spark , GCP</t>
+          <t>Sr. Software Engineer, Enterprise Technology</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Rivian</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>GCP, BigQuery, Hadoop, Hive, Spark, PySpark, Scala, ETL, ELT, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MySQL, NoSQL, Splunk, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81999129979e18ac</t>
+          <t>https://www.indeed.com/viewjob?jk=fab081dda06a1ba5</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Cloud AI Application Administrator</t>
+          <t>Senior GCP IAM Engineer</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -4503,15 +4503,15 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, Dataflow, Cloud Storage, Scala, Oracle, ETL, ELT, dbt, Tableau</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,32 +4521,32 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd193e360372af33</t>
+          <t>https://www.indeed.com/viewjob?jk=4e01ee86f0306e6c</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Data Engineer II, Mobile Game Analytics</t>
+          <t>QA Analyst / ETL Tester</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Mattel, Inc.</t>
+          <t>CSpring</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>El Segundo, CA, US USA</t>
+          <t>Springfield, IL, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>RDS, Medallion Architecture, GCP, BigQuery, Dimensional Modeling, ETL, dbt, Tableau, CI/CD, Airflow</t>
+          <t>RDS, Azure, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Data Modeling, Snowflake Schema, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4556,24 +4556,24 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=087868e735e87a06</t>
+          <t>https://www.indeed.com/viewjob?jk=1ebf7b3987a302e8</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Urology Centers of Alabama</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, BigQuery, Vertex AI, Spark, Scala, Spark Streaming, Kafka, CI/CD, Git</t>
+          <t>AWS, EMR, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, ETL</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,24 +4591,24 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f192cf981191d4cd</t>
+          <t>https://www.indeed.com/viewjob?jk=28cb24ea6139fcb9</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Pearson</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Hoboken, NJ, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, Terraform, Docker, Jenkins</t>
+          <t>AWS, RDS, Scala, MongoDB, DynamoDB, Data Modeling, ETL, ELT, DataOps, CI/CD</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,24 +4626,24 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7e0844f636778b5</t>
+          <t>https://www.indeed.com/viewjob?jk=05547d65aabdfcf0</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>GCP Support Associate</t>
+          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, GCP, Dataflow, Cloud Storage, CI/CD, Jenkins, Terraform, Docker, Jenkins</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4661,24 +4661,24 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=908520f92505a147</t>
+          <t>https://www.indeed.com/viewjob?jk=34c37a226b547d01</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Leidos</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Seaside, CA, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Splunk, CI/CD, Terraform, Docker, Kubernetes, Git, CloudWatch</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4696,24 +4696,24 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=727ac8d7c715b1a1</t>
+          <t>https://www.indeed.com/viewjob?jk=e7d77afce6f60e6f</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Test Automation Architect (Data Migration &amp; Snowflake)</t>
+          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Atlantis IT Group</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Kansas City, KS, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4721,7 +4721,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Scala, Snowflake, Oracle, SQL Server, ETL, ELT, CI/CD, pytest, Python, SQL</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4731,24 +4731,24 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=706847de763fb7d8</t>
+          <t>https://www.indeed.com/viewjob?jk=225c5a8131dc6595</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Software Engineer - AI Augmented Development</t>
+          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>PowerPay</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Wayne, PA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, ECS, IAM, RDS, Snowflake, ETL, Terraform</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4766,24 +4766,24 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=039bac65ddb8c30e</t>
+          <t>https://www.indeed.com/viewjob?jk=301dbd1e2eb0bb70</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Sr Associate Engineer/Engineer, IT Software</t>
+          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4791,7 +4791,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -4801,24 +4801,24 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf657c9771abb6db</t>
+          <t>https://www.indeed.com/viewjob?jk=d88e7121c2db79d6</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>DevOps Engineer (GCP)</t>
+          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Vertex AI, Spark, MLflow, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4836,24 +4836,24 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a53e6510409c717</t>
+          <t>https://www.indeed.com/viewjob?jk=18d3f9fdcfa07035</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Remote</t>
+          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4861,34 +4861,34 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, CI/CD, Docker, Kubernetes, AKS</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d50aa63bcb3363ae</t>
+          <t>https://www.indeed.com/viewjob?jk=9d2d16258cfd6718</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Remote</t>
+          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4896,34 +4896,34 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, CI/CD, Docker, Kubernetes, AKS</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc9c5148720fcbf9</t>
+          <t>https://www.indeed.com/viewjob?jk=5be8f9b4535b406c</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Azure data factory developer with Snowflake exp</t>
+          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4931,7 +4931,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Blob Storage, Snowflake, SQL Server, ETL, ELT, CI/CD</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -4941,24 +4941,24 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b0baa93de5c3410</t>
+          <t>https://www.indeed.com/viewjob?jk=26ef52c65261360a</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>AI Application Architect</t>
+          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>WY, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4966,15 +4966,1345 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f9240b7b96545a4d</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>McLean, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D131" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=42ae72f7d4a97700</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Tempe, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D132" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dab5b1b68cc6402c</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Arlington, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D133" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fde8d1831ca7f9b7</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Minneapolis, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D134" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7a056659ad4aebd2</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Nashville, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D135" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e5402962c321dcba</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Detroit, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D136" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f45ad39ec1fe503a</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Kansas City, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D137" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=86cfc919b4ccc768</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D138" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c9a866cff6a0e3bd</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Morristown, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D139" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ab68f1e4ba82ad10</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D140" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=df163d5906a30146</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Cincinnati, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D141" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2f0c32c0bdf67710</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Columbus, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D142" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=25f63312ec2e267e</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Miami, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D143" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=be379ec08f5c5e6f</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Stamford, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D144" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8deeb1ab1ebcdccd</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Indianapolis, IN, US USA</t>
+        </is>
+      </c>
+      <c r="D145" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=92aa87419ba8e5df</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D146" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=da334d3b3eda0eb4</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Los Angeles, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D147" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2c314e6df20a4157</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Denver, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D148" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b90a165cff732e70</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>San Diego, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D149" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=26bc98921360165c</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Tampa, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D150" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c5359f322821abe9</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Sacramento, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D151" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=562ea8307dd5c91d</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Costa Mesa, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D152" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=70a64e543cdeb49a</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D153" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ed3e28c9a543299a</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>San Jose, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D154" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1735f01363643535</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Data Engineer II, Mobile Game Analytics</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Mattel, Inc.</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>El Segundo, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D155" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>RDS, Medallion Architecture, GCP, BigQuery, Dimensional Modeling, ETL, dbt, Tableau, CI/CD, Airflow</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=087868e735e87a06</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - VAULT</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Bloomberg</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D156" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Azure, GCP, Hive, Spark, Scala, Kafka, Cassandra</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1d744cfcd1fce896</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>Cloud AI Application Administrator</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D157" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>RDS, Google Cloud Platform, Dataflow, Cloud Storage, Scala, Oracle, ETL, ELT, dbt, Tableau</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cd193e360372af33</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>AI Integration Engineer (Java + AI)</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>TN, US USA</t>
+        </is>
+      </c>
+      <c r="D158" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>RDS, Google Cloud Platform, BigQuery, Vertex AI, Spark, Scala, Spark Streaming, Kafka, CI/CD, Git</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f192cf981191d4cd</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>AI Integration Engineer (Java + AI)</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D159" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, Terraform, Docker, Jenkins</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e7e0844f636778b5</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>GCP Support Associate</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D160" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>IAM, Google Cloud Platform, GCP, Dataflow, Cloud Storage, CI/CD, Jenkins, Terraform, Docker, Jenkins</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=908520f92505a147</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>Cloud Engineer</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Leidos</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Seaside, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D161" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Scala, Splunk, CI/CD, Terraform, Docker, Kubernetes, Git, CloudWatch</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=727ac8d7c715b1a1</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>Engineer II-Software Development</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Microchip Technology</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D162" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLOps, CI/CD</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3013681a0e1c4f81</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>Engineer II-Software Development</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Microchip Technology</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D163" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLOps, CI/CD</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2649d75a044fe7bd</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>Test Automation Architect (Data Migration &amp; Snowflake)</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Atlantis IT Group</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Kansas City, KS, US USA</t>
+        </is>
+      </c>
+      <c r="D164" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>Scala, Snowflake, Oracle, SQL Server, ETL, ELT, CI/CD, pytest, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=706847de763fb7d8</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>Software Engineer - AI Augmented Development</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>PowerPay</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Wayne, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D165" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, SQS, ECS, IAM, RDS, Snowflake, ETL, Terraform</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=039bac65ddb8c30e</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>Sr Associate Engineer/Engineer, IT Software</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>American Airlines</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Fort Worth, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D166" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cf657c9771abb6db</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>DevOps Engineer (GCP)</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D167" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Vertex AI, Spark, MLflow, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1a53e6510409c717</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>AI Application Architect</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>WY, US USA</t>
+        </is>
+      </c>
+      <c r="D168" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
           <t>AWS, Azure, Google Cloud Platform, Spark, Scala, Snowflake, ETL, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
-      <c r="F130" t="inlineStr">
-        <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="G130" t="inlineStr">
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=bdfa99adc53f817f</t>
         </is>

--- a/results/job_matches_2026-05-06.xlsx
+++ b/results/job_matches_2026-05-06.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G168"/>
+  <dimension ref="A1:G177"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -853,17 +853,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Junior DevOps Engineer (GCP)</t>
+          <t>Software Engineer - DevOps and MLOps</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>San Francisco Bay Area, CA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Kafka, PostgreSQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56a30f4a788f09b2</t>
+          <t>https://www.indeed.com/viewjob?jk=2fcad788d48ba696</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Software Engineer, Cloud Infrastructure (Multiple Seniority Levels)</t>
+          <t>Junior DevOps Engineer (GCP)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>San Carlos, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, SQS, ECS, IAM, RDS</t>
+          <t>AWS, SQS, SNS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,14 +916,14 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07cee960b10bf15e</t>
+          <t>https://www.indeed.com/viewjob?jk=56a30f4a788f09b2</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Software Engineer - DevOps and MLOps</t>
+          <t>Software Engineer, Cloud Infrastructure (Multiple Seniority Levels)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>San Francisco Bay Area, CA, US USA</t>
+          <t>San Carlos, CA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Kafka, PostgreSQL, MongoDB, Cassandra</t>
+          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, SQS, ECS, IAM, RDS</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2fcad788d48ba696</t>
+          <t>https://www.indeed.com/viewjob?jk=07cee960b10bf15e</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Commercial IT Senior Data Solution Developer</t>
+          <t>Senior Software Engineer – Oracle EPM/Senior Quadient Inspire Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>ConocoPhillips</t>
+          <t>SUPPORTSOFT TECHNOLOGIES</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,42 +976,42 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hive, Spark, Scala, Kafka, Snowflake, NoSQL</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1304cb2ffae316c6</t>
+          <t>https://www.indeed.com/viewjob?jk=75c533d77b3fd5ba</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Commercial IT Senior Data Solution Developer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>WSSC Water</t>
+          <t>ConocoPhillips</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Laurel, MD, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Blob Storage, GCP, Hadoop</t>
+          <t>AWS, RDS, Azure, Databricks, Hive, Spark, Scala, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=859b6255aab51697</t>
+          <t>https://www.indeed.com/viewjob?jk=1304cb2ffae316c6</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>WSSC Water</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Laurel, MD, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, API Gateway, RDS, Azure, Kafka</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Blob Storage, GCP, Hadoop</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,14 +1056,14 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b4a39c21c884e72</t>
+          <t>https://www.indeed.com/viewjob?jk=859b6255aab51697</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>GCP ETL Engineer</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, Spark, Scala, Snowflake, Oracle</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, API Gateway, RDS, Azure, Kafka</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,14 +1091,14 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e5fc76263d455e5</t>
+          <t>https://www.indeed.com/viewjob?jk=0b4a39c21c884e72</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Java API Integration Engineer</t>
+          <t>GCP ETL Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, API Gateway, RDS, Azure, Google Cloud Platform, Scala, Kafka, Splunk</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, Spark, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,67 +1126,67 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78afcf5aa1e7fc4b</t>
+          <t>https://www.indeed.com/viewjob?jk=4e5fc76263d455e5</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Sr Site Reliability Engineer</t>
+          <t>Software Engineer Big Data</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Commence</t>
+          <t>Sightview Software</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Leesburg, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, NoSQL, ETL, ELT</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, ECS, IAM</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9093ede7f2269db2</t>
+          <t>https://www.indeed.com/viewjob?jk=53f13dba60fcff4b</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Sr Data Engineer, Python + Spark (Data Federation skillset - Data Lakehouse - Eg: Starburst) - New York</t>
+          <t>Java API Integration Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Photon</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, S3, Azure, Databricks, Medallion Architecture, GCP, Spark, PySpark</t>
+          <t>AWS, SQS, SNS, API Gateway, RDS, Azure, Google Cloud Platform, Scala, Kafka, Splunk</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,59 +1196,59 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7767a92d7d08a3b</t>
+          <t>https://www.indeed.com/viewjob?jk=78afcf5aa1e7fc4b</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - ETL, Java</t>
+          <t>Health Account Intern</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>RevSpring, Inc</t>
+          <t>Booz Allen Hamilton</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Redshift, S3, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop, Scala</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Databricks, Hadoop, Hive, Spark, Scala</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a9c009a05948507</t>
+          <t>https://www.indeed.com/viewjob?jk=64329d0d0bf86853</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - ETL, Java</t>
+          <t>Sr Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>RevSpring, Inc</t>
+          <t>Commence</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Leesburg, VA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,34 +1256,34 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Redshift, S3, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop, Scala</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, NoSQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba5ba3f3a840901f</t>
+          <t>https://www.indeed.com/viewjob?jk=9093ede7f2269db2</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - ETL, Java</t>
+          <t>Sr Data Engineer, Python + Spark (Data Federation skillset - Data Lakehouse - Eg: Starburst) - New York</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>RevSpring, Inc</t>
+          <t>Photon</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Redshift, S3, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop, Scala</t>
+          <t>AWS, Glue, EMR, S3, Azure, Databricks, Medallion Architecture, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec9899d266d7f4ea</t>
+          <t>https://www.indeed.com/viewjob?jk=f7767a92d7d08a3b</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>DevOps Engineer (GCP)</t>
+          <t>Senior Software Engineer - ETL, Java</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>RevSpring, Inc</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark</t>
+          <t>Redshift, S3, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop, Scala</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d617836814bb437</t>
+          <t>https://www.indeed.com/viewjob?jk=4a9c009a05948507</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Junior GCP Cloud Engineer</t>
+          <t>Senior Software Engineer - ETL, Java</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>RevSpring, Inc</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Data Modeling, Kimball</t>
+          <t>Redshift, S3, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop, Scala</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11aa4a83b27dbdc6</t>
+          <t>https://www.indeed.com/viewjob?jk=ba5ba3f3a840901f</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Junior GCP Cloud Engineer</t>
+          <t>Senior Software Engineer - ETL, Java</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>RevSpring, Inc</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Azure, Google Cloud Platform, GCP, Kafka, NoSQL, Data Modeling, ETL, Talend, Tableau, Splunk</t>
+          <t>Redshift, S3, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop, Scala</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3e7636193fed6ce</t>
+          <t>https://www.indeed.com/viewjob?jk=ec9899d266d7f4ea</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>MLOps Engineer – Azure Databricks, Cloud-to-Edge ML Deployment</t>
+          <t>DevOps Engineer (GCP)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>KPIT Technologies</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, MLOps, MLflow, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,14 +1441,14 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1160b6a5ea3d30ad</t>
+          <t>https://www.indeed.com/viewjob?jk=9d617836814bb437</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Cloud Reliability Engineer</t>
+          <t>Junior GCP Cloud Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1462,11 +1462,11 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Spark, Scala, NoSQL, Data Modeling, MLOps</t>
+          <t>IAM, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Data Modeling, Kimball</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,19 +1476,19 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eae9d6ab07ed0b94</t>
+          <t>https://www.indeed.com/viewjob?jk=11aa4a83b27dbdc6</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Verisk</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1497,56 +1497,56 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, S3, RDS, Spark, Scala, PostgreSQL, Data Modeling</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, RDS, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb57edcbdb36ad26</t>
+          <t>https://www.indeed.com/viewjob?jk=df1902d36083d34f</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>DevOps/AI Ops Administrator</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Event Hubs, Dataflow, Scala, Snowflake, PostgreSQL, Power BI, CI/CD</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, RDS, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8de348813177f92b</t>
+          <t>https://www.indeed.com/viewjob?jk=5cb867686433b7a1</t>
         </is>
       </c>
     </row>
@@ -1558,30 +1558,30 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Metropolis</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Glue, SNS, RDS, Spark, PySpark, Scala, Snowflake, SQL Server, MySQL</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, RDS, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9fd5c209c01d504</t>
+          <t>https://www.indeed.com/viewjob?jk=b9c0e5823a5a0a57</t>
         </is>
       </c>
     </row>
@@ -1593,142 +1593,142 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>metropolis</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Glue, SNS, RDS, Spark, PySpark, Scala, Snowflake, SQL Server, MySQL</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, RDS, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d51453a1afa374b4</t>
+          <t>https://www.indeed.com/viewjob?jk=3aeafc948a2f0f6c</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Software Engineer – ETL, Java</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>RevSpring, Inc</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Redshift, S3, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop, Scala</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, RDS, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ebdf3dd92985403</t>
+          <t>https://www.indeed.com/viewjob?jk=c45b322f3e5694ad</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Software Engineer – ETL, Java</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>RevSpring, Inc</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Redshift, S3, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop, Scala</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, RDS, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c4b1e40555df27f</t>
+          <t>https://www.indeed.com/viewjob?jk=c4c63fb90b07eaf3</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Software Engineer – ETL, Java</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>RevSpring, Inc</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Redshift, S3, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop, Scala</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, RDS, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d1957e3729d8614</t>
+          <t>https://www.indeed.com/viewjob?jk=d67c28cbc09b5ad3</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Cloud Migration Engineer (GCP)</t>
+          <t>Junior GCP Cloud Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1738,15 +1738,15 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, Snowflake, SQL Server</t>
+          <t>Azure, Google Cloud Platform, GCP, Kafka, NoSQL, Data Modeling, ETL, Talend, Tableau, Splunk</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,137 +1756,137 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb7efc81616340cd</t>
+          <t>https://www.indeed.com/viewjob?jk=b3e7636193fed6ce</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Forward Deployment Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>Verisk</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Redshift, API Gateway, IAM, Azure, Databricks, GCP, BigQuery</t>
+          <t>AWS, Glue, Lambda, Athena, S3, RDS, Spark, Scala, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d83189697283beb7</t>
+          <t>https://www.indeed.com/viewjob?jk=cb57edcbdb36ad26</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>GCP Cloud Engineer</t>
+          <t>MLOps Engineer – Azure Databricks, Cloud-to-Edge ML Deployment</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>KPIT Technologies</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Vertex AI, Spark, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e5f23b132fd8132</t>
+          <t>https://www.indeed.com/viewjob?jk=1160b6a5ea3d30ad</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Databricks)</t>
+          <t>Cloud Reliability Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Infinitive Inc</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, S3, Azure, Databricks, Unity Catalog, GCP</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Spark, Scala, NoSQL, Data Modeling, MLOps</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aee5e62267dbbb6c</t>
+          <t>https://www.indeed.com/viewjob?jk=eae9d6ab07ed0b94</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Computing Architect 4 (contract)</t>
+          <t>DevOps/AI Ops Administrator</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Boeing</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Scala, Kafka, Data Modeling, ELT</t>
+          <t>RDS, Azure, Databricks, Event Hubs, Dataflow, Scala, Snowflake, PostgreSQL, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83fa749fc70ff9b5</t>
+          <t>https://www.indeed.com/viewjob?jk=8de348813177f92b</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Terraform MLOps Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Metropolis</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Vertex AI, Scala, Kafka, NoSQL, MLOps</t>
+          <t>AWS, Glue, SNS, RDS, Spark, PySpark, Scala, Snowflake, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1c091b77ba59917</t>
+          <t>https://www.indeed.com/viewjob?jk=b9fd5c209c01d504</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Software Developer II</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Floor &amp; Decor</t>
+          <t>metropolis</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL, Splunk, CI/CD</t>
+          <t>AWS, Glue, SNS, RDS, Spark, PySpark, Scala, Snowflake, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,32 +1966,32 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e331a6c4c6f76859</t>
+          <t>https://www.indeed.com/viewjob?jk=d51453a1afa374b4</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Sr. Streaming Engineer</t>
+          <t>Cloud Migration Engineer (GCP)</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Ness Digital Engineering</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, IAM, RDS, Spark, Scala, Kafka, NoSQL, Splunk</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,67 +2001,67 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f90fa0ab3164dcd1</t>
+          <t>https://www.indeed.com/viewjob?jk=fb7efc81616340cd</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer - Cloud Dev</t>
+          <t>Senior Data Engineer (Databricks)</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Transmedics</t>
+          <t>Infinitive Inc</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Andover, MA, US USA</t>
+          <t>Ashburn, VA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, Redshift, Step Functions, S3, SQS, SNS, API Gateway, IAM</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, S3, Azure, Databricks, Unity Catalog, GCP</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2efe7bed588da272</t>
+          <t>https://www.indeed.com/viewjob?jk=aee5e62267dbbb6c</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Cloud Service Desk Analyst</t>
+          <t>Software Engineer – ETL, Java</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>RevSpring, Inc</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, Azure, Scala, CI/CD, GitHub Actions, Terraform</t>
+          <t>Redshift, S3, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop, Scala</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e883ce8f9ac322fb</t>
+          <t>https://www.indeed.com/viewjob?jk=3ebdf3dd92985403</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Sr MERN engineer</t>
+          <t>Software Engineer – ETL, Java</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Purple Squirrels Software LLC</t>
+          <t>RevSpring, Inc</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Newark, CA, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>Redshift, S3, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop, Scala</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,137 +2106,137 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=edf2effb08935b9f</t>
+          <t>https://www.indeed.com/viewjob?jk=5c4b1e40555df27f</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>MLOps Engineer</t>
+          <t>Software Engineer – ETL, Java</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>RevSpring, Inc</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>Redshift, S3, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop, Scala</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56f1aa48ba26ae3c</t>
+          <t>https://www.indeed.com/viewjob?jk=9d1957e3729d8614</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Junior Cloud Security Analyst</t>
+          <t>Forward Deployment Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Databricks, Blob Storage, Unity Catalog, Google Cloud Platform, Spark</t>
+          <t>AWS, Glue, Kinesis, Redshift, API Gateway, IAM, Azure, Databricks, GCP, BigQuery</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb95dfff70e6d2a4</t>
+          <t>https://www.indeed.com/viewjob?jk=d83189697283beb7</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Business Intelligence Developer (Healthcare Data, EDI, ETL)</t>
+          <t>GCP Cloud Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>MicroHealth LLC</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Vienna, VA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Scala, Snowflake, SQL Server, PostgreSQL, Snowflake Schema, ETL, ELT</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Vertex AI, Spark, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ba3d7e28ab6494c</t>
+          <t>https://www.indeed.com/viewjob?jk=4e5f23b132fd8132</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Databricks Developer</t>
+          <t>Terraform MLOps Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Sloan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Franklin Park, IL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Vertex AI, Scala, Kafka, NoSQL, MLOps</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9921503eb16c8225</t>
+          <t>https://www.indeed.com/viewjob?jk=b1c091b77ba59917</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Computing Architect 4 (contract)</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Kroll Inc.</t>
+          <t>Boeing</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Scala, Polars, ETL, ELT, Power BI, Tableau</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Scala, Kafka, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d56048c057634cd1</t>
+          <t>https://www.indeed.com/viewjob?jk=83fa749fc70ff9b5</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>GCP ETL Engineer</t>
+          <t>Software Developer II</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Floor &amp; Decor</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Hadoop, Spark, Kafka, Snowflake, Dimensional Modeling, ETL, Talend</t>
+          <t>RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,32 +2316,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5268867584b4379</t>
+          <t>https://www.indeed.com/viewjob?jk=e331a6c4c6f76859</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Software Engineer - Specialist</t>
+          <t>Sr. Streaming Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Ness Digital Engineering</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, SQL Server, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, Kinesis, S3, IAM, RDS, Spark, Scala, Kafka, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,32 +2351,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=932c71a7f13aa9a1</t>
+          <t>https://www.indeed.com/viewjob?jk=f90fa0ab3164dcd1</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>GCP Support Associate</t>
+          <t>Senior Software Development Engineer - Cloud Dev</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Transmedics</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Andover, MA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, MySQL, Splunk, CI/CD</t>
+          <t>AWS, Lambda, Kinesis, Redshift, Step Functions, S3, SQS, SNS, API Gateway, IAM</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,32 +2386,32 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29c27657463cb6ea</t>
+          <t>https://www.indeed.com/viewjob?jk=2efe7bed588da272</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Cloud Database Engineer (Hybrid - Seattle, WA)</t>
+          <t>Cloud Service Desk Analyst</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Nordstrom</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Redshift, Athena, S3, RDS, Kafka, Oracle, SQL Server</t>
+          <t>AWS, Lambda, S3, ECS, IAM, Azure, Scala, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,32 +2421,32 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1666a61865ef57aa</t>
+          <t>https://www.indeed.com/viewjob?jk=e883ce8f9ac322fb</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr MERN engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Moore</t>
+          <t>Purple Squirrels Software LLC</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Westminster, CO, US USA</t>
+          <t>Newark, CA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT, dbt</t>
+          <t>AWS, S3, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,67 +2456,67 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8c5af154805cd95</t>
+          <t>https://www.indeed.com/viewjob?jk=edf2effb08935b9f</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>MLOps Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Paramount</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Fort Lauderdale, FL, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Dataflow, Scala, MongoDB, NoSQL, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a12925c69dfc7bed</t>
+          <t>https://www.indeed.com/viewjob?jk=56f1aa48ba26ae3c</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Data Engineer (ETL / Python Developer)</t>
+          <t>Junior Cloud Security Analyst</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>CSpring</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Springfield, IL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, S3, IAM, RDS, Azure, Databricks, Blob Storage, Unity Catalog, Google Cloud Platform, Spark</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b861e2c1a0a03133</t>
+          <t>https://www.indeed.com/viewjob?jk=cb95dfff70e6d2a4</t>
         </is>
       </c>
     </row>
@@ -2538,55 +2538,55 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Imprint</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Kinesis, S3, RDS, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Oracle, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e35bafcce4ab1000</t>
+          <t>https://www.indeed.com/viewjob?jk=d61e7d7639acc074</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Business Intelligence Developer (Healthcare Data, EDI, ETL)</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Imprint</t>
+          <t>MicroHealth LLC</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Vienna, VA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Kinesis, S3, RDS, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, EMR, RDS, Scala, Snowflake, SQL Server, PostgreSQL, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,32 +2596,32 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=baaf38c4500e2b06</t>
+          <t>https://www.indeed.com/viewjob?jk=3ba3d7e28ab6494c</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior AI Data Engineer</t>
+          <t>Databricks Developer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Velvetech</t>
+          <t>Sloan</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Franklin Park, IL, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Vertex AI, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,32 +2631,32 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2bec7882b34f08c9</t>
+          <t>https://www.indeed.com/viewjob?jk=9921503eb16c8225</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer - Specialist</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Westminster, CO, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, SQL Server, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,32 +2666,32 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d49164a52434e329</t>
+          <t>https://www.indeed.com/viewjob?jk=932c71a7f13aa9a1</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>AWS Data Engineer - Databricks</t>
+          <t>GCP ETL Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>RadCube</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Databricks, Scala, Databricks Lakehouse, Data Modeling</t>
+          <t>AWS, Azure, GCP, Hadoop, Spark, Kafka, Snowflake, Dimensional Modeling, ETL, Talend</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,94 +2701,94 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2dcfccb6b6d90b1</t>
+          <t>https://www.indeed.com/viewjob?jk=d5268867584b4379</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Software Engineer - Cloud</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Carnegie Robotics LLC</t>
+          <t>Kroll Inc.</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, PostgreSQL, MongoDB, DynamoDB, NoSQL</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Scala, Polars, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2f5b0b9c556cdca</t>
+          <t>https://www.indeed.com/viewjob?jk=d56048c057634cd1</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Python/PySpark/AWS)</t>
+          <t>GCP Support Associate</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Infinitive Inc</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Azure, Spark, PySpark, Scala, Spark Streaming, Data Modeling, ETL, CI/CD, Jenkins</t>
+          <t>IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, MySQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2025-02-18</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45083db400feff94</t>
+          <t>https://www.indeed.com/viewjob?jk=29c27657463cb6ea</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data Engineer (Python/PySpark/AWS)</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Infinitive Inc</t>
+          <t>Miami Marlins</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Azure, Spark, PySpark, Scala, Spark Streaming, Data Modeling, ETL, CI/CD, Jenkins</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, GCP, Scala, Snowflake, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2025-01-27</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e742c4bedd2037b</t>
+          <t>https://www.indeed.com/viewjob?jk=ff87deef607d5450</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Miami Marlins</t>
+          <t>Paramount</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Fort Lauderdale, FL, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, GCP, Scala, Snowflake, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, GCP, BigQuery, Dataflow, Scala, MongoDB, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff87deef607d5450</t>
+          <t>https://www.indeed.com/viewjob?jk=a12925c69dfc7bed</t>
         </is>
       </c>
     </row>
@@ -2883,17 +2883,17 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Full Stack Engineer, Experienced</t>
+          <t>Senior Cloud Database Engineer (Hybrid - Seattle, WA)</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Blue Shield of California</t>
+          <t>Nordstrom</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, NoSQL, CI/CD, Terraform</t>
+          <t>AWS, Glue, Kinesis, Redshift, Athena, S3, RDS, Kafka, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93fe5a9749607800</t>
+          <t>https://www.indeed.com/viewjob?jk=1666a61865ef57aa</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Full Stack Engineer, Senior</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Blue Shield of California</t>
+          <t>Moore</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Westminster, CO, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, NoSQL, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bcc6fa1baccf83e5</t>
+          <t>https://www.indeed.com/viewjob?jk=b8c5af154805cd95</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Full Stack Engineer, Consultant</t>
+          <t>Data Engineer (ETL / Python Developer)</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Blue Shield of California</t>
+          <t>CSpring</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Springfield, IL, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, NoSQL, CI/CD, Terraform</t>
+          <t>Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3a7d3c5d7336760</t>
+          <t>https://www.indeed.com/viewjob?jk=b861e2c1a0a03133</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Summer Intern, Platform Engineering</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Outfront Media</t>
+          <t>Imprint</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD, Docker</t>
+          <t>Kinesis, S3, RDS, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2aa35bb9483f10ad</t>
+          <t>https://www.indeed.com/viewjob?jk=e35bafcce4ab1000</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Java Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Imprint</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>Kinesis, S3, RDS, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=257d265c3f7e2882</t>
+          <t>https://www.indeed.com/viewjob?jk=baaf38c4500e2b06</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Docker MLOps Engineer</t>
+          <t>Senior AI Data Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Velvetech</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, Kafka, Snowflake, Data Modeling, MLOps</t>
+          <t>AWS, IAM, Azure, GCP, Vertex AI, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,14 +3086,14 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3cd445b405cda13</t>
+          <t>https://www.indeed.com/viewjob?jk=2bec7882b34f08c9</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Customer Centric Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Westminster, CO, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Scala, Snowflake, ELT, dbt, Tableau, Docker</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29a2186b968dd17c</t>
+          <t>https://www.indeed.com/viewjob?jk=d49164a52434e329</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Salesforce Data Cloud Architect</t>
+          <t>AWS Data Engineer - Databricks</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Skechers</t>
+          <t>RadCube</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Manhattan Beach, CA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,147 +3146,147 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ETL, ELT, MLflow</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Databricks, Scala, Databricks Lakehouse, Data Modeling</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebe8dee39468099e</t>
+          <t>https://www.indeed.com/viewjob?jk=d2dcfccb6b6d90b1</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Software Engineer - Cloud</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Clayco</t>
+          <t>Carnegie Robotics LLC</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, PostgreSQL, MongoDB, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61cc49187bd6e01d</t>
+          <t>https://www.indeed.com/viewjob?jk=e2f5b0b9c556cdca</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Data Engineering - E&amp;A - Data Engineer I</t>
+          <t>Senior Data Engineer (Python/PySpark/AWS)</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Genesis Global Group</t>
+          <t>Infinitive Inc</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Myrtle Point, OR, US USA</t>
+          <t>Ashburn, VA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
+          <t>AWS, Azure, Spark, PySpark, Scala, Spark Streaming, Data Modeling, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2025-02-18</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2526bf14df16c3e8</t>
+          <t>https://www.indeed.com/viewjob?jk=45083db400feff94</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Data Engineer (Python/PySpark/AWS)</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Versant</t>
+          <t>Infinitive Inc</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Ashburn, VA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, GCP, Spark, NoSQL, ETL</t>
+          <t>AWS, Azure, Spark, PySpark, Scala, Spark Streaming, Data Modeling, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2025-01-27</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fbef82ce93a90ed</t>
+          <t>https://www.indeed.com/viewjob?jk=5e742c4bedd2037b</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior, Data Engineer</t>
+          <t>Full Stack Engineer, Experienced</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Carrington Mortgage Services, LLC</t>
+          <t>Blue Shield of California</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, ETL, Microsoft SSIS</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,32 +3296,32 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfdf1b9d489fb8ec</t>
+          <t>https://www.indeed.com/viewjob?jk=93fe5a9749607800</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>GCP Support Associate</t>
+          <t>Full Stack Engineer, Senior</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Blue Shield of California</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>ECS, IAM, Google Cloud Platform, GCP, Dataflow, Cloud Storage, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,102 +3331,102 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9acaddb632586c1</t>
+          <t>https://www.indeed.com/viewjob?jk=bcc6fa1baccf83e5</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Data Systems Engineer</t>
+          <t>Full Stack Engineer, Consultant</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Central Health</t>
+          <t>Blue Shield of California</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41eed22913274d81</t>
+          <t>https://www.indeed.com/viewjob?jk=a3a7d3c5d7336760</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>mSupply</t>
+          <t>Terra Quantum</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Medallion Architecture, Dataflow, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=faaa8b1f4d565bbd</t>
+          <t>https://www.indeed.com/viewjob?jk=15eb90498bcba242</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>AI/ML Engineer</t>
+          <t>Summer Intern, Platform Engineering</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Redapt inc</t>
+          <t>Outfront Media</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Woodinville, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, GCP, Vertex AI, Spark, Snowflake, Data Modeling, ELT</t>
+          <t>AWS, Lambda, S3, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,32 +3436,32 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9c94059f3dd29b3</t>
+          <t>https://www.indeed.com/viewjob?jk=2aa35bb9483f10ad</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer - News</t>
+          <t>Java Software Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Step Functions, SQS, SNS, RDS, Databricks, Spark</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,32 +3471,32 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c5ae4f292525796</t>
+          <t>https://www.indeed.com/viewjob?jk=257d265c3f7e2882</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Docker MLOps Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Victory Live</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Snowflake, SQL Server, DynamoDB, ELT, dbt, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, Kafka, Snowflake, Data Modeling, MLOps</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,32 +3506,32 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1c259f0b00d1299</t>
+          <t>https://www.indeed.com/viewjob?jk=e3cd445b405cda13</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>AI Senior Engineer</t>
+          <t>Customer Centric Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Wood Mackenzie</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, ECS, Azure, Scala, DynamoDB, ETL, CI/CD</t>
+          <t>AWS, Azure, GCP, BigQuery, Scala, Snowflake, ELT, dbt, Tableau, Docker</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69e1b61070a9b37b</t>
+          <t>https://www.indeed.com/viewjob?jk=29a2186b968dd17c</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>AI Systems Administrator</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Versant</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>ECS, RDS, Azure, Databricks, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, GCP, Spark, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a338fa1fa96ea390</t>
+          <t>https://www.indeed.com/viewjob?jk=1fbef82ce93a90ed</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Sr. ML Engineer – ML &amp; Applied AI</t>
+          <t>AI/ML Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Gap Inc.</t>
+          <t>Redapt inc</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Woodinville, WA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,34 +3601,34 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MLOps, CI/CD</t>
+          <t>AWS, Redshift, Azure, Databricks, GCP, Vertex AI, Spark, Snowflake, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9323c5e89dc8edb</t>
+          <t>https://www.indeed.com/viewjob?jk=b9c94059f3dd29b3</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Sr. ML Engineer – ML &amp; Applied AI</t>
+          <t>Senior Machine Learning Engineer - News</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Gap Inc.</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Pleasanton, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,42 +3636,42 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MLOps, CI/CD</t>
+          <t>AWS, Glue, Lambda, Kinesis, Step Functions, SQS, SNS, RDS, Databricks, Spark</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7aa4ac97e72f7a6d</t>
+          <t>https://www.indeed.com/viewjob?jk=6c5ae4f292525796</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Snowflake Platform Engineer</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Clayco</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Scala, Snowflake, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,32 +3681,32 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecb6b777a849d07c</t>
+          <t>https://www.indeed.com/viewjob?jk=61cc49187bd6e01d</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Snowflake Platform Engineer</t>
+          <t>Data Engineering - E&amp;A - Data Engineer I</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Genesis Global Group</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Myrtle Point, OR, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Scala, Snowflake, CI/CD, Terraform, Kubernetes</t>
+          <t>Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,32 +3716,32 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=136f0d6f19e6f0c6</t>
+          <t>https://www.indeed.com/viewjob?jk=2526bf14df16c3e8</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Sr. Professional, Software Engineering (Python)</t>
+          <t>Senior, Data Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Cotality</t>
+          <t>Carrington Mortgage Services, LLC</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, Tableau, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, ETL, Microsoft SSIS</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,32 +3751,32 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83e013cc49a29087</t>
+          <t>https://www.indeed.com/viewjob?jk=dfdf1b9d489fb8ec</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>GCP Support Associate</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Vertex AI, Scala, Data Modeling, Jenkins, Terraform, Jenkins</t>
+          <t>ECS, IAM, Google Cloud Platform, GCP, Dataflow, Cloud Storage, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,67 +3786,67 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bbf23a169f18dbc</t>
+          <t>https://www.indeed.com/viewjob?jk=a9acaddb632586c1</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Systems Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Central Health</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Vertex AI, Scala, Data Modeling, Jenkins, Terraform, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b05514433681d42</t>
+          <t>https://www.indeed.com/viewjob?jk=41eed22913274d81</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Clark Construction</t>
+          <t>Victory Live</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, dbt</t>
+          <t>AWS, RDS, Azure, Data Factory, Snowflake, SQL Server, DynamoDB, ELT, dbt, Terraform</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,32 +3856,32 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f199bfc2e975b58</t>
+          <t>https://www.indeed.com/viewjob?jk=a1c259f0b00d1299</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Senior Platform/DevOps Engineer (Kubernetes-Linux)</t>
+          <t>AI Senior Engineer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>ARMADA</t>
+          <t>Wood Mackenzie</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, Redshift, S3, ECS, Azure, Scala, DynamoDB, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,32 +3891,32 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b0e9b75e0f5558d</t>
+          <t>https://www.indeed.com/viewjob?jk=69e1b61070a9b37b</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Senior Platform/DevOps Engineer (Kubernetes-Linux)</t>
+          <t>AI Systems Administrator</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>ARMADA</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Sammamish, WA, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>ECS, RDS, Azure, Databricks, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=efa4e4e3099a0ae2</t>
+          <t>https://www.indeed.com/viewjob?jk=a338fa1fa96ea390</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Senior Platform/DevOps Engineer (Kubernetes-Linux)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>ARMADA</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Kirkland, WA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>RDS, GCP, BigQuery, Dataflow, Vertex AI, Scala, Data Modeling, Jenkins, Terraform, Jenkins</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33ae1f1f9d08c546</t>
+          <t>https://www.indeed.com/viewjob?jk=4bbf23a169f18dbc</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Senior Platform/DevOps Engineer (Kubernetes-Linux)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>ARMADA</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Renton, WA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>RDS, GCP, BigQuery, Dataflow, Vertex AI, Scala, Data Modeling, Jenkins, Terraform, Jenkins</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d25130b996402485</t>
+          <t>https://www.indeed.com/viewjob?jk=4b05514433681d42</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Senior Platform/DevOps Engineer (Kubernetes-Linux)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>ARMADA</t>
+          <t>Clark Construction</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Bothell, WA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Azure, GCP, Spark, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, dbt</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6f9224460f3210c</t>
+          <t>https://www.indeed.com/viewjob?jk=6f199bfc2e975b58</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Senior Platform/DevOps Engineer (Kubernetes-Linux)</t>
+          <t>Junior GCP Cloud Engineer</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>ARMADA</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Redmond, WA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Google Cloud Platform, GCP, Dataflow, Cloud Storage, Scala, Oracle, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,24 +4066,24 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b86c940f686047d8</t>
+          <t>https://www.indeed.com/viewjob?jk=817a2d7d06f177a9</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Snowflake Platform Engineer</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Somerville, MA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Scala, Snowflake, ETL, ELT, dbt, Tableau, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Scala, Snowflake, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,24 +4101,24 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75339d7552c524c1</t>
+          <t>https://www.indeed.com/viewjob?jk=ecb6b777a849d07c</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Sr. Site Reliability Engineer</t>
+          <t>Snowflake Platform Engineer</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>PitchBook</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, SQL Server, PostgreSQL, MySQL, Terraform, Docker, Kubernetes</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Scala, Snowflake, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,24 +4136,24 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=181ce2100b853c3a</t>
+          <t>https://www.indeed.com/viewjob?jk=136f0d6f19e6f0c6</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Junior GCP Cloud Engineer</t>
+          <t>Sr. Professional, Software Engineering (Python)</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Cotality</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, Dataflow, Cloud Storage, Scala, Oracle, ETL, ELT, dbt</t>
+          <t>RDS, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, Tableau, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,24 +4171,24 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=817a2d7d06f177a9</t>
+          <t>https://www.indeed.com/viewjob?jk=83e013cc49a29087</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Senior Data Engineer / Data Architect</t>
+          <t>Senior Platform/DevOps Engineer (Kubernetes-Linux)</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>ARMADA</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,24 +4206,24 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e83d1768e75b1203</t>
+          <t>https://www.indeed.com/viewjob?jk=7b0e9b75e0f5558d</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Snowflake Data Movement Engineer</t>
+          <t>Senior Platform/DevOps Engineer (Kubernetes-Linux)</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Smart Tech Skills LLC</t>
+          <t>ARMADA</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Sammamish, WA, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, ETL, CI/CD, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,24 +4241,24 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12ef21c70e148f1d</t>
+          <t>https://www.indeed.com/viewjob?jk=efa4e4e3099a0ae2</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Site Reliability / Infrastructure Engineer</t>
+          <t>Senior Platform/DevOps Engineer (Kubernetes-Linux)</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>General Intuition &amp; Medal</t>
+          <t>ARMADA</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Kirkland, WA, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Scala, MySQL, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,24 +4276,24 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a84d1c588e106220</t>
+          <t>https://www.indeed.com/viewjob?jk=33ae1f1f9d08c546</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Kubernetes MLOps Engineer</t>
+          <t>Senior Platform/DevOps Engineer (Kubernetes-Linux)</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>ARMADA</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Renton, WA, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, Scala, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,24 +4311,24 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82d92ef7ef6e6f18</t>
+          <t>https://www.indeed.com/viewjob?jk=d25130b996402485</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Sr. Data Architect Specialist</t>
+          <t>Senior Platform/DevOps Engineer (Kubernetes-Linux)</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>SAMYANG AMERICA INC</t>
+          <t>ARMADA</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Brea, CA, US USA</t>
+          <t>Bothell, WA, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,24 +4346,24 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2086e3e44cfc021</t>
+          <t>https://www.indeed.com/viewjob?jk=b6f9224460f3210c</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Full Stack Product Engineer (Java)</t>
+          <t>Senior Platform/DevOps Engineer (Kubernetes-Linux)</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Allstate Insurance</t>
+          <t>ARMADA</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Redmond, WA, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, ELT, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,24 +4381,24 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d15adff582efc740</t>
+          <t>https://www.indeed.com/viewjob?jk=b86c940f686047d8</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>DevOps &amp; Infrastructure Engineer - Level I</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>SPRING ARBOR UNIVERSITY</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Spring Arbor, MI, US USA</t>
+          <t>Somerville, MA, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Oracle, CI/CD, Jenkins, GitHub Actions, Docker, Jenkins</t>
+          <t>Redshift, RDS, Azure, Scala, Snowflake, ETL, ELT, dbt, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,24 +4416,24 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0b216de71eb3804</t>
+          <t>https://www.indeed.com/viewjob?jk=75339d7552c524c1</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Senior GCP Kubernetes Engineer</t>
+          <t>Sr. Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>PitchBook</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Kafka, Oracle, PostgreSQL, CI/CD, Jenkins, Maven</t>
+          <t>AWS, RDS, GCP, Scala, SQL Server, PostgreSQL, MySQL, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,24 +4451,24 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a77679969db6e94b</t>
+          <t>https://www.indeed.com/viewjob?jk=181ce2100b853c3a</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer, Enterprise Technology</t>
+          <t>Senior Data Engineer / Data Architect</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Rivian</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,34 +4476,34 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MySQL, NoSQL, Splunk, Docker, Kubernetes</t>
+          <t>AWS, Kinesis, Redshift, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fab081dda06a1ba5</t>
+          <t>https://www.indeed.com/viewjob?jk=e83d1768e75b1203</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Senior GCP IAM Engineer</t>
+          <t>Snowflake Data Movement Engineer</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Smart Tech Skills LLC</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Kafka, Snowflake</t>
+          <t>RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, ETL, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,24 +4521,24 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e01ee86f0306e6c</t>
+          <t>https://www.indeed.com/viewjob?jk=12ef21c70e148f1d</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>QA Analyst / ETL Tester</t>
+          <t>Site Reliability / Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>CSpring</t>
+          <t>General Intuition &amp; Medal</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Springfield, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>RDS, Azure, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Data Modeling, Snowflake Schema, ETL, CI/CD</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Scala, MySQL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4556,32 +4556,32 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ebf7b3987a302e8</t>
+          <t>https://www.indeed.com/viewjob?jk=a84d1c588e106220</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Kubernetes MLOps Engineer</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Urology Centers of Alabama</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, ETL</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, Scala, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,32 +4591,32 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28cb24ea6139fcb9</t>
+          <t>https://www.indeed.com/viewjob?jk=82d92ef7ef6e6f18</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr. Data Architect Specialist</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Pearson</t>
+          <t>SAMYANG AMERICA INC</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Hoboken, NJ, US USA</t>
+          <t>Brea, CA, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, MongoDB, DynamoDB, Data Modeling, ETL, ELT, DataOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,32 +4626,32 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05547d65aabdfcf0</t>
+          <t>https://www.indeed.com/viewjob?jk=f2086e3e44cfc021</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
+          <t>Full Stack Product Engineer (Java)</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Allstate Insurance</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, ELT, CI/CD, Git</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4661,32 +4661,32 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34c37a226b547d01</t>
+          <t>https://www.indeed.com/viewjob?jk=d15adff582efc740</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
+          <t>DevOps &amp; Infrastructure Engineer - Level I</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>SPRING ARBOR UNIVERSITY</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Spring Arbor, MI, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
+          <t>AWS, Azure, GCP, Scala, Oracle, CI/CD, Jenkins, GitHub Actions, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4696,32 +4696,32 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7d77afce6f60e6f</t>
+          <t>https://www.indeed.com/viewjob?jk=b0b216de71eb3804</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
+          <t>Senior GCP Kubernetes Engineer</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, Oracle, PostgreSQL, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4731,102 +4731,102 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=225c5a8131dc6595</t>
+          <t>https://www.indeed.com/viewjob?jk=a77679969db6e94b</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
+          <t>Software Engineer – Enterprise Software</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Rivian</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MySQL, NoSQL, Splunk, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=301dbd1e2eb0bb70</t>
+          <t>https://www.indeed.com/viewjob?jk=90124173401e2437</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
+          <t>Sr. Software Engineer, Enterprise Technology</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Rivian</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MySQL, NoSQL, Splunk, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d88e7121c2db79d6</t>
+          <t>https://www.indeed.com/viewjob?jk=fab081dda06a1ba5</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
+          <t>Senior GCP IAM Engineer</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4836,32 +4836,32 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18d3f9fdcfa07035</t>
+          <t>https://www.indeed.com/viewjob?jk=4e01ee86f0306e6c</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
+          <t>QA Analyst / ETL Tester</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>CSpring</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Springfield, IL, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
+          <t>RDS, Azure, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Data Modeling, Snowflake Schema, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -4871,24 +4871,24 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d2d16258cfd6718</t>
+          <t>https://www.indeed.com/viewjob?jk=1ebf7b3987a302e8</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
+          <t>Engineer II-Software Development</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Microchip Technology</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4896,7 +4896,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -4906,24 +4906,24 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5be8f9b4535b406c</t>
+          <t>https://www.indeed.com/viewjob?jk=3013681a0e1c4f81</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
+          <t>Engineer II-Software Development</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Microchip Technology</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4931,7 +4931,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -4941,24 +4941,24 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26ef52c65261360a</t>
+          <t>https://www.indeed.com/viewjob?jk=2649d75a044fe7bd</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
+          <t>Senior Software Engineer - VAULT</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Bloomberg</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4966,7 +4966,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
+          <t>AWS, S3, RDS, Azure, GCP, Hive, Spark, Scala, Kafka, Cassandra</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -4976,24 +4976,24 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9240b7b96545a4d</t>
+          <t>https://www.indeed.com/viewjob?jk=1d744cfcd1fce896</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
+          <t>Cloud AI Application Administrator</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5001,7 +5001,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
+          <t>RDS, Google Cloud Platform, Dataflow, Cloud Storage, Scala, Oracle, ETL, ELT, dbt, Tableau</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -5011,24 +5011,24 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42ae72f7d4a97700</t>
+          <t>https://www.indeed.com/viewjob?jk=cd193e360372af33</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Urology Centers of Alabama</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5036,7 +5036,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
+          <t>AWS, EMR, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, ETL</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -5046,24 +5046,24 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dab5b1b68cc6402c</t>
+          <t>https://www.indeed.com/viewjob?jk=28cb24ea6139fcb9</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Pearson</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Hoboken, NJ, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
+          <t>AWS, RDS, Scala, MongoDB, DynamoDB, Data Modeling, ETL, ELT, DataOps, CI/CD</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fde8d1831ca7f9b7</t>
+          <t>https://www.indeed.com/viewjob?jk=05547d65aabdfcf0</t>
         </is>
       </c>
     </row>
@@ -5098,7 +5098,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5116,7 +5116,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a056659ad4aebd2</t>
+          <t>https://www.indeed.com/viewjob?jk=34c37a226b547d01</t>
         </is>
       </c>
     </row>
@@ -5133,7 +5133,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5151,7 +5151,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5402962c321dcba</t>
+          <t>https://www.indeed.com/viewjob?jk=e7d77afce6f60e6f</t>
         </is>
       </c>
     </row>
@@ -5168,7 +5168,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5186,7 +5186,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f45ad39ec1fe503a</t>
+          <t>https://www.indeed.com/viewjob?jk=225c5a8131dc6595</t>
         </is>
       </c>
     </row>
@@ -5203,7 +5203,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5221,7 +5221,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86cfc919b4ccc768</t>
+          <t>https://www.indeed.com/viewjob?jk=301dbd1e2eb0bb70</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5256,7 +5256,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9a866cff6a0e3bd</t>
+          <t>https://www.indeed.com/viewjob?jk=d88e7121c2db79d6</t>
         </is>
       </c>
     </row>
@@ -5273,7 +5273,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5291,7 +5291,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab68f1e4ba82ad10</t>
+          <t>https://www.indeed.com/viewjob?jk=18d3f9fdcfa07035</t>
         </is>
       </c>
     </row>
@@ -5308,7 +5308,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5326,7 +5326,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df163d5906a30146</t>
+          <t>https://www.indeed.com/viewjob?jk=9d2d16258cfd6718</t>
         </is>
       </c>
     </row>
@@ -5343,7 +5343,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5361,7 +5361,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f0c32c0bdf67710</t>
+          <t>https://www.indeed.com/viewjob?jk=5be8f9b4535b406c</t>
         </is>
       </c>
     </row>
@@ -5378,7 +5378,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5396,7 +5396,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25f63312ec2e267e</t>
+          <t>https://www.indeed.com/viewjob?jk=26ef52c65261360a</t>
         </is>
       </c>
     </row>
@@ -5413,7 +5413,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be379ec08f5c5e6f</t>
+          <t>https://www.indeed.com/viewjob?jk=f9240b7b96545a4d</t>
         </is>
       </c>
     </row>
@@ -5448,7 +5448,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -5466,7 +5466,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8deeb1ab1ebcdccd</t>
+          <t>https://www.indeed.com/viewjob?jk=42ae72f7d4a97700</t>
         </is>
       </c>
     </row>
@@ -5483,7 +5483,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92aa87419ba8e5df</t>
+          <t>https://www.indeed.com/viewjob?jk=dab5b1b68cc6402c</t>
         </is>
       </c>
     </row>
@@ -5518,7 +5518,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -5536,7 +5536,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da334d3b3eda0eb4</t>
+          <t>https://www.indeed.com/viewjob?jk=fde8d1831ca7f9b7</t>
         </is>
       </c>
     </row>
@@ -5553,7 +5553,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D147" t="n">
@@ -5571,7 +5571,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c314e6df20a4157</t>
+          <t>https://www.indeed.com/viewjob?jk=7a056659ad4aebd2</t>
         </is>
       </c>
     </row>
@@ -5588,7 +5588,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D148" t="n">
@@ -5606,7 +5606,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b90a165cff732e70</t>
+          <t>https://www.indeed.com/viewjob?jk=e5402962c321dcba</t>
         </is>
       </c>
     </row>
@@ -5623,7 +5623,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D149" t="n">
@@ -5641,7 +5641,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26bc98921360165c</t>
+          <t>https://www.indeed.com/viewjob?jk=f45ad39ec1fe503a</t>
         </is>
       </c>
     </row>
@@ -5658,7 +5658,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D150" t="n">
@@ -5676,7 +5676,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5359f322821abe9</t>
+          <t>https://www.indeed.com/viewjob?jk=86cfc919b4ccc768</t>
         </is>
       </c>
     </row>
@@ -5693,7 +5693,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D151" t="n">
@@ -5711,7 +5711,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=562ea8307dd5c91d</t>
+          <t>https://www.indeed.com/viewjob?jk=c9a866cff6a0e3bd</t>
         </is>
       </c>
     </row>
@@ -5728,7 +5728,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D152" t="n">
@@ -5746,7 +5746,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70a64e543cdeb49a</t>
+          <t>https://www.indeed.com/viewjob?jk=ab68f1e4ba82ad10</t>
         </is>
       </c>
     </row>
@@ -5763,7 +5763,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D153" t="n">
@@ -5781,7 +5781,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed3e28c9a543299a</t>
+          <t>https://www.indeed.com/viewjob?jk=df163d5906a30146</t>
         </is>
       </c>
     </row>
@@ -5798,7 +5798,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D154" t="n">
@@ -5816,24 +5816,24 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1735f01363643535</t>
+          <t>https://www.indeed.com/viewjob?jk=2f0c32c0bdf67710</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Data Engineer II, Mobile Game Analytics</t>
+          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Mattel, Inc.</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>El Segundo, CA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D155" t="n">
@@ -5841,7 +5841,7 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>RDS, Medallion Architecture, GCP, BigQuery, Dimensional Modeling, ETL, dbt, Tableau, CI/CD, Airflow</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
@@ -5851,24 +5851,24 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=087868e735e87a06</t>
+          <t>https://www.indeed.com/viewjob?jk=25f63312ec2e267e</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - VAULT</t>
+          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Bloomberg</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D156" t="n">
@@ -5876,7 +5876,7 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Hive, Spark, Scala, Kafka, Cassandra</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
@@ -5886,24 +5886,24 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d744cfcd1fce896</t>
+          <t>https://www.indeed.com/viewjob?jk=be379ec08f5c5e6f</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Cloud AI Application Administrator</t>
+          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D157" t="n">
@@ -5911,7 +5911,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, Dataflow, Cloud Storage, Scala, Oracle, ETL, ELT, dbt, Tableau</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -5921,24 +5921,24 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd193e360372af33</t>
+          <t>https://www.indeed.com/viewjob?jk=8deeb1ab1ebcdccd</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D158" t="n">
@@ -5946,7 +5946,7 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, BigQuery, Vertex AI, Spark, Scala, Spark Streaming, Kafka, CI/CD, Git</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
@@ -5956,24 +5956,24 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f192cf981191d4cd</t>
+          <t>https://www.indeed.com/viewjob?jk=92aa87419ba8e5df</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D159" t="n">
@@ -5981,7 +5981,7 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, Terraform, Docker, Jenkins</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
@@ -5991,24 +5991,24 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7e0844f636778b5</t>
+          <t>https://www.indeed.com/viewjob?jk=da334d3b3eda0eb4</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>GCP Support Associate</t>
+          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D160" t="n">
@@ -6016,7 +6016,7 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, GCP, Dataflow, Cloud Storage, CI/CD, Jenkins, Terraform, Docker, Jenkins</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
@@ -6026,24 +6026,24 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=908520f92505a147</t>
+          <t>https://www.indeed.com/viewjob?jk=2c314e6df20a4157</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Leidos</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Seaside, CA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D161" t="n">
@@ -6051,7 +6051,7 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Splunk, CI/CD, Terraform, Docker, Kubernetes, Git, CloudWatch</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
@@ -6061,24 +6061,24 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=727ac8d7c715b1a1</t>
+          <t>https://www.indeed.com/viewjob?jk=b90a165cff732e70</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Engineer II-Software Development</t>
+          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Microchip Technology</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D162" t="n">
@@ -6086,7 +6086,7 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLOps, CI/CD</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
@@ -6096,24 +6096,24 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3013681a0e1c4f81</t>
+          <t>https://www.indeed.com/viewjob?jk=26bc98921360165c</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Engineer II-Software Development</t>
+          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Microchip Technology</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D163" t="n">
@@ -6121,7 +6121,7 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLOps, CI/CD</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
@@ -6131,24 +6131,24 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2649d75a044fe7bd</t>
+          <t>https://www.indeed.com/viewjob?jk=c5359f322821abe9</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Test Automation Architect (Data Migration &amp; Snowflake)</t>
+          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Atlantis IT Group</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Kansas City, KS, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D164" t="n">
@@ -6156,7 +6156,7 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Scala, Snowflake, Oracle, SQL Server, ETL, ELT, CI/CD, pytest, Python, SQL</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
@@ -6166,24 +6166,24 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=706847de763fb7d8</t>
+          <t>https://www.indeed.com/viewjob?jk=562ea8307dd5c91d</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Software Engineer - AI Augmented Development</t>
+          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>PowerPay</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Wayne, PA, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D165" t="n">
@@ -6191,7 +6191,7 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, ECS, IAM, RDS, Snowflake, ETL, Terraform</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
@@ -6201,24 +6201,24 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=039bac65ddb8c30e</t>
+          <t>https://www.indeed.com/viewjob?jk=70a64e543cdeb49a</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Sr Associate Engineer/Engineer, IT Software</t>
+          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D166" t="n">
@@ -6226,7 +6226,7 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
@@ -6236,24 +6236,24 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf657c9771abb6db</t>
+          <t>https://www.indeed.com/viewjob?jk=ed3e28c9a543299a</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>DevOps Engineer (GCP)</t>
+          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D167" t="n">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Vertex AI, Spark, MLflow, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
@@ -6271,24 +6271,24 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a53e6510409c717</t>
+          <t>https://www.indeed.com/viewjob?jk=1735f01363643535</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>AI Application Architect</t>
+          <t>Data Engineer II, Mobile Game Analytics</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Mattel, Inc.</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>WY, US USA</t>
+          <t>El Segundo, CA, US USA</t>
         </is>
       </c>
       <c r="D168" t="n">
@@ -6296,15 +6296,330 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
+          <t>RDS, Medallion Architecture, GCP, BigQuery, Dimensional Modeling, ETL, dbt, Tableau, CI/CD, Airflow</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=087868e735e87a06</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>AI Integration Engineer (Java + AI)</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>TN, US USA</t>
+        </is>
+      </c>
+      <c r="D169" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>RDS, Google Cloud Platform, BigQuery, Vertex AI, Spark, Scala, Spark Streaming, Kafka, CI/CD, Git</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f192cf981191d4cd</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>AI Integration Engineer (Java + AI)</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D170" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, Terraform, Docker, Jenkins</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e7e0844f636778b5</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>GCP Support Associate</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D171" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>IAM, Google Cloud Platform, GCP, Dataflow, Cloud Storage, CI/CD, Jenkins, Terraform, Docker, Jenkins</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=908520f92505a147</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>Cloud Engineer</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Leidos</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Seaside, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D172" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Scala, Splunk, CI/CD, Terraform, Docker, Kubernetes, Git, CloudWatch</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=727ac8d7c715b1a1</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>Enterprise AI Architect</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Radwell International</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Willingboro, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D173" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Scala, PostgreSQL, MySQL, NoSQL, MLOps, CI/CD</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=56c80236c3727026</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>Software Engineer - AI Augmented Development</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>PowerPay</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Wayne, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D174" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, SQS, ECS, IAM, RDS, Snowflake, ETL, Terraform</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=039bac65ddb8c30e</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>Sr Associate Engineer/Engineer, IT Software</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>American Airlines</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Fort Worth, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D175" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cf657c9771abb6db</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>DevOps Engineer (GCP)</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D176" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Vertex AI, Spark, MLflow, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1a53e6510409c717</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>AI Application Architect</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>WY, US USA</t>
+        </is>
+      </c>
+      <c r="D177" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
           <t>AWS, Azure, Google Cloud Platform, Spark, Scala, Snowflake, ETL, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
-      <c r="F168" t="inlineStr">
-        <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="G168" t="inlineStr">
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=bdfa99adc53f817f</t>
         </is>

--- a/results/job_matches_2026-05-06.xlsx
+++ b/results/job_matches_2026-05-06.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G177"/>
+  <dimension ref="A1:G175"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1028,17 +1028,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Health Account Intern</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>WSSC Water</t>
+          <t>Booz Allen Hamilton</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Laurel, MD, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,34 +1046,34 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Blob Storage, GCP, Hadoop</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Databricks, Hadoop, Hive, Spark, Scala</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=859b6255aab51697</t>
+          <t>https://www.indeed.com/viewjob?jk=64329d0d0bf86853</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>WSSC Water</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Laurel, MD, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, API Gateway, RDS, Azure, Kafka</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Blob Storage, GCP, Hadoop</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,14 +1091,14 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b4a39c21c884e72</t>
+          <t>https://www.indeed.com/viewjob?jk=859b6255aab51697</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>GCP ETL Engineer</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, Spark, Scala, Snowflake, Oracle</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, API Gateway, RDS, Azure, Kafka</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e5fc76263d455e5</t>
+          <t>https://www.indeed.com/viewjob?jk=0b4a39c21c884e72</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Software Engineer Big Data</t>
+          <t>GCP ETL Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Sightview Software</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, ECS, IAM</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, Spark, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53f13dba60fcff4b</t>
+          <t>https://www.indeed.com/viewjob?jk=4e5fc76263d455e5</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Java API Integration Engineer</t>
+          <t>Software Engineer Big Data</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Sightview Software</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, API Gateway, RDS, Azure, Google Cloud Platform, Scala, Kafka, Splunk</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, ECS, IAM</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78afcf5aa1e7fc4b</t>
+          <t>https://www.indeed.com/viewjob?jk=53f13dba60fcff4b</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Health Account Intern</t>
+          <t>Java API Integration Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Booz Allen Hamilton</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,34 +1221,34 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Databricks, Hadoop, Hive, Spark, Scala</t>
+          <t>AWS, SQS, SNS, API Gateway, RDS, Azure, Google Cloud Platform, Scala, Kafka, Splunk</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64329d0d0bf86853</t>
+          <t>https://www.indeed.com/viewjob?jk=78afcf5aa1e7fc4b</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Sr Site Reliability Engineer</t>
+          <t>Databricks Engineer and Architect</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Commence</t>
+          <t>Lincoln Financial Group</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Leesburg, VA, US USA</t>
+          <t>Radnor, PA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,34 +1256,34 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, NoSQL, ETL, ELT</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, RDS, Databricks, Unity Catalog</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9093ede7f2269db2</t>
+          <t>https://www.indeed.com/viewjob?jk=d7862c3c59e06d56</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Sr Data Engineer, Python + Spark (Data Federation skillset - Data Lakehouse - Eg: Starburst) - New York</t>
+          <t>Software Engineer Intern</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Photon</t>
+          <t>Norstella</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, S3, Azure, Databricks, Medallion Architecture, GCP, Spark, PySpark</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Azure, Blob Storage, GCP, PostgreSQL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7767a92d7d08a3b</t>
+          <t>https://www.indeed.com/viewjob?jk=49a129c7a487aae4</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - ETL, Java</t>
+          <t>Sr Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>RevSpring, Inc</t>
+          <t>Commence</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Leesburg, VA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,34 +1326,34 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Redshift, S3, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop, Scala</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, NoSQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a9c009a05948507</t>
+          <t>https://www.indeed.com/viewjob?jk=9093ede7f2269db2</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - ETL, Java</t>
+          <t>Sr Data Engineer, Python + Spark (Data Federation skillset - Data Lakehouse - Eg: Starburst) - New York</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>RevSpring, Inc</t>
+          <t>Photon</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Redshift, S3, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop, Scala</t>
+          <t>AWS, Glue, EMR, S3, Azure, Databricks, Medallion Architecture, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba5ba3f3a840901f</t>
+          <t>https://www.indeed.com/viewjob?jk=f7767a92d7d08a3b</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec9899d266d7f4ea</t>
+          <t>https://www.indeed.com/viewjob?jk=4a9c009a05948507</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>DevOps Engineer (GCP)</t>
+          <t>Senior Software Engineer - ETL, Java</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>RevSpring, Inc</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark</t>
+          <t>Redshift, S3, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop, Scala</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d617836814bb437</t>
+          <t>https://www.indeed.com/viewjob?jk=ba5ba3f3a840901f</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Junior GCP Cloud Engineer</t>
+          <t>Senior Software Engineer - ETL, Java</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>RevSpring, Inc</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Data Modeling, Kimball</t>
+          <t>Redshift, S3, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop, Scala</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11aa4a83b27dbdc6</t>
+          <t>https://www.indeed.com/viewjob?jk=ec9899d266d7f4ea</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>DevOps Engineer (GCP)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,34 +1501,34 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, RDS, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df1902d36083d34f</t>
+          <t>https://www.indeed.com/viewjob?jk=9d617836814bb437</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Junior GCP Cloud Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,17 +1536,17 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, RDS, Scala, Kafka, PostgreSQL</t>
+          <t>IAM, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Data Modeling, Kimball</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cb867686433b7a1</t>
+          <t>https://www.indeed.com/viewjob?jk=11aa4a83b27dbdc6</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9c0e5823a5a0a57</t>
+          <t>https://www.indeed.com/viewjob?jk=df1902d36083d34f</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3aeafc948a2f0f6c</t>
+          <t>https://www.indeed.com/viewjob?jk=5cb867686433b7a1</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c45b322f3e5694ad</t>
+          <t>https://www.indeed.com/viewjob?jk=3aeafc948a2f0f6c</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4c63fb90b07eaf3</t>
+          <t>https://www.indeed.com/viewjob?jk=c45b322f3e5694ad</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Junior GCP Cloud Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,42 +1711,42 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, RDS, Scala, Kafka, PostgreSQL</t>
+          <t>Azure, Google Cloud Platform, GCP, Kafka, NoSQL, Data Modeling, ETL, Talend, Tableau, Splunk</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d67c28cbc09b5ad3</t>
+          <t>https://www.indeed.com/viewjob?jk=b3e7636193fed6ce</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Junior GCP Cloud Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Verisk</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Azure, Google Cloud Platform, GCP, Kafka, NoSQL, Data Modeling, ETL, Talend, Tableau, Splunk</t>
+          <t>AWS, Glue, Lambda, Athena, S3, RDS, Spark, Scala, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3e7636193fed6ce</t>
+          <t>https://www.indeed.com/viewjob?jk=cb57edcbdb36ad26</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>MLOps Engineer – Azure Databricks, Cloud-to-Edge ML Deployment</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Verisk</t>
+          <t>KPIT Technologies</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, S3, RDS, Spark, Scala, PostgreSQL, Data Modeling</t>
+          <t>Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb57edcbdb36ad26</t>
+          <t>https://www.indeed.com/viewjob?jk=1160b6a5ea3d30ad</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>MLOps Engineer – Azure Databricks, Cloud-to-Edge ML Deployment</t>
+          <t>Cloud Reliability Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>KPIT Technologies</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, MLOps, MLflow, CI/CD</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Spark, Scala, NoSQL, Data Modeling, MLOps</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,14 +1826,14 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1160b6a5ea3d30ad</t>
+          <t>https://www.indeed.com/viewjob?jk=eae9d6ab07ed0b94</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Cloud Reliability Engineer</t>
+          <t>DevOps/AI Ops Administrator</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Spark, Scala, NoSQL, Data Modeling, MLOps</t>
+          <t>RDS, Azure, Databricks, Event Hubs, Dataflow, Scala, Snowflake, PostgreSQL, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eae9d6ab07ed0b94</t>
+          <t>https://www.indeed.com/viewjob?jk=8de348813177f92b</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>DevOps/AI Ops Administrator</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Metropolis</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Event Hubs, Dataflow, Scala, Snowflake, PostgreSQL, Power BI, CI/CD</t>
+          <t>AWS, Glue, SNS, RDS, Spark, PySpark, Scala, Snowflake, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8de348813177f92b</t>
+          <t>https://www.indeed.com/viewjob?jk=b9fd5c209c01d504</t>
         </is>
       </c>
     </row>
@@ -1908,12 +1908,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Metropolis</t>
+          <t>metropolis</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9fd5c209c01d504</t>
+          <t>https://www.indeed.com/viewjob?jk=d51453a1afa374b4</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Cloud Migration Engineer (GCP)</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>metropolis</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Glue, SNS, RDS, Spark, PySpark, Scala, Snowflake, SQL Server, MySQL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d51453a1afa374b4</t>
+          <t>https://www.indeed.com/viewjob?jk=fb7efc81616340cd</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Cloud Migration Engineer (GCP)</t>
+          <t>Senior Data Engineer (Databricks)</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Infinitive Inc</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Ashburn, VA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,34 +1991,34 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, Snowflake, SQL Server</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, S3, Azure, Databricks, Unity Catalog, GCP</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb7efc81616340cd</t>
+          <t>https://www.indeed.com/viewjob?jk=aee5e62267dbbb6c</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Databricks)</t>
+          <t>Software Engineer – ETL, Java</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Infinitive Inc</t>
+          <t>RevSpring, Inc</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,17 +2026,17 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, S3, Azure, Databricks, Unity Catalog, GCP</t>
+          <t>Redshift, S3, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop, Scala</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aee5e62267dbbb6c</t>
+          <t>https://www.indeed.com/viewjob?jk=3ebdf3dd92985403</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ebdf3dd92985403</t>
+          <t>https://www.indeed.com/viewjob?jk=5c4b1e40555df27f</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c4b1e40555df27f</t>
+          <t>https://www.indeed.com/viewjob?jk=9d1957e3729d8614</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Software Engineer – ETL, Java</t>
+          <t>Computing Architect 4 (contract)</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>RevSpring, Inc</t>
+          <t>Boeing</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Redshift, S3, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop, Scala</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Scala, Kafka, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d1957e3729d8614</t>
+          <t>https://www.indeed.com/viewjob?jk=83fa749fc70ff9b5</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Forward Deployment Engineer</t>
+          <t>Software Developer II</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>Floor &amp; Decor</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,147 +2166,147 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Redshift, API Gateway, IAM, Azure, Databricks, GCP, BigQuery</t>
+          <t>RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d83189697283beb7</t>
+          <t>https://www.indeed.com/viewjob?jk=e331a6c4c6f76859</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>GCP Cloud Engineer</t>
+          <t>Sr. Streaming Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>Ness Digital Engineering</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Vertex AI, Spark, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Kinesis, S3, IAM, RDS, Spark, Scala, Kafka, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e5f23b132fd8132</t>
+          <t>https://www.indeed.com/viewjob?jk=f90fa0ab3164dcd1</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Terraform MLOps Engineer</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>SOFTILITY INC</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Vertex AI, Scala, Kafka, NoSQL, MLOps</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1c091b77ba59917</t>
+          <t>https://www.indeed.com/viewjob?jk=3faf69463891ca3f</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Computing Architect 4 (contract)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Boeing</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Scala, Kafka, Data Modeling, ELT</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Oracle, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83fa749fc70ff9b5</t>
+          <t>https://www.indeed.com/viewjob?jk=d61e7d7639acc074</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Software Developer II</t>
+          <t>Senior Software Development Engineer - Cloud Dev</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Floor &amp; Decor</t>
+          <t>Transmedics</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Andover, MA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL, Splunk, CI/CD</t>
+          <t>AWS, Lambda, Kinesis, Redshift, Step Functions, S3, SQS, SNS, API Gateway, IAM</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e331a6c4c6f76859</t>
+          <t>https://www.indeed.com/viewjob?jk=2efe7bed588da272</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Sr. Streaming Engineer</t>
+          <t>Cloud Service Desk Analyst</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Ness Digital Engineering</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, IAM, RDS, Spark, Scala, Kafka, NoSQL, Splunk</t>
+          <t>AWS, Lambda, S3, ECS, IAM, Azure, Scala, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f90fa0ab3164dcd1</t>
+          <t>https://www.indeed.com/viewjob?jk=e883ce8f9ac322fb</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer - Cloud Dev</t>
+          <t>Sr MERN engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Transmedics</t>
+          <t>Purple Squirrels Software LLC</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Andover, MA, US USA</t>
+          <t>Newark, CA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, Redshift, Step Functions, S3, SQS, SNS, API Gateway, IAM</t>
+          <t>AWS, S3, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2efe7bed588da272</t>
+          <t>https://www.indeed.com/viewjob?jk=edf2effb08935b9f</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Cloud Service Desk Analyst</t>
+          <t>MLOps Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, Azure, Scala, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e883ce8f9ac322fb</t>
+          <t>https://www.indeed.com/viewjob?jk=56f1aa48ba26ae3c</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Sr MERN engineer</t>
+          <t>Junior Cloud Security Analyst</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Purple Squirrels Software LLC</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Newark, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, S3, IAM, RDS, Azure, Databricks, Blob Storage, Unity Catalog, Google Cloud Platform, Spark</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=edf2effb08935b9f</t>
+          <t>https://www.indeed.com/viewjob?jk=cb95dfff70e6d2a4</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>MLOps Engineer</t>
+          <t>Business Intelligence Developer (Healthcare Data, EDI, ETL)</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>MicroHealth LLC</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Vienna, VA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, EMR, RDS, Scala, Snowflake, SQL Server, PostgreSQL, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56f1aa48ba26ae3c</t>
+          <t>https://www.indeed.com/viewjob?jk=3ba3d7e28ab6494c</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Junior Cloud Security Analyst</t>
+          <t>Databricks Developer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Sloan</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Franklin Park, IL, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Databricks, Blob Storage, Unity Catalog, Google Cloud Platform, Spark</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,67 +2526,67 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb95dfff70e6d2a4</t>
+          <t>https://www.indeed.com/viewjob?jk=9921503eb16c8225</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer - Specialist</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Oracle, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, SQL Server, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d61e7d7639acc074</t>
+          <t>https://www.indeed.com/viewjob?jk=932c71a7f13aa9a1</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Business Intelligence Developer (Healthcare Data, EDI, ETL)</t>
+          <t>GCP ETL Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>MicroHealth LLC</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Vienna, VA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Scala, Snowflake, SQL Server, PostgreSQL, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, Azure, GCP, Hadoop, Spark, Kafka, Snowflake, Dimensional Modeling, ETL, Talend</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,32 +2596,32 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ba3d7e28ab6494c</t>
+          <t>https://www.indeed.com/viewjob?jk=d5268867584b4379</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Databricks Developer</t>
+          <t>Senior Site Reliability Engineer, Data &amp; Analytics</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Sloan</t>
+          <t>Blizzard Entertainment</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Franklin Park, IL, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, GCP, BigQuery, Dataflow, Kafka, dbt, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9921503eb16c8225</t>
+          <t>https://www.indeed.com/viewjob?jk=f56eabb97941a731</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Software Engineer - Specialist</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Kroll Inc.</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, SQL Server, MySQL, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Scala, Polars, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,14 +2666,14 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=932c71a7f13aa9a1</t>
+          <t>https://www.indeed.com/viewjob?jk=d56048c057634cd1</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>GCP ETL Engineer</t>
+          <t>GCP Support Associate</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Hadoop, Spark, Kafka, Snowflake, Dimensional Modeling, ETL, Talend</t>
+          <t>IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, MySQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,32 +2701,32 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5268867584b4379</t>
+          <t>https://www.indeed.com/viewjob?jk=29c27657463cb6ea</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Kroll Inc.</t>
+          <t>Miami Marlins</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Scala, Polars, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, GCP, Scala, Snowflake, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,32 +2736,32 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d56048c057634cd1</t>
+          <t>https://www.indeed.com/viewjob?jk=ff87deef607d5450</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>GCP Support Associate</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Paramount</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Fort Lauderdale, FL, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, MySQL, Splunk, CI/CD</t>
+          <t>AWS, RDS, GCP, BigQuery, Dataflow, Scala, MongoDB, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29c27657463cb6ea</t>
+          <t>https://www.indeed.com/viewjob?jk=a12925c69dfc7bed</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>AI Agent Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Miami Marlins</t>
+          <t>Momentive Software</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, GCP, Scala, Snowflake, CI/CD, GitHub Actions</t>
+          <t>AWS, Lambda, Athena, SQS, SNS, API Gateway, ECS, RDS, Azure, GCP</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff87deef607d5450</t>
+          <t>https://www.indeed.com/viewjob?jk=6ac9574b3f75cc2c</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Senior Cloud Database Engineer (Hybrid - Seattle, WA)</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Paramount</t>
+          <t>Nordstrom</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Fort Lauderdale, FL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Dataflow, Scala, MongoDB, NoSQL, Docker, Kubernetes</t>
+          <t>AWS, Glue, Kinesis, Redshift, Athena, S3, RDS, Kafka, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a12925c69dfc7bed</t>
+          <t>https://www.indeed.com/viewjob?jk=1666a61865ef57aa</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>AI Agent Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Momentive Software</t>
+          <t>Moore</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Westminster, CO, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Athena, SQS, SNS, API Gateway, ECS, RDS, Azure, GCP</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ac9574b3f75cc2c</t>
+          <t>https://www.indeed.com/viewjob?jk=b8c5af154805cd95</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Cloud Database Engineer (Hybrid - Seattle, WA)</t>
+          <t>Data Engineer (ETL / Python Developer)</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Nordstrom</t>
+          <t>CSpring</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Springfield, IL, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Redshift, Athena, S3, RDS, Kafka, Oracle, SQL Server</t>
+          <t>Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1666a61865ef57aa</t>
+          <t>https://www.indeed.com/viewjob?jk=b861e2c1a0a03133</t>
         </is>
       </c>
     </row>
@@ -2923,12 +2923,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Moore</t>
+          <t>Imprint</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Westminster, CO, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT, dbt</t>
+          <t>Kinesis, S3, RDS, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8c5af154805cd95</t>
+          <t>https://www.indeed.com/viewjob?jk=e35bafcce4ab1000</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Data Engineer (ETL / Python Developer)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>CSpring</t>
+          <t>Imprint</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Springfield, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Data Modeling</t>
+          <t>Kinesis, S3, RDS, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b861e2c1a0a03133</t>
+          <t>https://www.indeed.com/viewjob?jk=baaf38c4500e2b06</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior AI Data Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Imprint</t>
+          <t>Velvetech</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Kinesis, S3, RDS, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, IAM, Azure, GCP, Vertex AI, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e35bafcce4ab1000</t>
+          <t>https://www.indeed.com/viewjob?jk=2bec7882b34f08c9</t>
         </is>
       </c>
     </row>
@@ -3028,12 +3028,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Imprint</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Westminster, CO, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Kinesis, S3, RDS, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=baaf38c4500e2b06</t>
+          <t>https://www.indeed.com/viewjob?jk=d49164a52434e329</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior AI Data Engineer</t>
+          <t>AWS Data Engineer - Databricks</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Velvetech</t>
+          <t>RadCube</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Vertex AI, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Databricks, Scala, Databricks Lakehouse, Data Modeling</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2bec7882b34f08c9</t>
+          <t>https://www.indeed.com/viewjob?jk=d2dcfccb6b6d90b1</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer - Cloud</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Carnegie Robotics LLC</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Westminster, CO, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,34 +3111,34 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT, dbt</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, PostgreSQL, MongoDB, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d49164a52434e329</t>
+          <t>https://www.indeed.com/viewjob?jk=e2f5b0b9c556cdca</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>AWS Data Engineer - Databricks</t>
+          <t>Senior Data Engineer (Python/PySpark/AWS)</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>RadCube</t>
+          <t>Infinitive Inc</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Ashburn, VA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Databricks, Scala, Databricks Lakehouse, Data Modeling</t>
+          <t>AWS, Azure, Spark, PySpark, Scala, Spark Streaming, Data Modeling, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2025-02-18</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2dcfccb6b6d90b1</t>
+          <t>https://www.indeed.com/viewjob?jk=45083db400feff94</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Software Engineer - Cloud</t>
+          <t>Data Engineer (Python/PySpark/AWS)</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Carnegie Robotics LLC</t>
+          <t>Infinitive Inc</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Ashburn, VA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,34 +3181,34 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, PostgreSQL, MongoDB, DynamoDB, NoSQL</t>
+          <t>AWS, Azure, Spark, PySpark, Scala, Spark Streaming, Data Modeling, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2025-01-27</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2f5b0b9c556cdca</t>
+          <t>https://www.indeed.com/viewjob?jk=5e742c4bedd2037b</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Python/PySpark/AWS)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Infinitive Inc</t>
+          <t>Terra Quantum</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,34 +3216,34 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Azure, Spark, PySpark, Scala, Spark Streaming, Data Modeling, ETL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2025-02-18</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45083db400feff94</t>
+          <t>https://www.indeed.com/viewjob?jk=15eb90498bcba242</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Data Engineer (Python/PySpark/AWS)</t>
+          <t>Full Stack Engineer, Experienced</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Infinitive Inc</t>
+          <t>Blue Shield of California</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,24 +3251,24 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Azure, Spark, PySpark, Scala, Spark Streaming, Data Modeling, ETL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2025-01-27</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e742c4bedd2037b</t>
+          <t>https://www.indeed.com/viewjob?jk=93fe5a9749607800</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Full Stack Engineer, Experienced</t>
+          <t>Full Stack Engineer, Senior</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3296,14 +3296,14 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93fe5a9749607800</t>
+          <t>https://www.indeed.com/viewjob?jk=bcc6fa1baccf83e5</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Full Stack Engineer, Senior</t>
+          <t>Full Stack Engineer, Consultant</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bcc6fa1baccf83e5</t>
+          <t>https://www.indeed.com/viewjob?jk=a3a7d3c5d7336760</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Full Stack Engineer, Consultant</t>
+          <t>Summer Intern, Platform Engineering</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Blue Shield of California</t>
+          <t>Outfront Media</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, NoSQL, CI/CD, Terraform</t>
+          <t>AWS, Lambda, S3, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3a7d3c5d7336760</t>
+          <t>https://www.indeed.com/viewjob?jk=2aa35bb9483f10ad</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Java Software Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Terra Quantum</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,34 +3391,34 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15eb90498bcba242</t>
+          <t>https://www.indeed.com/viewjob?jk=257d265c3f7e2882</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Summer Intern, Platform Engineering</t>
+          <t>Customer Centric Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Outfront Media</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD, Docker</t>
+          <t>AWS, Azure, GCP, BigQuery, Scala, Snowflake, ELT, dbt, Tableau, Docker</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,32 +3436,32 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2aa35bb9483f10ad</t>
+          <t>https://www.indeed.com/viewjob?jk=29a2186b968dd17c</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Java Software Engineer</t>
+          <t>Mid-Level Software Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>State Farm</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Bloomington, IL, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, MongoDB, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,32 +3471,32 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=257d265c3f7e2882</t>
+          <t>https://www.indeed.com/viewjob?jk=da08c5cf76c3287c</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Docker MLOps Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Versant</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, Kafka, Snowflake, Data Modeling, MLOps</t>
+          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, GCP, Spark, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,32 +3506,32 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3cd445b405cda13</t>
+          <t>https://www.indeed.com/viewjob?jk=1fbef82ce93a90ed</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Customer Centric Engineer</t>
+          <t>AI/ML Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Redapt inc</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Woodinville, WA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Scala, Snowflake, ELT, dbt, Tableau, Docker</t>
+          <t>AWS, Redshift, Azure, Databricks, GCP, Vertex AI, Spark, Snowflake, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29a2186b968dd17c</t>
+          <t>https://www.indeed.com/viewjob?jk=b9c94059f3dd29b3</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Senior Machine Learning Engineer - News</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Versant</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, GCP, Spark, NoSQL, ETL</t>
+          <t>AWS, Glue, Lambda, Kinesis, Step Functions, SQS, SNS, RDS, Databricks, Spark</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fbef82ce93a90ed</t>
+          <t>https://www.indeed.com/viewjob?jk=6c5ae4f292525796</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>AI/ML Engineer</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Redapt inc</t>
+          <t>Clayco</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Woodinville, WA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, GCP, Vertex AI, Spark, Snowflake, Data Modeling, ELT</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9c94059f3dd29b3</t>
+          <t>https://www.indeed.com/viewjob?jk=61cc49187bd6e01d</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer - News</t>
+          <t>Data Engineering - E&amp;A - Data Engineer I</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Genesis Global Group</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Myrtle Point, OR, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Step Functions, SQS, SNS, RDS, Databricks, Spark</t>
+          <t>Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c5ae4f292525796</t>
+          <t>https://www.indeed.com/viewjob?jk=2526bf14df16c3e8</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Senior, Data Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Clayco</t>
+          <t>Carrington Mortgage Services, LLC</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, ETL, Microsoft SSIS</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61cc49187bd6e01d</t>
+          <t>https://www.indeed.com/viewjob?jk=dfdf1b9d489fb8ec</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Data Engineering - E&amp;A - Data Engineer I</t>
+          <t>GCP Support Associate</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Genesis Global Group</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Myrtle Point, OR, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
+          <t>ECS, IAM, Google Cloud Platform, GCP, Dataflow, Cloud Storage, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2526bf14df16c3e8</t>
+          <t>https://www.indeed.com/viewjob?jk=a9acaddb632586c1</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Senior, Data Engineer</t>
+          <t>Data Systems Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Carrington Mortgage Services, LLC</t>
+          <t>Central Health</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,34 +3741,34 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, ETL, Microsoft SSIS</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfdf1b9d489fb8ec</t>
+          <t>https://www.indeed.com/viewjob?jk=41eed22913274d81</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>GCP Support Associate</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Victory Live</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>ECS, IAM, Google Cloud Platform, GCP, Dataflow, Cloud Storage, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Data Factory, Snowflake, SQL Server, DynamoDB, ELT, dbt, Terraform</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9acaddb632586c1</t>
+          <t>https://www.indeed.com/viewjob?jk=a1c259f0b00d1299</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Data Systems Engineer</t>
+          <t>AI Senior Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Central Health</t>
+          <t>Wood Mackenzie</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,34 +3811,34 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, Lambda, Redshift, S3, ECS, Azure, Scala, DynamoDB, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41eed22913274d81</t>
+          <t>https://www.indeed.com/viewjob?jk=69e1b61070a9b37b</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>AI Systems Administrator</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Victory Live</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Snowflake, SQL Server, DynamoDB, ELT, dbt, Terraform</t>
+          <t>ECS, RDS, Azure, Databricks, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,32 +3856,32 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1c259f0b00d1299</t>
+          <t>https://www.indeed.com/viewjob?jk=a338fa1fa96ea390</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>AI Senior Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Wood Mackenzie</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, ECS, Azure, Scala, DynamoDB, ETL, CI/CD</t>
+          <t>RDS, GCP, BigQuery, Dataflow, Vertex AI, Scala, Data Modeling, Jenkins, Terraform, Jenkins</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,32 +3891,32 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69e1b61070a9b37b</t>
+          <t>https://www.indeed.com/viewjob?jk=4bbf23a169f18dbc</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>AI Systems Administrator</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>ECS, RDS, Azure, Databricks, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>RDS, GCP, BigQuery, Dataflow, Vertex AI, Scala, Data Modeling, Jenkins, Terraform, Jenkins</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a338fa1fa96ea390</t>
+          <t>https://www.indeed.com/viewjob?jk=4b05514433681d42</t>
         </is>
       </c>
     </row>
@@ -3938,12 +3938,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Clark Construction</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Vertex AI, Scala, Data Modeling, Jenkins, Terraform, Jenkins</t>
+          <t>AWS, Azure, GCP, Spark, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, dbt</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bbf23a169f18dbc</t>
+          <t>https://www.indeed.com/viewjob?jk=6f199bfc2e975b58</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Junior GCP Cloud Engineer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Vertex AI, Scala, Data Modeling, Jenkins, Terraform, Jenkins</t>
+          <t>RDS, Google Cloud Platform, GCP, Dataflow, Cloud Storage, Scala, Oracle, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b05514433681d42</t>
+          <t>https://www.indeed.com/viewjob?jk=817a2d7d06f177a9</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer - Warehouse Management Systems (WMS)</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Clark Construction</t>
+          <t>Staples</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Framingham, MA, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, dbt</t>
+          <t>AWS, RDS, Azure, GCP, HBase, Scala, Kafka, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f199bfc2e975b58</t>
+          <t>https://www.indeed.com/viewjob?jk=654753ccda866d62</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Junior GCP Cloud Engineer</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,34 +4056,34 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, Dataflow, Cloud Storage, Scala, Oracle, ETL, ELT, dbt</t>
+          <t>AWS, S3, IAM, Databricks, Spark, Scala, DynamoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=817a2d7d06f177a9</t>
+          <t>https://www.indeed.com/viewjob?jk=6f9ad7c8c6b989c1</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Snowflake Platform Engineer</t>
+          <t>Sr. Professional, Software Engineering (Python)</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Cotality</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Scala, Snowflake, CI/CD, Terraform, Kubernetes</t>
+          <t>RDS, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, Tableau, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,24 +4101,24 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecb6b777a849d07c</t>
+          <t>https://www.indeed.com/viewjob?jk=83e013cc49a29087</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Snowflake Platform Engineer</t>
+          <t>Senior Platform/DevOps Engineer (Kubernetes-Linux)</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>ARMADA</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Scala, Snowflake, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,24 +4136,24 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=136f0d6f19e6f0c6</t>
+          <t>https://www.indeed.com/viewjob?jk=7b0e9b75e0f5558d</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Sr. Professional, Software Engineering (Python)</t>
+          <t>Senior Platform/DevOps Engineer (Kubernetes-Linux)</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Cotality</t>
+          <t>ARMADA</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Sammamish, WA, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, Tableau, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83e013cc49a29087</t>
+          <t>https://www.indeed.com/viewjob?jk=efa4e4e3099a0ae2</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Kirkland, WA, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b0e9b75e0f5558d</t>
+          <t>https://www.indeed.com/viewjob?jk=33ae1f1f9d08c546</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Sammamish, WA, US USA</t>
+          <t>Renton, WA, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=efa4e4e3099a0ae2</t>
+          <t>https://www.indeed.com/viewjob?jk=d25130b996402485</t>
         </is>
       </c>
     </row>
@@ -4258,7 +4258,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Kirkland, WA, US USA</t>
+          <t>Bothell, WA, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33ae1f1f9d08c546</t>
+          <t>https://www.indeed.com/viewjob?jk=b6f9224460f3210c</t>
         </is>
       </c>
     </row>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Renton, WA, US USA</t>
+          <t>Redmond, WA, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4311,24 +4311,24 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d25130b996402485</t>
+          <t>https://www.indeed.com/viewjob?jk=b86c940f686047d8</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Senior Platform/DevOps Engineer (Kubernetes-Linux)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>ARMADA</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Bothell, WA, US USA</t>
+          <t>Somerville, MA, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>Redshift, RDS, Azure, Scala, Snowflake, ETL, ELT, dbt, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,24 +4346,24 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6f9224460f3210c</t>
+          <t>https://www.indeed.com/viewjob?jk=75339d7552c524c1</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Senior Platform/DevOps Engineer (Kubernetes-Linux)</t>
+          <t>Sr. Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>ARMADA</t>
+          <t>PitchBook</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Redmond, WA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, GCP, Scala, SQL Server, PostgreSQL, MySQL, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,24 +4381,24 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b86c940f686047d8</t>
+          <t>https://www.indeed.com/viewjob?jk=181ce2100b853c3a</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer / Data Architect</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Somerville, MA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Scala, Snowflake, ETL, ELT, dbt, Tableau, CI/CD</t>
+          <t>AWS, Kinesis, Redshift, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,24 +4416,24 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75339d7552c524c1</t>
+          <t>https://www.indeed.com/viewjob?jk=e83d1768e75b1203</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Sr. Site Reliability Engineer</t>
+          <t>Snowflake Data Movement Engineer</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>PitchBook</t>
+          <t>Smart Tech Skills LLC</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, SQL Server, PostgreSQL, MySQL, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, ETL, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,24 +4451,24 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=181ce2100b853c3a</t>
+          <t>https://www.indeed.com/viewjob?jk=12ef21c70e148f1d</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Senior Data Engineer / Data Architect</t>
+          <t>Site Reliability / Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>General Intuition &amp; Medal</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Scala, MySQL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,24 +4486,24 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e83d1768e75b1203</t>
+          <t>https://www.indeed.com/viewjob?jk=a84d1c588e106220</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Snowflake Data Movement Engineer</t>
+          <t>Sr. Data Architect Specialist</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Smart Tech Skills LLC</t>
+          <t>SAMYANG AMERICA INC</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Brea, CA, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, ETL, CI/CD, Airflow</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,24 +4521,24 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12ef21c70e148f1d</t>
+          <t>https://www.indeed.com/viewjob?jk=f2086e3e44cfc021</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Site Reliability / Infrastructure Engineer</t>
+          <t>Full Stack Product Engineer (Java)</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>General Intuition &amp; Medal</t>
+          <t>Allstate Insurance</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Scala, MySQL, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, ELT, CI/CD, Git</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4556,24 +4556,24 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a84d1c588e106220</t>
+          <t>https://www.indeed.com/viewjob?jk=d15adff582efc740</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Kubernetes MLOps Engineer</t>
+          <t>DevOps &amp; Infrastructure Engineer - Level I</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>SPRING ARBOR UNIVERSITY</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Spring Arbor, MI, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, Scala, MLOps, CI/CD</t>
+          <t>AWS, Azure, GCP, Scala, Oracle, CI/CD, Jenkins, GitHub Actions, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,24 +4591,24 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82d92ef7ef6e6f18</t>
+          <t>https://www.indeed.com/viewjob?jk=b0b216de71eb3804</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Sr. Data Architect Specialist</t>
+          <t>Senior GCP Kubernetes Engineer</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>SAMYANG AMERICA INC</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Brea, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, Oracle, PostgreSQL, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,24 +4626,24 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2086e3e44cfc021</t>
+          <t>https://www.indeed.com/viewjob?jk=a77679969db6e94b</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Full Stack Product Engineer (Java)</t>
+          <t>Software Engineer – Enterprise Software</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Allstate Insurance</t>
+          <t>Rivian</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,34 +4651,34 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, ELT, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MySQL, NoSQL, Splunk, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d15adff582efc740</t>
+          <t>https://www.indeed.com/viewjob?jk=90124173401e2437</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>DevOps &amp; Infrastructure Engineer - Level I</t>
+          <t>Sr. Software Engineer, Enterprise Technology</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>SPRING ARBOR UNIVERSITY</t>
+          <t>Rivian</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Spring Arbor, MI, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,24 +4686,24 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Oracle, CI/CD, Jenkins, GitHub Actions, Docker, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MySQL, NoSQL, Splunk, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0b216de71eb3804</t>
+          <t>https://www.indeed.com/viewjob?jk=fab081dda06a1ba5</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Senior GCP Kubernetes Engineer</t>
+          <t>Senior GCP IAM Engineer</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -4713,7 +4713,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4721,7 +4721,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Kafka, Oracle, PostgreSQL, CI/CD, Jenkins, Maven</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4731,24 +4731,24 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a77679969db6e94b</t>
+          <t>https://www.indeed.com/viewjob?jk=4e01ee86f0306e6c</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Software Engineer – Enterprise Software</t>
+          <t>QA Analyst / ETL Tester</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Rivian</t>
+          <t>CSpring</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Springfield, IL, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4756,77 +4756,77 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MySQL, NoSQL, Splunk, Docker, Kubernetes</t>
+          <t>RDS, Azure, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Data Modeling, Snowflake Schema, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90124173401e2437</t>
+          <t>https://www.indeed.com/viewjob?jk=1ebf7b3987a302e8</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer, Enterprise Technology</t>
+          <t>Engineer II-Software Development</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Rivian</t>
+          <t>Microchip Technology</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MySQL, NoSQL, Splunk, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fab081dda06a1ba5</t>
+          <t>https://www.indeed.com/viewjob?jk=3013681a0e1c4f81</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Senior GCP IAM Engineer</t>
+          <t>Engineer II-Software Development</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Microchip Technology</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4836,32 +4836,32 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e01ee86f0306e6c</t>
+          <t>https://www.indeed.com/viewjob?jk=2649d75a044fe7bd</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>QA Analyst / ETL Tester</t>
+          <t>Senior Software Engineer - VAULT</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>CSpring</t>
+          <t>Bloomberg</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Springfield, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>RDS, Azure, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Data Modeling, Snowflake Schema, ETL, CI/CD</t>
+          <t>AWS, S3, RDS, Azure, GCP, Hive, Spark, Scala, Kafka, Cassandra</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -4871,24 +4871,24 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ebf7b3987a302e8</t>
+          <t>https://www.indeed.com/viewjob?jk=1d744cfcd1fce896</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Engineer II-Software Development</t>
+          <t>Cloud AI Application Administrator</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Microchip Technology</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4896,7 +4896,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLOps, CI/CD</t>
+          <t>RDS, Google Cloud Platform, Dataflow, Cloud Storage, Scala, Oracle, ETL, ELT, dbt, Tableau</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -4906,24 +4906,24 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3013681a0e1c4f81</t>
+          <t>https://www.indeed.com/viewjob?jk=cd193e360372af33</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Engineer II-Software Development</t>
+          <t>Data Scientist, Senior Associate – Product, Experience and Technology (PXT) Analytics Team</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Microchip Technology</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4931,34 +4931,34 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLOps, CI/CD</t>
+          <t>Redshift, RDS, Databricks, Scala, Snowflake, dbt, Tableau, CI/CD, Airflow, Git</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2649d75a044fe7bd</t>
+          <t>https://www.indeed.com/viewjob?jk=4b0bfe4f7e93a067</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - VAULT</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Bloomberg</t>
+          <t>Urology Centers of Alabama</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4966,7 +4966,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Hive, Spark, Scala, Kafka, Cassandra</t>
+          <t>AWS, EMR, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, ETL</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -4976,24 +4976,24 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d744cfcd1fce896</t>
+          <t>https://www.indeed.com/viewjob?jk=28cb24ea6139fcb9</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Cloud AI Application Administrator</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Pearson</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Hoboken, NJ, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5001,7 +5001,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, Dataflow, Cloud Storage, Scala, Oracle, ETL, ELT, dbt, Tableau</t>
+          <t>AWS, RDS, Scala, MongoDB, DynamoDB, Data Modeling, ETL, ELT, DataOps, CI/CD</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -5011,24 +5011,24 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd193e360372af33</t>
+          <t>https://www.indeed.com/viewjob?jk=05547d65aabdfcf0</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Urology Centers of Alabama</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5036,7 +5036,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, ETL</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -5046,24 +5046,24 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28cb24ea6139fcb9</t>
+          <t>https://www.indeed.com/viewjob?jk=34c37a226b547d01</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Pearson</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Hoboken, NJ, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, MongoDB, DynamoDB, Data Modeling, ETL, ELT, DataOps, CI/CD</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05547d65aabdfcf0</t>
+          <t>https://www.indeed.com/viewjob?jk=e7d77afce6f60e6f</t>
         </is>
       </c>
     </row>
@@ -5098,7 +5098,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5116,7 +5116,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34c37a226b547d01</t>
+          <t>https://www.indeed.com/viewjob?jk=225c5a8131dc6595</t>
         </is>
       </c>
     </row>
@@ -5133,7 +5133,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5151,7 +5151,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7d77afce6f60e6f</t>
+          <t>https://www.indeed.com/viewjob?jk=301dbd1e2eb0bb70</t>
         </is>
       </c>
     </row>
@@ -5168,7 +5168,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5186,7 +5186,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=225c5a8131dc6595</t>
+          <t>https://www.indeed.com/viewjob?jk=d88e7121c2db79d6</t>
         </is>
       </c>
     </row>
@@ -5203,7 +5203,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5221,7 +5221,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=301dbd1e2eb0bb70</t>
+          <t>https://www.indeed.com/viewjob?jk=18d3f9fdcfa07035</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5256,7 +5256,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d88e7121c2db79d6</t>
+          <t>https://www.indeed.com/viewjob?jk=9d2d16258cfd6718</t>
         </is>
       </c>
     </row>
@@ -5273,7 +5273,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5291,7 +5291,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18d3f9fdcfa07035</t>
+          <t>https://www.indeed.com/viewjob?jk=5be8f9b4535b406c</t>
         </is>
       </c>
     </row>
@@ -5308,7 +5308,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5326,7 +5326,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d2d16258cfd6718</t>
+          <t>https://www.indeed.com/viewjob?jk=26ef52c65261360a</t>
         </is>
       </c>
     </row>
@@ -5343,7 +5343,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5361,7 +5361,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5be8f9b4535b406c</t>
+          <t>https://www.indeed.com/viewjob?jk=f9240b7b96545a4d</t>
         </is>
       </c>
     </row>
@@ -5378,7 +5378,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5396,7 +5396,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26ef52c65261360a</t>
+          <t>https://www.indeed.com/viewjob?jk=42ae72f7d4a97700</t>
         </is>
       </c>
     </row>
@@ -5413,7 +5413,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9240b7b96545a4d</t>
+          <t>https://www.indeed.com/viewjob?jk=dab5b1b68cc6402c</t>
         </is>
       </c>
     </row>
@@ -5448,7 +5448,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -5466,7 +5466,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42ae72f7d4a97700</t>
+          <t>https://www.indeed.com/viewjob?jk=fde8d1831ca7f9b7</t>
         </is>
       </c>
     </row>
@@ -5483,7 +5483,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dab5b1b68cc6402c</t>
+          <t>https://www.indeed.com/viewjob?jk=7a056659ad4aebd2</t>
         </is>
       </c>
     </row>
@@ -5518,7 +5518,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -5536,7 +5536,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fde8d1831ca7f9b7</t>
+          <t>https://www.indeed.com/viewjob?jk=e5402962c321dcba</t>
         </is>
       </c>
     </row>
@@ -5553,7 +5553,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D147" t="n">
@@ -5571,7 +5571,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a056659ad4aebd2</t>
+          <t>https://www.indeed.com/viewjob?jk=f45ad39ec1fe503a</t>
         </is>
       </c>
     </row>
@@ -5588,7 +5588,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D148" t="n">
@@ -5606,7 +5606,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5402962c321dcba</t>
+          <t>https://www.indeed.com/viewjob?jk=86cfc919b4ccc768</t>
         </is>
       </c>
     </row>
@@ -5623,7 +5623,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D149" t="n">
@@ -5641,7 +5641,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f45ad39ec1fe503a</t>
+          <t>https://www.indeed.com/viewjob?jk=c9a866cff6a0e3bd</t>
         </is>
       </c>
     </row>
@@ -5658,7 +5658,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D150" t="n">
@@ -5676,7 +5676,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86cfc919b4ccc768</t>
+          <t>https://www.indeed.com/viewjob?jk=ab68f1e4ba82ad10</t>
         </is>
       </c>
     </row>
@@ -5693,7 +5693,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D151" t="n">
@@ -5711,7 +5711,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9a866cff6a0e3bd</t>
+          <t>https://www.indeed.com/viewjob?jk=df163d5906a30146</t>
         </is>
       </c>
     </row>
@@ -5728,7 +5728,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D152" t="n">
@@ -5746,7 +5746,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab68f1e4ba82ad10</t>
+          <t>https://www.indeed.com/viewjob?jk=2f0c32c0bdf67710</t>
         </is>
       </c>
     </row>
@@ -5763,7 +5763,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D153" t="n">
@@ -5781,7 +5781,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df163d5906a30146</t>
+          <t>https://www.indeed.com/viewjob?jk=25f63312ec2e267e</t>
         </is>
       </c>
     </row>
@@ -5798,7 +5798,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D154" t="n">
@@ -5816,7 +5816,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f0c32c0bdf67710</t>
+          <t>https://www.indeed.com/viewjob?jk=be379ec08f5c5e6f</t>
         </is>
       </c>
     </row>
@@ -5833,7 +5833,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D155" t="n">
@@ -5851,7 +5851,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25f63312ec2e267e</t>
+          <t>https://www.indeed.com/viewjob?jk=8deeb1ab1ebcdccd</t>
         </is>
       </c>
     </row>
@@ -5868,7 +5868,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D156" t="n">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be379ec08f5c5e6f</t>
+          <t>https://www.indeed.com/viewjob?jk=92aa87419ba8e5df</t>
         </is>
       </c>
     </row>
@@ -5903,7 +5903,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D157" t="n">
@@ -5921,7 +5921,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8deeb1ab1ebcdccd</t>
+          <t>https://www.indeed.com/viewjob?jk=da334d3b3eda0eb4</t>
         </is>
       </c>
     </row>
@@ -5938,7 +5938,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D158" t="n">
@@ -5956,7 +5956,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92aa87419ba8e5df</t>
+          <t>https://www.indeed.com/viewjob?jk=2c314e6df20a4157</t>
         </is>
       </c>
     </row>
@@ -5973,7 +5973,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D159" t="n">
@@ -5991,7 +5991,7 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da334d3b3eda0eb4</t>
+          <t>https://www.indeed.com/viewjob?jk=b90a165cff732e70</t>
         </is>
       </c>
     </row>
@@ -6008,7 +6008,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D160" t="n">
@@ -6026,7 +6026,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c314e6df20a4157</t>
+          <t>https://www.indeed.com/viewjob?jk=26bc98921360165c</t>
         </is>
       </c>
     </row>
@@ -6043,7 +6043,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D161" t="n">
@@ -6061,7 +6061,7 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b90a165cff732e70</t>
+          <t>https://www.indeed.com/viewjob?jk=c5359f322821abe9</t>
         </is>
       </c>
     </row>
@@ -6078,7 +6078,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D162" t="n">
@@ -6096,7 +6096,7 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26bc98921360165c</t>
+          <t>https://www.indeed.com/viewjob?jk=562ea8307dd5c91d</t>
         </is>
       </c>
     </row>
@@ -6113,7 +6113,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D163" t="n">
@@ -6131,7 +6131,7 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5359f322821abe9</t>
+          <t>https://www.indeed.com/viewjob?jk=70a64e543cdeb49a</t>
         </is>
       </c>
     </row>
@@ -6148,7 +6148,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D164" t="n">
@@ -6166,7 +6166,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=562ea8307dd5c91d</t>
+          <t>https://www.indeed.com/viewjob?jk=ed3e28c9a543299a</t>
         </is>
       </c>
     </row>
@@ -6183,7 +6183,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D165" t="n">
@@ -6201,24 +6201,24 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70a64e543cdeb49a</t>
+          <t>https://www.indeed.com/viewjob?jk=1735f01363643535</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
+          <t>Data Engineer II, Mobile Game Analytics</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Mattel, Inc.</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>El Segundo, CA, US USA</t>
         </is>
       </c>
       <c r="D166" t="n">
@@ -6226,7 +6226,7 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
+          <t>RDS, Medallion Architecture, GCP, BigQuery, Dimensional Modeling, ETL, dbt, Tableau, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
@@ -6236,24 +6236,24 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed3e28c9a543299a</t>
+          <t>https://www.indeed.com/viewjob?jk=087868e735e87a06</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D167" t="n">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
+          <t>RDS, Google Cloud Platform, BigQuery, Vertex AI, Spark, Scala, Spark Streaming, Kafka, CI/CD, Git</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
@@ -6271,24 +6271,24 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1735f01363643535</t>
+          <t>https://www.indeed.com/viewjob?jk=f192cf981191d4cd</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Data Engineer II, Mobile Game Analytics</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Mattel, Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>El Segundo, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D168" t="n">
@@ -6296,7 +6296,7 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>RDS, Medallion Architecture, GCP, BigQuery, Dimensional Modeling, ETL, dbt, Tableau, CI/CD, Airflow</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, Terraform, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
@@ -6306,14 +6306,14 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=087868e735e87a06</t>
+          <t>https://www.indeed.com/viewjob?jk=e7e0844f636778b5</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>GCP Support Associate</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -6323,7 +6323,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D169" t="n">
@@ -6331,7 +6331,7 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, BigQuery, Vertex AI, Spark, Scala, Spark Streaming, Kafka, CI/CD, Git</t>
+          <t>IAM, Google Cloud Platform, GCP, Dataflow, Cloud Storage, CI/CD, Jenkins, Terraform, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
@@ -6341,24 +6341,24 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f192cf981191d4cd</t>
+          <t>https://www.indeed.com/viewjob?jk=908520f92505a147</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Leidos</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Seaside, CA, US USA</t>
         </is>
       </c>
       <c r="D170" t="n">
@@ -6366,7 +6366,7 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, Terraform, Docker, Jenkins</t>
+          <t>AWS, Azure, Scala, Splunk, CI/CD, Terraform, Docker, Kubernetes, Git, CloudWatch</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
@@ -6376,24 +6376,24 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7e0844f636778b5</t>
+          <t>https://www.indeed.com/viewjob?jk=727ac8d7c715b1a1</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>GCP Support Associate</t>
+          <t>Software Engineer - AI Augmented Development</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>PowerPay</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Wayne, PA, US USA</t>
         </is>
       </c>
       <c r="D171" t="n">
@@ -6401,7 +6401,7 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, GCP, Dataflow, Cloud Storage, CI/CD, Jenkins, Terraform, Docker, Jenkins</t>
+          <t>AWS, Lambda, S3, SQS, ECS, IAM, RDS, Snowflake, ETL, Terraform</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
@@ -6411,24 +6411,24 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=908520f92505a147</t>
+          <t>https://www.indeed.com/viewjob?jk=039bac65ddb8c30e</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Sr Associate Engineer/Engineer, IT Software</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Leidos</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Seaside, CA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D172" t="n">
@@ -6436,7 +6436,7 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Splunk, CI/CD, Terraform, Docker, Kubernetes, Git, CloudWatch</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
@@ -6446,24 +6446,24 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=727ac8d7c715b1a1</t>
+          <t>https://www.indeed.com/viewjob?jk=cf657c9771abb6db</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Enterprise AI Architect</t>
+          <t>DevOps Engineer (GCP)</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Radwell International</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Willingboro, NJ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D173" t="n">
@@ -6471,34 +6471,34 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, PostgreSQL, MySQL, NoSQL, MLOps, CI/CD</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Vertex AI, Spark, MLflow, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56c80236c3727026</t>
+          <t>https://www.indeed.com/viewjob?jk=1a53e6510409c717</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Software Engineer - AI Augmented Development</t>
+          <t>Enterprise AI Architect</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>PowerPay</t>
+          <t>Radwell International</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Wayne, PA, US USA</t>
+          <t>Willingboro, NJ, US USA</t>
         </is>
       </c>
       <c r="D174" t="n">
@@ -6506,34 +6506,34 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, ECS, IAM, RDS, Snowflake, ETL, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, PostgreSQL, MySQL, NoSQL, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=039bac65ddb8c30e</t>
+          <t>https://www.indeed.com/viewjob?jk=56c80236c3727026</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Sr Associate Engineer/Engineer, IT Software</t>
+          <t>AI Application Architect</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D175" t="n">
@@ -6541,7 +6541,7 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, Snowflake, ETL, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
@@ -6550,76 +6550,6 @@
         </is>
       </c>
       <c r="G175" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=cf657c9771abb6db</t>
-        </is>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" t="inlineStr">
-        <is>
-          <t>DevOps Engineer (GCP)</t>
-        </is>
-      </c>
-      <c r="B176" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C176" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D176" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E176" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Vertex AI, Spark, MLflow, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F176" t="inlineStr">
-        <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="G176" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1a53e6510409c717</t>
-        </is>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" t="inlineStr">
-        <is>
-          <t>AI Application Architect</t>
-        </is>
-      </c>
-      <c r="B177" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C177" t="inlineStr">
-        <is>
-          <t>WY, US USA</t>
-        </is>
-      </c>
-      <c r="D177" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E177" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, Snowflake, ETL, MLOps, MLflow, CI/CD</t>
-        </is>
-      </c>
-      <c r="F177" t="inlineStr">
-        <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="G177" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=bdfa99adc53f817f</t>
         </is>

--- a/results/job_matches_2026-05-06.xlsx
+++ b/results/job_matches_2026-05-06.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G175"/>
+  <dimension ref="A1:G181"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1028,17 +1028,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Health Account Intern</t>
+          <t>API Threat Intelligence Analyst</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Booz Allen Hamilton</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Databricks, Hadoop, Hive, Spark, Scala</t>
+          <t>AWS, SQS, SNS, API Gateway, RDS, Azure, Google Cloud Platform, Scala, Kafka, Splunk</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64329d0d0bf86853</t>
+          <t>https://www.indeed.com/viewjob?jk=427f6933d7d21e16</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Health Account Intern</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>WSSC Water</t>
+          <t>Booz Allen Hamilton</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Laurel, MD, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,34 +1081,34 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Blob Storage, GCP, Hadoop</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Databricks, Hadoop, Hive, Spark, Scala</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=859b6255aab51697</t>
+          <t>https://www.indeed.com/viewjob?jk=64329d0d0bf86853</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>WSSC Water</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Laurel, MD, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, API Gateway, RDS, Azure, Kafka</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Blob Storage, GCP, Hadoop</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,14 +1126,14 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b4a39c21c884e72</t>
+          <t>https://www.indeed.com/viewjob?jk=859b6255aab51697</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>GCP ETL Engineer</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, Spark, Scala, Snowflake, Oracle</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, API Gateway, RDS, Azure, Kafka</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e5fc76263d455e5</t>
+          <t>https://www.indeed.com/viewjob?jk=0b4a39c21c884e72</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Software Engineer Big Data</t>
+          <t>GCP ETL Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Sightview Software</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, ECS, IAM</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, Spark, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53f13dba60fcff4b</t>
+          <t>https://www.indeed.com/viewjob?jk=4e5fc76263d455e5</t>
         </is>
       </c>
     </row>
@@ -1273,17 +1273,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Software Engineer Intern</t>
+          <t>Sr Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Norstella</t>
+          <t>Commence</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Leesburg, VA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,34 +1291,34 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Azure, Blob Storage, GCP, PostgreSQL</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, NoSQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49a129c7a487aae4</t>
+          <t>https://www.indeed.com/viewjob?jk=9093ede7f2269db2</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Sr Site Reliability Engineer</t>
+          <t>Sr Data Engineer, Python + Spark (Data Federation skillset - Data Lakehouse - Eg: Starburst) - New York</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Commence</t>
+          <t>Photon</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Leesburg, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,34 +1326,34 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, NoSQL, ETL, ELT</t>
+          <t>AWS, Glue, EMR, S3, Azure, Databricks, Medallion Architecture, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9093ede7f2269db2</t>
+          <t>https://www.indeed.com/viewjob?jk=f7767a92d7d08a3b</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Sr Data Engineer, Python + Spark (Data Federation skillset - Data Lakehouse - Eg: Starburst) - New York</t>
+          <t>Senior Software Engineer - ETL, Java</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Photon</t>
+          <t>RevSpring, Inc</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, S3, Azure, Databricks, Medallion Architecture, GCP, Spark, PySpark</t>
+          <t>Redshift, S3, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop, Scala</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7767a92d7d08a3b</t>
+          <t>https://www.indeed.com/viewjob?jk=4a9c009a05948507</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a9c009a05948507</t>
+          <t>https://www.indeed.com/viewjob?jk=ba5ba3f3a840901f</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba5ba3f3a840901f</t>
+          <t>https://www.indeed.com/viewjob?jk=ec9899d266d7f4ea</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - ETL, Java</t>
+          <t>DevOps Engineer (GCP)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>RevSpring, Inc</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Redshift, S3, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,14 +1476,14 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec9899d266d7f4ea</t>
+          <t>https://www.indeed.com/viewjob?jk=9d617836814bb437</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>DevOps Engineer (GCP)</t>
+          <t>Junior GCP Cloud Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark</t>
+          <t>IAM, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Data Modeling, Kimball</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d617836814bb437</t>
+          <t>https://www.indeed.com/viewjob?jk=11aa4a83b27dbdc6</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Junior GCP Cloud Engineer</t>
+          <t>Software Engineer Intern</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Norstella</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Data Modeling, Kimball</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Azure, Blob Storage, GCP, PostgreSQL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11aa4a83b27dbdc6</t>
+          <t>https://www.indeed.com/viewjob?jk=49a129c7a487aae4</t>
         </is>
       </c>
     </row>
@@ -1833,7 +1833,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>DevOps/AI Ops Administrator</t>
+          <t>API Threat Intelligence Analyst</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,77 +1851,77 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Event Hubs, Dataflow, Scala, Snowflake, PostgreSQL, Power BI, CI/CD</t>
+          <t>Azure, Google Cloud Platform, Kafka, NoSQL, Data Modeling, ETL, Talend, Tableau, Splunk, MicroStrategy</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8de348813177f92b</t>
+          <t>https://www.indeed.com/viewjob?jk=e918fa70b2a1920e</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Backend (Python)</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Metropolis</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Glue, SNS, RDS, Spark, PySpark, Scala, Snowflake, SQL Server, MySQL</t>
+          <t>Azure, Google Cloud Platform, Kafka, NoSQL, Data Modeling, ETL, Talend, Tableau, Splunk, MicroStrategy</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9fd5c209c01d504</t>
+          <t>https://www.indeed.com/viewjob?jk=d711bd4394cb404e</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>DevOps/AI Ops Administrator</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>metropolis</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Glue, SNS, RDS, Spark, PySpark, Scala, Snowflake, SQL Server, MySQL</t>
+          <t>RDS, Azure, Databricks, Event Hubs, Dataflow, Scala, Snowflake, PostgreSQL, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d51453a1afa374b4</t>
+          <t>https://www.indeed.com/viewjob?jk=8de348813177f92b</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Cloud Migration Engineer (GCP)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Metropolis</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, Snowflake, SQL Server</t>
+          <t>AWS, Glue, SNS, RDS, Spark, PySpark, Scala, Snowflake, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb7efc81616340cd</t>
+          <t>https://www.indeed.com/viewjob?jk=b9fd5c209c01d504</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Databricks)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Infinitive Inc</t>
+          <t>metropolis</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,34 +1991,34 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, S3, Azure, Databricks, Unity Catalog, GCP</t>
+          <t>AWS, Glue, SNS, RDS, Spark, PySpark, Scala, Snowflake, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aee5e62267dbbb6c</t>
+          <t>https://www.indeed.com/viewjob?jk=d51453a1afa374b4</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Software Engineer – ETL, Java</t>
+          <t>Cloud Migration Engineer (GCP)</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>RevSpring, Inc</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Redshift, S3, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop, Scala</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ebdf3dd92985403</t>
+          <t>https://www.indeed.com/viewjob?jk=fb7efc81616340cd</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Software Engineer – ETL, Java</t>
+          <t>Senior Data Engineer (Databricks)</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>RevSpring, Inc</t>
+          <t>Infinitive Inc</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Ashburn, VA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,17 +2061,17 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Redshift, S3, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop, Scala</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, S3, Azure, Databricks, Unity Catalog, GCP</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c4b1e40555df27f</t>
+          <t>https://www.indeed.com/viewjob?jk=aee5e62267dbbb6c</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d1957e3729d8614</t>
+          <t>https://www.indeed.com/viewjob?jk=3ebdf3dd92985403</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Computing Architect 4 (contract)</t>
+          <t>Software Engineer – ETL, Java</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Boeing</t>
+          <t>RevSpring, Inc</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Scala, Kafka, Data Modeling, ELT</t>
+          <t>Redshift, S3, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop, Scala</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83fa749fc70ff9b5</t>
+          <t>https://www.indeed.com/viewjob?jk=5c4b1e40555df27f</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Software Developer II</t>
+          <t>Software Engineer – ETL, Java</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Floor &amp; Decor</t>
+          <t>RevSpring, Inc</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL, Splunk, CI/CD</t>
+          <t>Redshift, S3, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop, Scala</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,32 +2176,32 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e331a6c4c6f76859</t>
+          <t>https://www.indeed.com/viewjob?jk=9d1957e3729d8614</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Sr. Streaming Engineer</t>
+          <t>Computing Architect 4 (contract)</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Ness Digital Engineering</t>
+          <t>Boeing</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, IAM, RDS, Spark, Scala, Kafka, NoSQL, Splunk</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Scala, Kafka, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,59 +2211,59 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f90fa0ab3164dcd1</t>
+          <t>https://www.indeed.com/viewjob?jk=83fa749fc70ff9b5</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Software Developer II</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>SOFTILITY INC</t>
+          <t>Floor &amp; Decor</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD</t>
+          <t>RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3faf69463891ca3f</t>
+          <t>https://www.indeed.com/viewjob?jk=e331a6c4c6f76859</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>SOFTILITY INC</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Oracle, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d61e7d7639acc074</t>
+          <t>https://www.indeed.com/viewjob?jk=3faf69463891ca3f</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer - Cloud Dev</t>
+          <t>Sr. Streaming Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Transmedics</t>
+          <t>Ness Digital Engineering</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Andover, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, Redshift, Step Functions, S3, SQS, SNS, API Gateway, IAM</t>
+          <t>AWS, Kinesis, S3, IAM, RDS, Spark, Scala, Kafka, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2efe7bed588da272</t>
+          <t>https://www.indeed.com/viewjob?jk=f90fa0ab3164dcd1</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Cloud Service Desk Analyst</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, Azure, Scala, CI/CD, GitHub Actions, Terraform</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Oracle, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e883ce8f9ac322fb</t>
+          <t>https://www.indeed.com/viewjob?jk=d61e7d7639acc074</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Sr MERN engineer</t>
+          <t>Senior Software Development Engineer - Cloud Dev</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Purple Squirrels Software LLC</t>
+          <t>Transmedics</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Newark, CA, US USA</t>
+          <t>Andover, MA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, Lambda, Kinesis, Redshift, Step Functions, S3, SQS, SNS, API Gateway, IAM</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=edf2effb08935b9f</t>
+          <t>https://www.indeed.com/viewjob?jk=2efe7bed588da272</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>MLOps Engineer</t>
+          <t>Cloud Service Desk Analyst</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, Lambda, S3, ECS, IAM, Azure, Scala, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56f1aa48ba26ae3c</t>
+          <t>https://www.indeed.com/viewjob?jk=e883ce8f9ac322fb</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Junior Cloud Security Analyst</t>
+          <t>MLOps Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Databricks, Blob Storage, Unity Catalog, Google Cloud Platform, Spark</t>
+          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb95dfff70e6d2a4</t>
+          <t>https://www.indeed.com/viewjob?jk=56f1aa48ba26ae3c</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Business Intelligence Developer (Healthcare Data, EDI, ETL)</t>
+          <t>Junior Cloud Security Analyst</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>MicroHealth LLC</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Vienna, VA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Scala, Snowflake, SQL Server, PostgreSQL, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, S3, IAM, RDS, Azure, Databricks, Blob Storage, Unity Catalog, Google Cloud Platform, Spark</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ba3d7e28ab6494c</t>
+          <t>https://www.indeed.com/viewjob?jk=cb95dfff70e6d2a4</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Databricks Developer</t>
+          <t>Business Intelligence Developer (Healthcare Data, EDI, ETL)</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Sloan</t>
+          <t>MicroHealth LLC</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Franklin Park, IL, US USA</t>
+          <t>Vienna, VA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, EMR, RDS, Scala, Snowflake, SQL Server, PostgreSQL, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,32 +2526,32 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9921503eb16c8225</t>
+          <t>https://www.indeed.com/viewjob?jk=3ba3d7e28ab6494c</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Software Engineer - Specialist</t>
+          <t>Databricks Developer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Sloan</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Franklin Park, IL, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, SQL Server, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=932c71a7f13aa9a1</t>
+          <t>https://www.indeed.com/viewjob?jk=9921503eb16c8225</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>GCP ETL Engineer</t>
+          <t>Software Engineer - Specialist</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Hadoop, Spark, Kafka, Snowflake, Dimensional Modeling, ETL, Talend</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, SQL Server, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5268867584b4379</t>
+          <t>https://www.indeed.com/viewjob?jk=932c71a7f13aa9a1</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer, Data &amp; Analytics</t>
+          <t>GCP ETL Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Blizzard Entertainment</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Dataflow, Kafka, dbt, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Azure, GCP, Hadoop, Spark, Kafka, Snowflake, Dimensional Modeling, ETL, Talend</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f56eabb97941a731</t>
+          <t>https://www.indeed.com/viewjob?jk=d5268867584b4379</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Site Reliability Engineer, Data &amp; Analytics</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Kroll Inc.</t>
+          <t>Blizzard Entertainment</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Scala, Polars, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, RDS, GCP, BigQuery, Dataflow, Kafka, dbt, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d56048c057634cd1</t>
+          <t>https://www.indeed.com/viewjob?jk=f56eabb97941a731</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>GCP Support Associate</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Kroll Inc.</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, MySQL, Splunk, CI/CD</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Scala, Polars, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,67 +2701,67 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29c27657463cb6ea</t>
+          <t>https://www.indeed.com/viewjob?jk=d56048c057634cd1</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>FastAPI</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Miami Marlins</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, GCP, Scala, Snowflake, CI/CD, GitHub Actions</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, PostgreSQL, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff87deef607d5450</t>
+          <t>https://www.indeed.com/viewjob?jk=550e29553f2a099b</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>GCP Support Associate</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Paramount</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Fort Lauderdale, FL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Dataflow, Scala, MongoDB, NoSQL, Docker, Kubernetes</t>
+          <t>IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, MySQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a12925c69dfc7bed</t>
+          <t>https://www.indeed.com/viewjob?jk=29c27657463cb6ea</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>AI Agent Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Momentive Software</t>
+          <t>Miami Marlins</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Athena, SQS, SNS, API Gateway, ECS, RDS, Azure, GCP</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, GCP, Scala, Snowflake, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ac9574b3f75cc2c</t>
+          <t>https://www.indeed.com/viewjob?jk=ff87deef607d5450</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Cloud Database Engineer (Hybrid - Seattle, WA)</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Nordstrom</t>
+          <t>Paramount</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Fort Lauderdale, FL, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Redshift, Athena, S3, RDS, Kafka, Oracle, SQL Server</t>
+          <t>AWS, RDS, GCP, BigQuery, Dataflow, Scala, MongoDB, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1666a61865ef57aa</t>
+          <t>https://www.indeed.com/viewjob?jk=a12925c69dfc7bed</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI Agent Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Moore</t>
+          <t>Momentive Software</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Westminster, CO, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT, dbt</t>
+          <t>AWS, Lambda, Athena, SQS, SNS, API Gateway, ECS, RDS, Azure, GCP</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8c5af154805cd95</t>
+          <t>https://www.indeed.com/viewjob?jk=6ac9574b3f75cc2c</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Data Engineer (ETL / Python Developer)</t>
+          <t>Senior Cloud Database Engineer (Hybrid - Seattle, WA)</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>CSpring</t>
+          <t>Nordstrom</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Springfield, IL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, Glue, Kinesis, Redshift, Athena, S3, RDS, Kafka, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b861e2c1a0a03133</t>
+          <t>https://www.indeed.com/viewjob?jk=1666a61865ef57aa</t>
         </is>
       </c>
     </row>
@@ -2923,12 +2923,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Imprint</t>
+          <t>Moore</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Westminster, CO, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Kinesis, S3, RDS, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e35bafcce4ab1000</t>
+          <t>https://www.indeed.com/viewjob?jk=b8c5af154805cd95</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer (ETL / Python Developer)</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Imprint</t>
+          <t>CSpring</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Springfield, IL, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Kinesis, S3, RDS, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=baaf38c4500e2b06</t>
+          <t>https://www.indeed.com/viewjob?jk=b861e2c1a0a03133</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior AI Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Velvetech</t>
+          <t>Imprint</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Vertex AI, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD</t>
+          <t>Kinesis, S3, RDS, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2bec7882b34f08c9</t>
+          <t>https://www.indeed.com/viewjob?jk=e35bafcce4ab1000</t>
         </is>
       </c>
     </row>
@@ -3028,12 +3028,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Imprint</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Westminster, CO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT, dbt</t>
+          <t>Kinesis, S3, RDS, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d49164a52434e329</t>
+          <t>https://www.indeed.com/viewjob?jk=baaf38c4500e2b06</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>AWS Data Engineer - Databricks</t>
+          <t>Senior AI Data Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>RadCube</t>
+          <t>Velvetech</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Databricks, Scala, Databricks Lakehouse, Data Modeling</t>
+          <t>AWS, IAM, Azure, GCP, Vertex AI, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2dcfccb6b6d90b1</t>
+          <t>https://www.indeed.com/viewjob?jk=2bec7882b34f08c9</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Software Engineer - Cloud</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Carnegie Robotics LLC</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Westminster, CO, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,34 +3111,34 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, PostgreSQL, MongoDB, DynamoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2f5b0b9c556cdca</t>
+          <t>https://www.indeed.com/viewjob?jk=d49164a52434e329</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Python/PySpark/AWS)</t>
+          <t>AWS Data Engineer - Databricks</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Infinitive Inc</t>
+          <t>RadCube</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Azure, Spark, PySpark, Scala, Spark Streaming, Data Modeling, ETL, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Databricks, Scala, Databricks Lakehouse, Data Modeling</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2025-02-18</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45083db400feff94</t>
+          <t>https://www.indeed.com/viewjob?jk=d2dcfccb6b6d90b1</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Data Engineer (Python/PySpark/AWS)</t>
+          <t>Software Engineer - Cloud</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Infinitive Inc</t>
+          <t>Carnegie Robotics LLC</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,34 +3181,34 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Azure, Spark, PySpark, Scala, Spark Streaming, Data Modeling, ETL, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, PostgreSQL, MongoDB, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2025-01-27</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e742c4bedd2037b</t>
+          <t>https://www.indeed.com/viewjob?jk=e2f5b0b9c556cdca</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer (Python/PySpark/AWS)</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Terra Quantum</t>
+          <t>Infinitive Inc</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Ashburn, VA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,34 +3216,34 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, Azure, Spark, PySpark, Scala, Spark Streaming, Data Modeling, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2025-02-18</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15eb90498bcba242</t>
+          <t>https://www.indeed.com/viewjob?jk=45083db400feff94</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Full Stack Engineer, Experienced</t>
+          <t>Data Engineer (Python/PySpark/AWS)</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Blue Shield of California</t>
+          <t>Infinitive Inc</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Ashburn, VA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,34 +3251,34 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, NoSQL, CI/CD, Terraform</t>
+          <t>AWS, Azure, Spark, PySpark, Scala, Spark Streaming, Data Modeling, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2025-01-27</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93fe5a9749607800</t>
+          <t>https://www.indeed.com/viewjob?jk=5e742c4bedd2037b</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Full Stack Engineer, Senior</t>
+          <t>Senior Software Engineer (Python)</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Blue Shield of California</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,34 +3286,34 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, NoSQL, CI/CD, Terraform</t>
+          <t>RDS, Hadoop, Hive, MapReduce, Impala, Spark, PySpark, Oracle, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bcc6fa1baccf83e5</t>
+          <t>https://www.indeed.com/viewjob?jk=45974a79c5dfc2f4</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Full Stack Engineer, Consultant</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Blue Shield of California</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,34 +3321,34 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, NoSQL, CI/CD, Terraform</t>
+          <t>IAM, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage, MySQL, Splunk, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3a7d3c5d7336760</t>
+          <t>https://www.indeed.com/viewjob?jk=52b0e598b9832c43</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Summer Intern, Platform Engineering</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Outfront Media</t>
+          <t>Terra Quantum</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,34 +3356,34 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2aa35bb9483f10ad</t>
+          <t>https://www.indeed.com/viewjob?jk=15eb90498bcba242</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Java Software Engineer</t>
+          <t>Full Stack Engineer, Experienced</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Blue Shield of California</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=257d265c3f7e2882</t>
+          <t>https://www.indeed.com/viewjob?jk=93fe5a9749607800</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Customer Centric Engineer</t>
+          <t>Full Stack Engineer, Senior</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Blue Shield of California</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Scala, Snowflake, ELT, dbt, Tableau, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,32 +3436,32 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29a2186b968dd17c</t>
+          <t>https://www.indeed.com/viewjob?jk=bcc6fa1baccf83e5</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Mid-Level Software Engineer</t>
+          <t>Full Stack Engineer, Consultant</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>State Farm</t>
+          <t>Blue Shield of California</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Bloomington, IL, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, MongoDB, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,32 +3471,32 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da08c5cf76c3287c</t>
+          <t>https://www.indeed.com/viewjob?jk=a3a7d3c5d7336760</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Summer Intern, Platform Engineering</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Versant</t>
+          <t>Outfront Media</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, GCP, Spark, NoSQL, ETL</t>
+          <t>AWS, Lambda, S3, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,32 +3506,32 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fbef82ce93a90ed</t>
+          <t>https://www.indeed.com/viewjob?jk=2aa35bb9483f10ad</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>AI/ML Engineer</t>
+          <t>Java Software Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Redapt inc</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Woodinville, WA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, GCP, Vertex AI, Spark, Snowflake, Data Modeling, ELT</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,14 +3541,14 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9c94059f3dd29b3</t>
+          <t>https://www.indeed.com/viewjob?jk=257d265c3f7e2882</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer - News</t>
+          <t>Customer Centric Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -3558,15 +3558,15 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Step Functions, SQS, SNS, RDS, Databricks, Spark</t>
+          <t>AWS, Azure, GCP, BigQuery, Scala, Snowflake, ELT, dbt, Tableau, Docker</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c5ae4f292525796</t>
+          <t>https://www.indeed.com/viewjob?jk=29a2186b968dd17c</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>FastAPI</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Clayco</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,34 +3601,34 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
+          <t>AWS, Glue, ECS, IAM, RDS, Spark, PySpark, Scala, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61cc49187bd6e01d</t>
+          <t>https://www.indeed.com/viewjob?jk=36490e4938cafc8b</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Data Engineering - E&amp;A - Data Engineer I</t>
+          <t>Mid-Level Software Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Genesis Global Group</t>
+          <t>State Farm</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Myrtle Point, OR, US USA</t>
+          <t>Bloomington, IL, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, MongoDB, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2526bf14df16c3e8</t>
+          <t>https://www.indeed.com/viewjob?jk=da08c5cf76c3287c</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Senior, Data Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Carrington Mortgage Services, LLC</t>
+          <t>Versant</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, ETL, Microsoft SSIS</t>
+          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, GCP, Spark, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfdf1b9d489fb8ec</t>
+          <t>https://www.indeed.com/viewjob?jk=1fbef82ce93a90ed</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>GCP Support Associate</t>
+          <t>AI/ML Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Redapt inc</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Woodinville, WA, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>ECS, IAM, Google Cloud Platform, GCP, Dataflow, Cloud Storage, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, Redshift, Azure, Databricks, GCP, Vertex AI, Spark, Snowflake, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9acaddb632586c1</t>
+          <t>https://www.indeed.com/viewjob?jk=b9c94059f3dd29b3</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Data Systems Engineer</t>
+          <t>Senior Machine Learning Engineer - News</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Central Health</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,34 +3741,34 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, Glue, Lambda, Kinesis, Step Functions, SQS, SNS, RDS, Databricks, Spark</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41eed22913274d81</t>
+          <t>https://www.indeed.com/viewjob?jk=6c5ae4f292525796</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Victory Live</t>
+          <t>Clayco</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Snowflake, SQL Server, DynamoDB, ELT, dbt, Terraform</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1c259f0b00d1299</t>
+          <t>https://www.indeed.com/viewjob?jk=61cc49187bd6e01d</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>AI Senior Engineer</t>
+          <t>Data Engineering - E&amp;A - Data Engineer I</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Wood Mackenzie</t>
+          <t>Genesis Global Group</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Myrtle Point, OR, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, ECS, Azure, Scala, DynamoDB, ETL, CI/CD</t>
+          <t>Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,24 +3821,24 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69e1b61070a9b37b</t>
+          <t>https://www.indeed.com/viewjob?jk=2526bf14df16c3e8</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>AI Systems Administrator</t>
+          <t>Senior, Data Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Carrington Mortgage Services, LLC</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>ECS, RDS, Azure, Databricks, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, ETL, Microsoft SSIS</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,32 +3856,32 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a338fa1fa96ea390</t>
+          <t>https://www.indeed.com/viewjob?jk=dfdf1b9d489fb8ec</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>GCP Support Associate</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Vertex AI, Scala, Data Modeling, Jenkins, Terraform, Jenkins</t>
+          <t>ECS, IAM, Google Cloud Platform, GCP, Dataflow, Cloud Storage, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,67 +3891,67 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bbf23a169f18dbc</t>
+          <t>https://www.indeed.com/viewjob?jk=a9acaddb632586c1</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Systems Engineer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Central Health</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Vertex AI, Scala, Data Modeling, Jenkins, Terraform, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b05514433681d42</t>
+          <t>https://www.indeed.com/viewjob?jk=41eed22913274d81</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Clark Construction</t>
+          <t>Victory Live</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, dbt</t>
+          <t>AWS, RDS, Azure, Data Factory, Snowflake, SQL Server, DynamoDB, ELT, dbt, Terraform</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,32 +3961,32 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f199bfc2e975b58</t>
+          <t>https://www.indeed.com/viewjob?jk=a1c259f0b00d1299</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Junior GCP Cloud Engineer</t>
+          <t>AI Senior Engineer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Wood Mackenzie</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, Dataflow, Cloud Storage, Scala, Oracle, ETL, ELT, dbt</t>
+          <t>AWS, Lambda, Redshift, S3, ECS, Azure, Scala, DynamoDB, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,32 +3996,32 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=817a2d7d06f177a9</t>
+          <t>https://www.indeed.com/viewjob?jk=69e1b61070a9b37b</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Software Engineer - Warehouse Management Systems (WMS)</t>
+          <t>AI Systems Administrator</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Staples</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Framingham, MA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, HBase, Scala, Kafka, NoSQL, CI/CD, Docker</t>
+          <t>ECS, RDS, Azure, Databricks, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=654753ccda866d62</t>
+          <t>https://www.indeed.com/viewjob?jk=a338fa1fa96ea390</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>API Architect (Python)</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Databricks, Spark, Scala, DynamoDB, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, MLOps, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,24 +4066,24 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f9ad7c8c6b989c1</t>
+          <t>https://www.indeed.com/viewjob?jk=460c6fea55fa6849</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Sr. Professional, Software Engineering (Python)</t>
+          <t>Software Engineer - Warehouse Management Systems (WMS)</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Cotality</t>
+          <t>Staples</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Framingham, MA, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, Tableau, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, HBase, Scala, Kafka, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,24 +4101,24 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83e013cc49a29087</t>
+          <t>https://www.indeed.com/viewjob?jk=654753ccda866d62</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Senior Platform/DevOps Engineer (Kubernetes-Linux)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>ARMADA</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>RDS, GCP, BigQuery, Dataflow, Vertex AI, Scala, Data Modeling, Jenkins, Terraform, Jenkins</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,24 +4136,24 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b0e9b75e0f5558d</t>
+          <t>https://www.indeed.com/viewjob?jk=4bbf23a169f18dbc</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Senior Platform/DevOps Engineer (Kubernetes-Linux)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>ARMADA</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Sammamish, WA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>RDS, GCP, BigQuery, Dataflow, Vertex AI, Scala, Data Modeling, Jenkins, Terraform, Jenkins</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,24 +4171,24 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=efa4e4e3099a0ae2</t>
+          <t>https://www.indeed.com/viewjob?jk=4b05514433681d42</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Senior Platform/DevOps Engineer (Kubernetes-Linux)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>ARMADA</t>
+          <t>Clark Construction</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Kirkland, WA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Azure, GCP, Spark, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, dbt</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,24 +4206,24 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33ae1f1f9d08c546</t>
+          <t>https://www.indeed.com/viewjob?jk=6f199bfc2e975b58</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Senior Platform/DevOps Engineer (Kubernetes-Linux)</t>
+          <t>Junior GCP Cloud Engineer</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>ARMADA</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Renton, WA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Google Cloud Platform, GCP, Dataflow, Cloud Storage, Scala, Oracle, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,24 +4241,24 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d25130b996402485</t>
+          <t>https://www.indeed.com/viewjob?jk=817a2d7d06f177a9</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Senior Platform/DevOps Engineer (Kubernetes-Linux)</t>
+          <t>Sr. Professional, Software Engineering (Python)</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>ARMADA</t>
+          <t>Cotality</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Bothell, WA, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, Tableau, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6f9224460f3210c</t>
+          <t>https://www.indeed.com/viewjob?jk=83e013cc49a29087</t>
         </is>
       </c>
     </row>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Redmond, WA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4311,24 +4311,24 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b86c940f686047d8</t>
+          <t>https://www.indeed.com/viewjob?jk=7b0e9b75e0f5558d</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Platform/DevOps Engineer (Kubernetes-Linux)</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ARMADA</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Somerville, MA, US USA</t>
+          <t>Sammamish, WA, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Scala, Snowflake, ETL, ELT, dbt, Tableau, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,24 +4346,24 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75339d7552c524c1</t>
+          <t>https://www.indeed.com/viewjob?jk=efa4e4e3099a0ae2</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Sr. Site Reliability Engineer</t>
+          <t>Senior Platform/DevOps Engineer (Kubernetes-Linux)</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>PitchBook</t>
+          <t>ARMADA</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Kirkland, WA, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, SQL Server, PostgreSQL, MySQL, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,24 +4381,24 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=181ce2100b853c3a</t>
+          <t>https://www.indeed.com/viewjob?jk=33ae1f1f9d08c546</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Senior Data Engineer / Data Architect</t>
+          <t>Senior Platform/DevOps Engineer (Kubernetes-Linux)</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>ARMADA</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Renton, WA, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,24 +4416,24 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e83d1768e75b1203</t>
+          <t>https://www.indeed.com/viewjob?jk=d25130b996402485</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Snowflake Data Movement Engineer</t>
+          <t>Senior Platform/DevOps Engineer (Kubernetes-Linux)</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Smart Tech Skills LLC</t>
+          <t>ARMADA</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Bothell, WA, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, ETL, CI/CD, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,24 +4451,24 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12ef21c70e148f1d</t>
+          <t>https://www.indeed.com/viewjob?jk=b6f9224460f3210c</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Site Reliability / Infrastructure Engineer</t>
+          <t>Senior Platform/DevOps Engineer (Kubernetes-Linux)</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>General Intuition &amp; Medal</t>
+          <t>ARMADA</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Redmond, WA, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Scala, MySQL, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,24 +4486,24 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a84d1c588e106220</t>
+          <t>https://www.indeed.com/viewjob?jk=b86c940f686047d8</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Sr. Data Architect Specialist</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>SAMYANG AMERICA INC</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Brea, CA, US USA</t>
+          <t>Somerville, MA, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
+          <t>Redshift, RDS, Azure, Scala, Snowflake, ETL, ELT, dbt, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,24 +4521,24 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2086e3e44cfc021</t>
+          <t>https://www.indeed.com/viewjob?jk=75339d7552c524c1</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Full Stack Product Engineer (Java)</t>
+          <t>Sr. Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Allstate Insurance</t>
+          <t>PitchBook</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, ELT, CI/CD, Git</t>
+          <t>AWS, RDS, GCP, Scala, SQL Server, PostgreSQL, MySQL, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4556,24 +4556,24 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d15adff582efc740</t>
+          <t>https://www.indeed.com/viewjob?jk=181ce2100b853c3a</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>DevOps &amp; Infrastructure Engineer - Level I</t>
+          <t>Senior Data Engineer / Data Architect</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>SPRING ARBOR UNIVERSITY</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Spring Arbor, MI, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Oracle, CI/CD, Jenkins, GitHub Actions, Docker, Jenkins</t>
+          <t>AWS, Kinesis, Redshift, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,24 +4591,24 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0b216de71eb3804</t>
+          <t>https://www.indeed.com/viewjob?jk=e83d1768e75b1203</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Senior GCP Kubernetes Engineer</t>
+          <t>Snowflake Data Movement Engineer</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Smart Tech Skills LLC</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Kafka, Oracle, PostgreSQL, CI/CD, Jenkins, Maven</t>
+          <t>RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, ETL, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,24 +4626,24 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a77679969db6e94b</t>
+          <t>https://www.indeed.com/viewjob?jk=12ef21c70e148f1d</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Software Engineer – Enterprise Software</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Rivian</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,34 +4651,34 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MySQL, NoSQL, Splunk, Docker, Kubernetes</t>
+          <t>AWS, S3, IAM, Databricks, Spark, Scala, DynamoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90124173401e2437</t>
+          <t>https://www.indeed.com/viewjob?jk=6f9ad7c8c6b989c1</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer, Enterprise Technology</t>
+          <t>Sr. Data Architect Specialist</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Rivian</t>
+          <t>SAMYANG AMERICA INC</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Brea, CA, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,34 +4686,34 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MySQL, NoSQL, Splunk, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fab081dda06a1ba5</t>
+          <t>https://www.indeed.com/viewjob?jk=f2086e3e44cfc021</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Senior GCP IAM Engineer</t>
+          <t>Full Stack Product Engineer (Java)</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Allstate Insurance</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4721,7 +4721,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, ELT, CI/CD, Git</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4731,24 +4731,24 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e01ee86f0306e6c</t>
+          <t>https://www.indeed.com/viewjob?jk=d15adff582efc740</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>QA Analyst / ETL Tester</t>
+          <t>DevOps &amp; Infrastructure Engineer - Level I</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>CSpring</t>
+          <t>SPRING ARBOR UNIVERSITY</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Springfield, IL, US USA</t>
+          <t>Spring Arbor, MI, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>RDS, Azure, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Data Modeling, Snowflake Schema, ETL, CI/CD</t>
+          <t>AWS, Azure, GCP, Scala, Oracle, CI/CD, Jenkins, GitHub Actions, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4766,32 +4766,32 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ebf7b3987a302e8</t>
+          <t>https://www.indeed.com/viewjob?jk=b0b216de71eb3804</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Engineer II-Software Development</t>
+          <t>Senior GCP Kubernetes Engineer</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Microchip Technology</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, Oracle, PostgreSQL, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -4801,84 +4801,84 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3013681a0e1c4f81</t>
+          <t>https://www.indeed.com/viewjob?jk=a77679969db6e94b</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Engineer II-Software Development</t>
+          <t>Software Engineer – Enterprise Software</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Microchip Technology</t>
+          <t>Rivian</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MySQL, NoSQL, Splunk, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2649d75a044fe7bd</t>
+          <t>https://www.indeed.com/viewjob?jk=90124173401e2437</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - VAULT</t>
+          <t>Sr. Software Engineer, Enterprise Technology</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Bloomberg</t>
+          <t>Rivian</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Hive, Spark, Scala, Kafka, Cassandra</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MySQL, NoSQL, Splunk, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d744cfcd1fce896</t>
+          <t>https://www.indeed.com/viewjob?jk=fab081dda06a1ba5</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Cloud AI Application Administrator</t>
+          <t>Senior GCP IAM Engineer</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -4892,11 +4892,11 @@
         </is>
       </c>
       <c r="D128" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, Dataflow, Cloud Storage, Scala, Oracle, ETL, ELT, dbt, Tableau</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -4906,59 +4906,59 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd193e360372af33</t>
+          <t>https://www.indeed.com/viewjob?jk=4e01ee86f0306e6c</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Data Scientist, Senior Associate – Product, Experience and Technology (PXT) Analytics Team</t>
+          <t>QA Analyst / ETL Tester</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>CSpring</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Springfield, IL, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, Scala, Snowflake, dbt, Tableau, CI/CD, Airflow, Git</t>
+          <t>RDS, Azure, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Data Modeling, Snowflake Schema, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b0bfe4f7e93a067</t>
+          <t>https://www.indeed.com/viewjob?jk=1ebf7b3987a302e8</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Engineer II-Software Development</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Urology Centers of Alabama</t>
+          <t>Microchip Technology</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4966,7 +4966,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -4976,24 +4976,24 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28cb24ea6139fcb9</t>
+          <t>https://www.indeed.com/viewjob?jk=3013681a0e1c4f81</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Engineer II-Software Development</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Pearson</t>
+          <t>Microchip Technology</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Hoboken, NJ, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5001,7 +5001,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, MongoDB, DynamoDB, Data Modeling, ETL, ELT, DataOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -5011,24 +5011,24 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05547d65aabdfcf0</t>
+          <t>https://www.indeed.com/viewjob?jk=2649d75a044fe7bd</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
+          <t>Senior Software Engineer - VAULT</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Bloomberg</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5036,7 +5036,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
+          <t>AWS, S3, RDS, Azure, GCP, Hive, Spark, Scala, Kafka, Cassandra</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -5046,24 +5046,24 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34c37a226b547d01</t>
+          <t>https://www.indeed.com/viewjob?jk=1d744cfcd1fce896</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
+          <t>Cloud AI Application Administrator</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
+          <t>RDS, Google Cloud Platform, Dataflow, Cloud Storage, Scala, Oracle, ETL, ELT, dbt, Tableau</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -5081,24 +5081,24 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7d77afce6f60e6f</t>
+          <t>https://www.indeed.com/viewjob?jk=cd193e360372af33</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
+          <t>FastAPI</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5106,34 +5106,34 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
+          <t>RDS, Google Cloud Platform, BigQuery, Vertex AI, Spark, Scala, Spark Streaming, Kafka, CI/CD, Git</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=225c5a8131dc6595</t>
+          <t>https://www.indeed.com/viewjob?jk=0bc1141188a8604a</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Urology Centers of Alabama</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5141,7 +5141,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
+          <t>AWS, EMR, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, ETL</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -5151,24 +5151,24 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=301dbd1e2eb0bb70</t>
+          <t>https://www.indeed.com/viewjob?jk=28cb24ea6139fcb9</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Pearson</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Hoboken, NJ, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5176,7 +5176,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
+          <t>AWS, RDS, Scala, MongoDB, DynamoDB, Data Modeling, ETL, ELT, DataOps, CI/CD</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -5186,7 +5186,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d88e7121c2db79d6</t>
+          <t>https://www.indeed.com/viewjob?jk=05547d65aabdfcf0</t>
         </is>
       </c>
     </row>
@@ -5203,7 +5203,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5221,7 +5221,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18d3f9fdcfa07035</t>
+          <t>https://www.indeed.com/viewjob?jk=34c37a226b547d01</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5256,7 +5256,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d2d16258cfd6718</t>
+          <t>https://www.indeed.com/viewjob?jk=e7d77afce6f60e6f</t>
         </is>
       </c>
     </row>
@@ -5273,7 +5273,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5291,7 +5291,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5be8f9b4535b406c</t>
+          <t>https://www.indeed.com/viewjob?jk=225c5a8131dc6595</t>
         </is>
       </c>
     </row>
@@ -5308,7 +5308,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5326,7 +5326,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26ef52c65261360a</t>
+          <t>https://www.indeed.com/viewjob?jk=301dbd1e2eb0bb70</t>
         </is>
       </c>
     </row>
@@ -5343,7 +5343,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5361,7 +5361,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9240b7b96545a4d</t>
+          <t>https://www.indeed.com/viewjob?jk=d88e7121c2db79d6</t>
         </is>
       </c>
     </row>
@@ -5378,7 +5378,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5396,7 +5396,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42ae72f7d4a97700</t>
+          <t>https://www.indeed.com/viewjob?jk=18d3f9fdcfa07035</t>
         </is>
       </c>
     </row>
@@ -5413,7 +5413,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dab5b1b68cc6402c</t>
+          <t>https://www.indeed.com/viewjob?jk=9d2d16258cfd6718</t>
         </is>
       </c>
     </row>
@@ -5448,7 +5448,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -5466,7 +5466,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fde8d1831ca7f9b7</t>
+          <t>https://www.indeed.com/viewjob?jk=5be8f9b4535b406c</t>
         </is>
       </c>
     </row>
@@ -5483,7 +5483,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a056659ad4aebd2</t>
+          <t>https://www.indeed.com/viewjob?jk=26ef52c65261360a</t>
         </is>
       </c>
     </row>
@@ -5518,7 +5518,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -5536,7 +5536,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5402962c321dcba</t>
+          <t>https://www.indeed.com/viewjob?jk=f9240b7b96545a4d</t>
         </is>
       </c>
     </row>
@@ -5553,7 +5553,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D147" t="n">
@@ -5571,7 +5571,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f45ad39ec1fe503a</t>
+          <t>https://www.indeed.com/viewjob?jk=42ae72f7d4a97700</t>
         </is>
       </c>
     </row>
@@ -5588,7 +5588,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D148" t="n">
@@ -5606,7 +5606,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86cfc919b4ccc768</t>
+          <t>https://www.indeed.com/viewjob?jk=dab5b1b68cc6402c</t>
         </is>
       </c>
     </row>
@@ -5623,7 +5623,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D149" t="n">
@@ -5641,7 +5641,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9a866cff6a0e3bd</t>
+          <t>https://www.indeed.com/viewjob?jk=fde8d1831ca7f9b7</t>
         </is>
       </c>
     </row>
@@ -5658,7 +5658,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D150" t="n">
@@ -5676,7 +5676,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab68f1e4ba82ad10</t>
+          <t>https://www.indeed.com/viewjob?jk=7a056659ad4aebd2</t>
         </is>
       </c>
     </row>
@@ -5693,7 +5693,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D151" t="n">
@@ -5711,7 +5711,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df163d5906a30146</t>
+          <t>https://www.indeed.com/viewjob?jk=e5402962c321dcba</t>
         </is>
       </c>
     </row>
@@ -5728,7 +5728,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D152" t="n">
@@ -5746,7 +5746,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f0c32c0bdf67710</t>
+          <t>https://www.indeed.com/viewjob?jk=f45ad39ec1fe503a</t>
         </is>
       </c>
     </row>
@@ -5763,7 +5763,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D153" t="n">
@@ -5781,7 +5781,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25f63312ec2e267e</t>
+          <t>https://www.indeed.com/viewjob?jk=86cfc919b4ccc768</t>
         </is>
       </c>
     </row>
@@ -5798,7 +5798,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D154" t="n">
@@ -5816,7 +5816,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be379ec08f5c5e6f</t>
+          <t>https://www.indeed.com/viewjob?jk=c9a866cff6a0e3bd</t>
         </is>
       </c>
     </row>
@@ -5833,7 +5833,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D155" t="n">
@@ -5851,7 +5851,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8deeb1ab1ebcdccd</t>
+          <t>https://www.indeed.com/viewjob?jk=ab68f1e4ba82ad10</t>
         </is>
       </c>
     </row>
@@ -5868,7 +5868,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D156" t="n">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92aa87419ba8e5df</t>
+          <t>https://www.indeed.com/viewjob?jk=df163d5906a30146</t>
         </is>
       </c>
     </row>
@@ -5903,7 +5903,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D157" t="n">
@@ -5921,7 +5921,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da334d3b3eda0eb4</t>
+          <t>https://www.indeed.com/viewjob?jk=2f0c32c0bdf67710</t>
         </is>
       </c>
     </row>
@@ -5938,7 +5938,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D158" t="n">
@@ -5956,7 +5956,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c314e6df20a4157</t>
+          <t>https://www.indeed.com/viewjob?jk=25f63312ec2e267e</t>
         </is>
       </c>
     </row>
@@ -5973,7 +5973,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D159" t="n">
@@ -5991,7 +5991,7 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b90a165cff732e70</t>
+          <t>https://www.indeed.com/viewjob?jk=be379ec08f5c5e6f</t>
         </is>
       </c>
     </row>
@@ -6008,7 +6008,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D160" t="n">
@@ -6026,7 +6026,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26bc98921360165c</t>
+          <t>https://www.indeed.com/viewjob?jk=8deeb1ab1ebcdccd</t>
         </is>
       </c>
     </row>
@@ -6043,7 +6043,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D161" t="n">
@@ -6061,7 +6061,7 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5359f322821abe9</t>
+          <t>https://www.indeed.com/viewjob?jk=92aa87419ba8e5df</t>
         </is>
       </c>
     </row>
@@ -6078,7 +6078,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D162" t="n">
@@ -6096,7 +6096,7 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=562ea8307dd5c91d</t>
+          <t>https://www.indeed.com/viewjob?jk=da334d3b3eda0eb4</t>
         </is>
       </c>
     </row>
@@ -6113,7 +6113,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D163" t="n">
@@ -6131,7 +6131,7 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70a64e543cdeb49a</t>
+          <t>https://www.indeed.com/viewjob?jk=2c314e6df20a4157</t>
         </is>
       </c>
     </row>
@@ -6148,7 +6148,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D164" t="n">
@@ -6166,7 +6166,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed3e28c9a543299a</t>
+          <t>https://www.indeed.com/viewjob?jk=b90a165cff732e70</t>
         </is>
       </c>
     </row>
@@ -6183,7 +6183,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D165" t="n">
@@ -6201,24 +6201,24 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1735f01363643535</t>
+          <t>https://www.indeed.com/viewjob?jk=26bc98921360165c</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Data Engineer II, Mobile Game Analytics</t>
+          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Mattel, Inc.</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>El Segundo, CA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D166" t="n">
@@ -6226,7 +6226,7 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>RDS, Medallion Architecture, GCP, BigQuery, Dimensional Modeling, ETL, dbt, Tableau, CI/CD, Airflow</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
@@ -6236,24 +6236,24 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=087868e735e87a06</t>
+          <t>https://www.indeed.com/viewjob?jk=c5359f322821abe9</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D167" t="n">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, BigQuery, Vertex AI, Spark, Scala, Spark Streaming, Kafka, CI/CD, Git</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
@@ -6271,24 +6271,24 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f192cf981191d4cd</t>
+          <t>https://www.indeed.com/viewjob?jk=562ea8307dd5c91d</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D168" t="n">
@@ -6296,7 +6296,7 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, Terraform, Docker, Jenkins</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
@@ -6306,24 +6306,24 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7e0844f636778b5</t>
+          <t>https://www.indeed.com/viewjob?jk=70a64e543cdeb49a</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>GCP Support Associate</t>
+          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D169" t="n">
@@ -6331,7 +6331,7 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, GCP, Dataflow, Cloud Storage, CI/CD, Jenkins, Terraform, Docker, Jenkins</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
@@ -6341,24 +6341,24 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=908520f92505a147</t>
+          <t>https://www.indeed.com/viewjob?jk=ed3e28c9a543299a</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Leidos</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Seaside, CA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D170" t="n">
@@ -6366,7 +6366,7 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Splunk, CI/CD, Terraform, Docker, Kubernetes, Git, CloudWatch</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
@@ -6376,24 +6376,24 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=727ac8d7c715b1a1</t>
+          <t>https://www.indeed.com/viewjob?jk=1735f01363643535</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Software Engineer - AI Augmented Development</t>
+          <t>Data Engineer II, Mobile Game Analytics</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>PowerPay</t>
+          <t>Mattel, Inc.</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Wayne, PA, US USA</t>
+          <t>El Segundo, CA, US USA</t>
         </is>
       </c>
       <c r="D171" t="n">
@@ -6401,7 +6401,7 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, ECS, IAM, RDS, Snowflake, ETL, Terraform</t>
+          <t>RDS, Medallion Architecture, GCP, BigQuery, Dimensional Modeling, ETL, dbt, Tableau, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
@@ -6411,24 +6411,24 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=039bac65ddb8c30e</t>
+          <t>https://www.indeed.com/viewjob?jk=087868e735e87a06</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Sr Associate Engineer/Engineer, IT Software</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D172" t="n">
@@ -6436,7 +6436,7 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>RDS, Google Cloud Platform, BigQuery, Vertex AI, Spark, Scala, Spark Streaming, Kafka, CI/CD, Git</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
@@ -6446,14 +6446,14 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf657c9771abb6db</t>
+          <t>https://www.indeed.com/viewjob?jk=f192cf981191d4cd</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>DevOps Engineer (GCP)</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -6471,7 +6471,7 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Vertex AI, Spark, MLflow, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, Terraform, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
@@ -6481,24 +6481,24 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a53e6510409c717</t>
+          <t>https://www.indeed.com/viewjob?jk=e7e0844f636778b5</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Enterprise AI Architect</t>
+          <t>GCP Support Associate</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Radwell International</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Willingboro, NJ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D174" t="n">
@@ -6506,34 +6506,34 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, PostgreSQL, MySQL, NoSQL, MLOps, CI/CD</t>
+          <t>IAM, Google Cloud Platform, GCP, Dataflow, Cloud Storage, CI/CD, Jenkins, Terraform, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56c80236c3727026</t>
+          <t>https://www.indeed.com/viewjob?jk=908520f92505a147</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>AI Application Architect</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Leidos</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Seaside, CA, US USA</t>
         </is>
       </c>
       <c r="D175" t="n">
@@ -6541,15 +6541,225 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
+          <t>AWS, Azure, Scala, Splunk, CI/CD, Terraform, Docker, Kubernetes, Git, CloudWatch</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=727ac8d7c715b1a1</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>Data Scientist, Senior Associate – Product, Experience and Technology (PXT) Analytics Team</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D176" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>Redshift, RDS, Databricks, Scala, Snowflake, dbt, Tableau, CI/CD, Airflow, Git</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4b0bfe4f7e93a067</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>Software Engineer - AI Augmented Development</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>PowerPay</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Wayne, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D177" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, SQS, ECS, IAM, RDS, Snowflake, ETL, Terraform</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=039bac65ddb8c30e</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>Sr Associate Engineer/Engineer, IT Software</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>American Airlines</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Fort Worth, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D178" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cf657c9771abb6db</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>DevOps Engineer (GCP)</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D179" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Vertex AI, Spark, MLflow, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1a53e6510409c717</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>Enterprise AI Architect</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Radwell International</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Willingboro, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D180" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Scala, PostgreSQL, MySQL, NoSQL, MLOps, CI/CD</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=56c80236c3727026</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>AI Application Architect</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D181" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
           <t>AWS, Azure, Google Cloud Platform, Spark, Scala, Snowflake, ETL, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
-      <c r="F175" t="inlineStr">
-        <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="G175" t="inlineStr">
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=bdfa99adc53f817f</t>
         </is>

--- a/results/job_matches_2026-05-06.xlsx
+++ b/results/job_matches_2026-05-06.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G181"/>
+  <dimension ref="A1:G192"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1028,17 +1028,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>API Threat Intelligence Analyst</t>
+          <t>Health Account Intern</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Booz Allen Hamilton</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, API Gateway, RDS, Azure, Google Cloud Platform, Scala, Kafka, Splunk</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Databricks, Hadoop, Hive, Spark, Scala</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=427f6933d7d21e16</t>
+          <t>https://www.indeed.com/viewjob?jk=64329d0d0bf86853</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Health Account Intern</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Booz Allen Hamilton</t>
+          <t>WSSC Water</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Laurel, MD, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,34 +1081,34 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Databricks, Hadoop, Hive, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Blob Storage, GCP, Hadoop</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64329d0d0bf86853</t>
+          <t>https://www.indeed.com/viewjob?jk=859b6255aab51697</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>WSSC Water</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Laurel, MD, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Blob Storage, GCP, Hadoop</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, API Gateway, RDS, Azure, Kafka</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,14 +1126,14 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=859b6255aab51697</t>
+          <t>https://www.indeed.com/viewjob?jk=0b4a39c21c884e72</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>GCP ETL Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, API Gateway, RDS, Azure, Kafka</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, Spark, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,14 +1161,14 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b4a39c21c884e72</t>
+          <t>https://www.indeed.com/viewjob?jk=4e5fc76263d455e5</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>GCP ETL Engineer</t>
+          <t>API Threat Intelligence Analyst</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,17 +1186,17 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, Spark, Scala, Snowflake, Oracle</t>
+          <t>AWS, SQS, SNS, API Gateway, RDS, Azure, Google Cloud Platform, Scala, Kafka, Splunk</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e5fc76263d455e5</t>
+          <t>https://www.indeed.com/viewjob?jk=427f6933d7d21e16</t>
         </is>
       </c>
     </row>
@@ -1238,17 +1238,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Databricks Engineer and Architect</t>
+          <t>Sr Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Lincoln Financial Group</t>
+          <t>Commence</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Radnor, PA, US USA</t>
+          <t>Leesburg, VA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,34 +1256,34 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, RDS, Databricks, Unity Catalog</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, NoSQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7862c3c59e06d56</t>
+          <t>https://www.indeed.com/viewjob?jk=9093ede7f2269db2</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Sr Site Reliability Engineer</t>
+          <t>Sr Data Engineer, Python + Spark (Data Federation skillset - Data Lakehouse - Eg: Starburst) - New York</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Commence</t>
+          <t>Photon</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Leesburg, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,34 +1291,34 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, NoSQL, ETL, ELT</t>
+          <t>AWS, Glue, EMR, S3, Azure, Databricks, Medallion Architecture, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9093ede7f2269db2</t>
+          <t>https://www.indeed.com/viewjob?jk=f7767a92d7d08a3b</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Sr Data Engineer, Python + Spark (Data Federation skillset - Data Lakehouse - Eg: Starburst) - New York</t>
+          <t>Senior Software Engineer - ETL, Java</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Photon</t>
+          <t>RevSpring, Inc</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, S3, Azure, Databricks, Medallion Architecture, GCP, Spark, PySpark</t>
+          <t>Redshift, S3, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop, Scala</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7767a92d7d08a3b</t>
+          <t>https://www.indeed.com/viewjob?jk=4a9c009a05948507</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a9c009a05948507</t>
+          <t>https://www.indeed.com/viewjob?jk=ba5ba3f3a840901f</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba5ba3f3a840901f</t>
+          <t>https://www.indeed.com/viewjob?jk=ec9899d266d7f4ea</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - ETL, Java</t>
+          <t>DevOps Engineer (GCP)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>RevSpring, Inc</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Redshift, S3, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,14 +1441,14 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec9899d266d7f4ea</t>
+          <t>https://www.indeed.com/viewjob?jk=9d617836814bb437</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>DevOps Engineer (GCP)</t>
+          <t>Junior GCP Cloud Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark</t>
+          <t>IAM, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Data Modeling, Kimball</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d617836814bb437</t>
+          <t>https://www.indeed.com/viewjob?jk=11aa4a83b27dbdc6</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Junior GCP Cloud Engineer</t>
+          <t>Databricks Engineer and Architect</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Lincoln Financial Group</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Radnor, PA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,17 +1501,17 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Data Modeling, Kimball</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, RDS, Databricks, Unity Catalog</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11aa4a83b27dbdc6</t>
+          <t>https://www.indeed.com/viewjob?jk=d7862c3c59e06d56</t>
         </is>
       </c>
     </row>
@@ -1763,17 +1763,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>MLOps Engineer – Azure Databricks, Cloud-to-Edge ML Deployment</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>KPIT Technologies</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,34 +1781,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, MLOps, MLflow, CI/CD</t>
+          <t>AWS, Kinesis, Redshift, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1160b6a5ea3d30ad</t>
+          <t>https://www.indeed.com/viewjob?jk=f544b0c492f55ad5</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Cloud Reliability Engineer</t>
+          <t>MLOps Engineer – Azure Databricks, Cloud-to-Edge ML Deployment</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>KPIT Technologies</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Spark, Scala, NoSQL, Data Modeling, MLOps</t>
+          <t>Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,14 +1826,14 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eae9d6ab07ed0b94</t>
+          <t>https://www.indeed.com/viewjob?jk=1160b6a5ea3d30ad</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>API Threat Intelligence Analyst</t>
+          <t>Cloud Reliability Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,24 +1851,24 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Azure, Google Cloud Platform, Kafka, NoSQL, Data Modeling, ETL, Talend, Tableau, Splunk, MicroStrategy</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Spark, Scala, NoSQL, Data Modeling, MLOps</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e918fa70b2a1920e</t>
+          <t>https://www.indeed.com/viewjob?jk=eae9d6ab07ed0b94</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Backend (Python)</t>
+          <t>DevOps/AI Ops Administrator</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1886,24 +1886,24 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Azure, Google Cloud Platform, Kafka, NoSQL, Data Modeling, ETL, Talend, Tableau, Splunk, MicroStrategy</t>
+          <t>RDS, Azure, Databricks, Event Hubs, Dataflow, Scala, Snowflake, PostgreSQL, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d711bd4394cb404e</t>
+          <t>https://www.indeed.com/viewjob?jk=8de348813177f92b</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>DevOps/AI Ops Administrator</t>
+          <t>API Threat Intelligence Analyst</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,69 +1921,69 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Event Hubs, Dataflow, Scala, Snowflake, PostgreSQL, Power BI, CI/CD</t>
+          <t>Azure, Google Cloud Platform, Kafka, NoSQL, Data Modeling, ETL, Talend, Tableau, Splunk, MicroStrategy</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8de348813177f92b</t>
+          <t>https://www.indeed.com/viewjob?jk=e918fa70b2a1920e</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Backend (Python)</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Metropolis</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Glue, SNS, RDS, Spark, PySpark, Scala, Snowflake, SQL Server, MySQL</t>
+          <t>Azure, Google Cloud Platform, Kafka, NoSQL, Data Modeling, ETL, Talend, Tableau, Splunk, MicroStrategy</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9fd5c209c01d504</t>
+          <t>https://www.indeed.com/viewjob?jk=d711bd4394cb404e</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>metropolis</t>
+          <t>Netsecure360</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,34 +1991,34 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Glue, SNS, RDS, Spark, PySpark, Scala, Snowflake, SQL Server, MySQL</t>
+          <t>AWS, RDS, Azure, Cloud Storage, Hadoop, Hive, Spark, Scala, Kafka, Oracle</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d51453a1afa374b4</t>
+          <t>https://www.indeed.com/viewjob?jk=ca7e816524d9406c</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Cloud Migration Engineer (GCP)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Metropolis</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, Snowflake, SQL Server</t>
+          <t>AWS, Glue, SNS, RDS, Spark, PySpark, Scala, Snowflake, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb7efc81616340cd</t>
+          <t>https://www.indeed.com/viewjob?jk=b9fd5c209c01d504</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Databricks)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Infinitive Inc</t>
+          <t>metropolis</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,34 +2061,34 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, S3, Azure, Databricks, Unity Catalog, GCP</t>
+          <t>AWS, Glue, SNS, RDS, Spark, PySpark, Scala, Snowflake, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aee5e62267dbbb6c</t>
+          <t>https://www.indeed.com/viewjob?jk=d51453a1afa374b4</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Software Engineer – ETL, Java</t>
+          <t>Cloud Migration Engineer (GCP)</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>RevSpring, Inc</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Redshift, S3, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop, Scala</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ebdf3dd92985403</t>
+          <t>https://www.indeed.com/viewjob?jk=fb7efc81616340cd</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Software Engineer – ETL, Java</t>
+          <t>Senior Data Engineer (Databricks)</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>RevSpring, Inc</t>
+          <t>Infinitive Inc</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Ashburn, VA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,17 +2131,17 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Redshift, S3, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop, Scala</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, S3, Azure, Databricks, Unity Catalog, GCP</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c4b1e40555df27f</t>
+          <t>https://www.indeed.com/viewjob?jk=aee5e62267dbbb6c</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d1957e3729d8614</t>
+          <t>https://www.indeed.com/viewjob?jk=3ebdf3dd92985403</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Computing Architect 4 (contract)</t>
+          <t>Software Engineer – ETL, Java</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Boeing</t>
+          <t>RevSpring, Inc</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Scala, Kafka, Data Modeling, ELT</t>
+          <t>Redshift, S3, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop, Scala</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83fa749fc70ff9b5</t>
+          <t>https://www.indeed.com/viewjob?jk=5c4b1e40555df27f</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Software Developer II</t>
+          <t>Software Engineer – ETL, Java</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Floor &amp; Decor</t>
+          <t>RevSpring, Inc</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL, Splunk, CI/CD</t>
+          <t>Redshift, S3, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop, Scala</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,102 +2246,102 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e331a6c4c6f76859</t>
+          <t>https://www.indeed.com/viewjob?jk=9d1957e3729d8614</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Computing Architect 4 (contract)</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>SOFTILITY INC</t>
+          <t>Boeing</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Scala, Kafka, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3faf69463891ca3f</t>
+          <t>https://www.indeed.com/viewjob?jk=83fa749fc70ff9b5</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Sr. Streaming Engineer</t>
+          <t>Software Developer II</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Ness Digital Engineering</t>
+          <t>Floor &amp; Decor</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, IAM, RDS, Spark, Scala, Kafka, NoSQL, Splunk</t>
+          <t>RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f90fa0ab3164dcd1</t>
+          <t>https://www.indeed.com/viewjob?jk=4a21fec712255df2</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>MarketAxess Holdings</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Oracle, Data Modeling, ETL</t>
+          <t>AWS, Athena, Step Functions, S3, ECS, IAM, RDS, Kafka, Polars, CI/CD</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d61e7d7639acc074</t>
+          <t>https://www.indeed.com/viewjob?jk=0e88c480437dd451</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer - Cloud Dev</t>
+          <t>Sr. Streaming Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Transmedics</t>
+          <t>Ness Digital Engineering</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Andover, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, Redshift, Step Functions, S3, SQS, SNS, API Gateway, IAM</t>
+          <t>AWS, Kinesis, S3, IAM, RDS, Spark, Scala, Kafka, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2efe7bed588da272</t>
+          <t>https://www.indeed.com/viewjob?jk=f90fa0ab3164dcd1</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Cloud Service Desk Analyst</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>SOFTILITY INC</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,24 +2411,24 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, Azure, Scala, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e883ce8f9ac322fb</t>
+          <t>https://www.indeed.com/viewjob?jk=3faf69463891ca3f</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>MLOps Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Oracle, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56f1aa48ba26ae3c</t>
+          <t>https://www.indeed.com/viewjob?jk=d61e7d7639acc074</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Junior Cloud Security Analyst</t>
+          <t>Senior Software Development Engineer - Cloud Dev</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Transmedics</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Andover, MA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Databricks, Blob Storage, Unity Catalog, Google Cloud Platform, Spark</t>
+          <t>AWS, Lambda, Kinesis, Redshift, Step Functions, S3, SQS, SNS, API Gateway, IAM</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb95dfff70e6d2a4</t>
+          <t>https://www.indeed.com/viewjob?jk=2efe7bed588da272</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Business Intelligence Developer (Healthcare Data, EDI, ETL)</t>
+          <t>Cloud Service Desk Analyst</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>MicroHealth LLC</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Vienna, VA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Scala, Snowflake, SQL Server, PostgreSQL, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, Lambda, S3, ECS, IAM, Azure, Scala, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ba3d7e28ab6494c</t>
+          <t>https://www.indeed.com/viewjob?jk=e883ce8f9ac322fb</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Databricks Developer</t>
+          <t>Senior ServiceNow Developer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Sloan</t>
+          <t>Global Enterprise Systems</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Franklin Park, IL, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,42 +2551,42 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9921503eb16c8225</t>
+          <t>https://www.indeed.com/viewjob?jk=0c766bb333faacdc</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Software Engineer - Specialist</t>
+          <t>Junior Cloud Security Analyst</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, SQL Server, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, S3, IAM, RDS, Azure, Databricks, Blob Storage, Unity Catalog, Google Cloud Platform, Spark</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,67 +2596,67 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=932c71a7f13aa9a1</t>
+          <t>https://www.indeed.com/viewjob?jk=cb95dfff70e6d2a4</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>GCP ETL Engineer</t>
+          <t>MLOps Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Hadoop, Spark, Kafka, Snowflake, Dimensional Modeling, ETL, Talend</t>
+          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5268867584b4379</t>
+          <t>https://www.indeed.com/viewjob?jk=56f1aa48ba26ae3c</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer, Data &amp; Analytics</t>
+          <t>Business Intelligence Developer (Healthcare Data, EDI, ETL)</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Blizzard Entertainment</t>
+          <t>MicroHealth LLC</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Vienna, VA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Dataflow, Kafka, dbt, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, EMR, RDS, Scala, Snowflake, SQL Server, PostgreSQL, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,32 +2666,32 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f56eabb97941a731</t>
+          <t>https://www.indeed.com/viewjob?jk=3ba3d7e28ab6494c</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Databricks Developer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Kroll Inc.</t>
+          <t>Sloan</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Franklin Park, IL, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Scala, Polars, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d56048c057634cd1</t>
+          <t>https://www.indeed.com/viewjob?jk=9921503eb16c8225</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>FastAPI</t>
+          <t>Software Engineer - Specialist</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,24 +2726,24 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, PostgreSQL, DynamoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, SQL Server, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=550e29553f2a099b</t>
+          <t>https://www.indeed.com/viewjob?jk=932c71a7f13aa9a1</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>GCP Support Associate</t>
+          <t>GCP ETL Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, MySQL, Splunk, CI/CD</t>
+          <t>AWS, Azure, GCP, Hadoop, Spark, Kafka, Snowflake, Dimensional Modeling, ETL, Talend</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29c27657463cb6ea</t>
+          <t>https://www.indeed.com/viewjob?jk=d5268867584b4379</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Senior Site Reliability Engineer, Data &amp; Analytics</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Miami Marlins</t>
+          <t>Blizzard Entertainment</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, GCP, Scala, Snowflake, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, GCP, BigQuery, Dataflow, Kafka, dbt, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff87deef607d5450</t>
+          <t>https://www.indeed.com/viewjob?jk=f56eabb97941a731</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Paramount</t>
+          <t>Kroll Inc.</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Fort Lauderdale, FL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Dataflow, Scala, MongoDB, NoSQL, Docker, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Scala, Polars, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,102 +2841,102 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a12925c69dfc7bed</t>
+          <t>https://www.indeed.com/viewjob?jk=d56048c057634cd1</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>AI Agent Engineer</t>
+          <t>Senior Software Engineer - Cloud Fullstack</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Momentive Software</t>
+          <t>Rivian and Volkswagen Group Technologies</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Athena, SQS, SNS, API Gateway, ECS, RDS, Azure, GCP</t>
+          <t>AWS, RDS, Scala, Kafka, MongoDB, DynamoDB, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ac9574b3f75cc2c</t>
+          <t>https://www.indeed.com/viewjob?jk=059fe198bd3f948a</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Cloud Database Engineer (Hybrid - Seattle, WA)</t>
+          <t>FastAPI</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Nordstrom</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Redshift, Athena, S3, RDS, Kafka, Oracle, SQL Server</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, PostgreSQL, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1666a61865ef57aa</t>
+          <t>https://www.indeed.com/viewjob?jk=550e29553f2a099b</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>GCP Support Associate</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Moore</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Westminster, CO, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT, dbt</t>
+          <t>IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, MySQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8c5af154805cd95</t>
+          <t>https://www.indeed.com/viewjob?jk=29c27657463cb6ea</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Data Engineer (ETL / Python Developer)</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>CSpring</t>
+          <t>Miami Marlins</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Springfield, IL, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, GCP, Scala, Snowflake, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b861e2c1a0a03133</t>
+          <t>https://www.indeed.com/viewjob?jk=ff87deef607d5450</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Imprint</t>
+          <t>Paramount</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Fort Lauderdale, FL, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Kinesis, S3, RDS, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, RDS, GCP, BigQuery, Dataflow, Scala, MongoDB, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e35bafcce4ab1000</t>
+          <t>https://www.indeed.com/viewjob?jk=a12925c69dfc7bed</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI Agent Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Imprint</t>
+          <t>Momentive Software</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Kinesis, S3, RDS, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, Athena, SQS, SNS, API Gateway, ECS, RDS, Azure, GCP</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=baaf38c4500e2b06</t>
+          <t>https://www.indeed.com/viewjob?jk=6ac9574b3f75cc2c</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior AI Data Engineer</t>
+          <t>Senior Software Engineer - Cloud Gateway</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Velvetech</t>
+          <t>Rivian and Volkswagen Group Technologies</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,34 +3076,34 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Vertex AI, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD</t>
+          <t>AWS, RDS, Scala, Kafka, MongoDB, DynamoDB, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2bec7882b34f08c9</t>
+          <t>https://www.indeed.com/viewjob?jk=7b72e865e6bee153</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Cloud Database Engineer (Hybrid - Seattle, WA)</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Nordstrom</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Westminster, CO, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT, dbt</t>
+          <t>AWS, Glue, Kinesis, Redshift, Athena, S3, RDS, Kafka, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d49164a52434e329</t>
+          <t>https://www.indeed.com/viewjob?jk=1666a61865ef57aa</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>AWS Data Engineer - Databricks</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>RadCube</t>
+          <t>Moore</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Westminster, CO, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Databricks, Scala, Databricks Lakehouse, Data Modeling</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2dcfccb6b6d90b1</t>
+          <t>https://www.indeed.com/viewjob?jk=b8c5af154805cd95</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Software Engineer - Cloud</t>
+          <t>Data Engineer (ETL / Python Developer)</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Carnegie Robotics LLC</t>
+          <t>CSpring</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Springfield, IL, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,34 +3181,34 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, PostgreSQL, MongoDB, DynamoDB, NoSQL</t>
+          <t>Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2f5b0b9c556cdca</t>
+          <t>https://www.indeed.com/viewjob?jk=b861e2c1a0a03133</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Python/PySpark/AWS)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Infinitive Inc</t>
+          <t>Imprint</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,34 +3216,34 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Azure, Spark, PySpark, Scala, Spark Streaming, Data Modeling, ETL, CI/CD, Jenkins</t>
+          <t>Kinesis, S3, RDS, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2025-02-18</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45083db400feff94</t>
+          <t>https://www.indeed.com/viewjob?jk=e35bafcce4ab1000</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Data Engineer (Python/PySpark/AWS)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Infinitive Inc</t>
+          <t>Imprint</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,34 +3251,34 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Azure, Spark, PySpark, Scala, Spark Streaming, Data Modeling, ETL, CI/CD, Jenkins</t>
+          <t>Kinesis, S3, RDS, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2025-01-27</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e742c4bedd2037b</t>
+          <t>https://www.indeed.com/viewjob?jk=baaf38c4500e2b06</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Python)</t>
+          <t>Senior AI Data Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Velvetech</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,34 +3286,34 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, MapReduce, Impala, Spark, PySpark, Oracle, SQL Server, MySQL</t>
+          <t>AWS, IAM, Azure, GCP, Vertex AI, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45974a79c5dfc2f4</t>
+          <t>https://www.indeed.com/viewjob?jk=2bec7882b34f08c9</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Westminster, CO, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,34 +3321,34 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage, MySQL, Splunk, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52b0e598b9832c43</t>
+          <t>https://www.indeed.com/viewjob?jk=d49164a52434e329</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>AWS Data Engineer - Databricks</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Terra Quantum</t>
+          <t>RadCube</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,34 +3356,34 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Databricks, Scala, Databricks Lakehouse, Data Modeling</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15eb90498bcba242</t>
+          <t>https://www.indeed.com/viewjob?jk=d2dcfccb6b6d90b1</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Full Stack Engineer, Experienced</t>
+          <t>Software Engineer - Cloud</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Blue Shield of California</t>
+          <t>Carnegie Robotics LLC</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,34 +3391,34 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, NoSQL, CI/CD, Terraform</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, PostgreSQL, MongoDB, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93fe5a9749607800</t>
+          <t>https://www.indeed.com/viewjob?jk=e2f5b0b9c556cdca</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Full Stack Engineer, Senior</t>
+          <t>Senior Data Engineer (Python/PySpark/AWS)</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Blue Shield of California</t>
+          <t>Infinitive Inc</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Ashburn, VA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,34 +3426,34 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, NoSQL, CI/CD, Terraform</t>
+          <t>AWS, Azure, Spark, PySpark, Scala, Spark Streaming, Data Modeling, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2025-02-18</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bcc6fa1baccf83e5</t>
+          <t>https://www.indeed.com/viewjob?jk=45083db400feff94</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Full Stack Engineer, Consultant</t>
+          <t>Data Engineer (Python/PySpark/AWS)</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Blue Shield of California</t>
+          <t>Infinitive Inc</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Ashburn, VA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,34 +3461,34 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, NoSQL, CI/CD, Terraform</t>
+          <t>AWS, Azure, Spark, PySpark, Scala, Spark Streaming, Data Modeling, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2025-01-27</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3a7d3c5d7336760</t>
+          <t>https://www.indeed.com/viewjob?jk=5e742c4bedd2037b</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Summer Intern, Platform Engineering</t>
+          <t>Senior Software Engineer (Python)</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Outfront Media</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,24 +3496,24 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD, Docker</t>
+          <t>RDS, Hadoop, Hive, MapReduce, Impala, Spark, PySpark, Oracle, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2aa35bb9483f10ad</t>
+          <t>https://www.indeed.com/viewjob?jk=45974a79c5dfc2f4</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Java Software Engineer</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -3531,34 +3531,34 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>IAM, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage, MySQL, Splunk, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=257d265c3f7e2882</t>
+          <t>https://www.indeed.com/viewjob?jk=52b0e598b9832c43</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Customer Centric Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Terra Quantum</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,77 +3566,77 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Scala, Snowflake, ELT, dbt, Tableau, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29a2186b968dd17c</t>
+          <t>https://www.indeed.com/viewjob?jk=15eb90498bcba242</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>FastAPI</t>
+          <t>Full Stack Engineer, Experienced</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Blue Shield of California</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, Glue, ECS, IAM, RDS, Spark, PySpark, Scala, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36490e4938cafc8b</t>
+          <t>https://www.indeed.com/viewjob?jk=93fe5a9749607800</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Mid-Level Software Engineer</t>
+          <t>Full Stack Engineer, Senior</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>State Farm</t>
+          <t>Blue Shield of California</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Bloomington, IL, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, MongoDB, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,32 +3646,32 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da08c5cf76c3287c</t>
+          <t>https://www.indeed.com/viewjob?jk=bcc6fa1baccf83e5</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Full Stack Engineer, Consultant</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Versant</t>
+          <t>Blue Shield of California</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, GCP, Spark, NoSQL, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,32 +3681,32 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fbef82ce93a90ed</t>
+          <t>https://www.indeed.com/viewjob?jk=a3a7d3c5d7336760</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>AI/ML Engineer</t>
+          <t>Summer Intern, Platform Engineering</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Redapt inc</t>
+          <t>Outfront Media</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Woodinville, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, GCP, Vertex AI, Spark, Snowflake, Data Modeling, ELT</t>
+          <t>AWS, Lambda, S3, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,32 +3716,32 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9c94059f3dd29b3</t>
+          <t>https://www.indeed.com/viewjob?jk=2aa35bb9483f10ad</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer - News</t>
+          <t>Java Software Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Step Functions, SQS, SNS, RDS, Databricks, Spark</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,32 +3751,32 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c5ae4f292525796</t>
+          <t>https://www.indeed.com/viewjob?jk=257d265c3f7e2882</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Customer Centric Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Clayco</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
+          <t>AWS, Azure, GCP, BigQuery, Scala, Snowflake, ELT, dbt, Tableau, Docker</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61cc49187bd6e01d</t>
+          <t>https://www.indeed.com/viewjob?jk=29a2186b968dd17c</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Data Engineering - E&amp;A - Data Engineer I</t>
+          <t>Mid-Level Software Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Genesis Global Group</t>
+          <t>State Farm</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Myrtle Point, OR, US USA</t>
+          <t>Bloomington, IL, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, MongoDB, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,24 +3821,24 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2526bf14df16c3e8</t>
+          <t>https://www.indeed.com/viewjob?jk=da08c5cf76c3287c</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Senior, Data Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Carrington Mortgage Services, LLC</t>
+          <t>Versant</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, ETL, Microsoft SSIS</t>
+          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, GCP, Spark, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfdf1b9d489fb8ec</t>
+          <t>https://www.indeed.com/viewjob?jk=1fbef82ce93a90ed</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>GCP Support Associate</t>
+          <t>AI/ML Engineer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Redapt inc</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Woodinville, WA, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>ECS, IAM, Google Cloud Platform, GCP, Dataflow, Cloud Storage, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, Redshift, Azure, Databricks, GCP, Vertex AI, Spark, Snowflake, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9acaddb632586c1</t>
+          <t>https://www.indeed.com/viewjob?jk=b9c94059f3dd29b3</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Data Systems Engineer</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Central Health</t>
+          <t>Clayco</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,34 +3916,34 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41eed22913274d81</t>
+          <t>https://www.indeed.com/viewjob?jk=61cc49187bd6e01d</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineering - E&amp;A - Data Engineer I</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Victory Live</t>
+          <t>Genesis Global Group</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Myrtle Point, OR, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Snowflake, SQL Server, DynamoDB, ELT, dbt, Terraform</t>
+          <t>Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1c259f0b00d1299</t>
+          <t>https://www.indeed.com/viewjob?jk=2526bf14df16c3e8</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>AI Senior Engineer</t>
+          <t>Senior, Data Engineer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Wood Mackenzie</t>
+          <t>Carrington Mortgage Services, LLC</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, ECS, Azure, Scala, DynamoDB, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, ETL, Microsoft SSIS</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,14 +3996,14 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69e1b61070a9b37b</t>
+          <t>https://www.indeed.com/viewjob?jk=dfdf1b9d489fb8ec</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>AI Systems Administrator</t>
+          <t>GCP Support Associate</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>ECS, RDS, Azure, Databricks, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>ECS, IAM, Google Cloud Platform, GCP, Dataflow, Cloud Storage, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,189 +4031,189 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a338fa1fa96ea390</t>
+          <t>https://www.indeed.com/viewjob?jk=a9acaddb632586c1</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>API Architect (Python)</t>
+          <t>Data Systems Engineer</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Central Health</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, MLOps, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=460c6fea55fa6849</t>
+          <t>https://www.indeed.com/viewjob?jk=41eed22913274d81</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Software Engineer - Warehouse Management Systems (WMS)</t>
+          <t>Full Stack Data Engineer</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Staples</t>
+          <t>Millennium Management</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Framingham, MA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, HBase, Scala, Kafka, NoSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Scala, Snowflake, NoSQL, ELT, dbt, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=654753ccda866d62</t>
+          <t>https://www.indeed.com/viewjob?jk=b224fb124b25e580</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr Database Administrator</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Atlantic Union Bank</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Glen Allen, VA, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Vertex AI, Scala, Data Modeling, Jenkins, Terraform, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bbf23a169f18dbc</t>
+          <t>https://www.indeed.com/viewjob?jk=fadd8b2210e032b2</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>FastAPI</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Vertex AI, Scala, Data Modeling, Jenkins, Terraform, Jenkins</t>
+          <t>AWS, Glue, ECS, IAM, RDS, Spark, PySpark, Scala, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b05514433681d42</t>
+          <t>https://www.indeed.com/viewjob?jk=36490e4938cafc8b</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior DevOps Software Engineer, Firmware &amp; CI/CD</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Clark Construction</t>
+          <t>Rivian and Volkswagen Group Technologies</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, dbt</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f199bfc2e975b58</t>
+          <t>https://www.indeed.com/viewjob?jk=d5f621c8ad4f69fd</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Junior GCP Cloud Engineer</t>
+          <t>AI Systems Administrator</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -4227,11 +4227,11 @@
         </is>
       </c>
       <c r="D109" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, Dataflow, Cloud Storage, Scala, Oracle, ETL, ELT, dbt</t>
+          <t>ECS, RDS, Azure, Databricks, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,32 +4241,32 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=817a2d7d06f177a9</t>
+          <t>https://www.indeed.com/viewjob?jk=a338fa1fa96ea390</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Sr. Professional, Software Engineering (Python)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Cotality</t>
+          <t>Victory Live</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, Tableau, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, Snowflake, SQL Server, DynamoDB, ELT, dbt, Terraform</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,94 +4276,94 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83e013cc49a29087</t>
+          <t>https://www.indeed.com/viewjob?jk=a1c259f0b00d1299</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Senior Platform/DevOps Engineer (Kubernetes-Linux)</t>
+          <t>Snowflake/Tableau Developer / Dallas Texas</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>ARMADA</t>
+          <t>FirstNet Global</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Napa, CA, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b0e9b75e0f5558d</t>
+          <t>https://www.indeed.com/viewjob?jk=a4ab4d99e440e9b4</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Senior Platform/DevOps Engineer (Kubernetes-Linux)</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>ARMADA</t>
+          <t>Klaxontech</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Sammamish, WA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=efa4e4e3099a0ae2</t>
+          <t>https://www.indeed.com/viewjob?jk=193935f590ab7020</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Senior Platform/DevOps Engineer (Kubernetes-Linux)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>ARMADA</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Kirkland, WA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>RDS, GCP, BigQuery, Dataflow, Vertex AI, Scala, Data Modeling, Jenkins, Terraform, Jenkins</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,24 +4381,24 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33ae1f1f9d08c546</t>
+          <t>https://www.indeed.com/viewjob?jk=4bbf23a169f18dbc</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Senior Platform/DevOps Engineer (Kubernetes-Linux)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>ARMADA</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Renton, WA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>RDS, GCP, BigQuery, Dataflow, Vertex AI, Scala, Data Modeling, Jenkins, Terraform, Jenkins</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,24 +4416,24 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d25130b996402485</t>
+          <t>https://www.indeed.com/viewjob?jk=4b05514433681d42</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Senior Platform/DevOps Engineer (Kubernetes-Linux)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>ARMADA</t>
+          <t>Clark Construction</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Bothell, WA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Azure, GCP, Spark, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, dbt</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,24 +4451,24 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6f9224460f3210c</t>
+          <t>https://www.indeed.com/viewjob?jk=6f199bfc2e975b58</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Senior Platform/DevOps Engineer (Kubernetes-Linux)</t>
+          <t>Junior GCP Cloud Engineer</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>ARMADA</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Redmond, WA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Google Cloud Platform, GCP, Dataflow, Cloud Storage, Scala, Oracle, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,24 +4486,24 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b86c940f686047d8</t>
+          <t>https://www.indeed.com/viewjob?jk=817a2d7d06f177a9</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Professional, Software Engineering (Python)</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Cotality</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Somerville, MA, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Scala, Snowflake, ETL, ELT, dbt, Tableau, CI/CD</t>
+          <t>RDS, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, Tableau, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,19 +4521,19 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75339d7552c524c1</t>
+          <t>https://www.indeed.com/viewjob?jk=83e013cc49a29087</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Sr. Site Reliability Engineer</t>
+          <t>Senior Platform/DevOps Engineer (Kubernetes-Linux)</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>PitchBook</t>
+          <t>ARMADA</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, SQL Server, PostgreSQL, MySQL, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4556,24 +4556,24 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=181ce2100b853c3a</t>
+          <t>https://www.indeed.com/viewjob?jk=7b0e9b75e0f5558d</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Senior Data Engineer / Data Architect</t>
+          <t>Senior Platform/DevOps Engineer (Kubernetes-Linux)</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>ARMADA</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Sammamish, WA, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,24 +4591,24 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e83d1768e75b1203</t>
+          <t>https://www.indeed.com/viewjob?jk=efa4e4e3099a0ae2</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Snowflake Data Movement Engineer</t>
+          <t>Senior Platform/DevOps Engineer (Kubernetes-Linux)</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Smart Tech Skills LLC</t>
+          <t>ARMADA</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Kirkland, WA, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, ETL, CI/CD, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,24 +4626,24 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12ef21c70e148f1d</t>
+          <t>https://www.indeed.com/viewjob?jk=33ae1f1f9d08c546</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Senior Platform/DevOps Engineer (Kubernetes-Linux)</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>ARMADA</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Renton, WA, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,34 +4651,34 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Databricks, Spark, Scala, DynamoDB, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f9ad7c8c6b989c1</t>
+          <t>https://www.indeed.com/viewjob?jk=d25130b996402485</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Sr. Data Architect Specialist</t>
+          <t>Senior Platform/DevOps Engineer (Kubernetes-Linux)</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>SAMYANG AMERICA INC</t>
+          <t>ARMADA</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Brea, CA, US USA</t>
+          <t>Bothell, WA, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4696,24 +4696,24 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2086e3e44cfc021</t>
+          <t>https://www.indeed.com/viewjob?jk=b6f9224460f3210c</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Full Stack Product Engineer (Java)</t>
+          <t>Senior Platform/DevOps Engineer (Kubernetes-Linux)</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Allstate Insurance</t>
+          <t>ARMADA</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Redmond, WA, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4721,7 +4721,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, ELT, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4731,24 +4731,24 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d15adff582efc740</t>
+          <t>https://www.indeed.com/viewjob?jk=b86c940f686047d8</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>DevOps &amp; Infrastructure Engineer - Level I</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>SPRING ARBOR UNIVERSITY</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Spring Arbor, MI, US USA</t>
+          <t>Somerville, MA, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Oracle, CI/CD, Jenkins, GitHub Actions, Docker, Jenkins</t>
+          <t>Redshift, RDS, Azure, Scala, Snowflake, ETL, ELT, dbt, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4766,24 +4766,24 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0b216de71eb3804</t>
+          <t>https://www.indeed.com/viewjob?jk=75339d7552c524c1</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Senior GCP Kubernetes Engineer</t>
+          <t>Sr. Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>PitchBook</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4791,7 +4791,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Kafka, Oracle, PostgreSQL, CI/CD, Jenkins, Maven</t>
+          <t>AWS, RDS, GCP, Scala, SQL Server, PostgreSQL, MySQL, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -4801,24 +4801,24 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a77679969db6e94b</t>
+          <t>https://www.indeed.com/viewjob?jk=181ce2100b853c3a</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Software Engineer – Enterprise Software</t>
+          <t>Senior Data Engineer / Data Architect</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Rivian</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,34 +4826,34 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MySQL, NoSQL, Splunk, Docker, Kubernetes</t>
+          <t>AWS, Kinesis, Redshift, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90124173401e2437</t>
+          <t>https://www.indeed.com/viewjob?jk=e83d1768e75b1203</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer, Enterprise Technology</t>
+          <t>API Architect (Python)</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Rivian</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4861,34 +4861,34 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MySQL, NoSQL, Splunk, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, MLOps, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fab081dda06a1ba5</t>
+          <t>https://www.indeed.com/viewjob?jk=460c6fea55fa6849</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Senior GCP IAM Engineer</t>
+          <t>Software Engineer - Warehouse Management Systems (WMS)</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Staples</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Framingham, MA, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4896,7 +4896,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, GCP, HBase, Scala, Kafka, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -4906,24 +4906,24 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e01ee86f0306e6c</t>
+          <t>https://www.indeed.com/viewjob?jk=654753ccda866d62</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>QA Analyst / ETL Tester</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>CSpring</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Springfield, IL, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4931,42 +4931,42 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>RDS, Azure, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Data Modeling, Snowflake Schema, ETL, CI/CD</t>
+          <t>AWS, S3, IAM, Databricks, Spark, Scala, DynamoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ebf7b3987a302e8</t>
+          <t>https://www.indeed.com/viewjob?jk=6f9ad7c8c6b989c1</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Engineer II-Software Development</t>
+          <t>Sr. Data Architect Specialist</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Microchip Technology</t>
+          <t>SAMYANG AMERICA INC</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Brea, CA, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -4976,32 +4976,32 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3013681a0e1c4f81</t>
+          <t>https://www.indeed.com/viewjob?jk=f2086e3e44cfc021</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Engineer II-Software Development</t>
+          <t>Senior GCP IAM Engineer</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Microchip Technology</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLOps, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -5011,19 +5011,19 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2649d75a044fe7bd</t>
+          <t>https://www.indeed.com/viewjob?jk=4e01ee86f0306e6c</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - VAULT</t>
+          <t>Software Engineer - DevOps Mobile</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Bloomberg</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -5032,46 +5032,46 @@
         </is>
       </c>
       <c r="D132" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Hive, Spark, Scala, Kafka, Cassandra</t>
+          <t>AWS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Maven, Terraform, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d744cfcd1fce896</t>
+          <t>https://www.indeed.com/viewjob?jk=537b207b8aaf9dd0</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Cloud AI Application Administrator</t>
+          <t>Full Stack Product Engineer (Java)</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Allstate Insurance</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, Dataflow, Cloud Storage, Scala, Oracle, ETL, ELT, dbt, Tableau</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, ELT, CI/CD, Git</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -5081,67 +5081,67 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd193e360372af33</t>
+          <t>https://www.indeed.com/viewjob?jk=d15adff582efc740</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>FastAPI</t>
+          <t>DevOps &amp; Infrastructure Engineer - Level I</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>SPRING ARBOR UNIVERSITY</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Spring Arbor, MI, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, BigQuery, Vertex AI, Spark, Scala, Spark Streaming, Kafka, CI/CD, Git</t>
+          <t>AWS, Azure, GCP, Scala, Oracle, CI/CD, Jenkins, GitHub Actions, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0bc1141188a8604a</t>
+          <t>https://www.indeed.com/viewjob?jk=b0b216de71eb3804</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior GCP Kubernetes Engineer</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Urology Centers of Alabama</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, Oracle, PostgreSQL, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -5151,102 +5151,102 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28cb24ea6139fcb9</t>
+          <t>https://www.indeed.com/viewjob?jk=a77679969db6e94b</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer – Enterprise Software</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Pearson</t>
+          <t>Rivian</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Hoboken, NJ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, MongoDB, DynamoDB, Data Modeling, ETL, ELT, DataOps, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MySQL, NoSQL, Splunk, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05547d65aabdfcf0</t>
+          <t>https://www.indeed.com/viewjob?jk=90124173401e2437</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
+          <t>Sr. Software Engineer, Enterprise Technology</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Rivian</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MySQL, NoSQL, Splunk, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34c37a226b547d01</t>
+          <t>https://www.indeed.com/viewjob?jk=fab081dda06a1ba5</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
+          <t>QA Analyst / ETL Tester</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>CSpring</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Springfield, IL, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
+          <t>RDS, Azure, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Data Modeling, Snowflake Schema, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -5256,24 +5256,24 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7d77afce6f60e6f</t>
+          <t>https://www.indeed.com/viewjob?jk=1ebf7b3987a302e8</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
+          <t>Senior Full Stack Engineer - Python &amp; React JS</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Checkmate</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5281,34 +5281,34 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
+          <t>AWS, RDS, Scala, PostgreSQL, MySQL, CI/CD, GitHub Actions, Docker, Git, Datadog</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=225c5a8131dc6595</t>
+          <t>https://www.indeed.com/viewjob?jk=6ba3d00c3fb0ee25</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
+          <t>Engineer II-Software Development</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Microchip Technology</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5316,7 +5316,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -5326,24 +5326,24 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=301dbd1e2eb0bb70</t>
+          <t>https://www.indeed.com/viewjob?jk=3013681a0e1c4f81</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
+          <t>Engineer II-Software Development</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Microchip Technology</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5351,7 +5351,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -5361,24 +5361,24 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d88e7121c2db79d6</t>
+          <t>https://www.indeed.com/viewjob?jk=2649d75a044fe7bd</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
+          <t>Senior Software Engineer - VAULT</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Bloomberg</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5386,7 +5386,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
+          <t>AWS, S3, RDS, Azure, GCP, Hive, Spark, Scala, Kafka, Cassandra</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -5396,24 +5396,24 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18d3f9fdcfa07035</t>
+          <t>https://www.indeed.com/viewjob?jk=1d744cfcd1fce896</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
+          <t>BigData ,Python and Py Spark , GCP</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5421,7 +5421,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
+          <t>GCP, BigQuery, Hadoop, Hive, Spark, PySpark, Scala, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -5431,24 +5431,24 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d2d16258cfd6718</t>
+          <t>https://www.indeed.com/viewjob?jk=81999129979e18ac</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
+          <t>Cloud AI Application Administrator</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
+          <t>RDS, Google Cloud Platform, Dataflow, Cloud Storage, Scala, Oracle, ETL, ELT, dbt, Tableau</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -5466,24 +5466,24 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5be8f9b4535b406c</t>
+          <t>https://www.indeed.com/viewjob?jk=cd193e360372af33</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
+          <t>FastAPI</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -5491,34 +5491,34 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
+          <t>RDS, Google Cloud Platform, BigQuery, Vertex AI, Spark, Scala, Spark Streaming, Kafka, CI/CD, Git</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26ef52c65261360a</t>
+          <t>https://www.indeed.com/viewjob?jk=0bc1141188a8604a</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Urology Centers of Alabama</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
+          <t>AWS, EMR, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, ETL</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -5536,24 +5536,24 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9240b7b96545a4d</t>
+          <t>https://www.indeed.com/viewjob?jk=28cb24ea6139fcb9</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Pearson</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Hoboken, NJ, US USA</t>
         </is>
       </c>
       <c r="D147" t="n">
@@ -5561,7 +5561,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
+          <t>AWS, RDS, Scala, MongoDB, DynamoDB, Data Modeling, ETL, ELT, DataOps, CI/CD</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -5571,7 +5571,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42ae72f7d4a97700</t>
+          <t>https://www.indeed.com/viewjob?jk=05547d65aabdfcf0</t>
         </is>
       </c>
     </row>
@@ -5588,7 +5588,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D148" t="n">
@@ -5606,7 +5606,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dab5b1b68cc6402c</t>
+          <t>https://www.indeed.com/viewjob?jk=34c37a226b547d01</t>
         </is>
       </c>
     </row>
@@ -5623,7 +5623,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D149" t="n">
@@ -5641,7 +5641,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fde8d1831ca7f9b7</t>
+          <t>https://www.indeed.com/viewjob?jk=e7d77afce6f60e6f</t>
         </is>
       </c>
     </row>
@@ -5658,7 +5658,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D150" t="n">
@@ -5676,7 +5676,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a056659ad4aebd2</t>
+          <t>https://www.indeed.com/viewjob?jk=225c5a8131dc6595</t>
         </is>
       </c>
     </row>
@@ -5693,7 +5693,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D151" t="n">
@@ -5711,7 +5711,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5402962c321dcba</t>
+          <t>https://www.indeed.com/viewjob?jk=301dbd1e2eb0bb70</t>
         </is>
       </c>
     </row>
@@ -5728,7 +5728,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D152" t="n">
@@ -5746,7 +5746,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f45ad39ec1fe503a</t>
+          <t>https://www.indeed.com/viewjob?jk=d88e7121c2db79d6</t>
         </is>
       </c>
     </row>
@@ -5763,7 +5763,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D153" t="n">
@@ -5781,7 +5781,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86cfc919b4ccc768</t>
+          <t>https://www.indeed.com/viewjob?jk=18d3f9fdcfa07035</t>
         </is>
       </c>
     </row>
@@ -5798,7 +5798,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D154" t="n">
@@ -5816,7 +5816,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9a866cff6a0e3bd</t>
+          <t>https://www.indeed.com/viewjob?jk=9d2d16258cfd6718</t>
         </is>
       </c>
     </row>
@@ -5833,7 +5833,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D155" t="n">
@@ -5851,7 +5851,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab68f1e4ba82ad10</t>
+          <t>https://www.indeed.com/viewjob?jk=5be8f9b4535b406c</t>
         </is>
       </c>
     </row>
@@ -5868,7 +5868,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D156" t="n">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df163d5906a30146</t>
+          <t>https://www.indeed.com/viewjob?jk=26ef52c65261360a</t>
         </is>
       </c>
     </row>
@@ -5903,7 +5903,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D157" t="n">
@@ -5921,7 +5921,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f0c32c0bdf67710</t>
+          <t>https://www.indeed.com/viewjob?jk=f9240b7b96545a4d</t>
         </is>
       </c>
     </row>
@@ -5938,7 +5938,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D158" t="n">
@@ -5956,7 +5956,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25f63312ec2e267e</t>
+          <t>https://www.indeed.com/viewjob?jk=42ae72f7d4a97700</t>
         </is>
       </c>
     </row>
@@ -5973,7 +5973,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D159" t="n">
@@ -5991,7 +5991,7 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be379ec08f5c5e6f</t>
+          <t>https://www.indeed.com/viewjob?jk=dab5b1b68cc6402c</t>
         </is>
       </c>
     </row>
@@ -6008,7 +6008,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D160" t="n">
@@ -6026,7 +6026,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8deeb1ab1ebcdccd</t>
+          <t>https://www.indeed.com/viewjob?jk=fde8d1831ca7f9b7</t>
         </is>
       </c>
     </row>
@@ -6043,7 +6043,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D161" t="n">
@@ -6061,7 +6061,7 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92aa87419ba8e5df</t>
+          <t>https://www.indeed.com/viewjob?jk=7a056659ad4aebd2</t>
         </is>
       </c>
     </row>
@@ -6078,7 +6078,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D162" t="n">
@@ -6096,7 +6096,7 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da334d3b3eda0eb4</t>
+          <t>https://www.indeed.com/viewjob?jk=e5402962c321dcba</t>
         </is>
       </c>
     </row>
@@ -6113,7 +6113,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D163" t="n">
@@ -6131,7 +6131,7 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c314e6df20a4157</t>
+          <t>https://www.indeed.com/viewjob?jk=f45ad39ec1fe503a</t>
         </is>
       </c>
     </row>
@@ -6148,7 +6148,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D164" t="n">
@@ -6166,7 +6166,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b90a165cff732e70</t>
+          <t>https://www.indeed.com/viewjob?jk=86cfc919b4ccc768</t>
         </is>
       </c>
     </row>
@@ -6183,7 +6183,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D165" t="n">
@@ -6201,7 +6201,7 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26bc98921360165c</t>
+          <t>https://www.indeed.com/viewjob?jk=c9a866cff6a0e3bd</t>
         </is>
       </c>
     </row>
@@ -6218,7 +6218,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D166" t="n">
@@ -6236,7 +6236,7 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5359f322821abe9</t>
+          <t>https://www.indeed.com/viewjob?jk=ab68f1e4ba82ad10</t>
         </is>
       </c>
     </row>
@@ -6253,7 +6253,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D167" t="n">
@@ -6271,7 +6271,7 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=562ea8307dd5c91d</t>
+          <t>https://www.indeed.com/viewjob?jk=df163d5906a30146</t>
         </is>
       </c>
     </row>
@@ -6288,7 +6288,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D168" t="n">
@@ -6306,7 +6306,7 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70a64e543cdeb49a</t>
+          <t>https://www.indeed.com/viewjob?jk=2f0c32c0bdf67710</t>
         </is>
       </c>
     </row>
@@ -6323,7 +6323,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D169" t="n">
@@ -6341,7 +6341,7 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed3e28c9a543299a</t>
+          <t>https://www.indeed.com/viewjob?jk=25f63312ec2e267e</t>
         </is>
       </c>
     </row>
@@ -6358,7 +6358,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D170" t="n">
@@ -6376,24 +6376,24 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1735f01363643535</t>
+          <t>https://www.indeed.com/viewjob?jk=be379ec08f5c5e6f</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Data Engineer II, Mobile Game Analytics</t>
+          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Mattel, Inc.</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>El Segundo, CA, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D171" t="n">
@@ -6401,7 +6401,7 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>RDS, Medallion Architecture, GCP, BigQuery, Dimensional Modeling, ETL, dbt, Tableau, CI/CD, Airflow</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
@@ -6411,24 +6411,24 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=087868e735e87a06</t>
+          <t>https://www.indeed.com/viewjob?jk=8deeb1ab1ebcdccd</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D172" t="n">
@@ -6436,7 +6436,7 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, BigQuery, Vertex AI, Spark, Scala, Spark Streaming, Kafka, CI/CD, Git</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
@@ -6446,24 +6446,24 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f192cf981191d4cd</t>
+          <t>https://www.indeed.com/viewjob?jk=92aa87419ba8e5df</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D173" t="n">
@@ -6471,7 +6471,7 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, Terraform, Docker, Jenkins</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
@@ -6481,24 +6481,24 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7e0844f636778b5</t>
+          <t>https://www.indeed.com/viewjob?jk=da334d3b3eda0eb4</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>GCP Support Associate</t>
+          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D174" t="n">
@@ -6506,7 +6506,7 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, GCP, Dataflow, Cloud Storage, CI/CD, Jenkins, Terraform, Docker, Jenkins</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
@@ -6516,24 +6516,24 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=908520f92505a147</t>
+          <t>https://www.indeed.com/viewjob?jk=2c314e6df20a4157</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Leidos</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Seaside, CA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D175" t="n">
@@ -6541,7 +6541,7 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Splunk, CI/CD, Terraform, Docker, Kubernetes, Git, CloudWatch</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
@@ -6551,24 +6551,24 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=727ac8d7c715b1a1</t>
+          <t>https://www.indeed.com/viewjob?jk=b90a165cff732e70</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Data Scientist, Senior Associate – Product, Experience and Technology (PXT) Analytics Team</t>
+          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D176" t="n">
@@ -6576,34 +6576,34 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, Scala, Snowflake, dbt, Tableau, CI/CD, Airflow, Git</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b0bfe4f7e93a067</t>
+          <t>https://www.indeed.com/viewjob?jk=26bc98921360165c</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Software Engineer - AI Augmented Development</t>
+          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>PowerPay</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Wayne, PA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D177" t="n">
@@ -6611,7 +6611,7 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, ECS, IAM, RDS, Snowflake, ETL, Terraform</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
@@ -6621,24 +6621,24 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=039bac65ddb8c30e</t>
+          <t>https://www.indeed.com/viewjob?jk=c5359f322821abe9</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Sr Associate Engineer/Engineer, IT Software</t>
+          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D178" t="n">
@@ -6646,7 +6646,7 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
@@ -6656,24 +6656,24 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf657c9771abb6db</t>
+          <t>https://www.indeed.com/viewjob?jk=562ea8307dd5c91d</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>DevOps Engineer (GCP)</t>
+          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D179" t="n">
@@ -6681,7 +6681,7 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Vertex AI, Spark, MLflow, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
@@ -6691,24 +6691,24 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a53e6510409c717</t>
+          <t>https://www.indeed.com/viewjob?jk=70a64e543cdeb49a</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Enterprise AI Architect</t>
+          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Radwell International</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Willingboro, NJ, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D180" t="n">
@@ -6716,34 +6716,34 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, PostgreSQL, MySQL, NoSQL, MLOps, CI/CD</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56c80236c3727026</t>
+          <t>https://www.indeed.com/viewjob?jk=ed3e28c9a543299a</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>AI Application Architect</t>
+          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D181" t="n">
@@ -6751,15 +6751,400 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1735f01363643535</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>Data Engineer II, Mobile Game Analytics</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Mattel, Inc.</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>El Segundo, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D182" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>RDS, Medallion Architecture, GCP, BigQuery, Dimensional Modeling, ETL, dbt, Tableau, CI/CD, Airflow</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=087868e735e87a06</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>AI Integration Engineer (Java + AI)</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D183" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>RDS, Google Cloud Platform, BigQuery, Vertex AI, Spark, Scala, Spark Streaming, Kafka, CI/CD, Git</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f192cf981191d4cd</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>AI Integration Engineer (Java + AI)</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D184" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, Terraform, Docker, Jenkins</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e7e0844f636778b5</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>GCP Support Associate</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D185" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>IAM, Google Cloud Platform, GCP, Dataflow, Cloud Storage, CI/CD, Jenkins, Terraform, Docker, Jenkins</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=908520f92505a147</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>Sr. Software Engineer, Full-Stack (Factory Systems)</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>Rivian and Volkswagen Group Technologies</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>Palo Alto, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D186" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=68c700567606c4e9</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>Data Scientist, Senior Associate – Product, Experience and Technology (PXT) Analytics Team</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D187" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>Redshift, RDS, Databricks, Scala, Snowflake, dbt, Tableau, CI/CD, Airflow, Git</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4b0bfe4f7e93a067</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>Software Engineer - AI Augmented Development</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>PowerPay</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>Wayne, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D188" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, SQS, ECS, IAM, RDS, Snowflake, ETL, Terraform</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=039bac65ddb8c30e</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>Enterprise AI Architect</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Radwell International</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>Willingboro, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D189" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Scala, PostgreSQL, MySQL, NoSQL, MLOps, CI/CD</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=56c80236c3727026</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>Sr Associate Engineer/Engineer, IT Software</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>American Airlines</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>Fort Worth, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D190" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cf657c9771abb6db</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>DevOps Engineer (GCP)</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D191" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Vertex AI, Spark, MLflow, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1a53e6510409c717</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>AI Application Architect</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D192" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
           <t>AWS, Azure, Google Cloud Platform, Spark, Scala, Snowflake, ETL, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
-      <c r="F181" t="inlineStr">
-        <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="G181" t="inlineStr">
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=bdfa99adc53f817f</t>
         </is>

--- a/results/job_matches_2026-05-06.xlsx
+++ b/results/job_matches_2026-05-06.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G192"/>
+  <dimension ref="A1:G172"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,25 +538,25 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Skyventure Management LLC</t>
+          <t>Capital Bank, N.A.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Rockville, MD, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>21.5</v>
+        <v>19.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL</t>
+          <t>Redshift, RDS, Azure, Data Factory, BigQuery, Spark, Scala, Kafka, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2cf4e196f6f8959b</t>
+          <t>https://www.indeed.com/viewjob?jk=3488abdd8c4dc725</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Capital Bank, N.A.</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Rockville, MD, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>19.4</v>
+        <v>18.8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Data Factory, BigQuery, Spark, Scala, Kafka, Snowflake, SQL Server</t>
+          <t>AWS, Glue, EMR, S3, RDS, Azure, Data Factory, Databricks, GCP, Spark</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,7 +601,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3488abdd8c4dc725</t>
+          <t>https://www.indeed.com/viewjob?jk=ad171c93c1899d21</t>
         </is>
       </c>
     </row>
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad171c93c1899d21</t>
+          <t>https://www.indeed.com/viewjob?jk=98f8265780f793dd</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>Warner Bros. Discovery</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>18.8</v>
+        <v>18.1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, S3, RDS, Azure, Data Factory, Databricks, GCP, Spark</t>
+          <t>AWS, Glue, EMR, Kinesis, Redshift, Athena, S3, RDS, Azure, Databricks</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98f8265780f793dd</t>
+          <t>https://www.indeed.com/viewjob?jk=0585eb3ca3cd8f48</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0585eb3ca3cd8f48</t>
+          <t>https://www.indeed.com/viewjob?jk=ea66a6dbd0690c3b</t>
         </is>
       </c>
     </row>
@@ -741,7 +741,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea66a6dbd0690c3b</t>
+          <t>https://www.indeed.com/viewjob?jk=ec9442df01efef1b</t>
         </is>
       </c>
     </row>
@@ -776,7 +776,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec9442df01efef1b</t>
+          <t>https://www.indeed.com/viewjob?jk=341798717a6ce508</t>
         </is>
       </c>
     </row>
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=341798717a6ce508</t>
+          <t>https://www.indeed.com/viewjob?jk=29381ac7399ddbb0</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer - DevOps and MLOps</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Warner Bros. Discovery</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Francisco Bay Area, CA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Kinesis, Redshift, Athena, S3, RDS, Azure, Databricks</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Kafka, PostgreSQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,14 +846,14 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29381ac7399ddbb0</t>
+          <t>https://www.indeed.com/viewjob?jk=2fcad788d48ba696</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Software Engineer - DevOps and MLOps</t>
+          <t>Software Engineer, Cloud Infrastructure (Multiple Seniority Levels)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -863,7 +863,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>San Francisco Bay Area, CA, US USA</t>
+          <t>San Carlos, CA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Kafka, PostgreSQL, MongoDB, Cassandra</t>
+          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, SQS, ECS, IAM, RDS</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2fcad788d48ba696</t>
+          <t>https://www.indeed.com/viewjob?jk=07cee960b10bf15e</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Junior DevOps Engineer (GCP)</t>
+          <t>Commercial IT Senior Data Solution Developer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>ConocoPhillips</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Databricks, Hive, Spark, Scala, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,67 +916,67 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56a30f4a788f09b2</t>
+          <t>https://www.indeed.com/viewjob?jk=1304cb2ffae316c6</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Software Engineer, Cloud Infrastructure (Multiple Seniority Levels)</t>
+          <t>Azure Network Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>San Carlos, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, SQS, ECS, IAM, RDS</t>
+          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Event Hubs, Unity Catalog, Medallion Architecture, Spark, PySpark</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07cee960b10bf15e</t>
+          <t>https://www.indeed.com/viewjob?jk=b4c4141e761a1d57</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Software Engineer – Oracle EPM/Senior Quadient Inspire Engineer</t>
+          <t>Health Account Intern</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>SUPPORTSOFT TECHNOLOGIES</t>
+          <t>Booz Allen Hamilton</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Databricks, Hadoop, Hive, Spark, Scala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75c533d77b3fd5ba</t>
+          <t>https://www.indeed.com/viewjob?jk=64329d0d0bf86853</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Commercial IT Senior Data Solution Developer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>ConocoPhillips</t>
+          <t>WSSC Water</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Laurel, MD, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hive, Spark, Scala, Kafka, Snowflake, NoSQL</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Blob Storage, GCP, Hadoop</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1304cb2ffae316c6</t>
+          <t>https://www.indeed.com/viewjob?jk=859b6255aab51697</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Health Account Intern</t>
+          <t>Sr Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Booz Allen Hamilton</t>
+          <t>Commence</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Leesburg, VA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Databricks, Hadoop, Hive, Spark, Scala</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, NoSQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64329d0d0bf86853</t>
+          <t>https://www.indeed.com/viewjob?jk=9093ede7f2269db2</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Sr Data Engineer, Python + Spark (Data Federation skillset - Data Lakehouse - Eg: Starburst) - New York</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>WSSC Water</t>
+          <t>Photon</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Laurel, MD, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Blob Storage, GCP, Hadoop</t>
+          <t>AWS, Glue, EMR, S3, Azure, Databricks, Medallion Architecture, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=859b6255aab51697</t>
+          <t>https://www.indeed.com/viewjob?jk=f7767a92d7d08a3b</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>Senior Software Engineer - ETL, Java</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>RevSpring, Inc</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, API Gateway, RDS, Azure, Kafka</t>
+          <t>Redshift, S3, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop, Scala</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b4a39c21c884e72</t>
+          <t>https://www.indeed.com/viewjob?jk=4a9c009a05948507</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>GCP ETL Engineer</t>
+          <t>Senior Software Engineer - ETL, Java</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>RevSpring, Inc</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, Spark, Scala, Snowflake, Oracle</t>
+          <t>Redshift, S3, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop, Scala</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,94 +1161,94 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e5fc76263d455e5</t>
+          <t>https://www.indeed.com/viewjob?jk=ba5ba3f3a840901f</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>API Threat Intelligence Analyst</t>
+          <t>Senior Software Engineer - ETL, Java</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>RevSpring, Inc</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, API Gateway, RDS, Azure, Google Cloud Platform, Scala, Kafka, Splunk</t>
+          <t>Redshift, S3, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop, Scala</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=427f6933d7d21e16</t>
+          <t>https://www.indeed.com/viewjob?jk=ec9899d266d7f4ea</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Java API Integration Engineer</t>
+          <t>Databricks Engineer and Architect</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Lincoln Financial Group</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Radnor, PA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, API Gateway, RDS, Azure, Google Cloud Platform, Scala, Kafka, Splunk</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, RDS, Databricks, Unity Catalog</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78afcf5aa1e7fc4b</t>
+          <t>https://www.indeed.com/viewjob?jk=d7862c3c59e06d56</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Sr Site Reliability Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Commence</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Leesburg, VA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,29 +1256,29 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, NoSQL, ETL, ELT</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, RDS, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9093ede7f2269db2</t>
+          <t>https://www.indeed.com/viewjob?jk=df1902d36083d34f</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Sr Data Engineer, Python + Spark (Data Federation skillset - Data Lakehouse - Eg: Starburst) - New York</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Photon</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1291,29 +1291,29 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, S3, Azure, Databricks, Medallion Architecture, GCP, Spark, PySpark</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, RDS, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7767a92d7d08a3b</t>
+          <t>https://www.indeed.com/viewjob?jk=5cb867686433b7a1</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - ETL, Java</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>RevSpring, Inc</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1326,34 +1326,34 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Redshift, S3, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop, Scala</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, RDS, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a9c009a05948507</t>
+          <t>https://www.indeed.com/viewjob?jk=3aeafc948a2f0f6c</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - ETL, Java</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>RevSpring, Inc</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,34 +1361,34 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Redshift, S3, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop, Scala</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, RDS, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba5ba3f3a840901f</t>
+          <t>https://www.indeed.com/viewjob?jk=c45b322f3e5694ad</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - ETL, Java</t>
+          <t>Software Engineer Intern</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>RevSpring, Inc</t>
+          <t>Norstella</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Redshift, S3, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop, Scala</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Azure, Blob Storage, GCP, PostgreSQL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec9899d266d7f4ea</t>
+          <t>https://www.indeed.com/viewjob?jk=49a129c7a487aae4</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>DevOps Engineer (GCP)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Verisk</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark</t>
+          <t>AWS, Glue, Lambda, Athena, S3, RDS, Spark, Scala, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d617836814bb437</t>
+          <t>https://www.indeed.com/viewjob?jk=cb57edcbdb36ad26</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Junior GCP Cloud Engineer</t>
+          <t>MLOps Engineer – Azure Databricks, Cloud-to-Edge ML Deployment</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>KPIT Technologies</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Data Modeling, Kimball</t>
+          <t>Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,112 +1476,112 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11aa4a83b27dbdc6</t>
+          <t>https://www.indeed.com/viewjob?jk=1160b6a5ea3d30ad</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Databricks Engineer and Architect</t>
+          <t>API Threat Intelligence Analyst</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Lincoln Financial Group</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Radnor, PA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, RDS, Databricks, Unity Catalog</t>
+          <t>Azure, Google Cloud Platform, Kafka, NoSQL, Data Modeling, ETL, Talend, Tableau, Splunk, MicroStrategy</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7862c3c59e06d56</t>
+          <t>https://www.indeed.com/viewjob?jk=e918fa70b2a1920e</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Software Engineer Intern</t>
+          <t>Backend (Python)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Norstella</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Azure, Blob Storage, GCP, PostgreSQL</t>
+          <t>Azure, Google Cloud Platform, Kafka, NoSQL, Data Modeling, ETL, Talend, Tableau, Splunk, MicroStrategy</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49a129c7a487aae4</t>
+          <t>https://www.indeed.com/viewjob?jk=d711bd4394cb404e</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Netsecure360</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>16</v>
+        <v>14.6</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, RDS, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Cloud Storage, Hadoop, Hive, Spark, Scala, Kafka, Oracle</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df1902d36083d34f</t>
+          <t>https://www.indeed.com/viewjob?jk=ca7e816524d9406c</t>
         </is>
       </c>
     </row>
@@ -1593,30 +1593,30 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Metropolis</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>16</v>
+        <v>14.6</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, RDS, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, Glue, SNS, RDS, Spark, PySpark, Scala, Snowflake, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cb867686433b7a1</t>
+          <t>https://www.indeed.com/viewjob?jk=b9fd5c209c01d504</t>
         </is>
       </c>
     </row>
@@ -1628,90 +1628,90 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>metropolis</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>16</v>
+        <v>14.6</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, RDS, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, Glue, SNS, RDS, Spark, PySpark, Scala, Snowflake, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3aeafc948a2f0f6c</t>
+          <t>https://www.indeed.com/viewjob?jk=d51453a1afa374b4</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Engineer (Databricks)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Infinitive Inc</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Ashburn, VA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>16</v>
+        <v>14.6</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, RDS, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, S3, Azure, Databricks, Unity Catalog, GCP</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c45b322f3e5694ad</t>
+          <t>https://www.indeed.com/viewjob?jk=aee5e62267dbbb6c</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Junior GCP Cloud Engineer</t>
+          <t>Software Engineer – ETL, Java</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>RevSpring, Inc</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>16</v>
+        <v>14.6</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Azure, Google Cloud Platform, GCP, Kafka, NoSQL, Data Modeling, ETL, Talend, Tableau, Splunk</t>
+          <t>Redshift, S3, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop, Scala</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,32 +1721,32 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3e7636193fed6ce</t>
+          <t>https://www.indeed.com/viewjob?jk=3ebdf3dd92985403</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer – ETL, Java</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Verisk</t>
+          <t>RevSpring, Inc</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, S3, RDS, Spark, Scala, PostgreSQL, Data Modeling</t>
+          <t>Redshift, S3, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop, Scala</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,67 +1756,67 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb57edcbdb36ad26</t>
+          <t>https://www.indeed.com/viewjob?jk=5c4b1e40555df27f</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer – ETL, Java</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>RevSpring, Inc</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka</t>
+          <t>Redshift, S3, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop, Scala</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f544b0c492f55ad5</t>
+          <t>https://www.indeed.com/viewjob?jk=9d1957e3729d8614</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>MLOps Engineer – Azure Databricks, Cloud-to-Edge ML Deployment</t>
+          <t>Computing Architect 4 (contract)</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>KPIT Technologies</t>
+          <t>Boeing</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, MLOps, MLflow, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Scala, Kafka, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,67 +1826,67 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1160b6a5ea3d30ad</t>
+          <t>https://www.indeed.com/viewjob?jk=83fa749fc70ff9b5</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Cloud Reliability Engineer</t>
+          <t>Software Developer II</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Floor &amp; Decor</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Spark, Scala, NoSQL, Data Modeling, MLOps</t>
+          <t>RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eae9d6ab07ed0b94</t>
+          <t>https://www.indeed.com/viewjob?jk=4a21fec712255df2</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>DevOps/AI Ops Administrator</t>
+          <t>Sr. Streaming Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Ness Digital Engineering</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Event Hubs, Dataflow, Scala, Snowflake, PostgreSQL, Power BI, CI/CD</t>
+          <t>AWS, Kinesis, S3, IAM, RDS, Spark, Scala, Kafka, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,32 +1896,32 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8de348813177f92b</t>
+          <t>https://www.indeed.com/viewjob?jk=f90fa0ab3164dcd1</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>API Threat Intelligence Analyst</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>SOFTILITY INC</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Azure, Google Cloud Platform, Kafka, NoSQL, Data Modeling, ETL, Talend, Tableau, Splunk, MicroStrategy</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,32 +1931,32 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e918fa70b2a1920e</t>
+          <t>https://www.indeed.com/viewjob?jk=3faf69463891ca3f</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Backend (Python)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Azure, Google Cloud Platform, Kafka, NoSQL, Data Modeling, ETL, Talend, Tableau, Splunk, MicroStrategy</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Oracle, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,102 +1966,102 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d711bd4394cb404e</t>
+          <t>https://www.indeed.com/viewjob?jk=d61e7d7639acc074</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Development Engineer - Cloud Dev</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Netsecure360</t>
+          <t>Transmedics</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Andover, MA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Cloud Storage, Hadoop, Hive, Spark, Scala, Kafka, Oracle</t>
+          <t>AWS, Lambda, Kinesis, Redshift, Step Functions, S3, SQS, SNS, API Gateway, IAM</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca7e816524d9406c</t>
+          <t>https://www.indeed.com/viewjob?jk=2efe7bed588da272</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>MLOps Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Metropolis</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Glue, SNS, RDS, Spark, PySpark, Scala, Snowflake, SQL Server, MySQL</t>
+          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9fd5c209c01d504</t>
+          <t>https://www.indeed.com/viewjob?jk=56f1aa48ba26ae3c</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Business Intelligence Developer (Healthcare Data, EDI, ETL)</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>metropolis</t>
+          <t>MicroHealth LLC</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Vienna, VA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Glue, SNS, RDS, Spark, PySpark, Scala, Snowflake, SQL Server, MySQL</t>
+          <t>AWS, EMR, RDS, Scala, Snowflake, SQL Server, PostgreSQL, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,102 +2071,102 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d51453a1afa374b4</t>
+          <t>https://www.indeed.com/viewjob?jk=3ba3d7e28ab6494c</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Cloud Migration Engineer (GCP)</t>
+          <t>Mid- Level Data Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Vantage Data Centers</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, Snowflake, SQL Server</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Spark, PySpark, Scala, Data Modeling, Dimension Tables, ETL</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb7efc81616340cd</t>
+          <t>https://www.indeed.com/viewjob?jk=a35201e2c76024aa</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Databricks)</t>
+          <t>Senior Site Reliability Engineer, Data &amp; Analytics</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Infinitive Inc</t>
+          <t>Blizzard Entertainment</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, S3, Azure, Databricks, Unity Catalog, GCP</t>
+          <t>AWS, RDS, GCP, BigQuery, Dataflow, Kafka, dbt, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aee5e62267dbbb6c</t>
+          <t>https://www.indeed.com/viewjob?jk=f56eabb97941a731</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Software Engineer – ETL, Java</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>RevSpring, Inc</t>
+          <t>Kroll Inc.</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Redshift, S3, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop, Scala</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Scala, Polars, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,67 +2176,67 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ebdf3dd92985403</t>
+          <t>https://www.indeed.com/viewjob?jk=d56048c057634cd1</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Software Engineer – ETL, Java</t>
+          <t>Cloud Network Architect</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>RevSpring, Inc</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Redshift, S3, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop, Scala</t>
+          <t>API Gateway, IAM, RDS, Google Cloud Platform, BigQuery, Dataflow, Scala, Kafka, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c4b1e40555df27f</t>
+          <t>https://www.indeed.com/viewjob?jk=3552e9ee02097f2c</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Software Engineer – ETL, Java</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>RevSpring, Inc</t>
+          <t>Miami Marlins</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>14.6</v>
+        <v>12.5</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Redshift, S3, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop, Scala</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, GCP, Scala, Snowflake, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d1957e3729d8614</t>
+          <t>https://www.indeed.com/viewjob?jk=ff87deef607d5450</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Computing Architect 4 (contract)</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Boeing</t>
+          <t>Paramount</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Fort Lauderdale, FL, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>14.6</v>
+        <v>12.5</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Scala, Kafka, Data Modeling, ELT</t>
+          <t>AWS, RDS, GCP, BigQuery, Dataflow, Scala, MongoDB, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,19 +2281,19 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83fa749fc70ff9b5</t>
+          <t>https://www.indeed.com/viewjob?jk=a12925c69dfc7bed</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Software Developer II</t>
+          <t>AI Agent Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Floor &amp; Decor</t>
+          <t>Momentive Software</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2302,46 +2302,46 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>14.6</v>
+        <v>12.5</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL, Splunk, CI/CD</t>
+          <t>AWS, Lambda, Athena, SQS, SNS, API Gateway, ECS, RDS, Azure, GCP</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a21fec712255df2</t>
+          <t>https://www.indeed.com/viewjob?jk=6ac9574b3f75cc2c</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Azure Network Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>MarketAxess Holdings</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>14.6</v>
+        <v>12.5</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Athena, Step Functions, S3, ECS, IAM, RDS, Kafka, Polars, CI/CD</t>
+          <t>IAM, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage, MySQL, Splunk, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,77 +2351,77 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e88c480437dd451</t>
+          <t>https://www.indeed.com/viewjob?jk=8bb3e3385b26a0b5</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Sr. Streaming Engineer</t>
+          <t>Senior Software Engineer - Cloud Gateway</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Ness Digital Engineering</t>
+          <t>Rivian and Volkswagen Group Technologies</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, IAM, RDS, Spark, Scala, Kafka, NoSQL, Splunk</t>
+          <t>AWS, RDS, Scala, Kafka, MongoDB, DynamoDB, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f90fa0ab3164dcd1</t>
+          <t>https://www.indeed.com/viewjob?jk=7b72e865e6bee153</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Senior Cloud Database Engineer (Hybrid - Seattle, WA)</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>SOFTILITY INC</t>
+          <t>Nordstrom</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD</t>
+          <t>AWS, Glue, Kinesis, Redshift, Athena, S3, RDS, Kafka, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3faf69463891ca3f</t>
+          <t>https://www.indeed.com/viewjob?jk=1666a61865ef57aa</t>
         </is>
       </c>
     </row>
@@ -2433,55 +2433,55 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Moore</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Westminster, CO, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Oracle, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d61e7d7639acc074</t>
+          <t>https://www.indeed.com/viewjob?jk=b8c5af154805cd95</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer - Cloud Dev</t>
+          <t>Data Engineer (ETL / Python Developer)</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Transmedics</t>
+          <t>CSpring</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Andover, MA, US USA</t>
+          <t>Springfield, IL, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, Redshift, Step Functions, S3, SQS, SNS, API Gateway, IAM</t>
+          <t>Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,32 +2491,32 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2efe7bed588da272</t>
+          <t>https://www.indeed.com/viewjob?jk=b861e2c1a0a03133</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Cloud Service Desk Analyst</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Imprint</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, Azure, Scala, CI/CD, GitHub Actions, Terraform</t>
+          <t>Kinesis, S3, RDS, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,67 +2526,67 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e883ce8f9ac322fb</t>
+          <t>https://www.indeed.com/viewjob?jk=e35bafcce4ab1000</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior ServiceNow Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Global Enterprise Systems</t>
+          <t>Imprint</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Jenkins</t>
+          <t>Kinesis, S3, RDS, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c766bb333faacdc</t>
+          <t>https://www.indeed.com/viewjob?jk=baaf38c4500e2b06</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Junior Cloud Security Analyst</t>
+          <t>Senior AI Data Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Velvetech</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Databricks, Blob Storage, Unity Catalog, Google Cloud Platform, Spark</t>
+          <t>AWS, IAM, Azure, GCP, Vertex AI, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,14 +2596,14 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb95dfff70e6d2a4</t>
+          <t>https://www.indeed.com/viewjob?jk=2bec7882b34f08c9</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>MLOps Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2613,50 +2613,50 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Westminster, CO, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56f1aa48ba26ae3c</t>
+          <t>https://www.indeed.com/viewjob?jk=d49164a52434e329</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Business Intelligence Developer (Healthcare Data, EDI, ETL)</t>
+          <t>AWS Data Engineer - Databricks</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>MicroHealth LLC</t>
+          <t>RadCube</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Vienna, VA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Scala, Snowflake, SQL Server, PostgreSQL, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Databricks, Scala, Databricks Lakehouse, Data Modeling</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,277 +2666,277 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ba3d7e28ab6494c</t>
+          <t>https://www.indeed.com/viewjob?jk=d2dcfccb6b6d90b1</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Databricks Developer</t>
+          <t>Software Engineer - Cloud</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Sloan</t>
+          <t>Carnegie Robotics LLC</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Franklin Park, IL, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, PostgreSQL, MongoDB, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9921503eb16c8225</t>
+          <t>https://www.indeed.com/viewjob?jk=e2f5b0b9c556cdca</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Software Engineer - Specialist</t>
+          <t>Senior Data Engineer (Python/PySpark/AWS)</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Infinitive Inc</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Ashburn, VA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, SQL Server, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, Azure, Spark, PySpark, Scala, Spark Streaming, Data Modeling, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2025-02-18</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=932c71a7f13aa9a1</t>
+          <t>https://www.indeed.com/viewjob?jk=45083db400feff94</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>GCP ETL Engineer</t>
+          <t>Data Engineer (Python/PySpark/AWS)</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Infinitive Inc</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Ashburn, VA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Hadoop, Spark, Kafka, Snowflake, Dimensional Modeling, ETL, Talend</t>
+          <t>AWS, Azure, Spark, PySpark, Scala, Spark Streaming, Data Modeling, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2025-01-27</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5268867584b4379</t>
+          <t>https://www.indeed.com/viewjob?jk=5e742c4bedd2037b</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer, Data &amp; Analytics</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Blizzard Entertainment</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Dataflow, Kafka, dbt, CI/CD, Jenkins, GitHub Actions</t>
+          <t>IAM, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage, MySQL, Splunk, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f56eabb97941a731</t>
+          <t>https://www.indeed.com/viewjob?jk=52b0e598b9832c43</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Kroll Inc.</t>
+          <t>Terra Quantum</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Scala, Polars, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d56048c057634cd1</t>
+          <t>https://www.indeed.com/viewjob?jk=15eb90498bcba242</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Cloud Fullstack</t>
+          <t>Full Stack Engineer, Experienced</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Rivian and Volkswagen Group Technologies</t>
+          <t>Blue Shield of California</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, MongoDB, DynamoDB, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=059fe198bd3f948a</t>
+          <t>https://www.indeed.com/viewjob?jk=93fe5a9749607800</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>FastAPI</t>
+          <t>Full Stack Engineer, Senior</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Blue Shield of California</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, PostgreSQL, DynamoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=550e29553f2a099b</t>
+          <t>https://www.indeed.com/viewjob?jk=bcc6fa1baccf83e5</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>GCP Support Associate</t>
+          <t>Full Stack Engineer, Consultant</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Blue Shield of California</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, MySQL, Splunk, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29c27657463cb6ea</t>
+          <t>https://www.indeed.com/viewjob?jk=a3a7d3c5d7336760</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Summer Intern, Platform Engineering</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Miami Marlins</t>
+          <t>Outfront Media</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, GCP, Scala, Snowflake, CI/CD, GitHub Actions</t>
+          <t>AWS, Lambda, S3, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff87deef607d5450</t>
+          <t>https://www.indeed.com/viewjob?jk=2aa35bb9483f10ad</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Artificial Intelligence/Machine Learning Data Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Paramount</t>
+          <t>Accenture</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Fort Lauderdale, FL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,34 +3006,34 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Dataflow, Scala, MongoDB, NoSQL, Docker, Kubernetes</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLflow</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a12925c69dfc7bed</t>
+          <t>https://www.indeed.com/viewjob?jk=b20f553bf3557e7a</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>AI Agent Engineer</t>
+          <t>Customer Centric Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Momentive Software</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Athena, SQS, SNS, API Gateway, ECS, RDS, Azure, GCP</t>
+          <t>AWS, Azure, GCP, BigQuery, Scala, Snowflake, ELT, dbt, Tableau, Docker</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,67 +3051,67 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ac9574b3f75cc2c</t>
+          <t>https://www.indeed.com/viewjob?jk=29a2186b968dd17c</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Cloud Gateway</t>
+          <t>Mid-Level Software Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Rivian and Volkswagen Group Technologies</t>
+          <t>State Farm</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Bloomington, IL, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, MongoDB, DynamoDB, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, MongoDB, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b72e865e6bee153</t>
+          <t>https://www.indeed.com/viewjob?jk=da08c5cf76c3287c</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Cloud Database Engineer (Hybrid - Seattle, WA)</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Nordstrom</t>
+          <t>Versant</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Redshift, Athena, S3, RDS, Kafka, Oracle, SQL Server</t>
+          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, GCP, Spark, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,32 +3121,32 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1666a61865ef57aa</t>
+          <t>https://www.indeed.com/viewjob?jk=1fbef82ce93a90ed</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI/ML Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Moore</t>
+          <t>Redapt inc</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Westminster, CO, US USA</t>
+          <t>Woodinville, WA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT, dbt</t>
+          <t>AWS, Redshift, Azure, Databricks, GCP, Vertex AI, Spark, Snowflake, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,102 +3156,102 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8c5af154805cd95</t>
+          <t>https://www.indeed.com/viewjob?jk=b9c94059f3dd29b3</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Data Engineer (ETL / Python Developer)</t>
+          <t>Cloud Network Architect</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>CSpring</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Springfield, IL, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Data Modeling</t>
+          <t>Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b861e2c1a0a03133</t>
+          <t>https://www.indeed.com/viewjob?jk=e874dfda20060e92</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Azure Network Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Imprint</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Kinesis, S3, RDS, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Event Hubs, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e35bafcce4ab1000</t>
+          <t>https://www.indeed.com/viewjob?jk=05dcb2c14af656a8</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Imprint</t>
+          <t>Clayco</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Kinesis, S3, RDS, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,32 +3261,32 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=baaf38c4500e2b06</t>
+          <t>https://www.indeed.com/viewjob?jk=61cc49187bd6e01d</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior AI Data Engineer</t>
+          <t>Data Engineering - E&amp;A - Data Engineer I</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Velvetech</t>
+          <t>Genesis Global Group</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Myrtle Point, OR, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Vertex AI, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD</t>
+          <t>Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,32 +3296,32 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2bec7882b34f08c9</t>
+          <t>https://www.indeed.com/viewjob?jk=2526bf14df16c3e8</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior, Data Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Carrington Mortgage Services, LLC</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Westminster, CO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, ETL, Microsoft SSIS</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,67 +3331,67 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d49164a52434e329</t>
+          <t>https://www.indeed.com/viewjob?jk=dfdf1b9d489fb8ec</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>AWS Data Engineer - Databricks</t>
+          <t>Data Systems Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>RadCube</t>
+          <t>Central Health</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Databricks, Scala, Databricks Lakehouse, Data Modeling</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2dcfccb6b6d90b1</t>
+          <t>https://www.indeed.com/viewjob?jk=41eed22913274d81</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Software Engineer - Cloud</t>
+          <t>Full Stack Data Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Carnegie Robotics LLC</t>
+          <t>Millennium Management</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, PostgreSQL, MongoDB, DynamoDB, NoSQL</t>
+          <t>AWS, RDS, Scala, Snowflake, NoSQL, ELT, dbt, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,102 +3401,102 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2f5b0b9c556cdca</t>
+          <t>https://www.indeed.com/viewjob?jk=b224fb124b25e580</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Python/PySpark/AWS)</t>
+          <t>Senior DevOps Software Engineer, Firmware &amp; CI/CD</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Infinitive Inc</t>
+          <t>Rivian and Volkswagen Group Technologies</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, Azure, Spark, PySpark, Scala, Spark Streaming, Data Modeling, ETL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2025-02-18</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45083db400feff94</t>
+          <t>https://www.indeed.com/viewjob?jk=d5f621c8ad4f69fd</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Data Engineer (Python/PySpark/AWS)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Infinitive Inc</t>
+          <t>Victory Live</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, Azure, Spark, PySpark, Scala, Spark Streaming, Data Modeling, ETL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Data Factory, Snowflake, SQL Server, DynamoDB, ELT, dbt, Terraform</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2025-01-27</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e742c4bedd2037b</t>
+          <t>https://www.indeed.com/viewjob?jk=a1c259f0b00d1299</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Python)</t>
+          <t>Snowflake/Tableau Developer / Dallas Texas</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>FirstNet Global</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Napa, CA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, MapReduce, Impala, Spark, PySpark, Oracle, SQL Server, MySQL</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,32 +3506,32 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45974a79c5dfc2f4</t>
+          <t>https://www.indeed.com/viewjob?jk=a4ab4d99e440e9b4</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Klaxontech</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage, MySQL, Splunk, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,32 +3541,32 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52b0e598b9832c43</t>
+          <t>https://www.indeed.com/viewjob?jk=193935f590ab7020</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Cloud Networking Consultant</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Terra Quantum</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>KS, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>RDS, Spark, Scala, Kafka, Snowflake, Splunk, CI/CD, Jenkins, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,67 +3576,67 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15eb90498bcba242</t>
+          <t>https://www.indeed.com/viewjob?jk=05bc8504be04f7d2</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Full Stack Engineer, Experienced</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Blue Shield of California</t>
+          <t>Montefiore Einstein</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Yonkers, NY, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, NoSQL, CI/CD, Terraform</t>
+          <t>AWS, RDS, Medallion Architecture, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ELT, dbt</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93fe5a9749607800</t>
+          <t>https://www.indeed.com/viewjob?jk=2d972b31a0cae529</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Full Stack Engineer, Senior</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Blue Shield of California</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, NoSQL, CI/CD, Terraform</t>
+          <t>RDS, GCP, BigQuery, Dataflow, Vertex AI, Scala, Data Modeling, Jenkins, Terraform, Jenkins</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,32 +3646,32 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bcc6fa1baccf83e5</t>
+          <t>https://www.indeed.com/viewjob?jk=4bbf23a169f18dbc</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Full Stack Engineer, Consultant</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Blue Shield of California</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, NoSQL, CI/CD, Terraform</t>
+          <t>RDS, GCP, BigQuery, Dataflow, Vertex AI, Scala, Data Modeling, Jenkins, Terraform, Jenkins</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,32 +3681,32 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3a7d3c5d7336760</t>
+          <t>https://www.indeed.com/viewjob?jk=4b05514433681d42</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Summer Intern, Platform Engineering</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Outfront Media</t>
+          <t>Clark Construction</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD, Docker</t>
+          <t>AWS, Azure, GCP, Spark, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, dbt</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,67 +3716,67 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2aa35bb9483f10ad</t>
+          <t>https://www.indeed.com/viewjob?jk=6f199bfc2e975b58</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Java Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=257d265c3f7e2882</t>
+          <t>https://www.indeed.com/viewjob?jk=c98f634775f326c6</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Customer Centric Engineer</t>
+          <t>Sr. Professional, Software Engineering (Python)</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Cotality</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Scala, Snowflake, ELT, dbt, Tableau, Docker</t>
+          <t>RDS, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, Tableau, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,32 +3786,32 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29a2186b968dd17c</t>
+          <t>https://www.indeed.com/viewjob?jk=83e013cc49a29087</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Mid-Level Software Engineer</t>
+          <t>Senior Platform/DevOps Engineer (Kubernetes-Linux)</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>State Farm</t>
+          <t>ARMADA</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Bloomington, IL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, MongoDB, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,32 +3821,32 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da08c5cf76c3287c</t>
+          <t>https://www.indeed.com/viewjob?jk=7b0e9b75e0f5558d</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Senior Platform/DevOps Engineer (Kubernetes-Linux)</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Versant</t>
+          <t>ARMADA</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Sammamish, WA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, GCP, Spark, NoSQL, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,32 +3856,32 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fbef82ce93a90ed</t>
+          <t>https://www.indeed.com/viewjob?jk=efa4e4e3099a0ae2</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>AI/ML Engineer</t>
+          <t>Senior Platform/DevOps Engineer (Kubernetes-Linux)</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Redapt inc</t>
+          <t>ARMADA</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Woodinville, WA, US USA</t>
+          <t>Kirkland, WA, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, GCP, Vertex AI, Spark, Snowflake, Data Modeling, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,32 +3891,32 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9c94059f3dd29b3</t>
+          <t>https://www.indeed.com/viewjob?jk=33ae1f1f9d08c546</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Senior Platform/DevOps Engineer (Kubernetes-Linux)</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Clayco</t>
+          <t>ARMADA</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Renton, WA, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,32 +3926,32 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61cc49187bd6e01d</t>
+          <t>https://www.indeed.com/viewjob?jk=d25130b996402485</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Data Engineering - E&amp;A - Data Engineer I</t>
+          <t>Senior Platform/DevOps Engineer (Kubernetes-Linux)</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Genesis Global Group</t>
+          <t>ARMADA</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Myrtle Point, OR, US USA</t>
+          <t>Bothell, WA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,32 +3961,32 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2526bf14df16c3e8</t>
+          <t>https://www.indeed.com/viewjob?jk=b6f9224460f3210c</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Senior, Data Engineer</t>
+          <t>Senior Platform/DevOps Engineer (Kubernetes-Linux)</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Carrington Mortgage Services, LLC</t>
+          <t>ARMADA</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Redmond, WA, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, ETL, Microsoft SSIS</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,32 +3996,32 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfdf1b9d489fb8ec</t>
+          <t>https://www.indeed.com/viewjob?jk=b86c940f686047d8</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>GCP Support Associate</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Somerville, MA, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>ECS, IAM, Google Cloud Platform, GCP, Dataflow, Cloud Storage, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>Redshift, RDS, Azure, Scala, Snowflake, ETL, ELT, dbt, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,102 +4031,102 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9acaddb632586c1</t>
+          <t>https://www.indeed.com/viewjob?jk=75339d7552c524c1</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Data Systems Engineer</t>
+          <t>Sr. Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Central Health</t>
+          <t>PitchBook</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, RDS, GCP, Scala, SQL Server, PostgreSQL, MySQL, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41eed22913274d81</t>
+          <t>https://www.indeed.com/viewjob?jk=181ce2100b853c3a</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Full Stack Data Engineer</t>
+          <t>Google Cloud Network Engineer</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Millennium Management</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, NoSQL, ELT, dbt, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b224fb124b25e580</t>
+          <t>https://www.indeed.com/viewjob?jk=c8d74c6d08304ab9</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Sr Database Administrator</t>
+          <t>DOCSIS Testing Engineer</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Atlantic Union Bank</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Glen Allen, VA, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Scala, Oracle, MongoDB, Splunk, CI/CD, Jenkins, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,32 +4136,32 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fadd8b2210e032b2</t>
+          <t>https://www.indeed.com/viewjob?jk=3102561596c9491c</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>FastAPI</t>
+          <t>Software Engineer - DevOps Mobile</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, Glue, ECS, IAM, RDS, Spark, PySpark, Scala, MLOps, CI/CD</t>
+          <t>AWS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Maven, Terraform, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,67 +4171,67 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36490e4938cafc8b</t>
+          <t>https://www.indeed.com/viewjob?jk=537b207b8aaf9dd0</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Senior DevOps Software Engineer, Firmware &amp; CI/CD</t>
+          <t>Software Engineer - Warehouse Management Systems (WMS)</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Rivian and Volkswagen Group Technologies</t>
+          <t>Staples</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Framingham, MA, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, HBase, Scala, Kafka, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5f621c8ad4f69fd</t>
+          <t>https://www.indeed.com/viewjob?jk=654753ccda866d62</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>AI Systems Administrator</t>
+          <t>Sr. Data Architect Specialist</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>SAMYANG AMERICA INC</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Brea, CA, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>ECS, RDS, Azure, Databricks, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,19 +4241,19 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a338fa1fa96ea390</t>
+          <t>https://www.indeed.com/viewjob?jk=f2086e3e44cfc021</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Full Stack Product Engineer (Java)</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Victory Live</t>
+          <t>Allstate Insurance</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -4262,11 +4262,11 @@
         </is>
       </c>
       <c r="D110" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Snowflake, SQL Server, DynamoDB, ELT, dbt, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, ELT, CI/CD, Git</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,54 +4276,54 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1c259f0b00d1299</t>
+          <t>https://www.indeed.com/viewjob?jk=d15adff582efc740</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Snowflake/Tableau Developer / Dallas Texas</t>
+          <t>DevOps &amp; Infrastructure Engineer - Level I</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>FirstNet Global</t>
+          <t>SPRING ARBOR UNIVERSITY</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Napa, CA, US USA</t>
+          <t>Spring Arbor, MI, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Azure, GCP, Scala, Oracle, CI/CD, Jenkins, GitHub Actions, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4ab4d99e440e9b4</t>
+          <t>https://www.indeed.com/viewjob?jk=b0b216de71eb3804</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Software Engineer – Enterprise Software</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Klaxontech</t>
+          <t>Rivian</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -4332,38 +4332,38 @@
         </is>
       </c>
       <c r="D112" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MySQL, NoSQL, Splunk, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=193935f590ab7020</t>
+          <t>https://www.indeed.com/viewjob?jk=90124173401e2437</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Software Engineer, Enterprise Technology</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Rivian</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,34 +4371,34 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Vertex AI, Scala, Data Modeling, Jenkins, Terraform, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MySQL, NoSQL, Splunk, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bbf23a169f18dbc</t>
+          <t>https://www.indeed.com/viewjob?jk=fab081dda06a1ba5</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,34 +4406,34 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Vertex AI, Scala, Data Modeling, Jenkins, Terraform, Jenkins</t>
+          <t>AWS, S3, IAM, Databricks, Spark, Scala, DynamoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b05514433681d42</t>
+          <t>https://www.indeed.com/viewjob?jk=6f9ad7c8c6b989c1</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>QA Analyst / ETL Tester</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Clark Construction</t>
+          <t>CSpring</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Springfield, IL, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, dbt</t>
+          <t>RDS, Azure, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Data Modeling, Snowflake Schema, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,67 +4451,67 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f199bfc2e975b58</t>
+          <t>https://www.indeed.com/viewjob?jk=1ebf7b3987a302e8</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Junior GCP Cloud Engineer</t>
+          <t>Senior Full Stack Engineer - Python &amp; React JS</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Checkmate</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, Dataflow, Cloud Storage, Scala, Oracle, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Scala, PostgreSQL, MySQL, CI/CD, GitHub Actions, Docker, Git, Datadog</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=817a2d7d06f177a9</t>
+          <t>https://www.indeed.com/viewjob?jk=6ba3d00c3fb0ee25</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Sr. Professional, Software Engineering (Python)</t>
+          <t>Engineer II-Software Development</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Cotality</t>
+          <t>Microchip Technology</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, Tableau, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,32 +4521,32 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83e013cc49a29087</t>
+          <t>https://www.indeed.com/viewjob?jk=3013681a0e1c4f81</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Senior Platform/DevOps Engineer (Kubernetes-Linux)</t>
+          <t>Engineer II-Software Development</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>ARMADA</t>
+          <t>Microchip Technology</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4556,32 +4556,32 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b0e9b75e0f5558d</t>
+          <t>https://www.indeed.com/viewjob?jk=2649d75a044fe7bd</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Senior Platform/DevOps Engineer (Kubernetes-Linux)</t>
+          <t>Senior Software Engineer - VAULT</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>ARMADA</t>
+          <t>Bloomberg</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Sammamish, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, S3, RDS, Azure, GCP, Hive, Spark, Scala, Kafka, Cassandra</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,32 +4591,32 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=efa4e4e3099a0ae2</t>
+          <t>https://www.indeed.com/viewjob?jk=1d744cfcd1fce896</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Senior Platform/DevOps Engineer (Kubernetes-Linux)</t>
+          <t>BigData ,Python and Py Spark , GCP</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>ARMADA</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Kirkland, WA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>GCP, BigQuery, Hadoop, Hive, Spark, PySpark, Scala, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,102 +4626,102 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33ae1f1f9d08c546</t>
+          <t>https://www.indeed.com/viewjob?jk=81999129979e18ac</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Senior Platform/DevOps Engineer (Kubernetes-Linux)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>ARMADA</t>
+          <t>Montefiore Einstein</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Renton, WA, US USA</t>
+          <t>Yonkers, NY, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, S3, RDS, Scala, Snowflake, Data Modeling, ELT, dbt, CI/CD, Git</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d25130b996402485</t>
+          <t>https://www.indeed.com/viewjob?jk=9a3ffcafc747cce2</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Senior Platform/DevOps Engineer (Kubernetes-Linux)</t>
+          <t>FastAPI</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>ARMADA</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Bothell, WA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Google Cloud Platform, BigQuery, Vertex AI, Spark, Scala, Spark Streaming, Kafka, CI/CD, Git</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6f9224460f3210c</t>
+          <t>https://www.indeed.com/viewjob?jk=0bc1141188a8604a</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Senior Platform/DevOps Engineer (Kubernetes-Linux)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>ARMADA</t>
+          <t>Urology Centers of Alabama</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Redmond, WA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, EMR, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, ETL</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4731,32 +4731,32 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b86c940f686047d8</t>
+          <t>https://www.indeed.com/viewjob?jk=28cb24ea6139fcb9</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Pearson</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Somerville, MA, US USA</t>
+          <t>Hoboken, NJ, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Scala, Snowflake, ETL, ELT, dbt, Tableau, CI/CD</t>
+          <t>AWS, RDS, Scala, MongoDB, DynamoDB, Data Modeling, ETL, ELT, DataOps, CI/CD</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4766,19 +4766,19 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75339d7552c524c1</t>
+          <t>https://www.indeed.com/viewjob?jk=05547d65aabdfcf0</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Sr. Site Reliability Engineer</t>
+          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>PitchBook</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -4787,11 +4787,11 @@
         </is>
       </c>
       <c r="D125" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, SQL Server, PostgreSQL, MySQL, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -4801,32 +4801,32 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=181ce2100b853c3a</t>
+          <t>https://www.indeed.com/viewjob?jk=34c37a226b547d01</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Senior Data Engineer / Data Architect</t>
+          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4836,67 +4836,67 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e83d1768e75b1203</t>
+          <t>https://www.indeed.com/viewjob?jk=e7d77afce6f60e6f</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>API Architect (Python)</t>
+          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, MLOps, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=460c6fea55fa6849</t>
+          <t>https://www.indeed.com/viewjob?jk=225c5a8131dc6595</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Software Engineer - Warehouse Management Systems (WMS)</t>
+          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Staples</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Framingham, MA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, HBase, Scala, Kafka, NoSQL, CI/CD, Docker</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -4906,67 +4906,67 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=654753ccda866d62</t>
+          <t>https://www.indeed.com/viewjob?jk=301dbd1e2eb0bb70</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Databricks, Spark, Scala, DynamoDB, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f9ad7c8c6b989c1</t>
+          <t>https://www.indeed.com/viewjob?jk=d88e7121c2db79d6</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Sr. Data Architect Specialist</t>
+          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>SAMYANG AMERICA INC</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Brea, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -4976,32 +4976,32 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2086e3e44cfc021</t>
+          <t>https://www.indeed.com/viewjob?jk=18d3f9fdcfa07035</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Senior GCP IAM Engineer</t>
+          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Kafka, Snowflake</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -5011,67 +5011,67 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e01ee86f0306e6c</t>
+          <t>https://www.indeed.com/viewjob?jk=9d2d16258cfd6718</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Software Engineer - DevOps Mobile</t>
+          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Maven, Terraform, Docker, Jenkins</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=537b207b8aaf9dd0</t>
+          <t>https://www.indeed.com/viewjob?jk=5be8f9b4535b406c</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Full Stack Product Engineer (Java)</t>
+          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Allstate Insurance</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, ELT, CI/CD, Git</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -5081,32 +5081,32 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d15adff582efc740</t>
+          <t>https://www.indeed.com/viewjob?jk=26ef52c65261360a</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>DevOps &amp; Infrastructure Engineer - Level I</t>
+          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>SPRING ARBOR UNIVERSITY</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Spring Arbor, MI, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Oracle, CI/CD, Jenkins, GitHub Actions, Docker, Jenkins</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -5116,32 +5116,32 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0b216de71eb3804</t>
+          <t>https://www.indeed.com/viewjob?jk=f9240b7b96545a4d</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Senior GCP Kubernetes Engineer</t>
+          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Kafka, Oracle, PostgreSQL, CI/CD, Jenkins, Maven</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -5151,102 +5151,102 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a77679969db6e94b</t>
+          <t>https://www.indeed.com/viewjob?jk=42ae72f7d4a97700</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Software Engineer – Enterprise Software</t>
+          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Rivian</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MySQL, NoSQL, Splunk, Docker, Kubernetes</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90124173401e2437</t>
+          <t>https://www.indeed.com/viewjob?jk=dab5b1b68cc6402c</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer, Enterprise Technology</t>
+          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Rivian</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MySQL, NoSQL, Splunk, Docker, Kubernetes</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fab081dda06a1ba5</t>
+          <t>https://www.indeed.com/viewjob?jk=fde8d1831ca7f9b7</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>QA Analyst / ETL Tester</t>
+          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>CSpring</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Springfield, IL, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>RDS, Azure, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Data Modeling, Snowflake Schema, ETL, CI/CD</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -5256,24 +5256,24 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ebf7b3987a302e8</t>
+          <t>https://www.indeed.com/viewjob?jk=7a056659ad4aebd2</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer - Python &amp; React JS</t>
+          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Checkmate</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5281,34 +5281,34 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, PostgreSQL, MySQL, CI/CD, GitHub Actions, Docker, Git, Datadog</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ba3d00c3fb0ee25</t>
+          <t>https://www.indeed.com/viewjob?jk=e5402962c321dcba</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Engineer II-Software Development</t>
+          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Microchip Technology</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5316,7 +5316,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLOps, CI/CD</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -5326,24 +5326,24 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3013681a0e1c4f81</t>
+          <t>https://www.indeed.com/viewjob?jk=f45ad39ec1fe503a</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Engineer II-Software Development</t>
+          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Microchip Technology</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5351,7 +5351,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLOps, CI/CD</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -5361,24 +5361,24 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2649d75a044fe7bd</t>
+          <t>https://www.indeed.com/viewjob?jk=86cfc919b4ccc768</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - VAULT</t>
+          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Bloomberg</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5386,7 +5386,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Hive, Spark, Scala, Kafka, Cassandra</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -5396,24 +5396,24 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d744cfcd1fce896</t>
+          <t>https://www.indeed.com/viewjob?jk=c9a866cff6a0e3bd</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>BigData ,Python and Py Spark , GCP</t>
+          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5421,7 +5421,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>GCP, BigQuery, Hadoop, Hive, Spark, PySpark, Scala, ETL, ELT, Airflow</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -5431,24 +5431,24 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81999129979e18ac</t>
+          <t>https://www.indeed.com/viewjob?jk=ab68f1e4ba82ad10</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Cloud AI Application Administrator</t>
+          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, Dataflow, Cloud Storage, Scala, Oracle, ETL, ELT, dbt, Tableau</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -5466,24 +5466,24 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd193e360372af33</t>
+          <t>https://www.indeed.com/viewjob?jk=df163d5906a30146</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>FastAPI</t>
+          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -5491,34 +5491,34 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, BigQuery, Vertex AI, Spark, Scala, Spark Streaming, Kafka, CI/CD, Git</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0bc1141188a8604a</t>
+          <t>https://www.indeed.com/viewjob?jk=2f0c32c0bdf67710</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Urology Centers of Alabama</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, ETL</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -5536,24 +5536,24 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28cb24ea6139fcb9</t>
+          <t>https://www.indeed.com/viewjob?jk=25f63312ec2e267e</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Pearson</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Hoboken, NJ, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D147" t="n">
@@ -5561,7 +5561,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, MongoDB, DynamoDB, Data Modeling, ETL, ELT, DataOps, CI/CD</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -5571,7 +5571,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05547d65aabdfcf0</t>
+          <t>https://www.indeed.com/viewjob?jk=be379ec08f5c5e6f</t>
         </is>
       </c>
     </row>
@@ -5588,7 +5588,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D148" t="n">
@@ -5606,7 +5606,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34c37a226b547d01</t>
+          <t>https://www.indeed.com/viewjob?jk=8deeb1ab1ebcdccd</t>
         </is>
       </c>
     </row>
@@ -5623,7 +5623,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D149" t="n">
@@ -5641,7 +5641,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7d77afce6f60e6f</t>
+          <t>https://www.indeed.com/viewjob?jk=92aa87419ba8e5df</t>
         </is>
       </c>
     </row>
@@ -5658,7 +5658,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D150" t="n">
@@ -5676,7 +5676,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=225c5a8131dc6595</t>
+          <t>https://www.indeed.com/viewjob?jk=da334d3b3eda0eb4</t>
         </is>
       </c>
     </row>
@@ -5693,7 +5693,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D151" t="n">
@@ -5711,7 +5711,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=301dbd1e2eb0bb70</t>
+          <t>https://www.indeed.com/viewjob?jk=2c314e6df20a4157</t>
         </is>
       </c>
     </row>
@@ -5728,7 +5728,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D152" t="n">
@@ -5746,7 +5746,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d88e7121c2db79d6</t>
+          <t>https://www.indeed.com/viewjob?jk=b90a165cff732e70</t>
         </is>
       </c>
     </row>
@@ -5763,7 +5763,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D153" t="n">
@@ -5781,7 +5781,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18d3f9fdcfa07035</t>
+          <t>https://www.indeed.com/viewjob?jk=26bc98921360165c</t>
         </is>
       </c>
     </row>
@@ -5798,7 +5798,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D154" t="n">
@@ -5816,7 +5816,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d2d16258cfd6718</t>
+          <t>https://www.indeed.com/viewjob?jk=c5359f322821abe9</t>
         </is>
       </c>
     </row>
@@ -5833,7 +5833,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D155" t="n">
@@ -5851,7 +5851,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5be8f9b4535b406c</t>
+          <t>https://www.indeed.com/viewjob?jk=562ea8307dd5c91d</t>
         </is>
       </c>
     </row>
@@ -5868,7 +5868,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D156" t="n">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26ef52c65261360a</t>
+          <t>https://www.indeed.com/viewjob?jk=70a64e543cdeb49a</t>
         </is>
       </c>
     </row>
@@ -5903,7 +5903,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D157" t="n">
@@ -5921,7 +5921,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9240b7b96545a4d</t>
+          <t>https://www.indeed.com/viewjob?jk=ed3e28c9a543299a</t>
         </is>
       </c>
     </row>
@@ -5938,7 +5938,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D158" t="n">
@@ -5956,24 +5956,24 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42ae72f7d4a97700</t>
+          <t>https://www.indeed.com/viewjob?jk=1735f01363643535</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
+          <t>Data Engineer II, Mobile Game Analytics</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Mattel, Inc.</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>El Segundo, CA, US USA</t>
         </is>
       </c>
       <c r="D159" t="n">
@@ -5981,7 +5981,7 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
+          <t>RDS, Medallion Architecture, GCP, BigQuery, Dimensional Modeling, ETL, dbt, Tableau, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
@@ -5991,24 +5991,24 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dab5b1b68cc6402c</t>
+          <t>https://www.indeed.com/viewjob?jk=087868e735e87a06</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
+          <t>Senior Engineer, AI</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Harman</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Novi, MI, US USA</t>
         </is>
       </c>
       <c r="D160" t="n">
@@ -6016,34 +6016,34 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fde8d1831ca7f9b7</t>
+          <t>https://www.indeed.com/viewjob?jk=4a91d05d9ba98a3a</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
+          <t>Senior Data Integration Software Engineer</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D161" t="n">
@@ -6051,34 +6051,34 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, ETL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a056659ad4aebd2</t>
+          <t>https://www.indeed.com/viewjob?jk=b035b944f2ad4c37</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
+          <t>Senior Data Integration Software Engineer</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D162" t="n">
@@ -6086,34 +6086,34 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, ETL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5402962c321dcba</t>
+          <t>https://www.indeed.com/viewjob?jk=9ba6e4aacd5b6631</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
+          <t>Senior Data Integration Software Engineer</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Portsmouth, NH, US USA</t>
         </is>
       </c>
       <c r="D163" t="n">
@@ -6121,34 +6121,34 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, ETL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f45ad39ec1fe503a</t>
+          <t>https://www.indeed.com/viewjob?jk=93164fc43ac74193</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
+          <t>Data Integration Software Engineer</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Portsmouth, NH, US USA</t>
         </is>
       </c>
       <c r="D164" t="n">
@@ -6156,34 +6156,34 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, ETL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86cfc919b4ccc768</t>
+          <t>https://www.indeed.com/viewjob?jk=c4c7e0f49df408be</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
+          <t>Data Integration Software Engineer</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D165" t="n">
@@ -6191,34 +6191,34 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, ETL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9a866cff6a0e3bd</t>
+          <t>https://www.indeed.com/viewjob?jk=12a4fd124772d9d2</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
+          <t>Data Integration Software Engineer</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D166" t="n">
@@ -6226,34 +6226,34 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, ETL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab68f1e4ba82ad10</t>
+          <t>https://www.indeed.com/viewjob?jk=c38e2fae9b46f905</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
+          <t>Software Engineer - AI Augmented Development</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>PowerPay</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Wayne, PA, US USA</t>
         </is>
       </c>
       <c r="D167" t="n">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
+          <t>AWS, Lambda, S3, SQS, ECS, IAM, RDS, Snowflake, ETL, Terraform</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
@@ -6271,24 +6271,24 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df163d5906a30146</t>
+          <t>https://www.indeed.com/viewjob?jk=039bac65ddb8c30e</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
+          <t>Sr. Software Engineer, Full-Stack (Factory Systems)</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Rivian and Volkswagen Group Technologies</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D168" t="n">
@@ -6296,34 +6296,34 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f0c32c0bdf67710</t>
+          <t>https://www.indeed.com/viewjob?jk=68c700567606c4e9</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
+          <t>Sr Associate Engineer/Engineer, IT Software</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D169" t="n">
@@ -6331,7 +6331,7 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
@@ -6341,24 +6341,24 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25f63312ec2e267e</t>
+          <t>https://www.indeed.com/viewjob?jk=cf657c9771abb6db</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
+          <t>Data Scientist, Senior Associate – Product, Experience and Technology (PXT) Analytics Team</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D170" t="n">
@@ -6366,34 +6366,34 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
+          <t>Redshift, RDS, Databricks, Scala, Snowflake, dbt, Tableau, CI/CD, Airflow, Git</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be379ec08f5c5e6f</t>
+          <t>https://www.indeed.com/viewjob?jk=4b0bfe4f7e93a067</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
+          <t>Enterprise AI Architect</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Radwell International</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Willingboro, NJ, US USA</t>
         </is>
       </c>
       <c r="D171" t="n">
@@ -6401,34 +6401,34 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, PostgreSQL, MySQL, NoSQL, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8deeb1ab1ebcdccd</t>
+          <t>https://www.indeed.com/viewjob?jk=56c80236c3727026</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
+          <t>AI Engineer Clinical Data Science</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Katalyst Healthcares &amp; Life Sciences</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Manhattan, NY, US USA</t>
         </is>
       </c>
       <c r="D172" t="n">
@@ -6436,717 +6436,17 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
+          <t>RDS, Google Cloud Platform, GCP, Vertex AI, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker, Git</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92aa87419ba8e5df</t>
-        </is>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" t="inlineStr">
-        <is>
-          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B173" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C173" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D173" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E173" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
-        </is>
-      </c>
-      <c r="F173" t="inlineStr">
-        <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="G173" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=da334d3b3eda0eb4</t>
-        </is>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="inlineStr">
-        <is>
-          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B174" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C174" t="inlineStr">
-        <is>
-          <t>Los Angeles, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D174" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E174" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
-        </is>
-      </c>
-      <c r="F174" t="inlineStr">
-        <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="G174" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2c314e6df20a4157</t>
-        </is>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" t="inlineStr">
-        <is>
-          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B175" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C175" t="inlineStr">
-        <is>
-          <t>Denver, CO, US USA</t>
-        </is>
-      </c>
-      <c r="D175" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E175" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
-        </is>
-      </c>
-      <c r="F175" t="inlineStr">
-        <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="G175" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b90a165cff732e70</t>
-        </is>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" t="inlineStr">
-        <is>
-          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B176" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C176" t="inlineStr">
-        <is>
-          <t>San Diego, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D176" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E176" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
-        </is>
-      </c>
-      <c r="F176" t="inlineStr">
-        <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="G176" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=26bc98921360165c</t>
-        </is>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" t="inlineStr">
-        <is>
-          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B177" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C177" t="inlineStr">
-        <is>
-          <t>Tampa, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D177" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E177" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
-        </is>
-      </c>
-      <c r="F177" t="inlineStr">
-        <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="G177" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c5359f322821abe9</t>
-        </is>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" t="inlineStr">
-        <is>
-          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B178" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C178" t="inlineStr">
-        <is>
-          <t>Sacramento, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D178" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E178" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
-        </is>
-      </c>
-      <c r="F178" t="inlineStr">
-        <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="G178" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=562ea8307dd5c91d</t>
-        </is>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" t="inlineStr">
-        <is>
-          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B179" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C179" t="inlineStr">
-        <is>
-          <t>Costa Mesa, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D179" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E179" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
-        </is>
-      </c>
-      <c r="F179" t="inlineStr">
-        <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="G179" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=70a64e543cdeb49a</t>
-        </is>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" t="inlineStr">
-        <is>
-          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B180" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C180" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D180" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E180" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
-        </is>
-      </c>
-      <c r="F180" t="inlineStr">
-        <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="G180" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ed3e28c9a543299a</t>
-        </is>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" t="inlineStr">
-        <is>
-          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B181" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C181" t="inlineStr">
-        <is>
-          <t>San Jose, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D181" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E181" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
-        </is>
-      </c>
-      <c r="F181" t="inlineStr">
-        <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="G181" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1735f01363643535</t>
-        </is>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" t="inlineStr">
-        <is>
-          <t>Data Engineer II, Mobile Game Analytics</t>
-        </is>
-      </c>
-      <c r="B182" t="inlineStr">
-        <is>
-          <t>Mattel, Inc.</t>
-        </is>
-      </c>
-      <c r="C182" t="inlineStr">
-        <is>
-          <t>El Segundo, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D182" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E182" t="inlineStr">
-        <is>
-          <t>RDS, Medallion Architecture, GCP, BigQuery, Dimensional Modeling, ETL, dbt, Tableau, CI/CD, Airflow</t>
-        </is>
-      </c>
-      <c r="F182" t="inlineStr">
-        <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="G182" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=087868e735e87a06</t>
-        </is>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" t="inlineStr">
-        <is>
-          <t>AI Integration Engineer (Java + AI)</t>
-        </is>
-      </c>
-      <c r="B183" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C183" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D183" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E183" t="inlineStr">
-        <is>
-          <t>RDS, Google Cloud Platform, BigQuery, Vertex AI, Spark, Scala, Spark Streaming, Kafka, CI/CD, Git</t>
-        </is>
-      </c>
-      <c r="F183" t="inlineStr">
-        <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="G183" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f192cf981191d4cd</t>
-        </is>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" t="inlineStr">
-        <is>
-          <t>AI Integration Engineer (Java + AI)</t>
-        </is>
-      </c>
-      <c r="B184" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C184" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D184" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E184" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, Terraform, Docker, Jenkins</t>
-        </is>
-      </c>
-      <c r="F184" t="inlineStr">
-        <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="G184" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e7e0844f636778b5</t>
-        </is>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" t="inlineStr">
-        <is>
-          <t>GCP Support Associate</t>
-        </is>
-      </c>
-      <c r="B185" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C185" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D185" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E185" t="inlineStr">
-        <is>
-          <t>IAM, Google Cloud Platform, GCP, Dataflow, Cloud Storage, CI/CD, Jenkins, Terraform, Docker, Jenkins</t>
-        </is>
-      </c>
-      <c r="F185" t="inlineStr">
-        <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="G185" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=908520f92505a147</t>
-        </is>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" t="inlineStr">
-        <is>
-          <t>Sr. Software Engineer, Full-Stack (Factory Systems)</t>
-        </is>
-      </c>
-      <c r="B186" t="inlineStr">
-        <is>
-          <t>Rivian and Volkswagen Group Technologies</t>
-        </is>
-      </c>
-      <c r="C186" t="inlineStr">
-        <is>
-          <t>Palo Alto, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D186" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E186" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F186" t="inlineStr">
-        <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="G186" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=68c700567606c4e9</t>
-        </is>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" t="inlineStr">
-        <is>
-          <t>Data Scientist, Senior Associate – Product, Experience and Technology (PXT) Analytics Team</t>
-        </is>
-      </c>
-      <c r="B187" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C187" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D187" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E187" t="inlineStr">
-        <is>
-          <t>Redshift, RDS, Databricks, Scala, Snowflake, dbt, Tableau, CI/CD, Airflow, Git</t>
-        </is>
-      </c>
-      <c r="F187" t="inlineStr">
-        <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="G187" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4b0bfe4f7e93a067</t>
-        </is>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" t="inlineStr">
-        <is>
-          <t>Software Engineer - AI Augmented Development</t>
-        </is>
-      </c>
-      <c r="B188" t="inlineStr">
-        <is>
-          <t>PowerPay</t>
-        </is>
-      </c>
-      <c r="C188" t="inlineStr">
-        <is>
-          <t>Wayne, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D188" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E188" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, SQS, ECS, IAM, RDS, Snowflake, ETL, Terraform</t>
-        </is>
-      </c>
-      <c r="F188" t="inlineStr">
-        <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="G188" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=039bac65ddb8c30e</t>
-        </is>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" t="inlineStr">
-        <is>
-          <t>Enterprise AI Architect</t>
-        </is>
-      </c>
-      <c r="B189" t="inlineStr">
-        <is>
-          <t>Radwell International</t>
-        </is>
-      </c>
-      <c r="C189" t="inlineStr">
-        <is>
-          <t>Willingboro, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D189" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E189" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, PostgreSQL, MySQL, NoSQL, MLOps, CI/CD</t>
-        </is>
-      </c>
-      <c r="F189" t="inlineStr">
-        <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="G189" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=56c80236c3727026</t>
-        </is>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" t="inlineStr">
-        <is>
-          <t>Sr Associate Engineer/Engineer, IT Software</t>
-        </is>
-      </c>
-      <c r="B190" t="inlineStr">
-        <is>
-          <t>American Airlines</t>
-        </is>
-      </c>
-      <c r="C190" t="inlineStr">
-        <is>
-          <t>Fort Worth, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D190" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E190" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F190" t="inlineStr">
-        <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="G190" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=cf657c9771abb6db</t>
-        </is>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" t="inlineStr">
-        <is>
-          <t>DevOps Engineer (GCP)</t>
-        </is>
-      </c>
-      <c r="B191" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C191" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D191" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E191" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Vertex AI, Spark, MLflow, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F191" t="inlineStr">
-        <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="G191" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1a53e6510409c717</t>
-        </is>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" t="inlineStr">
-        <is>
-          <t>AI Application Architect</t>
-        </is>
-      </c>
-      <c r="B192" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C192" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D192" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E192" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, Snowflake, ETL, MLOps, MLflow, CI/CD</t>
-        </is>
-      </c>
-      <c r="F192" t="inlineStr">
-        <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="G192" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=bdfa99adc53f817f</t>
+          <t>https://www.indeed.com/viewjob?jk=47a06a95eff2f8b1</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-05-06.xlsx
+++ b/results/job_matches_2026-05-06.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G172"/>
+  <dimension ref="A1:G160"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Consultant - Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Torq Consulting</t>
+          <t>Capital Bank, N.A.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Rockville, MD, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>21.5</v>
+        <v>19.4</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, Google Cloud Platform, BigQuery, Scala, Kafka</t>
+          <t>Redshift, RDS, Azure, Data Factory, BigQuery, Spark, Scala, Kafka, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,7 +496,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27d1b768e1037d39</t>
+          <t>https://www.indeed.com/viewjob?jk=3488abdd8c4dc725</t>
         </is>
       </c>
     </row>
@@ -508,20 +508,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Redapt inc</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Woodinville, WA, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>21.5</v>
+        <v>18.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, Azure, Data Factory, Databricks, GCP, Spark</t>
+          <t>AWS, Glue, EMR, S3, RDS, Azure, Data Factory, Databricks, GCP, Spark</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ba1f68994568fe5</t>
+          <t>https://www.indeed.com/viewjob?jk=ad171c93c1899d21</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Capital Bank, N.A.</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Rockville, MD, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>19.4</v>
+        <v>18.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Data Factory, BigQuery, Spark, Scala, Kafka, Snowflake, SQL Server</t>
+          <t>AWS, Glue, EMR, S3, RDS, Azure, Data Factory, Databricks, GCP, Spark</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,7 +566,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3488abdd8c4dc725</t>
+          <t>https://www.indeed.com/viewjob?jk=98f8265780f793dd</t>
         </is>
       </c>
     </row>
@@ -578,55 +578,55 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>Analytica</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>18.8</v>
+        <v>18.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, S3, RDS, Azure, Data Factory, Databricks, GCP, Spark</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, IAM, RDS, Azure, Databricks</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad171c93c1899d21</t>
+          <t>https://www.indeed.com/viewjob?jk=7d9377a4724bf38c</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>Warner Bros. Discovery</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>18.8</v>
+        <v>18.1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, S3, RDS, Azure, Data Factory, Databricks, GCP, Spark</t>
+          <t>AWS, Glue, EMR, Kinesis, Redshift, Athena, S3, RDS, Azure, Databricks</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,7 +636,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98f8265780f793dd</t>
+          <t>https://www.indeed.com/viewjob?jk=0585eb3ca3cd8f48</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0585eb3ca3cd8f48</t>
+          <t>https://www.indeed.com/viewjob?jk=ea66a6dbd0690c3b</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea66a6dbd0690c3b</t>
+          <t>https://www.indeed.com/viewjob?jk=ec9442df01efef1b</t>
         </is>
       </c>
     </row>
@@ -741,7 +741,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec9442df01efef1b</t>
+          <t>https://www.indeed.com/viewjob?jk=341798717a6ce508</t>
         </is>
       </c>
     </row>
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=341798717a6ce508</t>
+          <t>https://www.indeed.com/viewjob?jk=29381ac7399ddbb0</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer, Cloud Infrastructure (Multiple Seniority Levels)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Warner Bros. Discovery</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Carlos, CA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Kinesis, Redshift, Athena, S3, RDS, Azure, Databricks</t>
+          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, SQS, ECS, IAM, RDS</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29381ac7399ddbb0</t>
+          <t>https://www.indeed.com/viewjob?jk=07cee960b10bf15e</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Software Engineer - DevOps and MLOps</t>
+          <t>Commercial IT Senior Data Solution Developer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ConocoPhillips</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>San Francisco Bay Area, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Kafka, PostgreSQL, MongoDB, Cassandra</t>
+          <t>AWS, RDS, Azure, Databricks, Hive, Spark, Scala, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,102 +846,102 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2fcad788d48ba696</t>
+          <t>https://www.indeed.com/viewjob?jk=1304cb2ffae316c6</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Software Engineer, Cloud Infrastructure (Multiple Seniority Levels)</t>
+          <t>Health Account Intern</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Booz Allen Hamilton</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>San Carlos, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, SQS, ECS, IAM, RDS</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Databricks, Hadoop, Hive, Spark, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07cee960b10bf15e</t>
+          <t>https://www.indeed.com/viewjob?jk=64329d0d0bf86853</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Commercial IT Senior Data Solution Developer</t>
+          <t>Azure Network Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ConocoPhillips</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hive, Spark, Scala, Kafka, Snowflake, NoSQL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Event Hubs, Unity Catalog, Medallion Architecture, Spark, PySpark</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1304cb2ffae316c6</t>
+          <t>https://www.indeed.com/viewjob?jk=b4c4141e761a1d57</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Azure Network Engineer</t>
+          <t>Sr Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Commence</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Leesburg, VA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Event Hubs, Unity Catalog, Medallion Architecture, Spark, PySpark</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, NoSQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,94 +951,94 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4c4141e761a1d57</t>
+          <t>https://www.indeed.com/viewjob?jk=9093ede7f2269db2</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Health Account Intern</t>
+          <t>Sr Data Engineer, Python + Spark (Data Federation skillset - Data Lakehouse - Eg: Starburst) - New York</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Booz Allen Hamilton</t>
+          <t>Photon</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Databricks, Hadoop, Hive, Spark, Scala</t>
+          <t>AWS, Glue, EMR, S3, Azure, Databricks, Medallion Architecture, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64329d0d0bf86853</t>
+          <t>https://www.indeed.com/viewjob?jk=f7767a92d7d08a3b</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Databricks Engineer and Architect</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>WSSC Water</t>
+          <t>Lincoln Financial Group</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Laurel, MD, US USA</t>
+          <t>Radnor, PA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Blob Storage, GCP, Hadoop</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, RDS, Databricks, Unity Catalog</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=859b6255aab51697</t>
+          <t>https://www.indeed.com/viewjob?jk=d7862c3c59e06d56</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Sr Site Reliability Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Commence</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Leesburg, VA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,29 +1046,29 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, NoSQL, ETL, ELT</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, RDS, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9093ede7f2269db2</t>
+          <t>https://www.indeed.com/viewjob?jk=df1902d36083d34f</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Sr Data Engineer, Python + Spark (Data Federation skillset - Data Lakehouse - Eg: Starburst) - New York</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Photon</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1081,29 +1081,29 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, S3, Azure, Databricks, Medallion Architecture, GCP, Spark, PySpark</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, RDS, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7767a92d7d08a3b</t>
+          <t>https://www.indeed.com/viewjob?jk=5cb867686433b7a1</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - ETL, Java</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>RevSpring, Inc</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1116,34 +1116,34 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Redshift, S3, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop, Scala</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, RDS, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a9c009a05948507</t>
+          <t>https://www.indeed.com/viewjob?jk=3aeafc948a2f0f6c</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - ETL, Java</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>RevSpring, Inc</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,34 +1151,34 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Redshift, S3, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop, Scala</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, RDS, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba5ba3f3a840901f</t>
+          <t>https://www.indeed.com/viewjob?jk=c45b322f3e5694ad</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - ETL, Java</t>
+          <t>Software Engineer Intern</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>RevSpring, Inc</t>
+          <t>Norstella</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Redshift, S3, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop, Scala</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Azure, Blob Storage, GCP, PostgreSQL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,54 +1196,54 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec9899d266d7f4ea</t>
+          <t>https://www.indeed.com/viewjob?jk=49a129c7a487aae4</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Databricks Engineer and Architect</t>
+          <t>MLOps Engineer – Azure Databricks, Cloud-to-Edge ML Deployment</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Lincoln Financial Group</t>
+          <t>KPIT Technologies</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Radnor, PA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, RDS, Databricks, Unity Catalog</t>
+          <t>Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7862c3c59e06d56</t>
+          <t>https://www.indeed.com/viewjob?jk=1160b6a5ea3d30ad</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Verisk</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1252,91 +1252,91 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, RDS, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, Glue, Lambda, Athena, S3, RDS, Spark, Scala, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df1902d36083d34f</t>
+          <t>https://www.indeed.com/viewjob?jk=cb57edcbdb36ad26</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>API Threat Intelligence Analyst</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, RDS, Scala, Kafka, PostgreSQL</t>
+          <t>Azure, Google Cloud Platform, Kafka, NoSQL, Data Modeling, ETL, Talend, Tableau, Splunk, MicroStrategy</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cb867686433b7a1</t>
+          <t>https://www.indeed.com/viewjob?jk=e918fa70b2a1920e</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Backend (Python)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, RDS, Scala, Kafka, PostgreSQL</t>
+          <t>Azure, Google Cloud Platform, Kafka, NoSQL, Data Modeling, ETL, Talend, Tableau, Splunk, MicroStrategy</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3aeafc948a2f0f6c</t>
+          <t>https://www.indeed.com/viewjob?jk=d711bd4394cb404e</t>
         </is>
       </c>
     </row>
@@ -1348,42 +1348,42 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Wavicle Data Solutions</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Oak Brook, IL, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>16</v>
+        <v>14.6</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, RDS, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, Lambda, Redshift, Azure, Databricks, GCP, Hadoop, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c45b322f3e5694ad</t>
+          <t>https://www.indeed.com/viewjob?jk=a435f9b94ff5d489</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Software Engineer Intern</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Norstella</t>
+          <t>Netsecure360</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1392,116 +1392,116 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>16</v>
+        <v>14.6</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Azure, Blob Storage, GCP, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Cloud Storage, Hadoop, Hive, Spark, Scala, Kafka, Oracle</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49a129c7a487aae4</t>
+          <t>https://www.indeed.com/viewjob?jk=ca7e816524d9406c</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer (Databricks)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Verisk</t>
+          <t>Infinitive Inc</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Ashburn, VA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, S3, RDS, Spark, Scala, PostgreSQL, Data Modeling</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, S3, Azure, Databricks, Unity Catalog, GCP</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb57edcbdb36ad26</t>
+          <t>https://www.indeed.com/viewjob?jk=aee5e62267dbbb6c</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>MLOps Engineer – Azure Databricks, Cloud-to-Edge ML Deployment</t>
+          <t>Software Developer II</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>KPIT Technologies</t>
+          <t>Floor &amp; Decor</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, MLOps, MLflow, CI/CD</t>
+          <t>RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1160b6a5ea3d30ad</t>
+          <t>https://www.indeed.com/viewjob?jk=4a21fec712255df2</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>API Threat Intelligence Analyst</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>SOFTILITY INC</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Azure, Google Cloud Platform, Kafka, NoSQL, Data Modeling, ETL, Talend, Tableau, Splunk, MicroStrategy</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e918fa70b2a1920e</t>
+          <t>https://www.indeed.com/viewjob?jk=3faf69463891ca3f</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Backend (Python)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Azure, Google Cloud Platform, Kafka, NoSQL, Data Modeling, ETL, Talend, Tableau, Splunk, MicroStrategy</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Oracle, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,19 +1546,19 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d711bd4394cb404e</t>
+          <t>https://www.indeed.com/viewjob?jk=d61e7d7639acc074</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Streaming Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Netsecure360</t>
+          <t>Ness Digital Engineering</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1567,81 +1567,81 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Cloud Storage, Hadoop, Hive, Spark, Scala, Kafka, Oracle</t>
+          <t>AWS, Kinesis, S3, IAM, RDS, Spark, Scala, Kafka, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca7e816524d9406c</t>
+          <t>https://www.indeed.com/viewjob?jk=f90fa0ab3164dcd1</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>MLOps Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Metropolis</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Glue, SNS, RDS, Spark, PySpark, Scala, Snowflake, SQL Server, MySQL</t>
+          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9fd5c209c01d504</t>
+          <t>https://www.indeed.com/viewjob?jk=56f1aa48ba26ae3c</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Business Intelligence Developer (Healthcare Data, EDI, ETL)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>metropolis</t>
+          <t>MicroHealth LLC</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Vienna, VA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Glue, SNS, RDS, Spark, PySpark, Scala, Snowflake, SQL Server, MySQL</t>
+          <t>AWS, EMR, RDS, Scala, Snowflake, SQL Server, PostgreSQL, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,102 +1651,102 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d51453a1afa374b4</t>
+          <t>https://www.indeed.com/viewjob?jk=3ba3d7e28ab6494c</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Databricks)</t>
+          <t>Senior Data analyst</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Infinitive Inc</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>Brentwood, TN, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, S3, Azure, Databricks, Unity Catalog, GCP</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aee5e62267dbbb6c</t>
+          <t>https://www.indeed.com/viewjob?jk=b7ed131be5ba5e96</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Software Engineer – ETL, Java</t>
+          <t>Mid- Level Data Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>RevSpring, Inc</t>
+          <t>Vantage Data Centers</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Redshift, S3, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop, Scala</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Spark, PySpark, Scala, Data Modeling, Dimension Tables, ETL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ebdf3dd92985403</t>
+          <t>https://www.indeed.com/viewjob?jk=a35201e2c76024aa</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Software Engineer – ETL, Java</t>
+          <t>Senior Site Reliability Engineer, Data &amp; Analytics</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>RevSpring, Inc</t>
+          <t>Blizzard Entertainment</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Redshift, S3, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop, Scala</t>
+          <t>AWS, RDS, GCP, BigQuery, Dataflow, Kafka, dbt, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c4b1e40555df27f</t>
+          <t>https://www.indeed.com/viewjob?jk=f56eabb97941a731</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Software Engineer – ETL, Java</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>RevSpring, Inc</t>
+          <t>Kroll Inc.</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Redshift, S3, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop, Scala</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Scala, Polars, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,67 +1791,67 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d1957e3729d8614</t>
+          <t>https://www.indeed.com/viewjob?jk=d56048c057634cd1</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Computing Architect 4 (contract)</t>
+          <t>Cloud Network Architect</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Boeing</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Scala, Kafka, Data Modeling, ELT</t>
+          <t>API Gateway, IAM, RDS, Google Cloud Platform, BigQuery, Dataflow, Scala, Kafka, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83fa749fc70ff9b5</t>
+          <t>https://www.indeed.com/viewjob?jk=3552e9ee02097f2c</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Software Developer II</t>
+          <t>Data Solutions Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Floor &amp; Decor</t>
+          <t>Epsilon</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>14.6</v>
+        <v>12.5</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL, Splunk, CI/CD</t>
+          <t>AWS, RDS, Databricks, Hadoop, HDFS, Spark, Scala, Kafka, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,67 +1861,67 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a21fec712255df2</t>
+          <t>https://www.indeed.com/viewjob?jk=22c6237fafdb9308</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Sr. Streaming Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Ness Digital Engineering</t>
+          <t>vectorsoft</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, IAM, RDS, Spark, Scala, Kafka, NoSQL, Splunk</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f90fa0ab3164dcd1</t>
+          <t>https://www.indeed.com/viewjob?jk=3bdce3e69ca5f6c4</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Azure Network Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>SOFTILITY INC</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD</t>
+          <t>IAM, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage, MySQL, Splunk, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,32 +1931,32 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3faf69463891ca3f</t>
+          <t>https://www.indeed.com/viewjob?jk=8bb3e3385b26a0b5</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer - Cloud Gateway</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Rivian and Volkswagen Group Technologies</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Oracle, Data Modeling, ETL</t>
+          <t>AWS, RDS, Scala, Kafka, MongoDB, DynamoDB, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,32 +1966,32 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d61e7d7639acc074</t>
+          <t>https://www.indeed.com/viewjob?jk=7b72e865e6bee153</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer - Cloud Dev</t>
+          <t>Senior Cloud Database Engineer (Hybrid - Seattle, WA)</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Transmedics</t>
+          <t>Nordstrom</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Andover, MA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, Redshift, Step Functions, S3, SQS, SNS, API Gateway, IAM</t>
+          <t>AWS, Glue, Kinesis, Redshift, Athena, S3, RDS, Kafka, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,67 +2001,67 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2efe7bed588da272</t>
+          <t>https://www.indeed.com/viewjob?jk=1666a61865ef57aa</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>MLOps Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Moore</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Westminster, CO, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56f1aa48ba26ae3c</t>
+          <t>https://www.indeed.com/viewjob?jk=b8c5af154805cd95</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Business Intelligence Developer (Healthcare Data, EDI, ETL)</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>MicroHealth LLC</t>
+          <t>Paramount</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Vienna, VA, US USA</t>
+          <t>Fort Lauderdale, FL, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Scala, Snowflake, SQL Server, PostgreSQL, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, RDS, GCP, BigQuery, Dataflow, Scala, MongoDB, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,67 +2071,67 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ba3d7e28ab6494c</t>
+          <t>https://www.indeed.com/viewjob?jk=a12925c69dfc7bed</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Mid- Level Data Engineer</t>
+          <t>Data Engineer (ETL / Python Developer)</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Vantage Data Centers</t>
+          <t>CSpring</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Springfield, IL, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Spark, PySpark, Scala, Data Modeling, Dimension Tables, ETL</t>
+          <t>Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a35201e2c76024aa</t>
+          <t>https://www.indeed.com/viewjob?jk=b861e2c1a0a03133</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer, Data &amp; Analytics</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Blizzard Entertainment</t>
+          <t>Imprint</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Dataflow, Kafka, dbt, CI/CD, Jenkins, GitHub Actions</t>
+          <t>Kinesis, S3, RDS, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f56eabb97941a731</t>
+          <t>https://www.indeed.com/viewjob?jk=e35bafcce4ab1000</t>
         </is>
       </c>
     </row>
@@ -2153,20 +2153,20 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Kroll Inc.</t>
+          <t>Imprint</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Scala, Polars, ETL, ELT, Power BI, Tableau</t>
+          <t>Kinesis, S3, RDS, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,59 +2176,59 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d56048c057634cd1</t>
+          <t>https://www.indeed.com/viewjob?jk=baaf38c4500e2b06</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Cloud Network Architect</t>
+          <t>Senior AI Data Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Velvetech</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>API Gateway, IAM, RDS, Google Cloud Platform, BigQuery, Dataflow, Scala, Kafka, CI/CD, Jenkins</t>
+          <t>AWS, IAM, Azure, GCP, Vertex AI, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3552e9ee02097f2c</t>
+          <t>https://www.indeed.com/viewjob?jk=2bec7882b34f08c9</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Miami Marlins</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Westminster, CO, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, GCP, Scala, Snowflake, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff87deef607d5450</t>
+          <t>https://www.indeed.com/viewjob?jk=d49164a52434e329</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Software Engineer - Cloud</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Paramount</t>
+          <t>Carnegie Robotics LLC</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Fort Lauderdale, FL, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,34 +2271,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Dataflow, Scala, MongoDB, NoSQL, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, PostgreSQL, MongoDB, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a12925c69dfc7bed</t>
+          <t>https://www.indeed.com/viewjob?jk=e2f5b0b9c556cdca</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>AI Agent Engineer</t>
+          <t>Senior Data Engineer (Python/PySpark/AWS)</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Momentive Software</t>
+          <t>Infinitive Inc</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Ashburn, VA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,34 +2306,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Athena, SQS, SNS, API Gateway, ECS, RDS, Azure, GCP</t>
+          <t>AWS, Azure, Spark, PySpark, Scala, Spark Streaming, Data Modeling, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2025-02-18</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ac9574b3f75cc2c</t>
+          <t>https://www.indeed.com/viewjob?jk=45083db400feff94</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Azure Network Engineer</t>
+          <t>Data Engineer (Python/PySpark/AWS)</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Infinitive Inc</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Ashburn, VA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage, MySQL, Splunk, CI/CD, GitHub Actions</t>
+          <t>AWS, Azure, Spark, PySpark, Scala, Spark Streaming, Data Modeling, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2025-01-27</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bb3e3385b26a0b5</t>
+          <t>https://www.indeed.com/viewjob?jk=5e742c4bedd2037b</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Cloud Gateway</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Rivian and Volkswagen Group Technologies</t>
+          <t>Miami Marlins</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, MongoDB, DynamoDB, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, GCP, Scala, Snowflake, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b72e865e6bee153</t>
+          <t>https://www.indeed.com/viewjob?jk=ff87deef607d5450</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Cloud Database Engineer (Hybrid - Seattle, WA)</t>
+          <t>AI Agent Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Nordstrom</t>
+          <t>Momentive Software</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Redshift, Athena, S3, RDS, Kafka, Oracle, SQL Server</t>
+          <t>AWS, Lambda, Athena, SQS, SNS, API Gateway, ECS, RDS, Azure, GCP</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1666a61865ef57aa</t>
+          <t>https://www.indeed.com/viewjob?jk=6ac9574b3f75cc2c</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Moore</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Westminster, CO, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT, dbt</t>
+          <t>IAM, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage, MySQL, Splunk, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8c5af154805cd95</t>
+          <t>https://www.indeed.com/viewjob?jk=52b0e598b9832c43</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Data Engineer (ETL / Python Developer)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>CSpring</t>
+          <t>Terra Quantum</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Springfield, IL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b861e2c1a0a03133</t>
+          <t>https://www.indeed.com/viewjob?jk=15eb90498bcba242</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Full Stack Engineer, Experienced</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Imprint</t>
+          <t>Blue Shield of California</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Kinesis, S3, RDS, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e35bafcce4ab1000</t>
+          <t>https://www.indeed.com/viewjob?jk=93fe5a9749607800</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Full Stack Engineer, Senior</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Imprint</t>
+          <t>Blue Shield of California</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Kinesis, S3, RDS, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=baaf38c4500e2b06</t>
+          <t>https://www.indeed.com/viewjob?jk=bcc6fa1baccf83e5</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior AI Data Engineer</t>
+          <t>Full Stack Engineer, Consultant</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Velvetech</t>
+          <t>Blue Shield of California</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Vertex AI, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2bec7882b34f08c9</t>
+          <t>https://www.indeed.com/viewjob?jk=a3a7d3c5d7336760</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Summer Intern, Platform Engineering</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Outfront Media</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Westminster, CO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT, dbt</t>
+          <t>AWS, Lambda, S3, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d49164a52434e329</t>
+          <t>https://www.indeed.com/viewjob?jk=2aa35bb9483f10ad</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>AWS Data Engineer - Databricks</t>
+          <t>Artificial Intelligence/Machine Learning Data Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>RadCube</t>
+          <t>Accenture</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,322 +2656,322 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Databricks, Scala, Databricks Lakehouse, Data Modeling</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLflow</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2dcfccb6b6d90b1</t>
+          <t>https://www.indeed.com/viewjob?jk=b20f553bf3557e7a</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Software Engineer - Cloud</t>
+          <t>Cloud Network Architect</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Carnegie Robotics LLC</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, PostgreSQL, MongoDB, DynamoDB, NoSQL</t>
+          <t>Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2f5b0b9c556cdca</t>
+          <t>https://www.indeed.com/viewjob?jk=e874dfda20060e92</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Python/PySpark/AWS)</t>
+          <t>Azure Network Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Infinitive Inc</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Azure, Spark, PySpark, Scala, Spark Streaming, Data Modeling, ETL, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Event Hubs, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2025-02-18</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45083db400feff94</t>
+          <t>https://www.indeed.com/viewjob?jk=05dcb2c14af656a8</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data Engineer (Python/PySpark/AWS)</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Infinitive Inc</t>
+          <t>Clayco</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Azure, Spark, PySpark, Scala, Spark Streaming, Data Modeling, ETL, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2025-01-27</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e742c4bedd2037b</t>
+          <t>https://www.indeed.com/viewjob?jk=61cc49187bd6e01d</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>Data Engineering - E&amp;A - Data Engineer I</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Genesis Global Group</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Myrtle Point, OR, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage, MySQL, Splunk, CI/CD, GitHub Actions</t>
+          <t>Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52b0e598b9832c43</t>
+          <t>https://www.indeed.com/viewjob?jk=2526bf14df16c3e8</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Terra Quantum</t>
+          <t>Versant</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, GCP, Spark, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15eb90498bcba242</t>
+          <t>https://www.indeed.com/viewjob?jk=1fbef82ce93a90ed</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Full Stack Engineer, Experienced</t>
+          <t>Data Systems Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Blue Shield of California</t>
+          <t>Central Health</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, NoSQL, CI/CD, Terraform</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93fe5a9749607800</t>
+          <t>https://www.indeed.com/viewjob?jk=41eed22913274d81</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Full Stack Engineer, Senior</t>
+          <t>Full Stack Data Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Blue Shield of California</t>
+          <t>Millennium Management</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, NoSQL, CI/CD, Terraform</t>
+          <t>AWS, RDS, Scala, Snowflake, NoSQL, ELT, dbt, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bcc6fa1baccf83e5</t>
+          <t>https://www.indeed.com/viewjob?jk=b224fb124b25e580</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Full Stack Engineer, Consultant</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Blue Shield of California</t>
+          <t>Laural Parke</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, NoSQL, CI/CD, Terraform</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3a7d3c5d7336760</t>
+          <t>https://www.indeed.com/viewjob?jk=19dac2449c2108f4</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Summer Intern, Platform Engineering</t>
+          <t>Mid-Level Software Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Outfront Media</t>
+          <t>State Farm</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Bloomington, IL, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD, Docker</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, MongoDB, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2aa35bb9483f10ad</t>
+          <t>https://www.indeed.com/viewjob?jk=da08c5cf76c3287c</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Artificial Intelligence/Machine Learning Data Engineer</t>
+          <t>Senior DevOps Software Engineer, Firmware &amp; CI/CD</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Accenture</t>
+          <t>Rivian and Volkswagen Group Technologies</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,32 +3016,32 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b20f553bf3557e7a</t>
+          <t>https://www.indeed.com/viewjob?jk=d5f621c8ad4f69fd</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Customer Centric Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Victory Live</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Scala, Snowflake, ELT, dbt, Tableau, Docker</t>
+          <t>AWS, RDS, Azure, Data Factory, Snowflake, SQL Server, DynamoDB, ELT, dbt, Terraform</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29a2186b968dd17c</t>
+          <t>https://www.indeed.com/viewjob?jk=a1c259f0b00d1299</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Mid-Level Software Engineer</t>
+          <t>Cloud Networking Consultant</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>State Farm</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Bloomington, IL, US USA</t>
+          <t>KS, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,34 +3076,34 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, MongoDB, CI/CD, Terraform</t>
+          <t>RDS, Spark, Scala, Kafka, Snowflake, Splunk, CI/CD, Jenkins, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da08c5cf76c3287c</t>
+          <t>https://www.indeed.com/viewjob?jk=05bc8504be04f7d2</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Versant</t>
+          <t>Montefiore Einstein</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Yonkers, NY, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,34 +3111,34 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, GCP, Spark, NoSQL, ETL</t>
+          <t>AWS, RDS, Medallion Architecture, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ELT, dbt</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fbef82ce93a90ed</t>
+          <t>https://www.indeed.com/viewjob?jk=2d972b31a0cae529</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>AI/ML Engineer</t>
+          <t>Snowflake/Tableau Developer / Dallas Texas</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Redapt inc</t>
+          <t>FirstNet Global</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Woodinville, WA, US USA</t>
+          <t>Napa, CA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, GCP, Vertex AI, Spark, Snowflake, Data Modeling, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9c94059f3dd29b3</t>
+          <t>https://www.indeed.com/viewjob?jk=a4ab4d99e440e9b4</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Cloud Network Architect</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Klaxontech</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,32 +3191,32 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e874dfda20060e92</t>
+          <t>https://www.indeed.com/viewjob?jk=193935f590ab7020</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Azure Network Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Event Hubs, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,32 +3226,32 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05dcb2c14af656a8</t>
+          <t>https://www.indeed.com/viewjob?jk=c98f634775f326c6</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Sr. Professional, Software Engineering (Python)</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Clayco</t>
+          <t>Cotality</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
+          <t>RDS, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, Tableau, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,32 +3261,32 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61cc49187bd6e01d</t>
+          <t>https://www.indeed.com/viewjob?jk=83e013cc49a29087</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Data Engineering - E&amp;A - Data Engineer I</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Genesis Global Group</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Myrtle Point, OR, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
+          <t>RDS, GCP, BigQuery, Dataflow, Vertex AI, Scala, Data Modeling, Jenkins, Terraform, Jenkins</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,32 +3296,32 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2526bf14df16c3e8</t>
+          <t>https://www.indeed.com/viewjob?jk=4bbf23a169f18dbc</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior, Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Carrington Mortgage Services, LLC</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, ETL, Microsoft SSIS</t>
+          <t>RDS, GCP, BigQuery, Dataflow, Vertex AI, Scala, Data Modeling, Jenkins, Terraform, Jenkins</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,137 +3331,137 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfdf1b9d489fb8ec</t>
+          <t>https://www.indeed.com/viewjob?jk=4b05514433681d42</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Data Systems Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Central Health</t>
+          <t>Clark Construction</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, Azure, GCP, Spark, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, dbt</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41eed22913274d81</t>
+          <t>https://www.indeed.com/viewjob?jk=6f199bfc2e975b58</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Full Stack Data Engineer</t>
+          <t>Senior Platform/DevOps Engineer (Kubernetes-Linux)</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Millennium Management</t>
+          <t>ARMADA</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, NoSQL, ELT, dbt, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b224fb124b25e580</t>
+          <t>https://www.indeed.com/viewjob?jk=7b0e9b75e0f5558d</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior DevOps Software Engineer, Firmware &amp; CI/CD</t>
+          <t>Senior Platform/DevOps Engineer (Kubernetes-Linux)</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Rivian and Volkswagen Group Technologies</t>
+          <t>ARMADA</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Sammamish, WA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5f621c8ad4f69fd</t>
+          <t>https://www.indeed.com/viewjob?jk=efa4e4e3099a0ae2</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Platform/DevOps Engineer (Kubernetes-Linux)</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Victory Live</t>
+          <t>ARMADA</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Kirkland, WA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Snowflake, SQL Server, DynamoDB, ELT, dbt, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,164 +3471,164 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1c259f0b00d1299</t>
+          <t>https://www.indeed.com/viewjob?jk=33ae1f1f9d08c546</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Snowflake/Tableau Developer / Dallas Texas</t>
+          <t>Senior Platform/DevOps Engineer (Kubernetes-Linux)</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>FirstNet Global</t>
+          <t>ARMADA</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Napa, CA, US USA</t>
+          <t>Renton, WA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4ab4d99e440e9b4</t>
+          <t>https://www.indeed.com/viewjob?jk=d25130b996402485</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Senior Platform/DevOps Engineer (Kubernetes-Linux)</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Klaxontech</t>
+          <t>ARMADA</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Bothell, WA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=193935f590ab7020</t>
+          <t>https://www.indeed.com/viewjob?jk=b6f9224460f3210c</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Cloud Networking Consultant</t>
+          <t>Senior Platform/DevOps Engineer (Kubernetes-Linux)</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>ARMADA</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>KS, US USA</t>
+          <t>Redmond, WA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>RDS, Spark, Scala, Kafka, Snowflake, Splunk, CI/CD, Jenkins, Docker, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05bc8504be04f7d2</t>
+          <t>https://www.indeed.com/viewjob?jk=b86c940f686047d8</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Montefiore Einstein</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Yonkers, NY, US USA</t>
+          <t>Somerville, MA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Medallion Architecture, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ELT, dbt</t>
+          <t>Redshift, RDS, Azure, Scala, Snowflake, ETL, ELT, dbt, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d972b31a0cae529</t>
+          <t>https://www.indeed.com/viewjob?jk=75339d7552c524c1</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Mango Chamba, LLC</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,34 +3636,34 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Vertex AI, Scala, Data Modeling, Jenkins, Terraform, Jenkins</t>
+          <t>AWS, ECS, RDS, Scala, Snowflake, Time Travel, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bbf23a169f18dbc</t>
+          <t>https://www.indeed.com/viewjob?jk=76b38f99ba86c67f</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Mesa Labs</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Lakewood, CO, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,34 +3671,34 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Vertex AI, Scala, Data Modeling, Jenkins, Terraform, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, PostgreSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b05514433681d42</t>
+          <t>https://www.indeed.com/viewjob?jk=71d54ee3197b525a</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Google Cloud Network Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Clark Construction</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,34 +3706,34 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, dbt</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f199bfc2e975b58</t>
+          <t>https://www.indeed.com/viewjob?jk=c8d74c6d08304ab9</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior .NET Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Aspira</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, S3, API Gateway, RDS, Scala, SQL Server, CI/CD, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c98f634775f326c6</t>
+          <t>https://www.indeed.com/viewjob?jk=f3201135d0d7e294</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Sr. Professional, Software Engineering (Python)</t>
+          <t>DOCSIS Testing Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Cotality</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,34 +3776,34 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, Tableau, CI/CD, Terraform</t>
+          <t>AWS, RDS, Scala, Oracle, MongoDB, Splunk, CI/CD, Jenkins, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83e013cc49a29087</t>
+          <t>https://www.indeed.com/viewjob?jk=3102561596c9491c</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Senior Platform/DevOps Engineer (Kubernetes-Linux)</t>
+          <t>Software Engineer - DevOps Mobile</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>ARMADA</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,34 +3811,34 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Maven, Terraform, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b0e9b75e0f5558d</t>
+          <t>https://www.indeed.com/viewjob?jk=537b207b8aaf9dd0</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Senior Platform/DevOps Engineer (Kubernetes-Linux)</t>
+          <t>Software Engineer - Warehouse Management Systems (WMS)</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>ARMADA</t>
+          <t>Staples</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Sammamish, WA, US USA</t>
+          <t>Framingham, MA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, HBase, Scala, Kafka, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=efa4e4e3099a0ae2</t>
+          <t>https://www.indeed.com/viewjob?jk=654753ccda866d62</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Senior Platform/DevOps Engineer (Kubernetes-Linux)</t>
+          <t>Sr. Data Architect Specialist</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>ARMADA</t>
+          <t>SAMYANG AMERICA INC</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Kirkland, WA, US USA</t>
+          <t>Brea, CA, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33ae1f1f9d08c546</t>
+          <t>https://www.indeed.com/viewjob?jk=f2086e3e44cfc021</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Senior Platform/DevOps Engineer (Kubernetes-Linux)</t>
+          <t>Full Stack Product Engineer (Java)</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>ARMADA</t>
+          <t>Allstate Insurance</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Renton, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, ELT, CI/CD, Git</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d25130b996402485</t>
+          <t>https://www.indeed.com/viewjob?jk=d15adff582efc740</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Senior Platform/DevOps Engineer (Kubernetes-Linux)</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>ARMADA</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Bothell, WA, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,34 +3951,34 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, S3, IAM, Databricks, Spark, Scala, DynamoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6f9224460f3210c</t>
+          <t>https://www.indeed.com/viewjob?jk=6f9ad7c8c6b989c1</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Senior Platform/DevOps Engineer (Kubernetes-Linux)</t>
+          <t>QA Analyst / ETL Tester</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>ARMADA</t>
+          <t>CSpring</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Redmond, WA, US USA</t>
+          <t>Springfield, IL, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Data Modeling, Snowflake Schema, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,207 +3996,207 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b86c940f686047d8</t>
+          <t>https://www.indeed.com/viewjob?jk=1ebf7b3987a302e8</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Montefiore Einstein</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Somerville, MA, US USA</t>
+          <t>Yonkers, NY, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Scala, Snowflake, ETL, ELT, dbt, Tableau, CI/CD</t>
+          <t>AWS, S3, RDS, Scala, Snowflake, Data Modeling, ELT, dbt, CI/CD, Git</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75339d7552c524c1</t>
+          <t>https://www.indeed.com/viewjob?jk=9a3ffcafc747cce2</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Sr. Site Reliability Engineer</t>
+          <t>FastAPI</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>PitchBook</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, SQL Server, PostgreSQL, MySQL, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Google Cloud Platform, BigQuery, Vertex AI, Spark, Scala, Spark Streaming, Kafka, CI/CD, Git</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=181ce2100b853c3a</t>
+          <t>https://www.indeed.com/viewjob?jk=0bc1141188a8604a</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Google Cloud Network Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Urology Centers of Alabama</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, EMR, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, ETL</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8d74c6d08304ab9</t>
+          <t>https://www.indeed.com/viewjob?jk=28cb24ea6139fcb9</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>DOCSIS Testing Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Pearson</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Hoboken, NJ, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Oracle, MongoDB, Splunk, CI/CD, Jenkins, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Scala, MongoDB, DynamoDB, Data Modeling, ETL, ELT, DataOps, CI/CD</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3102561596c9491c</t>
+          <t>https://www.indeed.com/viewjob?jk=05547d65aabdfcf0</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Software Engineer - DevOps Mobile</t>
+          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Maven, Terraform, Docker, Jenkins</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=537b207b8aaf9dd0</t>
+          <t>https://www.indeed.com/viewjob?jk=34c37a226b547d01</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Software Engineer - Warehouse Management Systems (WMS)</t>
+          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Staples</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Framingham, MA, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, HBase, Scala, Kafka, NoSQL, CI/CD, Docker</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,32 +4206,32 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=654753ccda866d62</t>
+          <t>https://www.indeed.com/viewjob?jk=e7d77afce6f60e6f</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Sr. Data Architect Specialist</t>
+          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>SAMYANG AMERICA INC</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Brea, CA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,32 +4241,32 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2086e3e44cfc021</t>
+          <t>https://www.indeed.com/viewjob?jk=225c5a8131dc6595</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Full Stack Product Engineer (Java)</t>
+          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Allstate Insurance</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, ELT, CI/CD, Git</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,32 +4276,32 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d15adff582efc740</t>
+          <t>https://www.indeed.com/viewjob?jk=301dbd1e2eb0bb70</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>DevOps &amp; Infrastructure Engineer - Level I</t>
+          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>SPRING ARBOR UNIVERSITY</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Spring Arbor, MI, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Oracle, CI/CD, Jenkins, GitHub Actions, Docker, Jenkins</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,137 +4311,137 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0b216de71eb3804</t>
+          <t>https://www.indeed.com/viewjob?jk=d88e7121c2db79d6</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Software Engineer – Enterprise Software</t>
+          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Rivian</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MySQL, NoSQL, Splunk, Docker, Kubernetes</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90124173401e2437</t>
+          <t>https://www.indeed.com/viewjob?jk=18d3f9fdcfa07035</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer, Enterprise Technology</t>
+          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Rivian</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MySQL, NoSQL, Splunk, Docker, Kubernetes</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fab081dda06a1ba5</t>
+          <t>https://www.indeed.com/viewjob?jk=9d2d16258cfd6718</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Databricks, Spark, Scala, DynamoDB, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f9ad7c8c6b989c1</t>
+          <t>https://www.indeed.com/viewjob?jk=5be8f9b4535b406c</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>QA Analyst / ETL Tester</t>
+          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>CSpring</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Springfield, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>RDS, Azure, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Data Modeling, Snowflake Schema, ETL, CI/CD</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,24 +4451,24 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ebf7b3987a302e8</t>
+          <t>https://www.indeed.com/viewjob?jk=26ef52c65261360a</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer - Python &amp; React JS</t>
+          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Checkmate</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,34 +4476,34 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, PostgreSQL, MySQL, CI/CD, GitHub Actions, Docker, Git, Datadog</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ba3d00c3fb0ee25</t>
+          <t>https://www.indeed.com/viewjob?jk=f9240b7b96545a4d</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Engineer II-Software Development</t>
+          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Microchip Technology</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLOps, CI/CD</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,24 +4521,24 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3013681a0e1c4f81</t>
+          <t>https://www.indeed.com/viewjob?jk=42ae72f7d4a97700</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Engineer II-Software Development</t>
+          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Microchip Technology</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLOps, CI/CD</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4556,24 +4556,24 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2649d75a044fe7bd</t>
+          <t>https://www.indeed.com/viewjob?jk=dab5b1b68cc6402c</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - VAULT</t>
+          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Bloomberg</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Hive, Spark, Scala, Kafka, Cassandra</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,24 +4591,24 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d744cfcd1fce896</t>
+          <t>https://www.indeed.com/viewjob?jk=fde8d1831ca7f9b7</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>BigData ,Python and Py Spark , GCP</t>
+          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>GCP, BigQuery, Hadoop, Hive, Spark, PySpark, Scala, ETL, ELT, Airflow</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,24 +4626,24 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81999129979e18ac</t>
+          <t>https://www.indeed.com/viewjob?jk=7a056659ad4aebd2</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Montefiore Einstein</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Yonkers, NY, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,34 +4651,34 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, Snowflake, Data Modeling, ELT, dbt, CI/CD, Git</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a3ffcafc747cce2</t>
+          <t>https://www.indeed.com/viewjob?jk=e5402962c321dcba</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>FastAPI</t>
+          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,34 +4686,34 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, BigQuery, Vertex AI, Spark, Scala, Spark Streaming, Kafka, CI/CD, Git</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0bc1141188a8604a</t>
+          <t>https://www.indeed.com/viewjob?jk=f45ad39ec1fe503a</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Urology Centers of Alabama</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4721,7 +4721,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, ETL</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4731,24 +4731,24 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28cb24ea6139fcb9</t>
+          <t>https://www.indeed.com/viewjob?jk=86cfc919b4ccc768</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Pearson</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Hoboken, NJ, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, MongoDB, DynamoDB, Data Modeling, ETL, ELT, DataOps, CI/CD</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05547d65aabdfcf0</t>
+          <t>https://www.indeed.com/viewjob?jk=c9a866cff6a0e3bd</t>
         </is>
       </c>
     </row>
@@ -4783,7 +4783,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4801,7 +4801,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34c37a226b547d01</t>
+          <t>https://www.indeed.com/viewjob?jk=ab68f1e4ba82ad10</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4836,7 +4836,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7d77afce6f60e6f</t>
+          <t>https://www.indeed.com/viewjob?jk=df163d5906a30146</t>
         </is>
       </c>
     </row>
@@ -4853,7 +4853,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=225c5a8131dc6595</t>
+          <t>https://www.indeed.com/viewjob?jk=2f0c32c0bdf67710</t>
         </is>
       </c>
     </row>
@@ -4888,7 +4888,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4906,7 +4906,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=301dbd1e2eb0bb70</t>
+          <t>https://www.indeed.com/viewjob?jk=25f63312ec2e267e</t>
         </is>
       </c>
     </row>
@@ -4923,7 +4923,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d88e7121c2db79d6</t>
+          <t>https://www.indeed.com/viewjob?jk=be379ec08f5c5e6f</t>
         </is>
       </c>
     </row>
@@ -4958,7 +4958,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18d3f9fdcfa07035</t>
+          <t>https://www.indeed.com/viewjob?jk=8deeb1ab1ebcdccd</t>
         </is>
       </c>
     </row>
@@ -4993,7 +4993,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5011,7 +5011,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d2d16258cfd6718</t>
+          <t>https://www.indeed.com/viewjob?jk=92aa87419ba8e5df</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5046,7 +5046,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5be8f9b4535b406c</t>
+          <t>https://www.indeed.com/viewjob?jk=da334d3b3eda0eb4</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26ef52c65261360a</t>
+          <t>https://www.indeed.com/viewjob?jk=2c314e6df20a4157</t>
         </is>
       </c>
     </row>
@@ -5098,7 +5098,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5116,7 +5116,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9240b7b96545a4d</t>
+          <t>https://www.indeed.com/viewjob?jk=b90a165cff732e70</t>
         </is>
       </c>
     </row>
@@ -5133,7 +5133,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5151,7 +5151,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42ae72f7d4a97700</t>
+          <t>https://www.indeed.com/viewjob?jk=26bc98921360165c</t>
         </is>
       </c>
     </row>
@@ -5168,7 +5168,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5186,7 +5186,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dab5b1b68cc6402c</t>
+          <t>https://www.indeed.com/viewjob?jk=c5359f322821abe9</t>
         </is>
       </c>
     </row>
@@ -5203,7 +5203,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5221,7 +5221,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fde8d1831ca7f9b7</t>
+          <t>https://www.indeed.com/viewjob?jk=562ea8307dd5c91d</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5256,7 +5256,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a056659ad4aebd2</t>
+          <t>https://www.indeed.com/viewjob?jk=70a64e543cdeb49a</t>
         </is>
       </c>
     </row>
@@ -5273,7 +5273,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5291,7 +5291,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5402962c321dcba</t>
+          <t>https://www.indeed.com/viewjob?jk=ed3e28c9a543299a</t>
         </is>
       </c>
     </row>
@@ -5308,7 +5308,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5326,24 +5326,24 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f45ad39ec1fe503a</t>
+          <t>https://www.indeed.com/viewjob?jk=1735f01363643535</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
+          <t>Data Engineer II, Mobile Game Analytics</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Mattel, Inc.</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>El Segundo, CA, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5351,7 +5351,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
+          <t>RDS, Medallion Architecture, GCP, BigQuery, Dimensional Modeling, ETL, dbt, Tableau, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -5361,24 +5361,24 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86cfc919b4ccc768</t>
+          <t>https://www.indeed.com/viewjob?jk=087868e735e87a06</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
+          <t>Senior Software Engineer - VAULT</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Bloomberg</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5386,7 +5386,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
+          <t>AWS, S3, RDS, Azure, GCP, Hive, Spark, Scala, Kafka, Cassandra</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -5396,24 +5396,24 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9a866cff6a0e3bd</t>
+          <t>https://www.indeed.com/viewjob?jk=1d744cfcd1fce896</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
+          <t>BigData ,Python and Py Spark , GCP</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5421,7 +5421,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
+          <t>GCP, BigQuery, Hadoop, Hive, Spark, PySpark, Scala, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -5431,24 +5431,24 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab68f1e4ba82ad10</t>
+          <t>https://www.indeed.com/viewjob?jk=81999129979e18ac</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
+          <t>Senior Full Stack Engineer - Python &amp; React JS</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Checkmate</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -5456,34 +5456,34 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
+          <t>AWS, RDS, Scala, PostgreSQL, MySQL, CI/CD, GitHub Actions, Docker, Git, Datadog</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df163d5906a30146</t>
+          <t>https://www.indeed.com/viewjob?jk=6ba3d00c3fb0ee25</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
+          <t>Engineer II-Software Development</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Microchip Technology</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -5491,7 +5491,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -5501,24 +5501,24 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f0c32c0bdf67710</t>
+          <t>https://www.indeed.com/viewjob?jk=3013681a0e1c4f81</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
+          <t>Engineer II-Software Development</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Microchip Technology</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -5536,24 +5536,24 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25f63312ec2e267e</t>
+          <t>https://www.indeed.com/viewjob?jk=2649d75a044fe7bd</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Litera</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D147" t="n">
@@ -5561,34 +5561,34 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
+          <t>RDS, Azure, Databricks, Spark, Scala, Snowflake, NoSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be379ec08f5c5e6f</t>
+          <t>https://www.indeed.com/viewjob?jk=cdf1ca20dc48c20f</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
+          <t>Senior Engineer, AI</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Harman</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Novi, MI, US USA</t>
         </is>
       </c>
       <c r="D148" t="n">
@@ -5596,34 +5596,34 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8deeb1ab1ebcdccd</t>
+          <t>https://www.indeed.com/viewjob?jk=4a91d05d9ba98a3a</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Onspring Technologies, LLC</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Overland Park, KS, US USA</t>
         </is>
       </c>
       <c r="D149" t="n">
@@ -5631,34 +5631,34 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, GCP, HBase, Scala, MongoDB, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92aa87419ba8e5df</t>
+          <t>https://www.indeed.com/viewjob?jk=1d56a66deeafe00f</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
+          <t>Senior Data Integration Software Engineer</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D150" t="n">
@@ -5666,34 +5666,34 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, ETL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da334d3b3eda0eb4</t>
+          <t>https://www.indeed.com/viewjob?jk=b035b944f2ad4c37</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
+          <t>Senior Data Integration Software Engineer</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D151" t="n">
@@ -5701,34 +5701,34 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, ETL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c314e6df20a4157</t>
+          <t>https://www.indeed.com/viewjob?jk=9ba6e4aacd5b6631</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
+          <t>Data Integration Software Engineer</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Portsmouth, NH, US USA</t>
         </is>
       </c>
       <c r="D152" t="n">
@@ -5736,34 +5736,34 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, ETL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b90a165cff732e70</t>
+          <t>https://www.indeed.com/viewjob?jk=c4c7e0f49df408be</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
+          <t>Senior Data Integration Software Engineer</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Portsmouth, NH, US USA</t>
         </is>
       </c>
       <c r="D153" t="n">
@@ -5771,34 +5771,34 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, ETL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26bc98921360165c</t>
+          <t>https://www.indeed.com/viewjob?jk=93164fc43ac74193</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
+          <t>Data Integration Software Engineer</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D154" t="n">
@@ -5806,34 +5806,34 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, ETL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5359f322821abe9</t>
+          <t>https://www.indeed.com/viewjob?jk=12a4fd124772d9d2</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
+          <t>Data Integration Software Engineer</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D155" t="n">
@@ -5841,34 +5841,34 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, ETL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=562ea8307dd5c91d</t>
+          <t>https://www.indeed.com/viewjob?jk=c38e2fae9b46f905</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
+          <t>Sr. Software Engineer, Full-Stack (Factory Systems)</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Rivian and Volkswagen Group Technologies</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D156" t="n">
@@ -5876,34 +5876,34 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70a64e543cdeb49a</t>
+          <t>https://www.indeed.com/viewjob?jk=68c700567606c4e9</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
+          <t>Sr Associate Engineer/Engineer, IT Software</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D157" t="n">
@@ -5911,7 +5911,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -5921,24 +5921,24 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed3e28c9a543299a</t>
+          <t>https://www.indeed.com/viewjob?jk=cf657c9771abb6db</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
+          <t>Data Scientist, Senior Associate – Product, Experience and Technology (PXT) Analytics Team</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D158" t="n">
@@ -5946,34 +5946,34 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
+          <t>Redshift, RDS, Databricks, Scala, Snowflake, dbt, Tableau, CI/CD, Airflow, Git</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1735f01363643535</t>
+          <t>https://www.indeed.com/viewjob?jk=4b0bfe4f7e93a067</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Data Engineer II, Mobile Game Analytics</t>
+          <t>Enterprise AI Architect</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Mattel, Inc.</t>
+          <t>Radwell International</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>El Segundo, CA, US USA</t>
+          <t>Willingboro, NJ, US USA</t>
         </is>
       </c>
       <c r="D159" t="n">
@@ -5981,34 +5981,34 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>RDS, Medallion Architecture, GCP, BigQuery, Dimensional Modeling, ETL, dbt, Tableau, CI/CD, Airflow</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, PostgreSQL, MySQL, NoSQL, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=087868e735e87a06</t>
+          <t>https://www.indeed.com/viewjob?jk=56c80236c3727026</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Senior Engineer, AI</t>
+          <t>AI Engineer Clinical Data Science</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Harman</t>
+          <t>Katalyst Healthcares &amp; Life Sciences</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Novi, MI, US USA</t>
+          <t>Manhattan, NY, US USA</t>
         </is>
       </c>
       <c r="D160" t="n">
@@ -6016,435 +6016,15 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Google Cloud Platform, GCP, Vertex AI, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker, Git</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4a91d05d9ba98a3a</t>
-        </is>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="inlineStr">
-        <is>
-          <t>Senior Data Integration Software Engineer</t>
-        </is>
-      </c>
-      <c r="B161" t="inlineStr">
-        <is>
-          <t>Liberty Mutual Insurance</t>
-        </is>
-      </c>
-      <c r="C161" t="inlineStr">
-        <is>
-          <t>Plano, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D161" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E161" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, ETL, CI/CD, Git</t>
-        </is>
-      </c>
-      <c r="F161" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="G161" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b035b944f2ad4c37</t>
-        </is>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="inlineStr">
-        <is>
-          <t>Senior Data Integration Software Engineer</t>
-        </is>
-      </c>
-      <c r="B162" t="inlineStr">
-        <is>
-          <t>Liberty Mutual Insurance</t>
-        </is>
-      </c>
-      <c r="C162" t="inlineStr">
-        <is>
-          <t>Boston, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D162" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E162" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, ETL, CI/CD, Git</t>
-        </is>
-      </c>
-      <c r="F162" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="G162" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9ba6e4aacd5b6631</t>
-        </is>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="inlineStr">
-        <is>
-          <t>Senior Data Integration Software Engineer</t>
-        </is>
-      </c>
-      <c r="B163" t="inlineStr">
-        <is>
-          <t>Liberty Mutual Insurance</t>
-        </is>
-      </c>
-      <c r="C163" t="inlineStr">
-        <is>
-          <t>Portsmouth, NH, US USA</t>
-        </is>
-      </c>
-      <c r="D163" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E163" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, ETL, CI/CD, Git</t>
-        </is>
-      </c>
-      <c r="F163" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="G163" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=93164fc43ac74193</t>
-        </is>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="inlineStr">
-        <is>
-          <t>Data Integration Software Engineer</t>
-        </is>
-      </c>
-      <c r="B164" t="inlineStr">
-        <is>
-          <t>Liberty Mutual Insurance</t>
-        </is>
-      </c>
-      <c r="C164" t="inlineStr">
-        <is>
-          <t>Portsmouth, NH, US USA</t>
-        </is>
-      </c>
-      <c r="D164" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E164" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, ETL, CI/CD, Git</t>
-        </is>
-      </c>
-      <c r="F164" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="G164" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c4c7e0f49df408be</t>
-        </is>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="inlineStr">
-        <is>
-          <t>Data Integration Software Engineer</t>
-        </is>
-      </c>
-      <c r="B165" t="inlineStr">
-        <is>
-          <t>Liberty Mutual Insurance</t>
-        </is>
-      </c>
-      <c r="C165" t="inlineStr">
-        <is>
-          <t>Boston, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D165" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E165" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, ETL, CI/CD, Git</t>
-        </is>
-      </c>
-      <c r="F165" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="G165" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=12a4fd124772d9d2</t>
-        </is>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="inlineStr">
-        <is>
-          <t>Data Integration Software Engineer</t>
-        </is>
-      </c>
-      <c r="B166" t="inlineStr">
-        <is>
-          <t>Liberty Mutual Insurance</t>
-        </is>
-      </c>
-      <c r="C166" t="inlineStr">
-        <is>
-          <t>Plano, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D166" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E166" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, ETL, CI/CD, Git</t>
-        </is>
-      </c>
-      <c r="F166" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="G166" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c38e2fae9b46f905</t>
-        </is>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" t="inlineStr">
-        <is>
-          <t>Software Engineer - AI Augmented Development</t>
-        </is>
-      </c>
-      <c r="B167" t="inlineStr">
-        <is>
-          <t>PowerPay</t>
-        </is>
-      </c>
-      <c r="C167" t="inlineStr">
-        <is>
-          <t>Wayne, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D167" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E167" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, SQS, ECS, IAM, RDS, Snowflake, ETL, Terraform</t>
-        </is>
-      </c>
-      <c r="F167" t="inlineStr">
-        <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="G167" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=039bac65ddb8c30e</t>
-        </is>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" t="inlineStr">
-        <is>
-          <t>Sr. Software Engineer, Full-Stack (Factory Systems)</t>
-        </is>
-      </c>
-      <c r="B168" t="inlineStr">
-        <is>
-          <t>Rivian and Volkswagen Group Technologies</t>
-        </is>
-      </c>
-      <c r="C168" t="inlineStr">
-        <is>
-          <t>Palo Alto, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D168" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E168" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F168" t="inlineStr">
-        <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="G168" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=68c700567606c4e9</t>
-        </is>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" t="inlineStr">
-        <is>
-          <t>Sr Associate Engineer/Engineer, IT Software</t>
-        </is>
-      </c>
-      <c r="B169" t="inlineStr">
-        <is>
-          <t>American Airlines</t>
-        </is>
-      </c>
-      <c r="C169" t="inlineStr">
-        <is>
-          <t>Fort Worth, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D169" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E169" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F169" t="inlineStr">
-        <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="G169" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=cf657c9771abb6db</t>
-        </is>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" t="inlineStr">
-        <is>
-          <t>Data Scientist, Senior Associate – Product, Experience and Technology (PXT) Analytics Team</t>
-        </is>
-      </c>
-      <c r="B170" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C170" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D170" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E170" t="inlineStr">
-        <is>
-          <t>Redshift, RDS, Databricks, Scala, Snowflake, dbt, Tableau, CI/CD, Airflow, Git</t>
-        </is>
-      </c>
-      <c r="F170" t="inlineStr">
-        <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="G170" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4b0bfe4f7e93a067</t>
-        </is>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" t="inlineStr">
-        <is>
-          <t>Enterprise AI Architect</t>
-        </is>
-      </c>
-      <c r="B171" t="inlineStr">
-        <is>
-          <t>Radwell International</t>
-        </is>
-      </c>
-      <c r="C171" t="inlineStr">
-        <is>
-          <t>Willingboro, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D171" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E171" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, PostgreSQL, MySQL, NoSQL, MLOps, CI/CD</t>
-        </is>
-      </c>
-      <c r="F171" t="inlineStr">
-        <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="G171" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=56c80236c3727026</t>
-        </is>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" t="inlineStr">
-        <is>
-          <t>AI Engineer Clinical Data Science</t>
-        </is>
-      </c>
-      <c r="B172" t="inlineStr">
-        <is>
-          <t>Katalyst Healthcares &amp; Life Sciences</t>
-        </is>
-      </c>
-      <c r="C172" t="inlineStr">
-        <is>
-          <t>Manhattan, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D172" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E172" t="inlineStr">
-        <is>
-          <t>RDS, Google Cloud Platform, GCP, Vertex AI, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker, Git</t>
-        </is>
-      </c>
-      <c r="F172" t="inlineStr">
-        <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="G172" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=47a06a95eff2f8b1</t>
         </is>

--- a/results/job_matches_2026-05-06.xlsx
+++ b/results/job_matches_2026-05-06.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G160"/>
+  <dimension ref="A1:G158"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,60 +468,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Capital Bank, N.A.</t>
+          <t>AMB Sports + Entertainment</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Rockville, MD, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>19.4</v>
+        <v>22.2</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Data Factory, BigQuery, Spark, Scala, Kafka, Snowflake, SQL Server</t>
+          <t>AWS, RDS, Azure, Databricks, Event Hubs, Unity Catalog, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3488abdd8c4dc725</t>
+          <t>https://www.indeed.com/viewjob?jk=0fac751a341ffed9</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>Capital Bank, N.A.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Rockville, MD, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>18.8</v>
+        <v>19.4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, S3, RDS, Azure, Data Factory, Databricks, GCP, Spark</t>
+          <t>Redshift, RDS, Azure, Data Factory, BigQuery, Spark, Scala, Kafka, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,7 +531,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad171c93c1899d21</t>
+          <t>https://www.indeed.com/viewjob?jk=3488abdd8c4dc725</t>
         </is>
       </c>
     </row>
@@ -543,47 +543,47 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>Analytica</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.8</v>
+        <v>18.1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, S3, RDS, Azure, Data Factory, Databricks, GCP, Spark</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, IAM, RDS, Azure, Databricks</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98f8265780f793dd</t>
+          <t>https://www.indeed.com/viewjob?jk=7d9377a4724bf38c</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Analytica</t>
+          <t>Warner Bros. Discovery</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,17 +591,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, IAM, RDS, Azure, Databricks</t>
+          <t>AWS, Glue, EMR, Kinesis, Redshift, Athena, S3, RDS, Azure, Databricks</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d9377a4724bf38c</t>
+          <t>https://www.indeed.com/viewjob?jk=0585eb3ca3cd8f48</t>
         </is>
       </c>
     </row>
@@ -636,7 +636,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0585eb3ca3cd8f48</t>
+          <t>https://www.indeed.com/viewjob?jk=ea66a6dbd0690c3b</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea66a6dbd0690c3b</t>
+          <t>https://www.indeed.com/viewjob?jk=ec9442df01efef1b</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec9442df01efef1b</t>
+          <t>https://www.indeed.com/viewjob?jk=341798717a6ce508</t>
         </is>
       </c>
     </row>
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=341798717a6ce508</t>
+          <t>https://www.indeed.com/viewjob?jk=29381ac7399ddbb0</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer, Cloud Infrastructure (Multiple Seniority Levels)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Warner Bros. Discovery</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Carlos, CA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Kinesis, Redshift, Athena, S3, RDS, Azure, Databricks</t>
+          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, SQS, ECS, IAM, RDS</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,94 +776,94 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29381ac7399ddbb0</t>
+          <t>https://www.indeed.com/viewjob?jk=07cee960b10bf15e</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Software Engineer, Cloud Infrastructure (Multiple Seniority Levels)</t>
+          <t>Azure Network Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>San Carlos, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, SQS, ECS, IAM, RDS</t>
+          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Event Hubs, Unity Catalog, Medallion Architecture, Spark, PySpark</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07cee960b10bf15e</t>
+          <t>https://www.indeed.com/viewjob?jk=b4c4141e761a1d57</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Commercial IT Senior Data Solution Developer</t>
+          <t>Health Account Intern</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ConocoPhillips</t>
+          <t>Booz Allen Hamilton</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hive, Spark, Scala, Kafka, Snowflake, NoSQL</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Databricks, Hadoop, Hive, Spark, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1304cb2ffae316c6</t>
+          <t>https://www.indeed.com/viewjob?jk=64329d0d0bf86853</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Health Account Intern</t>
+          <t>Compliance, Senior Backend Engineer (Java &amp; ETL Specialist), Dallas, Associate</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Booz Allen Hamilton</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Databricks, Hadoop, Hive, Spark, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64329d0d0bf86853</t>
+          <t>https://www.indeed.com/viewjob?jk=e21fade0470597e2</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Azure Network Engineer</t>
+          <t>Sr Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Commence</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Leesburg, VA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Event Hubs, Unity Catalog, Medallion Architecture, Spark, PySpark</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, NoSQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4c4141e761a1d57</t>
+          <t>https://www.indeed.com/viewjob?jk=9093ede7f2269db2</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Sr Site Reliability Engineer</t>
+          <t>Sr Data Engineer, Python + Spark (Data Federation skillset - Data Lakehouse - Eg: Starburst) - New York</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Commence</t>
+          <t>Photon</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Leesburg, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,34 +941,34 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, NoSQL, ETL, ELT</t>
+          <t>AWS, Glue, EMR, S3, Azure, Databricks, Medallion Architecture, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9093ede7f2269db2</t>
+          <t>https://www.indeed.com/viewjob?jk=f7767a92d7d08a3b</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Sr Data Engineer, Python + Spark (Data Federation skillset - Data Lakehouse - Eg: Starburst) - New York</t>
+          <t>Databricks Engineer and Architect</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Photon</t>
+          <t>Lincoln Financial Group</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Radnor, PA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,34 +976,34 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, S3, Azure, Databricks, Medallion Architecture, GCP, Spark, PySpark</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, RDS, Databricks, Unity Catalog</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7767a92d7d08a3b</t>
+          <t>https://www.indeed.com/viewjob?jk=d7862c3c59e06d56</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Databricks Engineer and Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Lincoln Financial Group</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Radnor, PA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,17 +1011,17 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, RDS, Databricks, Unity Catalog</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, RDS, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7862c3c59e06d56</t>
+          <t>https://www.indeed.com/viewjob?jk=df1902d36083d34f</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df1902d36083d34f</t>
+          <t>https://www.indeed.com/viewjob?jk=5cb867686433b7a1</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cb867686433b7a1</t>
+          <t>https://www.indeed.com/viewjob?jk=3aeafc948a2f0f6c</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3aeafc948a2f0f6c</t>
+          <t>https://www.indeed.com/viewjob?jk=c45b322f3e5694ad</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer Intern</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Norstella</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,42 +1151,42 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, RDS, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Azure, Blob Storage, GCP, PostgreSQL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c45b322f3e5694ad</t>
+          <t>https://www.indeed.com/viewjob?jk=49a129c7a487aae4</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Software Engineer Intern</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Norstella</t>
+          <t>Verisk</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Azure, Blob Storage, GCP, PostgreSQL</t>
+          <t>AWS, Glue, Lambda, Athena, S3, RDS, Spark, Scala, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49a129c7a487aae4</t>
+          <t>https://www.indeed.com/viewjob?jk=cb57edcbdb36ad26</t>
         </is>
       </c>
     </row>
@@ -1238,17 +1238,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>API Threat Intelligence Analyst</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Verisk</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,24 +1256,24 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, S3, RDS, Spark, Scala, PostgreSQL, Data Modeling</t>
+          <t>Azure, Google Cloud Platform, Kafka, NoSQL, Data Modeling, ETL, Talend, Tableau, Splunk, MicroStrategy</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb57edcbdb36ad26</t>
+          <t>https://www.indeed.com/viewjob?jk=e918fa70b2a1920e</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>API Threat Intelligence Analyst</t>
+          <t>Backend (Python)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e918fa70b2a1920e</t>
+          <t>https://www.indeed.com/viewjob?jk=d711bd4394cb404e</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Backend (Python)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Wavicle Data Solutions</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Oak Brook, IL, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Azure, Google Cloud Platform, Kafka, NoSQL, Data Modeling, ETL, Talend, Tableau, Splunk, MicroStrategy</t>
+          <t>AWS, Lambda, Redshift, Azure, Databricks, GCP, Hadoop, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d711bd4394cb404e</t>
+          <t>https://www.indeed.com/viewjob?jk=a435f9b94ff5d489</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Engineer (Databricks)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Wavicle Data Solutions</t>
+          <t>Infinitive Inc</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>Ashburn, VA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,34 +1361,34 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, Azure, Databricks, GCP, Hadoop, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, S3, Azure, Databricks, Unity Catalog, GCP</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a435f9b94ff5d489</t>
+          <t>https://www.indeed.com/viewjob?jk=aee5e62267dbbb6c</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Developer II</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Netsecure360</t>
+          <t>Floor &amp; Decor</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Cloud Storage, Hadoop, Hive, Spark, Scala, Kafka, Oracle</t>
+          <t>RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,67 +1406,67 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca7e816524d9406c</t>
+          <t>https://www.indeed.com/viewjob?jk=4a21fec712255df2</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Databricks)</t>
+          <t>Sr. Streaming Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Infinitive Inc</t>
+          <t>Ness Digital Engineering</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, S3, Azure, Databricks, Unity Catalog, GCP</t>
+          <t>AWS, Kinesis, S3, IAM, RDS, Spark, Scala, Kafka, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aee5e62267dbbb6c</t>
+          <t>https://www.indeed.com/viewjob?jk=f90fa0ab3164dcd1</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Software Developer II</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Floor &amp; Decor</t>
+          <t>SOFTILITY INC</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL, Splunk, CI/CD</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a21fec712255df2</t>
+          <t>https://www.indeed.com/viewjob?jk=3faf69463891ca3f</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>SOFTILITY INC</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Oracle, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,14 +1511,14 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3faf69463891ca3f</t>
+          <t>https://www.indeed.com/viewjob?jk=d61e7d7639acc074</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>MLOps Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Oracle, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d61e7d7639acc074</t>
+          <t>https://www.indeed.com/viewjob?jk=56f1aa48ba26ae3c</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Sr. Streaming Engineer</t>
+          <t>Business Intelligence Developer (Healthcare Data, EDI, ETL)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Ness Digital Engineering</t>
+          <t>MicroHealth LLC</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Vienna, VA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, IAM, RDS, Spark, Scala, Kafka, NoSQL, Splunk</t>
+          <t>AWS, EMR, RDS, Scala, Snowflake, SQL Server, PostgreSQL, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,94 +1581,94 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f90fa0ab3164dcd1</t>
+          <t>https://www.indeed.com/viewjob?jk=3ba3d7e28ab6494c</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>MLOps Engineer</t>
+          <t>Senior Data analyst</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Brentwood, TN, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56f1aa48ba26ae3c</t>
+          <t>https://www.indeed.com/viewjob?jk=b7ed131be5ba5e96</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Business Intelligence Developer (Healthcare Data, EDI, ETL)</t>
+          <t>Cloud Network Architect</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>MicroHealth LLC</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Vienna, VA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Scala, Snowflake, SQL Server, PostgreSQL, Snowflake Schema, ETL, ELT</t>
+          <t>API Gateway, IAM, RDS, Google Cloud Platform, BigQuery, Dataflow, Scala, Kafka, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ba3d7e28ab6494c</t>
+          <t>https://www.indeed.com/viewjob?jk=3552e9ee02097f2c</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Data analyst</t>
+          <t>Mid- Level Data Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Vantage Data Centers</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Brentwood, TN, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, ETL</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Spark, PySpark, Scala, Data Modeling, Dimension Tables, ETL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7ed131be5ba5e96</t>
+          <t>https://www.indeed.com/viewjob?jk=a35201e2c76024aa</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Mid- Level Data Engineer</t>
+          <t>Senior Site Reliability Engineer, Data &amp; Analytics</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Vantage Data Centers</t>
+          <t>Blizzard Entertainment</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,139 +1711,139 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Spark, PySpark, Scala, Data Modeling, Dimension Tables, ETL</t>
+          <t>AWS, RDS, GCP, BigQuery, Dataflow, Kafka, dbt, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a35201e2c76024aa</t>
+          <t>https://www.indeed.com/viewjob?jk=f56eabb97941a731</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer, Data &amp; Analytics</t>
+          <t>Data Solutions Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Blizzard Entertainment</t>
+          <t>Epsilon</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Dataflow, Kafka, dbt, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Databricks, Hadoop, HDFS, Spark, Scala, Kafka, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f56eabb97941a731</t>
+          <t>https://www.indeed.com/viewjob?jk=22c6237fafdb9308</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Kroll Inc.</t>
+          <t>vectorsoft</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Scala, Polars, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d56048c057634cd1</t>
+          <t>https://www.indeed.com/viewjob?jk=3bdce3e69ca5f6c4</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Cloud Network Architect</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Miami Marlins</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>API Gateway, IAM, RDS, Google Cloud Platform, BigQuery, Dataflow, Scala, Kafka, CI/CD, Jenkins</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, GCP, Scala, Snowflake, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3552e9ee02097f2c</t>
+          <t>https://www.indeed.com/viewjob?jk=ff87deef607d5450</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Data Solutions Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Epsilon</t>
+          <t>Paramount</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Fort Lauderdale, FL, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,34 +1851,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Hadoop, HDFS, Spark, Scala, Kafka, CI/CD, Docker</t>
+          <t>AWS, RDS, GCP, BigQuery, Dataflow, Scala, MongoDB, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22c6237fafdb9308</t>
+          <t>https://www.indeed.com/viewjob?jk=a12925c69dfc7bed</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI Agent Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>vectorsoft</t>
+          <t>Momentive Software</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,34 +1886,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>AWS, Lambda, Athena, SQS, SNS, API Gateway, ECS, RDS, Azure, GCP</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3bdce3e69ca5f6c4</t>
+          <t>https://www.indeed.com/viewjob?jk=6ac9574b3f75cc2c</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Azure Network Engineer</t>
+          <t>Data Engineer / Data Platform Engineer Internship Fall 2026 Semester at the Dow Delivery Center at UIUC (Champaign, IL)</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>DOW</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Kankakee, IL, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage, MySQL, Splunk, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bb3e3385b26a0b5</t>
+          <t>https://www.indeed.com/viewjob?jk=38a9f118a8e8f0ac</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Cloud Gateway</t>
+          <t>Azure Network Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Rivian and Volkswagen Group Technologies</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, MongoDB, DynamoDB, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>IAM, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage, MySQL, Splunk, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b72e865e6bee153</t>
+          <t>https://www.indeed.com/viewjob?jk=8bb3e3385b26a0b5</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Cloud Database Engineer (Hybrid - Seattle, WA)</t>
+          <t>Senior Software Engineer - Cloud Gateway</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Nordstrom</t>
+          <t>Rivian and Volkswagen Group Technologies</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,17 +1991,17 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Redshift, Athena, S3, RDS, Kafka, Oracle, SQL Server</t>
+          <t>AWS, RDS, Scala, Kafka, MongoDB, DynamoDB, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1666a61865ef57aa</t>
+          <t>https://www.indeed.com/viewjob?jk=7b72e865e6bee153</t>
         </is>
       </c>
     </row>
@@ -2043,17 +2043,17 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Data Engineer (ETL / Python Developer)</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Paramount</t>
+          <t>CSpring</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Fort Lauderdale, FL, US USA</t>
+          <t>Springfield, IL, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Dataflow, Scala, MongoDB, NoSQL, Docker, Kubernetes</t>
+          <t>Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a12925c69dfc7bed</t>
+          <t>https://www.indeed.com/viewjob?jk=b861e2c1a0a03133</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Data Engineer (ETL / Python Developer)</t>
+          <t>Senior Data Engineer (Python/PySpark/AWS)</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>CSpring</t>
+          <t>Infinitive Inc</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Springfield, IL, US USA</t>
+          <t>Ashburn, VA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,34 +2096,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, Azure, Spark, PySpark, Scala, Spark Streaming, Data Modeling, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2025-02-18</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b861e2c1a0a03133</t>
+          <t>https://www.indeed.com/viewjob?jk=45083db400feff94</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer (Python/PySpark/AWS)</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Imprint</t>
+          <t>Infinitive Inc</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Ashburn, VA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,34 +2131,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Kinesis, S3, RDS, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, Azure, Spark, PySpark, Scala, Spark Streaming, Data Modeling, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2025-01-27</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e35bafcce4ab1000</t>
+          <t>https://www.indeed.com/viewjob?jk=5e742c4bedd2037b</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Imprint</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,34 +2166,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Kinesis, S3, RDS, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>IAM, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage, MySQL, Splunk, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=baaf38c4500e2b06</t>
+          <t>https://www.indeed.com/viewjob?jk=52b0e598b9832c43</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior AI Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Velvetech</t>
+          <t>Terra Quantum</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Vertex AI, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2bec7882b34f08c9</t>
+          <t>https://www.indeed.com/viewjob?jk=15eb90498bcba242</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Full Stack Engineer, Experienced</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Blue Shield of California</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Westminster, CO, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d49164a52434e329</t>
+          <t>https://www.indeed.com/viewjob?jk=93fe5a9749607800</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Software Engineer - Cloud</t>
+          <t>Full Stack Engineer, Senior</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Carnegie Robotics LLC</t>
+          <t>Blue Shield of California</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,34 +2271,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, PostgreSQL, MongoDB, DynamoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2f5b0b9c556cdca</t>
+          <t>https://www.indeed.com/viewjob?jk=bcc6fa1baccf83e5</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Python/PySpark/AWS)</t>
+          <t>Full Stack Engineer, Consultant</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Infinitive Inc</t>
+          <t>Blue Shield of California</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,34 +2306,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Azure, Spark, PySpark, Scala, Spark Streaming, Data Modeling, ETL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2025-02-18</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45083db400feff94</t>
+          <t>https://www.indeed.com/viewjob?jk=a3a7d3c5d7336760</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Engineer (Python/PySpark/AWS)</t>
+          <t>Summer Intern, Platform Engineering</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Infinitive Inc</t>
+          <t>Outfront Media</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Azure, Spark, PySpark, Scala, Spark Streaming, Data Modeling, ETL, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, S3, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2025-01-27</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e742c4bedd2037b</t>
+          <t>https://www.indeed.com/viewjob?jk=2aa35bb9483f10ad</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Artificial Intelligence/Machine Learning Data Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Miami Marlins</t>
+          <t>Accenture</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, GCP, Scala, Snowflake, CI/CD, GitHub Actions</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLflow</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff87deef607d5450</t>
+          <t>https://www.indeed.com/viewjob?jk=b20f553bf3557e7a</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>AI Agent Engineer</t>
+          <t>Data Warehouse Developer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Momentive Software</t>
+          <t>New England Life Care</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Canton, MA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Athena, SQS, SNS, API Gateway, ECS, RDS, Azure, GCP</t>
+          <t>AWS, Azure, Data Factory, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, Fact Tables, Dimension Tables</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ac9574b3f75cc2c</t>
+          <t>https://www.indeed.com/viewjob?jk=b61fd67550df6c0b</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>Data Warehouse Developer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>New England Life Care</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Woburn, MA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage, MySQL, Splunk, CI/CD, GitHub Actions</t>
+          <t>AWS, Azure, Data Factory, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, Fact Tables, Dimension Tables</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52b0e598b9832c43</t>
+          <t>https://www.indeed.com/viewjob?jk=59fae488bfb069d7</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Warehouse Developer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Terra Quantum</t>
+          <t>New England Life Care</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Scarborough, ME, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, Azure, Data Factory, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, Fact Tables, Dimension Tables</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15eb90498bcba242</t>
+          <t>https://www.indeed.com/viewjob?jk=c511d00669b005c9</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Full Stack Engineer, Experienced</t>
+          <t>Data Warehouse Developer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Blue Shield of California</t>
+          <t>New England Life Care</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Concord, NH, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,42 +2516,42 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, NoSQL, CI/CD, Terraform</t>
+          <t>AWS, Azure, Data Factory, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, Fact Tables, Dimension Tables</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93fe5a9749607800</t>
+          <t>https://www.indeed.com/viewjob?jk=9e02714fa8eb1d57</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Full Stack Engineer, Senior</t>
+          <t>Mid-Level Software Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Blue Shield of California</t>
+          <t>State Farm</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Bloomington, IL, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, NoSQL, CI/CD, Terraform</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, MongoDB, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,102 +2561,102 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bcc6fa1baccf83e5</t>
+          <t>https://www.indeed.com/viewjob?jk=da08c5cf76c3287c</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Full Stack Engineer, Consultant</t>
+          <t>DevOps / AgentOps Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Blue Shield of California</t>
+          <t>Revelation Pharma</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, NoSQL, CI/CD, Terraform</t>
+          <t>AWS, Lambda, Step Functions, S3, ECS, IAM, RDS, Azure, Vertex AI, CI/CD</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3a7d3c5d7336760</t>
+          <t>https://www.indeed.com/viewjob?jk=265eee1218fa6fae</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Summer Intern, Platform Engineering</t>
+          <t>Cloud Network Architect</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Outfront Media</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD, Docker</t>
+          <t>Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2aa35bb9483f10ad</t>
+          <t>https://www.indeed.com/viewjob?jk=e874dfda20060e92</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Artificial Intelligence/Machine Learning Data Engineer</t>
+          <t>Azure Network Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Accenture</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLflow</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Event Hubs, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b20f553bf3557e7a</t>
+          <t>https://www.indeed.com/viewjob?jk=05dcb2c14af656a8</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Cloud Network Architect</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Clayco</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e874dfda20060e92</t>
+          <t>https://www.indeed.com/viewjob?jk=61cc49187bd6e01d</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Azure Network Engineer</t>
+          <t>Data Engineering - E&amp;A - Data Engineer I</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Genesis Global Group</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Myrtle Point, OR, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Event Hubs, Spark, PySpark, Scala, ETL</t>
+          <t>Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05dcb2c14af656a8</t>
+          <t>https://www.indeed.com/viewjob?jk=2526bf14df16c3e8</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Data Systems Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Clayco</t>
+          <t>Central Health</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61cc49187bd6e01d</t>
+          <t>https://www.indeed.com/viewjob?jk=41eed22913274d81</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data Engineering - E&amp;A - Data Engineer I</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Genesis Global Group</t>
+          <t>Laural Parke</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Myrtle Point, OR, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2526bf14df16c3e8</t>
+          <t>https://www.indeed.com/viewjob?jk=19dac2449c2108f4</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Senior DevOps Software Engineer, Firmware &amp; CI/CD</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Versant</t>
+          <t>Rivian and Volkswagen Group Technologies</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, GCP, Spark, NoSQL, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fbef82ce93a90ed</t>
+          <t>https://www.indeed.com/viewjob?jk=d5f621c8ad4f69fd</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Data Systems Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Central Health</t>
+          <t>Victory Live</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Data Factory, Snowflake, SQL Server, DynamoDB, ELT, dbt, Terraform</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41eed22913274d81</t>
+          <t>https://www.indeed.com/viewjob?jk=a1c259f0b00d1299</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Full Stack Data Engineer</t>
+          <t>Cloud Networking Consultant</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Millennium Management</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>KS, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, NoSQL, ELT, dbt, CI/CD, Jenkins, GitHub Actions</t>
+          <t>RDS, Spark, Scala, Kafka, Snowflake, Splunk, CI/CD, Jenkins, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b224fb124b25e580</t>
+          <t>https://www.indeed.com/viewjob?jk=05bc8504be04f7d2</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Laural Parke</t>
+          <t>Montefiore Einstein</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Yonkers, NY, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Medallion Architecture, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ELT, dbt</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19dac2449c2108f4</t>
+          <t>https://www.indeed.com/viewjob?jk=2d972b31a0cae529</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Mid-Level Software Engineer</t>
+          <t>Snowflake/Tableau Developer / Dallas Texas</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>State Farm</t>
+          <t>FirstNet Global</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Bloomington, IL, US USA</t>
+          <t>Napa, CA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, MongoDB, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da08c5cf76c3287c</t>
+          <t>https://www.indeed.com/viewjob?jk=a4ab4d99e440e9b4</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior DevOps Software Engineer, Firmware &amp; CI/CD</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Rivian and Volkswagen Group Technologies</t>
+          <t>Klaxontech</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,172 +3016,172 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5f621c8ad4f69fd</t>
+          <t>https://www.indeed.com/viewjob?jk=193935f590ab7020</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer with Python</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Victory Live</t>
+          <t>Tardus inc</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Snowflake, SQL Server, DynamoDB, ELT, dbt, Terraform</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1c259f0b00d1299</t>
+          <t>https://www.indeed.com/viewjob?jk=80c45bbb6f084151</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Cloud Networking Consultant</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>KS, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>RDS, Spark, Scala, Kafka, Snowflake, Splunk, CI/CD, Jenkins, Docker, Jenkins</t>
+          <t>RDS, GCP, BigQuery, Dataflow, Vertex AI, Scala, Data Modeling, Jenkins, Terraform, Jenkins</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05bc8504be04f7d2</t>
+          <t>https://www.indeed.com/viewjob?jk=4bbf23a169f18dbc</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Montefiore Einstein</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Yonkers, NY, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Medallion Architecture, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ELT, dbt</t>
+          <t>RDS, GCP, BigQuery, Dataflow, Vertex AI, Scala, Data Modeling, Jenkins, Terraform, Jenkins</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d972b31a0cae529</t>
+          <t>https://www.indeed.com/viewjob?jk=4b05514433681d42</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Snowflake/Tableau Developer / Dallas Texas</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>FirstNet Global</t>
+          <t>Clark Construction</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Napa, CA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Azure, GCP, Spark, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, dbt</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4ab4d99e440e9b4</t>
+          <t>https://www.indeed.com/viewjob?jk=6f199bfc2e975b58</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>SSIS / Azure Data Factory Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Klaxontech</t>
+          <t>Intone Networks</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Blob Storage, Scala, SQL Server, ETL, Power BI</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=193935f590ab7020</t>
+          <t>https://www.indeed.com/viewjob?jk=85c3cae0c83282a2</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Engineer Biloxi 5139</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Keesler Federal Credit Union</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Biloxi, MS, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, Data Modeling, ETL, ELT</t>
+          <t>RDS, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, CI/CD, Git</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c98f634775f326c6</t>
+          <t>https://www.indeed.com/viewjob?jk=923871eb4e708d96</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Sr. Professional, Software Engineering (Python)</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Cotality</t>
+          <t>Mango Chamba, LLC</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,34 +3251,34 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, Tableau, CI/CD, Terraform</t>
+          <t>AWS, ECS, RDS, Scala, Snowflake, Time Travel, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83e013cc49a29087</t>
+          <t>https://www.indeed.com/viewjob?jk=76b38f99ba86c67f</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Mesa Labs</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Lakewood, CO, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,34 +3286,34 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Vertex AI, Scala, Data Modeling, Jenkins, Terraform, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, PostgreSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bbf23a169f18dbc</t>
+          <t>https://www.indeed.com/viewjob?jk=71d54ee3197b525a</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Google Cloud Network Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,34 +3321,34 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Vertex AI, Scala, Data Modeling, Jenkins, Terraform, Jenkins</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b05514433681d42</t>
+          <t>https://www.indeed.com/viewjob?jk=c8d74c6d08304ab9</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Clark Construction</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,34 +3356,34 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, dbt</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f199bfc2e975b58</t>
+          <t>https://www.indeed.com/viewjob?jk=c98f634775f326c6</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Platform/DevOps Engineer (Kubernetes-Linux)</t>
+          <t>Sr. Professional, Software Engineering (Python)</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>ARMADA</t>
+          <t>Cotality</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, Tableau, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b0e9b75e0f5558d</t>
+          <t>https://www.indeed.com/viewjob?jk=83e013cc49a29087</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Sammamish, WA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=efa4e4e3099a0ae2</t>
+          <t>https://www.indeed.com/viewjob?jk=7b0e9b75e0f5558d</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Kirkland, WA, US USA</t>
+          <t>Sammamish, WA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33ae1f1f9d08c546</t>
+          <t>https://www.indeed.com/viewjob?jk=efa4e4e3099a0ae2</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Renton, WA, US USA</t>
+          <t>Kirkland, WA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d25130b996402485</t>
+          <t>https://www.indeed.com/viewjob?jk=33ae1f1f9d08c546</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Bothell, WA, US USA</t>
+          <t>Renton, WA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6f9224460f3210c</t>
+          <t>https://www.indeed.com/viewjob?jk=d25130b996402485</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Redmond, WA, US USA</t>
+          <t>Bothell, WA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b86c940f686047d8</t>
+          <t>https://www.indeed.com/viewjob?jk=b6f9224460f3210c</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Platform/DevOps Engineer (Kubernetes-Linux)</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ARMADA</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Somerville, MA, US USA</t>
+          <t>Redmond, WA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Scala, Snowflake, ETL, ELT, dbt, Tableau, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75339d7552c524c1</t>
+          <t>https://www.indeed.com/viewjob?jk=b86c940f686047d8</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Data Scientist, AI Data Foundations</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Mango Chamba, LLC</t>
+          <t>MeridianLink</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, Snowflake, Time Travel, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, Event Hubs, Unity Catalog, Spark, PySpark, Azure Cosmos DB, ELT</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76b38f99ba86c67f</t>
+          <t>https://www.indeed.com/viewjob?jk=31ee3a3fe27b4bf1</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Mesa Labs</t>
+          <t>Graybar</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Lakewood, CO, US USA</t>
+          <t>Clayton, MO, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, PostgreSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, ETL, ELT, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71d54ee3197b525a</t>
+          <t>https://www.indeed.com/viewjob?jk=82b455422eee9334</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Google Cloud Network Engineer</t>
+          <t>Senior .NET Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Aspira</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, Lambda, S3, API Gateway, RDS, Scala, SQL Server, CI/CD, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8d74c6d08304ab9</t>
+          <t>https://www.indeed.com/viewjob?jk=f3201135d0d7e294</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Senior .NET Engineer</t>
+          <t>Software Engineer - DevOps Mobile</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Aspira</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, RDS, Scala, SQL Server, CI/CD, Jenkins, Jenkins</t>
+          <t>AWS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Maven, Terraform, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3201135d0d7e294</t>
+          <t>https://www.indeed.com/viewjob?jk=537b207b8aaf9dd0</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>DOCSIS Testing Engineer</t>
+          <t>Software Engineer - Warehouse Management Systems (WMS)</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Staples</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Framingham, MA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,34 +3776,34 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Oracle, MongoDB, Splunk, CI/CD, Jenkins, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, HBase, Scala, Kafka, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3102561596c9491c</t>
+          <t>https://www.indeed.com/viewjob?jk=654753ccda866d62</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Software Engineer - DevOps Mobile</t>
+          <t>Sr. Data Architect Specialist</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>SAMYANG AMERICA INC</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Brea, CA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,34 +3811,34 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Maven, Terraform, Docker, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=537b207b8aaf9dd0</t>
+          <t>https://www.indeed.com/viewjob?jk=f2086e3e44cfc021</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Software Engineer - Warehouse Management Systems (WMS)</t>
+          <t>Full Stack Product Engineer (Java)</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Staples</t>
+          <t>Allstate Insurance</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Framingham, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, HBase, Scala, Kafka, NoSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, ELT, CI/CD, Git</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=654753ccda866d62</t>
+          <t>https://www.indeed.com/viewjob?jk=d15adff582efc740</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Sr. Data Architect Specialist</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>SAMYANG AMERICA INC</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Brea, CA, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,34 +3881,34 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, S3, IAM, Databricks, Spark, Scala, DynamoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2086e3e44cfc021</t>
+          <t>https://www.indeed.com/viewjob?jk=6f9ad7c8c6b989c1</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Full Stack Product Engineer (Java)</t>
+          <t>QA Analyst / ETL Tester</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Allstate Insurance</t>
+          <t>CSpring</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Springfield, IL, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, ELT, CI/CD, Git</t>
+          <t>RDS, Azure, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Data Modeling, Snowflake Schema, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d15adff582efc740</t>
+          <t>https://www.indeed.com/viewjob?jk=1ebf7b3987a302e8</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>DOCSIS Testing Engineer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Databricks, Spark, Scala, DynamoDB, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Scala, Oracle, MongoDB, Splunk, CI/CD, Jenkins, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,59 +3961,59 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f9ad7c8c6b989c1</t>
+          <t>https://www.indeed.com/viewjob?jk=3102561596c9491c</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>QA Analyst / ETL Tester</t>
+          <t>Senior Full Stack Engineer - Python &amp; React JS</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>CSpring</t>
+          <t>Checkmate</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Springfield, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>RDS, Azure, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Data Modeling, Snowflake Schema, ETL, CI/CD</t>
+          <t>AWS, RDS, Scala, PostgreSQL, MySQL, CI/CD, GitHub Actions, Docker, Git, Datadog</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ebf7b3987a302e8</t>
+          <t>https://www.indeed.com/viewjob?jk=6ba3d00c3fb0ee25</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Engineer II-Software Development</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Montefiore Einstein</t>
+          <t>Microchip Technology</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Yonkers, NY, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,34 +4021,34 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, Snowflake, Data Modeling, ELT, dbt, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a3ffcafc747cce2</t>
+          <t>https://www.indeed.com/viewjob?jk=3013681a0e1c4f81</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>FastAPI</t>
+          <t>Engineer II-Software Development</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Microchip Technology</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,34 +4056,34 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, BigQuery, Vertex AI, Spark, Scala, Spark Streaming, Kafka, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0bc1141188a8604a</t>
+          <t>https://www.indeed.com/viewjob?jk=2649d75a044fe7bd</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer - VAULT</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Urology Centers of Alabama</t>
+          <t>Bloomberg</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, ETL</t>
+          <t>AWS, S3, RDS, Azure, GCP, Hive, Spark, Scala, Kafka, Cassandra</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,24 +4101,24 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28cb24ea6139fcb9</t>
+          <t>https://www.indeed.com/viewjob?jk=1d744cfcd1fce896</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Pearson</t>
+          <t>Litera</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Hoboken, NJ, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,34 +4126,34 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, MongoDB, DynamoDB, Data Modeling, ETL, ELT, DataOps, CI/CD</t>
+          <t>RDS, Azure, Databricks, Spark, Scala, Snowflake, NoSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05547d65aabdfcf0</t>
+          <t>https://www.indeed.com/viewjob?jk=cdf1ca20dc48c20f</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
+          <t>Senior Engineer, AI</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Harman</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Novi, MI, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,34 +4161,34 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34c37a226b547d01</t>
+          <t>https://www.indeed.com/viewjob?jk=4a91d05d9ba98a3a</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Montefiore Einstein</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Yonkers, NY, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,34 +4196,34 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
+          <t>AWS, S3, RDS, Scala, Snowflake, Data Modeling, ELT, dbt, CI/CD, Git</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7d77afce6f60e6f</t>
+          <t>https://www.indeed.com/viewjob?jk=9a3ffcafc747cce2</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
+          <t>FastAPI</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,34 +4231,34 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
+          <t>RDS, Google Cloud Platform, BigQuery, Vertex AI, Spark, Scala, Spark Streaming, Kafka, CI/CD, Git</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=225c5a8131dc6595</t>
+          <t>https://www.indeed.com/viewjob?jk=0bc1141188a8604a</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Urology Centers of Alabama</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
+          <t>AWS, EMR, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, ETL</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,24 +4276,24 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=301dbd1e2eb0bb70</t>
+          <t>https://www.indeed.com/viewjob?jk=28cb24ea6139fcb9</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Pearson</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Hoboken, NJ, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
+          <t>AWS, RDS, Scala, MongoDB, DynamoDB, Data Modeling, ETL, ELT, DataOps, CI/CD</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d88e7121c2db79d6</t>
+          <t>https://www.indeed.com/viewjob?jk=05547d65aabdfcf0</t>
         </is>
       </c>
     </row>
@@ -4328,7 +4328,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18d3f9fdcfa07035</t>
+          <t>https://www.indeed.com/viewjob?jk=34c37a226b547d01</t>
         </is>
       </c>
     </row>
@@ -4363,7 +4363,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d2d16258cfd6718</t>
+          <t>https://www.indeed.com/viewjob?jk=e7d77afce6f60e6f</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5be8f9b4535b406c</t>
+          <t>https://www.indeed.com/viewjob?jk=225c5a8131dc6595</t>
         </is>
       </c>
     </row>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26ef52c65261360a</t>
+          <t>https://www.indeed.com/viewjob?jk=301dbd1e2eb0bb70</t>
         </is>
       </c>
     </row>
@@ -4468,7 +4468,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9240b7b96545a4d</t>
+          <t>https://www.indeed.com/viewjob?jk=d88e7121c2db79d6</t>
         </is>
       </c>
     </row>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4521,7 +4521,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42ae72f7d4a97700</t>
+          <t>https://www.indeed.com/viewjob?jk=18d3f9fdcfa07035</t>
         </is>
       </c>
     </row>
@@ -4538,7 +4538,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dab5b1b68cc6402c</t>
+          <t>https://www.indeed.com/viewjob?jk=9d2d16258cfd6718</t>
         </is>
       </c>
     </row>
@@ -4573,7 +4573,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4591,7 +4591,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fde8d1831ca7f9b7</t>
+          <t>https://www.indeed.com/viewjob?jk=5be8f9b4535b406c</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a056659ad4aebd2</t>
+          <t>https://www.indeed.com/viewjob?jk=26ef52c65261360a</t>
         </is>
       </c>
     </row>
@@ -4643,7 +4643,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4661,7 +4661,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5402962c321dcba</t>
+          <t>https://www.indeed.com/viewjob?jk=f9240b7b96545a4d</t>
         </is>
       </c>
     </row>
@@ -4678,7 +4678,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f45ad39ec1fe503a</t>
+          <t>https://www.indeed.com/viewjob?jk=42ae72f7d4a97700</t>
         </is>
       </c>
     </row>
@@ -4713,7 +4713,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4731,7 +4731,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86cfc919b4ccc768</t>
+          <t>https://www.indeed.com/viewjob?jk=dab5b1b68cc6402c</t>
         </is>
       </c>
     </row>
@@ -4748,7 +4748,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9a866cff6a0e3bd</t>
+          <t>https://www.indeed.com/viewjob?jk=fde8d1831ca7f9b7</t>
         </is>
       </c>
     </row>
@@ -4783,7 +4783,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4801,7 +4801,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab68f1e4ba82ad10</t>
+          <t>https://www.indeed.com/viewjob?jk=7a056659ad4aebd2</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4836,7 +4836,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df163d5906a30146</t>
+          <t>https://www.indeed.com/viewjob?jk=e5402962c321dcba</t>
         </is>
       </c>
     </row>
@@ -4853,7 +4853,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f0c32c0bdf67710</t>
+          <t>https://www.indeed.com/viewjob?jk=f45ad39ec1fe503a</t>
         </is>
       </c>
     </row>
@@ -4888,7 +4888,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4906,7 +4906,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25f63312ec2e267e</t>
+          <t>https://www.indeed.com/viewjob?jk=86cfc919b4ccc768</t>
         </is>
       </c>
     </row>
@@ -4923,7 +4923,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be379ec08f5c5e6f</t>
+          <t>https://www.indeed.com/viewjob?jk=c9a866cff6a0e3bd</t>
         </is>
       </c>
     </row>
@@ -4958,7 +4958,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8deeb1ab1ebcdccd</t>
+          <t>https://www.indeed.com/viewjob?jk=ab68f1e4ba82ad10</t>
         </is>
       </c>
     </row>
@@ -4993,7 +4993,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5011,7 +5011,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92aa87419ba8e5df</t>
+          <t>https://www.indeed.com/viewjob?jk=df163d5906a30146</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5046,7 +5046,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da334d3b3eda0eb4</t>
+          <t>https://www.indeed.com/viewjob?jk=2f0c32c0bdf67710</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c314e6df20a4157</t>
+          <t>https://www.indeed.com/viewjob?jk=25f63312ec2e267e</t>
         </is>
       </c>
     </row>
@@ -5098,7 +5098,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5116,7 +5116,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b90a165cff732e70</t>
+          <t>https://www.indeed.com/viewjob?jk=be379ec08f5c5e6f</t>
         </is>
       </c>
     </row>
@@ -5133,7 +5133,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5151,7 +5151,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26bc98921360165c</t>
+          <t>https://www.indeed.com/viewjob?jk=8deeb1ab1ebcdccd</t>
         </is>
       </c>
     </row>
@@ -5168,7 +5168,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5186,7 +5186,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5359f322821abe9</t>
+          <t>https://www.indeed.com/viewjob?jk=92aa87419ba8e5df</t>
         </is>
       </c>
     </row>
@@ -5203,7 +5203,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5221,7 +5221,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=562ea8307dd5c91d</t>
+          <t>https://www.indeed.com/viewjob?jk=da334d3b3eda0eb4</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5256,7 +5256,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70a64e543cdeb49a</t>
+          <t>https://www.indeed.com/viewjob?jk=2c314e6df20a4157</t>
         </is>
       </c>
     </row>
@@ -5273,7 +5273,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5291,7 +5291,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed3e28c9a543299a</t>
+          <t>https://www.indeed.com/viewjob?jk=b90a165cff732e70</t>
         </is>
       </c>
     </row>
@@ -5308,7 +5308,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5326,24 +5326,24 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1735f01363643535</t>
+          <t>https://www.indeed.com/viewjob?jk=26bc98921360165c</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Data Engineer II, Mobile Game Analytics</t>
+          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Mattel, Inc.</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>El Segundo, CA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5351,7 +5351,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>RDS, Medallion Architecture, GCP, BigQuery, Dimensional Modeling, ETL, dbt, Tableau, CI/CD, Airflow</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -5361,24 +5361,24 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=087868e735e87a06</t>
+          <t>https://www.indeed.com/viewjob?jk=c5359f322821abe9</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - VAULT</t>
+          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Bloomberg</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5386,7 +5386,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Hive, Spark, Scala, Kafka, Cassandra</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -5396,24 +5396,24 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d744cfcd1fce896</t>
+          <t>https://www.indeed.com/viewjob?jk=562ea8307dd5c91d</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>BigData ,Python and Py Spark , GCP</t>
+          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5421,7 +5421,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>GCP, BigQuery, Hadoop, Hive, Spark, PySpark, Scala, ETL, ELT, Airflow</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -5431,24 +5431,24 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81999129979e18ac</t>
+          <t>https://www.indeed.com/viewjob?jk=70a64e543cdeb49a</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer - Python &amp; React JS</t>
+          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Checkmate</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -5456,34 +5456,34 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, PostgreSQL, MySQL, CI/CD, GitHub Actions, Docker, Git, Datadog</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ba3d00c3fb0ee25</t>
+          <t>https://www.indeed.com/viewjob?jk=ed3e28c9a543299a</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Engineer II-Software Development</t>
+          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Microchip Technology</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -5491,7 +5491,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLOps, CI/CD</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -5501,24 +5501,24 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3013681a0e1c4f81</t>
+          <t>https://www.indeed.com/viewjob?jk=1735f01363643535</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Engineer II-Software Development</t>
+          <t>Data Engineer II, Mobile Game Analytics</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Microchip Technology</t>
+          <t>Mattel, Inc.</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>El Segundo, CA, US USA</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLOps, CI/CD</t>
+          <t>RDS, Medallion Architecture, GCP, BigQuery, Dimensional Modeling, ETL, dbt, Tableau, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -5536,24 +5536,24 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2649d75a044fe7bd</t>
+          <t>https://www.indeed.com/viewjob?jk=087868e735e87a06</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>AI Applications Engineer</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Litera</t>
+          <t>SEEQ</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D147" t="n">
@@ -5561,7 +5561,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, Scala, Snowflake, NoSQL, Data Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, RDS, Azure, Databricks, Scala, Snowflake, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -5571,24 +5571,24 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cdf1ca20dc48c20f</t>
+          <t>https://www.indeed.com/viewjob?jk=02ed320077d234a1</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Senior Engineer, AI</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Harman</t>
+          <t>Onspring Technologies, LLC</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Novi, MI, US USA</t>
+          <t>Overland Park, KS, US USA</t>
         </is>
       </c>
       <c r="D148" t="n">
@@ -5596,34 +5596,34 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, HBase, Scala, MongoDB, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a91d05d9ba98a3a</t>
+          <t>https://www.indeed.com/viewjob?jk=1d56a66deeafe00f</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Integration Software Engineer</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Onspring Technologies, LLC</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Overland Park, KS, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D149" t="n">
@@ -5631,17 +5631,17 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, HBase, Scala, MongoDB, NoSQL, CI/CD, Docker</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, ETL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d56a66deeafe00f</t>
+          <t>https://www.indeed.com/viewjob?jk=b035b944f2ad4c37</t>
         </is>
       </c>
     </row>
@@ -5658,7 +5658,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D150" t="n">
@@ -5676,14 +5676,14 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b035b944f2ad4c37</t>
+          <t>https://www.indeed.com/viewjob?jk=9ba6e4aacd5b6631</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Senior Data Integration Software Engineer</t>
+          <t>Data Integration Software Engineer</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -5693,7 +5693,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Portsmouth, NH, US USA</t>
         </is>
       </c>
       <c r="D151" t="n">
@@ -5711,14 +5711,14 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ba6e4aacd5b6631</t>
+          <t>https://www.indeed.com/viewjob?jk=c4c7e0f49df408be</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Data Integration Software Engineer</t>
+          <t>Senior Data Integration Software Engineer</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -5746,14 +5746,14 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4c7e0f49df408be</t>
+          <t>https://www.indeed.com/viewjob?jk=93164fc43ac74193</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Senior Data Integration Software Engineer</t>
+          <t>Data Integration Software Engineer</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -5763,7 +5763,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Portsmouth, NH, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D153" t="n">
@@ -5781,7 +5781,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93164fc43ac74193</t>
+          <t>https://www.indeed.com/viewjob?jk=12a4fd124772d9d2</t>
         </is>
       </c>
     </row>
@@ -5798,7 +5798,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D154" t="n">
@@ -5816,24 +5816,24 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12a4fd124772d9d2</t>
+          <t>https://www.indeed.com/viewjob?jk=c38e2fae9b46f905</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Data Integration Software Engineer</t>
+          <t>Sr. Software Engineer, Full-Stack (Factory Systems)</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>Rivian and Volkswagen Group Technologies</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D155" t="n">
@@ -5841,34 +5841,34 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, ETL, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c38e2fae9b46f905</t>
+          <t>https://www.indeed.com/viewjob?jk=68c700567606c4e9</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer, Full-Stack (Factory Systems)</t>
+          <t>Data Scientist, Senior Associate – Product, Experience and Technology (PXT) Analytics Team</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Rivian and Volkswagen Group Technologies</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D156" t="n">
@@ -5876,7 +5876,7 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>Redshift, RDS, Databricks, Scala, Snowflake, dbt, Tableau, CI/CD, Airflow, Git</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
@@ -5886,24 +5886,24 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68c700567606c4e9</t>
+          <t>https://www.indeed.com/viewjob?jk=4b0bfe4f7e93a067</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Sr Associate Engineer/Engineer, IT Software</t>
+          <t>Enterprise AI Architect</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Radwell International</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Willingboro, NJ, US USA</t>
         </is>
       </c>
       <c r="D157" t="n">
@@ -5911,34 +5911,34 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, PostgreSQL, MySQL, NoSQL, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf657c9771abb6db</t>
+          <t>https://www.indeed.com/viewjob?jk=56c80236c3727026</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Data Scientist, Senior Associate – Product, Experience and Technology (PXT) Analytics Team</t>
+          <t>AI Engineer Clinical Data Science</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Katalyst Healthcares &amp; Life Sciences</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Manhattan, NY, US USA</t>
         </is>
       </c>
       <c r="D158" t="n">
@@ -5946,7 +5946,7 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, Scala, Snowflake, dbt, Tableau, CI/CD, Airflow, Git</t>
+          <t>RDS, Google Cloud Platform, GCP, Vertex AI, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker, Git</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
@@ -5955,76 +5955,6 @@
         </is>
       </c>
       <c r="G158" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4b0bfe4f7e93a067</t>
-        </is>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="inlineStr">
-        <is>
-          <t>Enterprise AI Architect</t>
-        </is>
-      </c>
-      <c r="B159" t="inlineStr">
-        <is>
-          <t>Radwell International</t>
-        </is>
-      </c>
-      <c r="C159" t="inlineStr">
-        <is>
-          <t>Willingboro, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D159" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E159" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, PostgreSQL, MySQL, NoSQL, MLOps, CI/CD</t>
-        </is>
-      </c>
-      <c r="F159" t="inlineStr">
-        <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="G159" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=56c80236c3727026</t>
-        </is>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="inlineStr">
-        <is>
-          <t>AI Engineer Clinical Data Science</t>
-        </is>
-      </c>
-      <c r="B160" t="inlineStr">
-        <is>
-          <t>Katalyst Healthcares &amp; Life Sciences</t>
-        </is>
-      </c>
-      <c r="C160" t="inlineStr">
-        <is>
-          <t>Manhattan, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D160" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E160" t="inlineStr">
-        <is>
-          <t>RDS, Google Cloud Platform, GCP, Vertex AI, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker, Git</t>
-        </is>
-      </c>
-      <c r="F160" t="inlineStr">
-        <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="G160" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=47a06a95eff2f8b1</t>
         </is>

--- a/results/job_matches_2026-05-06.xlsx
+++ b/results/job_matches_2026-05-06.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G158"/>
+  <dimension ref="A1:G143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -573,25 +573,25 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer, Cloud Infrastructure (Multiple Seniority Levels)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Warner Bros. Discovery</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Carlos, CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Kinesis, Redshift, Athena, S3, RDS, Azure, Databricks</t>
+          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, SQS, ECS, IAM, RDS</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,54 +601,54 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0585eb3ca3cd8f48</t>
+          <t>https://www.indeed.com/viewjob?jk=07cee960b10bf15e</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Azure Network Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Warner Bros. Discovery</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>18.1</v>
+        <v>16.7</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Kinesis, Redshift, Athena, S3, RDS, Azure, Databricks</t>
+          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Event Hubs, Unity Catalog, Medallion Architecture, Spark, PySpark</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea66a6dbd0690c3b</t>
+          <t>https://www.indeed.com/viewjob?jk=b4c4141e761a1d57</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Health Account Intern</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Warner Bros. Discovery</t>
+          <t>Booz Allen Hamilton</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -657,248 +657,248 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>18.1</v>
+        <v>16.7</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Kinesis, Redshift, Athena, S3, RDS, Azure, Databricks</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Databricks, Hadoop, Hive, Spark, Scala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec9442df01efef1b</t>
+          <t>https://www.indeed.com/viewjob?jk=64329d0d0bf86853</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Compliance, Senior Backend Engineer (Java &amp; ETL Specialist), Dallas, Associate</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Warner Bros. Discovery</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>18.1</v>
+        <v>16.7</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Kinesis, Redshift, Athena, S3, RDS, Azure, Databricks</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=341798717a6ce508</t>
+          <t>https://www.indeed.com/viewjob?jk=e21fade0470597e2</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Warner Bros. Discovery</t>
+          <t>DocuSign</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>18.1</v>
+        <v>16</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Kinesis, Redshift, Athena, S3, RDS, Azure, Databricks</t>
+          <t>AWS, Redshift, SNS, RDS, BigQuery, Hadoop, Spark, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29381ac7399ddbb0</t>
+          <t>https://www.indeed.com/viewjob?jk=1636bf2e2935fd54</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Software Engineer, Cloud Infrastructure (Multiple Seniority Levels)</t>
+          <t>Sr Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Commence</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>San Carlos, CA, US USA</t>
+          <t>Leesburg, VA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>17.4</v>
+        <v>16</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, SQS, ECS, IAM, RDS</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, NoSQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07cee960b10bf15e</t>
+          <t>https://www.indeed.com/viewjob?jk=9093ede7f2269db2</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Azure Network Engineer</t>
+          <t>Sr Data Engineer, Python + Spark (Data Federation skillset - Data Lakehouse - Eg: Starburst) - New York</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Photon</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Event Hubs, Unity Catalog, Medallion Architecture, Spark, PySpark</t>
+          <t>AWS, Glue, EMR, S3, Azure, Databricks, Medallion Architecture, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4c4141e761a1d57</t>
+          <t>https://www.indeed.com/viewjob?jk=f7767a92d7d08a3b</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Health Account Intern</t>
+          <t>Databricks Engineer and Architect</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Booz Allen Hamilton</t>
+          <t>Lincoln Financial Group</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Radnor, PA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Databricks, Hadoop, Hive, Spark, Scala</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, RDS, Databricks, Unity Catalog</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64329d0d0bf86853</t>
+          <t>https://www.indeed.com/viewjob?jk=d7862c3c59e06d56</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Compliance, Senior Backend Engineer (Java &amp; ETL Specialist), Dallas, Associate</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MongoDB</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, RDS, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e21fade0470597e2</t>
+          <t>https://www.indeed.com/viewjob?jk=df1902d36083d34f</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Sr Site Reliability Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Commence</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Leesburg, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,34 +906,34 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, NoSQL, ETL, ELT</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, RDS, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9093ede7f2269db2</t>
+          <t>https://www.indeed.com/viewjob?jk=5cb867686433b7a1</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Sr Data Engineer, Python + Spark (Data Federation skillset - Data Lakehouse - Eg: Starburst) - New York</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Photon</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,34 +941,34 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, S3, Azure, Databricks, Medallion Architecture, GCP, Spark, PySpark</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, RDS, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7767a92d7d08a3b</t>
+          <t>https://www.indeed.com/viewjob?jk=3aeafc948a2f0f6c</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Databricks Engineer and Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Lincoln Financial Group</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Radnor, PA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,34 +976,34 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, RDS, Databricks, Unity Catalog</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, RDS, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7862c3c59e06d56</t>
+          <t>https://www.indeed.com/viewjob?jk=c45b322f3e5694ad</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer Intern</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Norstella</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,287 +1011,287 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, RDS, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Azure, Blob Storage, GCP, PostgreSQL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df1902d36083d34f</t>
+          <t>https://www.indeed.com/viewjob?jk=49a129c7a487aae4</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer, Data Engineering</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Cambridge Mobile Telematics</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, RDS, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, Glue, Kinesis, Redshift, S3, SQS, SNS, RDS, Databricks, Spark</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cb867686433b7a1</t>
+          <t>https://www.indeed.com/viewjob?jk=72e8b54f46d552d4</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>API Threat Intelligence Analyst</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, RDS, Scala, Kafka, PostgreSQL</t>
+          <t>Azure, Google Cloud Platform, Kafka, NoSQL, Data Modeling, ETL, Talend, Tableau, Splunk, MicroStrategy</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3aeafc948a2f0f6c</t>
+          <t>https://www.indeed.com/viewjob?jk=e918fa70b2a1920e</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Backend (Python)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, RDS, Scala, Kafka, PostgreSQL</t>
+          <t>Azure, Google Cloud Platform, Kafka, NoSQL, Data Modeling, ETL, Talend, Tableau, Splunk, MicroStrategy</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c45b322f3e5694ad</t>
+          <t>https://www.indeed.com/viewjob?jk=d711bd4394cb404e</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Software Engineer Intern</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Norstella</t>
+          <t>Wavicle Data Solutions</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Oak Brook, IL, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>16</v>
+        <v>14.6</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Azure, Blob Storage, GCP, PostgreSQL</t>
+          <t>AWS, Lambda, Redshift, Azure, Databricks, GCP, Hadoop, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49a129c7a487aae4</t>
+          <t>https://www.indeed.com/viewjob?jk=a435f9b94ff5d489</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer (Databricks)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Verisk</t>
+          <t>Infinitive Inc</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Ashburn, VA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, S3, RDS, Spark, Scala, PostgreSQL, Data Modeling</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, S3, Azure, Databricks, Unity Catalog, GCP</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb57edcbdb36ad26</t>
+          <t>https://www.indeed.com/viewjob?jk=aee5e62267dbbb6c</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>MLOps Engineer – Azure Databricks, Cloud-to-Edge ML Deployment</t>
+          <t>Software Developer II</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>KPIT Technologies</t>
+          <t>Floor &amp; Decor</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, MLOps, MLflow, CI/CD</t>
+          <t>RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1160b6a5ea3d30ad</t>
+          <t>https://www.indeed.com/viewjob?jk=4a21fec712255df2</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>API Threat Intelligence Analyst</t>
+          <t>Sr. Streaming Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Ness Digital Engineering</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Azure, Google Cloud Platform, Kafka, NoSQL, Data Modeling, ETL, Talend, Tableau, Splunk, MicroStrategy</t>
+          <t>AWS, Kinesis, S3, IAM, RDS, Spark, Scala, Kafka, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e918fa70b2a1920e</t>
+          <t>https://www.indeed.com/viewjob?jk=f90fa0ab3164dcd1</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Backend (Python)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Azure, Google Cloud Platform, Kafka, NoSQL, Data Modeling, ETL, Talend, Tableau, Splunk, MicroStrategy</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, SQL Server, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d711bd4394cb404e</t>
+          <t>https://www.indeed.com/viewjob?jk=2b748ea05c0bbf37</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Wavicle Data Solutions</t>
+          <t>SOFTILITY INC</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, Azure, Databricks, GCP, Hadoop, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,94 +1336,94 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a435f9b94ff5d489</t>
+          <t>https://www.indeed.com/viewjob?jk=3faf69463891ca3f</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Databricks)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Infinitive Inc</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, S3, Azure, Databricks, Unity Catalog, GCP</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Oracle, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aee5e62267dbbb6c</t>
+          <t>https://www.indeed.com/viewjob?jk=d61e7d7639acc074</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Software Developer II</t>
+          <t>MLOps Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Floor &amp; Decor</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL, Splunk, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a21fec712255df2</t>
+          <t>https://www.indeed.com/viewjob?jk=56f1aa48ba26ae3c</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Sr. Streaming Engineer</t>
+          <t>Business Intelligence Developer (Healthcare Data, EDI, ETL)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Ness Digital Engineering</t>
+          <t>MicroHealth LLC</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Vienna, VA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, IAM, RDS, Spark, Scala, Kafka, NoSQL, Splunk</t>
+          <t>AWS, EMR, RDS, Scala, Snowflake, SQL Server, PostgreSQL, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f90fa0ab3164dcd1</t>
+          <t>https://www.indeed.com/viewjob?jk=3ba3d7e28ab6494c</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Software Engineer III - PySpark/AWS</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>SOFTILITY INC</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD</t>
+          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Databricks, Spark, PySpark</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3faf69463891ca3f</t>
+          <t>https://www.indeed.com/viewjob?jk=e02c112e835bf775</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data analyst</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Brentwood, TN, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Oracle, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,67 +1511,67 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d61e7d7639acc074</t>
+          <t>https://www.indeed.com/viewjob?jk=b7ed131be5ba5e96</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>MLOps Engineer</t>
+          <t>Mid- Level Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Vantage Data Centers</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Spark, PySpark, Scala, Data Modeling, Dimension Tables, ETL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56f1aa48ba26ae3c</t>
+          <t>https://www.indeed.com/viewjob?jk=a35201e2c76024aa</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Business Intelligence Developer (Healthcare Data, EDI, ETL)</t>
+          <t>Senior Site Reliability Engineer, Data &amp; Analytics</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>MicroHealth LLC</t>
+          <t>Blizzard Entertainment</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Vienna, VA, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Scala, Snowflake, SQL Server, PostgreSQL, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, RDS, GCP, BigQuery, Dataflow, Kafka, dbt, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ba3d7e28ab6494c</t>
+          <t>https://www.indeed.com/viewjob?jk=f56eabb97941a731</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Data analyst</t>
+          <t>Data Solutions Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Epsilon</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Brentwood, TN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, ETL</t>
+          <t>AWS, RDS, Databricks, Hadoop, HDFS, Spark, Scala, Kafka, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7ed131be5ba5e96</t>
+          <t>https://www.indeed.com/viewjob?jk=22c6237fafdb9308</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Cloud Network Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>vectorsoft</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>API Gateway, IAM, RDS, Google Cloud Platform, BigQuery, Dataflow, Scala, Kafka, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,67 +1651,67 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3552e9ee02097f2c</t>
+          <t>https://www.indeed.com/viewjob?jk=3bdce3e69ca5f6c4</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Mid- Level Data Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Vantage Data Centers</t>
+          <t>Miami Marlins</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Spark, PySpark, Scala, Data Modeling, Dimension Tables, ETL</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, GCP, Scala, Snowflake, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a35201e2c76024aa</t>
+          <t>https://www.indeed.com/viewjob?jk=ff87deef607d5450</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer, Data &amp; Analytics</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Blizzard Entertainment</t>
+          <t>Paramount</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Fort Lauderdale, FL, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Dataflow, Kafka, dbt, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, GCP, BigQuery, Dataflow, Scala, MongoDB, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f56eabb97941a731</t>
+          <t>https://www.indeed.com/viewjob?jk=a12925c69dfc7bed</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Data Solutions Engineer</t>
+          <t>Data Engineer / Data Platform Engineer Internship Fall 2026 Semester at the Dow Delivery Center at UIUC (Champaign, IL)</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Epsilon</t>
+          <t>DOW</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Kankakee, IL, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Hadoop, HDFS, Spark, Scala, Kafka, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22c6237fafdb9308</t>
+          <t>https://www.indeed.com/viewjob?jk=38a9f118a8e8f0ac</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Azure Network Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>vectorsoft</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>IAM, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage, MySQL, Splunk, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3bdce3e69ca5f6c4</t>
+          <t>https://www.indeed.com/viewjob?jk=8bb3e3385b26a0b5</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Miami Marlins</t>
+          <t>Moore</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Westminster, CO, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, GCP, Scala, Snowflake, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff87deef607d5450</t>
+          <t>https://www.indeed.com/viewjob?jk=b8c5af154805cd95</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Senior Data Engineer (Python/PySpark/AWS)</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Paramount</t>
+          <t>Infinitive Inc</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Fort Lauderdale, FL, US USA</t>
+          <t>Ashburn, VA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,34 +1851,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Dataflow, Scala, MongoDB, NoSQL, Docker, Kubernetes</t>
+          <t>AWS, Azure, Spark, PySpark, Scala, Spark Streaming, Data Modeling, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2025-02-18</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a12925c69dfc7bed</t>
+          <t>https://www.indeed.com/viewjob?jk=45083db400feff94</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>AI Agent Engineer</t>
+          <t>Data Engineer (Python/PySpark/AWS)</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Momentive Software</t>
+          <t>Infinitive Inc</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Ashburn, VA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,34 +1886,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Athena, SQS, SNS, API Gateway, ECS, RDS, Azure, GCP</t>
+          <t>AWS, Azure, Spark, PySpark, Scala, Spark Streaming, Data Modeling, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2025-01-27</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ac9574b3f75cc2c</t>
+          <t>https://www.indeed.com/viewjob?jk=5e742c4bedd2037b</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Data Engineer / Data Platform Engineer Internship Fall 2026 Semester at the Dow Delivery Center at UIUC (Champaign, IL)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>DOW</t>
+          <t>Mustang Cat</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Kankakee, IL, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, Snowflake, Data Modeling</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, Fact Tables, ETL</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,14 +1931,14 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38a9f118a8e8f0ac</t>
+          <t>https://www.indeed.com/viewjob?jk=182574da3c06479e</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Azure Network Engineer</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bb3e3385b26a0b5</t>
+          <t>https://www.indeed.com/viewjob?jk=52b0e598b9832c43</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Cloud Gateway</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Rivian and Volkswagen Group Technologies</t>
+          <t>Terra Quantum</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, MongoDB, DynamoDB, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b72e865e6bee153</t>
+          <t>https://www.indeed.com/viewjob?jk=15eb90498bcba242</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Full Stack Engineer, Experienced</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Moore</t>
+          <t>Blue Shield of California</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Westminster, CO, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8c5af154805cd95</t>
+          <t>https://www.indeed.com/viewjob?jk=93fe5a9749607800</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Data Engineer (ETL / Python Developer)</t>
+          <t>Full Stack Engineer, Senior</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>CSpring</t>
+          <t>Blue Shield of California</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Springfield, IL, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b861e2c1a0a03133</t>
+          <t>https://www.indeed.com/viewjob?jk=bcc6fa1baccf83e5</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Python/PySpark/AWS)</t>
+          <t>Full Stack Engineer, Consultant</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Infinitive Inc</t>
+          <t>Blue Shield of California</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,34 +2096,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Azure, Spark, PySpark, Scala, Spark Streaming, Data Modeling, ETL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2025-02-18</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45083db400feff94</t>
+          <t>https://www.indeed.com/viewjob?jk=a3a7d3c5d7336760</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Data Engineer (Python/PySpark/AWS)</t>
+          <t>Summer Intern, Platform Engineering</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Infinitive Inc</t>
+          <t>Outfront Media</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,34 +2131,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Azure, Spark, PySpark, Scala, Spark Streaming, Data Modeling, ETL, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, S3, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2025-01-27</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e742c4bedd2037b</t>
+          <t>https://www.indeed.com/viewjob?jk=2aa35bb9483f10ad</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>Artificial Intelligence/Machine Learning Data Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Accenture</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage, MySQL, Splunk, CI/CD, GitHub Actions</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLflow</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52b0e598b9832c43</t>
+          <t>https://www.indeed.com/viewjob?jk=b20f553bf3557e7a</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Warehouse Developer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Terra Quantum</t>
+          <t>New England Life Care</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Canton, MA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, Azure, Data Factory, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, Fact Tables, Dimension Tables</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15eb90498bcba242</t>
+          <t>https://www.indeed.com/viewjob?jk=b61fd67550df6c0b</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Full Stack Engineer, Experienced</t>
+          <t>Data Warehouse Developer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Blue Shield of California</t>
+          <t>New England Life Care</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Woburn, MA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, NoSQL, CI/CD, Terraform</t>
+          <t>AWS, Azure, Data Factory, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, Fact Tables, Dimension Tables</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93fe5a9749607800</t>
+          <t>https://www.indeed.com/viewjob?jk=59fae488bfb069d7</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Full Stack Engineer, Senior</t>
+          <t>Data Warehouse Developer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Blue Shield of California</t>
+          <t>New England Life Care</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Scarborough, ME, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,34 +2271,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, NoSQL, CI/CD, Terraform</t>
+          <t>AWS, Azure, Data Factory, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, Fact Tables, Dimension Tables</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bcc6fa1baccf83e5</t>
+          <t>https://www.indeed.com/viewjob?jk=c511d00669b005c9</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Full Stack Engineer, Consultant</t>
+          <t>Data Warehouse Developer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Blue Shield of California</t>
+          <t>New England Life Care</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Concord, NH, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,42 +2306,42 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, NoSQL, CI/CD, Terraform</t>
+          <t>AWS, Azure, Data Factory, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, Fact Tables, Dimension Tables</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3a7d3c5d7336760</t>
+          <t>https://www.indeed.com/viewjob?jk=9e02714fa8eb1d57</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Summer Intern, Platform Engineering</t>
+          <t>Mid-Level Software Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Outfront Media</t>
+          <t>State Farm</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Bloomington, IL, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD, Docker</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, MongoDB, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,32 +2351,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2aa35bb9483f10ad</t>
+          <t>https://www.indeed.com/viewjob?jk=da08c5cf76c3287c</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Artificial Intelligence/Machine Learning Data Engineer</t>
+          <t>Cloud Network Architect</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Accenture</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLflow</t>
+          <t>Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,32 +2386,32 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b20f553bf3557e7a</t>
+          <t>https://www.indeed.com/viewjob?jk=e874dfda20060e92</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Data Warehouse Developer</t>
+          <t>Azure Network Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>New England Life Care</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Canton, MA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, Fact Tables, Dimension Tables</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Event Hubs, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,129 +2421,129 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b61fd67550df6c0b</t>
+          <t>https://www.indeed.com/viewjob?jk=05dcb2c14af656a8</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Data Warehouse Developer</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>New England Life Care</t>
+          <t>Clayco</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Woburn, MA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, Fact Tables, Dimension Tables</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59fae488bfb069d7</t>
+          <t>https://www.indeed.com/viewjob?jk=61cc49187bd6e01d</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Data Warehouse Developer</t>
+          <t>Data Systems Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>New England Life Care</t>
+          <t>Central Health</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Scarborough, ME, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, Fact Tables, Dimension Tables</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c511d00669b005c9</t>
+          <t>https://www.indeed.com/viewjob?jk=41eed22913274d81</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Data Warehouse Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>New England Life Care</t>
+          <t>Laural Parke</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Concord, NH, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, Fact Tables, Dimension Tables</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e02714fa8eb1d57</t>
+          <t>https://www.indeed.com/viewjob?jk=19dac2449c2108f4</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Mid-Level Software Engineer</t>
+          <t>DevOps / AgentOps Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>State Farm</t>
+          <t>Revelation Pharma</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Bloomington, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,34 +2551,34 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, MongoDB, CI/CD, Terraform</t>
+          <t>AWS, Lambda, Step Functions, S3, ECS, IAM, RDS, Azure, Vertex AI, CI/CD</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da08c5cf76c3287c</t>
+          <t>https://www.indeed.com/viewjob?jk=265eee1218fa6fae</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>DevOps / AgentOps Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Revelation Pharma</t>
+          <t>Victory Live</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,24 +2586,24 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, ECS, IAM, RDS, Azure, Vertex AI, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Snowflake, SQL Server, DynamoDB, ELT, dbt, Terraform</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=265eee1218fa6fae</t>
+          <t>https://www.indeed.com/viewjob?jk=a1c259f0b00d1299</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Cloud Network Architect</t>
+          <t>Cloud Networking Consultant</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>KS, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>RDS, Spark, Scala, Kafka, Snowflake, Splunk, CI/CD, Jenkins, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e874dfda20060e92</t>
+          <t>https://www.indeed.com/viewjob?jk=05bc8504be04f7d2</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Azure Network Engineer</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Montefiore Einstein</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Yonkers, NY, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Event Hubs, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, RDS, Medallion Architecture, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ELT, dbt</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05dcb2c14af656a8</t>
+          <t>https://www.indeed.com/viewjob?jk=2d972b31a0cae529</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Snowflake/Tableau Developer / Dallas Texas</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Clayco</t>
+          <t>FirstNet Global</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Napa, CA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61cc49187bd6e01d</t>
+          <t>https://www.indeed.com/viewjob?jk=a4ab4d99e440e9b4</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Data Engineering - E&amp;A - Data Engineer I</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Genesis Global Group</t>
+          <t>Klaxontech</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Myrtle Point, OR, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,52 +2726,52 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2526bf14df16c3e8</t>
+          <t>https://www.indeed.com/viewjob?jk=193935f590ab7020</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data Systems Engineer</t>
+          <t>Data Engineer with Python</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Central Health</t>
+          <t>Tardus inc</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41eed22913274d81</t>
+          <t>https://www.indeed.com/viewjob?jk=80c45bbb6f084151</t>
         </is>
       </c>
     </row>
@@ -2783,90 +2783,90 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Laural Parke</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>RDS, GCP, BigQuery, Dataflow, Vertex AI, Scala, Data Modeling, Jenkins, Terraform, Jenkins</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19dac2449c2108f4</t>
+          <t>https://www.indeed.com/viewjob?jk=4bbf23a169f18dbc</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior DevOps Software Engineer, Firmware &amp; CI/CD</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Rivian and Volkswagen Group Technologies</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>RDS, GCP, BigQuery, Dataflow, Vertex AI, Scala, Data Modeling, Jenkins, Terraform, Jenkins</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5f621c8ad4f69fd</t>
+          <t>https://www.indeed.com/viewjob?jk=4b05514433681d42</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Victory Live</t>
+          <t>Clark Construction</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Snowflake, SQL Server, DynamoDB, ELT, dbt, Terraform</t>
+          <t>AWS, Azure, GCP, Spark, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, dbt</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,32 +2876,32 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1c259f0b00d1299</t>
+          <t>https://www.indeed.com/viewjob?jk=6f199bfc2e975b58</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Cloud Networking Consultant</t>
+          <t>Data Scientist, AI Data Foundations</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>MeridianLink</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>KS, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RDS, Spark, Scala, Kafka, Snowflake, Splunk, CI/CD, Jenkins, Docker, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Event Hubs, Unity Catalog, Spark, PySpark, Azure Cosmos DB, ELT</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,32 +2911,32 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05bc8504be04f7d2</t>
+          <t>https://www.indeed.com/viewjob?jk=2390498da25e9e01</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>SSIS / Azure Data Factory Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Montefiore Einstein</t>
+          <t>Intone Networks</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Yonkers, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Medallion Architecture, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ELT, dbt</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Blob Storage, Scala, SQL Server, ETL, Power BI</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,32 +2946,32 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d972b31a0cae529</t>
+          <t>https://www.indeed.com/viewjob?jk=85c3cae0c83282a2</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Snowflake/Tableau Developer / Dallas Texas</t>
+          <t>Senior Data Engineer Biloxi 5139</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>FirstNet Global</t>
+          <t>Keesler Federal Credit Union</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Napa, CA, US USA</t>
+          <t>Biloxi, MS, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>RDS, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, CI/CD, Git</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4ab4d99e440e9b4</t>
+          <t>https://www.indeed.com/viewjob?jk=923871eb4e708d96</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Klaxontech</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=193935f590ab7020</t>
+          <t>https://www.indeed.com/viewjob?jk=c98f634775f326c6</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Data Engineer with Python</t>
+          <t>Sr. Professional, Software Engineering (Python)</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Tardus inc</t>
+          <t>Cotality</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,34 +3041,34 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>RDS, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, Tableau, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80c45bbb6f084151</t>
+          <t>https://www.indeed.com/viewjob?jk=83e013cc49a29087</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Platform/DevOps Engineer (Kubernetes-Linux)</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>ARMADA</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Vertex AI, Scala, Data Modeling, Jenkins, Terraform, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bbf23a169f18dbc</t>
+          <t>https://www.indeed.com/viewjob?jk=7b0e9b75e0f5558d</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Platform/DevOps Engineer (Kubernetes-Linux)</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>ARMADA</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Sammamish, WA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Vertex AI, Scala, Data Modeling, Jenkins, Terraform, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b05514433681d42</t>
+          <t>https://www.indeed.com/viewjob?jk=efa4e4e3099a0ae2</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Platform/DevOps Engineer (Kubernetes-Linux)</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Clark Construction</t>
+          <t>ARMADA</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Kirkland, WA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, dbt</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f199bfc2e975b58</t>
+          <t>https://www.indeed.com/viewjob?jk=33ae1f1f9d08c546</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>SSIS / Azure Data Factory Engineer</t>
+          <t>Senior Platform/DevOps Engineer (Kubernetes-Linux)</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>ARMADA</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Renton, WA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,34 +3181,34 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Blob Storage, Scala, SQL Server, ETL, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85c3cae0c83282a2</t>
+          <t>https://www.indeed.com/viewjob?jk=d25130b996402485</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Data Engineer Biloxi 5139</t>
+          <t>Senior Platform/DevOps Engineer (Kubernetes-Linux)</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Keesler Federal Credit Union</t>
+          <t>ARMADA</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Biloxi, MS, US USA</t>
+          <t>Bothell, WA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,34 +3216,34 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=923871eb4e708d96</t>
+          <t>https://www.indeed.com/viewjob?jk=b6f9224460f3210c</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Senior Platform/DevOps Engineer (Kubernetes-Linux)</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Mango Chamba, LLC</t>
+          <t>ARMADA</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Redmond, WA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,17 +3251,17 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, Snowflake, Time Travel, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76b38f99ba86c67f</t>
+          <t>https://www.indeed.com/viewjob?jk=b86c940f686047d8</t>
         </is>
       </c>
     </row>
@@ -3303,17 +3303,17 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Google Cloud Network Engineer</t>
+          <t>Software Engineer - DevOps Mobile</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Maven, Terraform, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8d74c6d08304ab9</t>
+          <t>https://www.indeed.com/viewjob?jk=537b207b8aaf9dd0</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer - Warehouse Management Systems (WMS)</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Staples</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Framingham, MA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,34 +3356,34 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, HBase, Scala, Kafka, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c98f634775f326c6</t>
+          <t>https://www.indeed.com/viewjob?jk=654753ccda866d62</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Sr. Professional, Software Engineering (Python)</t>
+          <t>Sr. Data Architect Specialist</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Cotality</t>
+          <t>SAMYANG AMERICA INC</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Brea, CA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, Tableau, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83e013cc49a29087</t>
+          <t>https://www.indeed.com/viewjob?jk=f2086e3e44cfc021</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Platform/DevOps Engineer (Kubernetes-Linux)</t>
+          <t>Senior IT Architect (Enterprise Applications / Clinical Platforms)</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>ARMADA</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,34 +3426,34 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, EMR, API Gateway, RDS, Azure, Databricks, GCP, Scala, Kafka, Oracle</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b0e9b75e0f5558d</t>
+          <t>https://www.indeed.com/viewjob?jk=beeef27a81e2ec58</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Platform/DevOps Engineer (Kubernetes-Linux)</t>
+          <t>Data Scientist, AI Data Foundations</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>ARMADA</t>
+          <t>MeridianLink</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Sammamish, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,34 +3461,34 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Event Hubs, Unity Catalog, Spark, PySpark, Azure Cosmos DB, ELT</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=efa4e4e3099a0ae2</t>
+          <t>https://www.indeed.com/viewjob?jk=31ee3a3fe27b4bf1</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior Platform/DevOps Engineer (Kubernetes-Linux)</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>ARMADA</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Kirkland, WA, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,34 +3496,34 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, S3, IAM, Databricks, Spark, Scala, DynamoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33ae1f1f9d08c546</t>
+          <t>https://www.indeed.com/viewjob?jk=6f9ad7c8c6b989c1</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior Platform/DevOps Engineer (Kubernetes-Linux)</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>ARMADA</t>
+          <t>Mango Chamba, LLC</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Renton, WA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,77 +3531,77 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, ECS, RDS, Scala, Snowflake, Time Travel, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d25130b996402485</t>
+          <t>https://www.indeed.com/viewjob?jk=76b38f99ba86c67f</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior Platform/DevOps Engineer (Kubernetes-Linux)</t>
+          <t>Senior Full Stack Engineer - Python &amp; React JS</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>ARMADA</t>
+          <t>Checkmate</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Bothell, WA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Scala, PostgreSQL, MySQL, CI/CD, GitHub Actions, Docker, Git, Datadog</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6f9224460f3210c</t>
+          <t>https://www.indeed.com/viewjob?jk=6ba3d00c3fb0ee25</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior Platform/DevOps Engineer (Kubernetes-Linux)</t>
+          <t>Engineer II-Software Development</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>ARMADA</t>
+          <t>Microchip Technology</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Redmond, WA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,67 +3611,67 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b86c940f686047d8</t>
+          <t>https://www.indeed.com/viewjob?jk=3013681a0e1c4f81</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Data Scientist, AI Data Foundations</t>
+          <t>Engineer II-Software Development</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>MeridianLink</t>
+          <t>Microchip Technology</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Event Hubs, Unity Catalog, Spark, PySpark, Azure Cosmos DB, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31ee3a3fe27b4bf1</t>
+          <t>https://www.indeed.com/viewjob?jk=2649d75a044fe7bd</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Graybar</t>
+          <t>Montefiore Einstein</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Clayton, MO, US USA</t>
+          <t>Yonkers, NY, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, ETL, ELT, MLOps, MLflow, CI/CD</t>
+          <t>AWS, S3, RDS, Scala, Snowflake, Data Modeling, ELT, dbt, CI/CD, Git</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,32 +3681,32 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82b455422eee9334</t>
+          <t>https://www.indeed.com/viewjob?jk=9a3ffcafc747cce2</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Senior .NET Engineer</t>
+          <t>FastAPI</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Aspira</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, RDS, Scala, SQL Server, CI/CD, Jenkins, Jenkins</t>
+          <t>RDS, Google Cloud Platform, BigQuery, Vertex AI, Spark, Scala, Spark Streaming, Kafka, CI/CD, Git</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,67 +3716,67 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3201135d0d7e294</t>
+          <t>https://www.indeed.com/viewjob?jk=0bc1141188a8604a</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Software Engineer - DevOps Mobile</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Urology Centers of Alabama</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Maven, Terraform, Docker, Jenkins</t>
+          <t>AWS, EMR, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, ETL</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=537b207b8aaf9dd0</t>
+          <t>https://www.indeed.com/viewjob?jk=28cb24ea6139fcb9</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Software Engineer - Warehouse Management Systems (WMS)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Staples</t>
+          <t>Pearson</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Framingham, MA, US USA</t>
+          <t>Hoboken, NJ, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, HBase, Scala, Kafka, NoSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Scala, MongoDB, DynamoDB, Data Modeling, ETL, ELT, DataOps, CI/CD</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,32 +3786,32 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=654753ccda866d62</t>
+          <t>https://www.indeed.com/viewjob?jk=05547d65aabdfcf0</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Sr. Data Architect Specialist</t>
+          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>SAMYANG AMERICA INC</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Brea, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,32 +3821,32 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2086e3e44cfc021</t>
+          <t>https://www.indeed.com/viewjob?jk=34c37a226b547d01</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Full Stack Product Engineer (Java)</t>
+          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Allstate Insurance</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, ELT, CI/CD, Git</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,67 +3856,67 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d15adff582efc740</t>
+          <t>https://www.indeed.com/viewjob?jk=e7d77afce6f60e6f</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Databricks, Spark, Scala, DynamoDB, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f9ad7c8c6b989c1</t>
+          <t>https://www.indeed.com/viewjob?jk=225c5a8131dc6595</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>QA Analyst / ETL Tester</t>
+          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>CSpring</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Springfield, IL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>RDS, Azure, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Data Modeling, Snowflake Schema, ETL, CI/CD</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,59 +3926,59 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ebf7b3987a302e8</t>
+          <t>https://www.indeed.com/viewjob?jk=301dbd1e2eb0bb70</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>DOCSIS Testing Engineer</t>
+          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Oracle, MongoDB, Splunk, CI/CD, Jenkins, Kubernetes, Jenkins</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3102561596c9491c</t>
+          <t>https://www.indeed.com/viewjob?jk=d88e7121c2db79d6</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer - Python &amp; React JS</t>
+          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Checkmate</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,34 +3986,34 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, PostgreSQL, MySQL, CI/CD, GitHub Actions, Docker, Git, Datadog</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ba3d00c3fb0ee25</t>
+          <t>https://www.indeed.com/viewjob?jk=18d3f9fdcfa07035</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Engineer II-Software Development</t>
+          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Microchip Technology</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLOps, CI/CD</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3013681a0e1c4f81</t>
+          <t>https://www.indeed.com/viewjob?jk=9d2d16258cfd6718</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Engineer II-Software Development</t>
+          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Microchip Technology</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLOps, CI/CD</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,19 +4066,19 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2649d75a044fe7bd</t>
+          <t>https://www.indeed.com/viewjob?jk=5be8f9b4535b406c</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - VAULT</t>
+          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Bloomberg</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Hive, Spark, Scala, Kafka, Cassandra</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,24 +4101,24 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d744cfcd1fce896</t>
+          <t>https://www.indeed.com/viewjob?jk=26ef52c65261360a</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Litera</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,34 +4126,34 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, Scala, Snowflake, NoSQL, Data Modeling, ETL, ELT</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cdf1ca20dc48c20f</t>
+          <t>https://www.indeed.com/viewjob?jk=f9240b7b96545a4d</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Senior Engineer, AI</t>
+          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Harman</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Novi, MI, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,34 +4161,34 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a91d05d9ba98a3a</t>
+          <t>https://www.indeed.com/viewjob?jk=42ae72f7d4a97700</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Montefiore Einstein</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Yonkers, NY, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,34 +4196,34 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, Snowflake, Data Modeling, ELT, dbt, CI/CD, Git</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a3ffcafc747cce2</t>
+          <t>https://www.indeed.com/viewjob?jk=dab5b1b68cc6402c</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>FastAPI</t>
+          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,34 +4231,34 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, BigQuery, Vertex AI, Spark, Scala, Spark Streaming, Kafka, CI/CD, Git</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0bc1141188a8604a</t>
+          <t>https://www.indeed.com/viewjob?jk=fde8d1831ca7f9b7</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Urology Centers of Alabama</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, ETL</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,24 +4276,24 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28cb24ea6139fcb9</t>
+          <t>https://www.indeed.com/viewjob?jk=7a056659ad4aebd2</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Pearson</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Hoboken, NJ, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, MongoDB, DynamoDB, Data Modeling, ETL, ELT, DataOps, CI/CD</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05547d65aabdfcf0</t>
+          <t>https://www.indeed.com/viewjob?jk=e5402962c321dcba</t>
         </is>
       </c>
     </row>
@@ -4328,7 +4328,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34c37a226b547d01</t>
+          <t>https://www.indeed.com/viewjob?jk=f45ad39ec1fe503a</t>
         </is>
       </c>
     </row>
@@ -4363,7 +4363,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7d77afce6f60e6f</t>
+          <t>https://www.indeed.com/viewjob?jk=86cfc919b4ccc768</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=225c5a8131dc6595</t>
+          <t>https://www.indeed.com/viewjob?jk=c9a866cff6a0e3bd</t>
         </is>
       </c>
     </row>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=301dbd1e2eb0bb70</t>
+          <t>https://www.indeed.com/viewjob?jk=ab68f1e4ba82ad10</t>
         </is>
       </c>
     </row>
@@ -4468,7 +4468,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d88e7121c2db79d6</t>
+          <t>https://www.indeed.com/viewjob?jk=df163d5906a30146</t>
         </is>
       </c>
     </row>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4521,7 +4521,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18d3f9fdcfa07035</t>
+          <t>https://www.indeed.com/viewjob?jk=2f0c32c0bdf67710</t>
         </is>
       </c>
     </row>
@@ -4538,7 +4538,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d2d16258cfd6718</t>
+          <t>https://www.indeed.com/viewjob?jk=25f63312ec2e267e</t>
         </is>
       </c>
     </row>
@@ -4573,7 +4573,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4591,7 +4591,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5be8f9b4535b406c</t>
+          <t>https://www.indeed.com/viewjob?jk=be379ec08f5c5e6f</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26ef52c65261360a</t>
+          <t>https://www.indeed.com/viewjob?jk=8deeb1ab1ebcdccd</t>
         </is>
       </c>
     </row>
@@ -4643,7 +4643,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4661,7 +4661,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9240b7b96545a4d</t>
+          <t>https://www.indeed.com/viewjob?jk=92aa87419ba8e5df</t>
         </is>
       </c>
     </row>
@@ -4678,7 +4678,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42ae72f7d4a97700</t>
+          <t>https://www.indeed.com/viewjob?jk=da334d3b3eda0eb4</t>
         </is>
       </c>
     </row>
@@ -4713,7 +4713,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4731,7 +4731,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dab5b1b68cc6402c</t>
+          <t>https://www.indeed.com/viewjob?jk=2c314e6df20a4157</t>
         </is>
       </c>
     </row>
@@ -4748,7 +4748,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fde8d1831ca7f9b7</t>
+          <t>https://www.indeed.com/viewjob?jk=b90a165cff732e70</t>
         </is>
       </c>
     </row>
@@ -4783,7 +4783,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4801,7 +4801,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a056659ad4aebd2</t>
+          <t>https://www.indeed.com/viewjob?jk=26bc98921360165c</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4836,7 +4836,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5402962c321dcba</t>
+          <t>https://www.indeed.com/viewjob?jk=c5359f322821abe9</t>
         </is>
       </c>
     </row>
@@ -4853,7 +4853,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f45ad39ec1fe503a</t>
+          <t>https://www.indeed.com/viewjob?jk=562ea8307dd5c91d</t>
         </is>
       </c>
     </row>
@@ -4888,7 +4888,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4906,7 +4906,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86cfc919b4ccc768</t>
+          <t>https://www.indeed.com/viewjob?jk=70a64e543cdeb49a</t>
         </is>
       </c>
     </row>
@@ -4923,7 +4923,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9a866cff6a0e3bd</t>
+          <t>https://www.indeed.com/viewjob?jk=ed3e28c9a543299a</t>
         </is>
       </c>
     </row>
@@ -4958,7 +4958,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4976,24 +4976,24 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab68f1e4ba82ad10</t>
+          <t>https://www.indeed.com/viewjob?jk=1735f01363643535</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
+          <t>Data Engineer II, Mobile Game Analytics</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Mattel, Inc.</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>El Segundo, CA, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5001,7 +5001,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
+          <t>RDS, Medallion Architecture, GCP, BigQuery, Dimensional Modeling, ETL, dbt, Tableau, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -5011,24 +5011,24 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df163d5906a30146</t>
+          <t>https://www.indeed.com/viewjob?jk=087868e735e87a06</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
+          <t>Senior Data Integration Software Engineer</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5036,34 +5036,34 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, ETL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f0c32c0bdf67710</t>
+          <t>https://www.indeed.com/viewjob?jk=b035b944f2ad4c37</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
+          <t>Senior Data Integration Software Engineer</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5071,34 +5071,34 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, ETL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25f63312ec2e267e</t>
+          <t>https://www.indeed.com/viewjob?jk=9ba6e4aacd5b6631</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
+          <t>Data Integration Software Engineer</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Portsmouth, NH, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5106,34 +5106,34 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, ETL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be379ec08f5c5e6f</t>
+          <t>https://www.indeed.com/viewjob?jk=c4c7e0f49df408be</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
+          <t>Senior Data Integration Software Engineer</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Portsmouth, NH, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5141,34 +5141,34 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, ETL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8deeb1ab1ebcdccd</t>
+          <t>https://www.indeed.com/viewjob?jk=93164fc43ac74193</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
+          <t>Data Integration Software Engineer</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5176,34 +5176,34 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, ETL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92aa87419ba8e5df</t>
+          <t>https://www.indeed.com/viewjob?jk=12a4fd124772d9d2</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
+          <t>Data Integration Software Engineer</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5211,34 +5211,34 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, ETL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da334d3b3eda0eb4</t>
+          <t>https://www.indeed.com/viewjob?jk=c38e2fae9b46f905</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Litera</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5246,34 +5246,34 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
+          <t>RDS, Azure, Databricks, Spark, Scala, Snowflake, NoSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c314e6df20a4157</t>
+          <t>https://www.indeed.com/viewjob?jk=cdf1ca20dc48c20f</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Onspring Technologies, LLC</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Overland Park, KS, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5281,34 +5281,34 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, GCP, HBase, Scala, MongoDB, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b90a165cff732e70</t>
+          <t>https://www.indeed.com/viewjob?jk=1d56a66deeafe00f</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
+          <t>AI Applications Engineer</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>SEEQ</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5316,34 +5316,34 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
+          <t>AWS, Lambda, RDS, Azure, Databricks, Scala, Snowflake, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26bc98921360165c</t>
+          <t>https://www.indeed.com/viewjob?jk=02ed320077d234a1</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
+          <t>Data Scientist, Senior Associate – Product, Experience and Technology (PXT) Analytics Team</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5351,34 +5351,34 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
+          <t>Redshift, RDS, Databricks, Scala, Snowflake, dbt, Tableau, CI/CD, Airflow, Git</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5359f322821abe9</t>
+          <t>https://www.indeed.com/viewjob?jk=4b0bfe4f7e93a067</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
+          <t>Enterprise AI Architect</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Radwell International</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Willingboro, NJ, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5386,34 +5386,34 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, PostgreSQL, MySQL, NoSQL, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=562ea8307dd5c91d</t>
+          <t>https://www.indeed.com/viewjob?jk=56c80236c3727026</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
+          <t>Senior Engineer, AI</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Harman</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Novi, MI, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5421,542 +5421,17 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70a64e543cdeb49a</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D144" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E144" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
-        </is>
-      </c>
-      <c r="F144" t="inlineStr">
-        <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="G144" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ed3e28c9a543299a</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>San Jose, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D145" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E145" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
-        </is>
-      </c>
-      <c r="F145" t="inlineStr">
-        <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="G145" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1735f01363643535</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>Data Engineer II, Mobile Game Analytics</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>Mattel, Inc.</t>
-        </is>
-      </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>El Segundo, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D146" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E146" t="inlineStr">
-        <is>
-          <t>RDS, Medallion Architecture, GCP, BigQuery, Dimensional Modeling, ETL, dbt, Tableau, CI/CD, Airflow</t>
-        </is>
-      </c>
-      <c r="F146" t="inlineStr">
-        <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="G146" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=087868e735e87a06</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>AI Applications Engineer</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>SEEQ</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D147" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E147" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, RDS, Azure, Databricks, Scala, Snowflake, Power BI, Tableau, CI/CD</t>
-        </is>
-      </c>
-      <c r="F147" t="inlineStr">
-        <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="G147" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=02ed320077d234a1</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>Onspring Technologies, LLC</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>Overland Park, KS, US USA</t>
-        </is>
-      </c>
-      <c r="D148" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E148" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, HBase, Scala, MongoDB, NoSQL, CI/CD, Docker</t>
-        </is>
-      </c>
-      <c r="F148" t="inlineStr">
-        <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="G148" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1d56a66deeafe00f</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>Senior Data Integration Software Engineer</t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>Liberty Mutual Insurance</t>
-        </is>
-      </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>Plano, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D149" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E149" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, ETL, CI/CD, Git</t>
-        </is>
-      </c>
-      <c r="F149" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="G149" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b035b944f2ad4c37</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>Senior Data Integration Software Engineer</t>
-        </is>
-      </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>Liberty Mutual Insurance</t>
-        </is>
-      </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>Boston, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D150" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E150" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, ETL, CI/CD, Git</t>
-        </is>
-      </c>
-      <c r="F150" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="G150" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9ba6e4aacd5b6631</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>Data Integration Software Engineer</t>
-        </is>
-      </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>Liberty Mutual Insurance</t>
-        </is>
-      </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>Portsmouth, NH, US USA</t>
-        </is>
-      </c>
-      <c r="D151" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E151" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, ETL, CI/CD, Git</t>
-        </is>
-      </c>
-      <c r="F151" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="G151" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c4c7e0f49df408be</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>Senior Data Integration Software Engineer</t>
-        </is>
-      </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>Liberty Mutual Insurance</t>
-        </is>
-      </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>Portsmouth, NH, US USA</t>
-        </is>
-      </c>
-      <c r="D152" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E152" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, ETL, CI/CD, Git</t>
-        </is>
-      </c>
-      <c r="F152" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="G152" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=93164fc43ac74193</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>Data Integration Software Engineer</t>
-        </is>
-      </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>Liberty Mutual Insurance</t>
-        </is>
-      </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>Boston, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D153" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E153" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, ETL, CI/CD, Git</t>
-        </is>
-      </c>
-      <c r="F153" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="G153" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=12a4fd124772d9d2</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>Data Integration Software Engineer</t>
-        </is>
-      </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>Liberty Mutual Insurance</t>
-        </is>
-      </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>Plano, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D154" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E154" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, ETL, CI/CD, Git</t>
-        </is>
-      </c>
-      <c r="F154" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="G154" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c38e2fae9b46f905</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>Sr. Software Engineer, Full-Stack (Factory Systems)</t>
-        </is>
-      </c>
-      <c r="B155" t="inlineStr">
-        <is>
-          <t>Rivian and Volkswagen Group Technologies</t>
-        </is>
-      </c>
-      <c r="C155" t="inlineStr">
-        <is>
-          <t>Palo Alto, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D155" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E155" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F155" t="inlineStr">
-        <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="G155" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=68c700567606c4e9</t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>Data Scientist, Senior Associate – Product, Experience and Technology (PXT) Analytics Team</t>
-        </is>
-      </c>
-      <c r="B156" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C156" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D156" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E156" t="inlineStr">
-        <is>
-          <t>Redshift, RDS, Databricks, Scala, Snowflake, dbt, Tableau, CI/CD, Airflow, Git</t>
-        </is>
-      </c>
-      <c r="F156" t="inlineStr">
-        <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="G156" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4b0bfe4f7e93a067</t>
-        </is>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="inlineStr">
-        <is>
-          <t>Enterprise AI Architect</t>
-        </is>
-      </c>
-      <c r="B157" t="inlineStr">
-        <is>
-          <t>Radwell International</t>
-        </is>
-      </c>
-      <c r="C157" t="inlineStr">
-        <is>
-          <t>Willingboro, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D157" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E157" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, PostgreSQL, MySQL, NoSQL, MLOps, CI/CD</t>
-        </is>
-      </c>
-      <c r="F157" t="inlineStr">
-        <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="G157" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=56c80236c3727026</t>
-        </is>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="inlineStr">
-        <is>
-          <t>AI Engineer Clinical Data Science</t>
-        </is>
-      </c>
-      <c r="B158" t="inlineStr">
-        <is>
-          <t>Katalyst Healthcares &amp; Life Sciences</t>
-        </is>
-      </c>
-      <c r="C158" t="inlineStr">
-        <is>
-          <t>Manhattan, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D158" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E158" t="inlineStr">
-        <is>
-          <t>RDS, Google Cloud Platform, GCP, Vertex AI, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker, Git</t>
-        </is>
-      </c>
-      <c r="F158" t="inlineStr">
-        <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="G158" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=47a06a95eff2f8b1</t>
+          <t>https://www.indeed.com/viewjob?jk=4a91d05d9ba98a3a</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-05-06.xlsx
+++ b/results/job_matches_2026-05-06.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G143"/>
+  <dimension ref="A1:G133"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,52 +503,52 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Capital Bank, N.A.</t>
+          <t>Analytica</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Rockville, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>19.4</v>
+        <v>18.1</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Data Factory, BigQuery, Spark, Scala, Kafka, Snowflake, SQL Server</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, IAM, RDS, Azure, Databricks</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3488abdd8c4dc725</t>
+          <t>https://www.indeed.com/viewjob?jk=7d9377a4724bf38c</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Google Cloud Data Architect – IAM Data Modernization</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Analytica</t>
+          <t>Recutify Inc.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,7 +556,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, IAM, RDS, Azure, Databricks</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop, HDFS, Hive</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,24 +566,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d9377a4724bf38c</t>
+          <t>https://www.indeed.com/viewjob?jk=047175a85485b584</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Software Engineer, Cloud Infrastructure (Multiple Seniority Levels)</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>SmartVault Corporation</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>San Carlos, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, SQS, ECS, IAM, RDS</t>
+          <t>AWS, Lambda, S3, SQS, SNS, ECS, RDS, HBase, Scala, PostgreSQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,42 +601,42 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07cee960b10bf15e</t>
+          <t>https://www.indeed.com/viewjob?jk=58fb938f03dcac58</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Azure Network Engineer</t>
+          <t>Software Engineer, Cloud Infrastructure (Multiple Seniority Levels)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>San Carlos, CA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Event Hubs, Unity Catalog, Medallion Architecture, Spark, PySpark</t>
+          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, SQS, ECS, IAM, RDS</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4c4141e761a1d57</t>
+          <t>https://www.indeed.com/viewjob?jk=07cee960b10bf15e</t>
         </is>
       </c>
     </row>
@@ -678,17 +678,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Compliance, Senior Backend Engineer (Java &amp; ETL Specialist), Dallas, Associate</t>
+          <t>Azure Network Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MongoDB</t>
+          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Event Hubs, Unity Catalog, Medallion Architecture, Spark, PySpark</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e21fade0470597e2</t>
+          <t>https://www.indeed.com/viewjob?jk=b4c4141e761a1d57</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Compliance, Senior Backend Engineer (Java &amp; ETL Specialist), Dallas, Associate</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>DocuSign</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Redshift, SNS, RDS, BigQuery, Hadoop, Spark, Scala, Snowflake, Oracle</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1636bf2e2935fd54</t>
+          <t>https://www.indeed.com/viewjob?jk=e21fade0470597e2</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Sr Site Reliability Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Commence</t>
+          <t>DocuSign</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Leesburg, VA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, NoSQL, ETL, ELT</t>
+          <t>AWS, Redshift, SNS, RDS, BigQuery, Hadoop, Spark, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9093ede7f2269db2</t>
+          <t>https://www.indeed.com/viewjob?jk=1636bf2e2935fd54</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Sr Data Engineer, Python + Spark (Data Federation skillset - Data Lakehouse - Eg: Starburst) - New York</t>
+          <t>Sr Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Photon</t>
+          <t>Commence</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Leesburg, VA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,34 +801,34 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, S3, Azure, Databricks, Medallion Architecture, GCP, Spark, PySpark</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, NoSQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7767a92d7d08a3b</t>
+          <t>https://www.indeed.com/viewjob?jk=9093ede7f2269db2</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Databricks Engineer and Architect</t>
+          <t>Sr Data Engineer, Python + Spark (Data Federation skillset - Data Lakehouse - Eg: Starburst) - New York</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Lincoln Financial Group</t>
+          <t>Photon</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Radnor, PA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,34 +836,34 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, RDS, Databricks, Unity Catalog</t>
+          <t>AWS, Glue, EMR, S3, Azure, Databricks, Medallion Architecture, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7862c3c59e06d56</t>
+          <t>https://www.indeed.com/viewjob?jk=f7767a92d7d08a3b</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Databricks Engineer and Architect</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Lincoln Financial Group</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Radnor, PA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,34 +871,34 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, RDS, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, RDS, Databricks, Unity Catalog</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df1902d36083d34f</t>
+          <t>https://www.indeed.com/viewjob?jk=d7862c3c59e06d56</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior AI Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,34 +906,34 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, RDS, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, Redshift, RDS, GCP, BigQuery, Hadoop, Hive, Spark, Snowflake, MLOps</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cb867686433b7a1</t>
+          <t>https://www.indeed.com/viewjob?jk=93e711d09b751f9f</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior AI Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,34 +941,34 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, RDS, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, Redshift, RDS, GCP, BigQuery, Hadoop, Hive, Spark, Snowflake, MLOps</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3aeafc948a2f0f6c</t>
+          <t>https://www.indeed.com/viewjob?jk=59f7199947e52d0f</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior AI Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,34 +976,34 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, RDS, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, Redshift, RDS, GCP, BigQuery, Hadoop, Hive, Spark, Snowflake, MLOps</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c45b322f3e5694ad</t>
+          <t>https://www.indeed.com/viewjob?jk=3191f6daeeba1ad3</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Software Engineer Intern</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Norstella</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,217 +1011,217 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Azure, Blob Storage, GCP, PostgreSQL</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, RDS, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49a129c7a487aae4</t>
+          <t>https://www.indeed.com/viewjob?jk=df1902d36083d34f</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Software Engineer, Data Engineering</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Cambridge Mobile Telematics</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Redshift, S3, SQS, SNS, RDS, Databricks, Spark</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, RDS, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72e8b54f46d552d4</t>
+          <t>https://www.indeed.com/viewjob?jk=5cb867686433b7a1</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>API Threat Intelligence Analyst</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Azure, Google Cloud Platform, Kafka, NoSQL, Data Modeling, ETL, Talend, Tableau, Splunk, MicroStrategy</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, RDS, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e918fa70b2a1920e</t>
+          <t>https://www.indeed.com/viewjob?jk=3aeafc948a2f0f6c</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Backend (Python)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Azure, Google Cloud Platform, Kafka, NoSQL, Data Modeling, ETL, Talend, Tableau, Splunk, MicroStrategy</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, RDS, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d711bd4394cb404e</t>
+          <t>https://www.indeed.com/viewjob?jk=c45b322f3e5694ad</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer Intern</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Wavicle Data Solutions</t>
+          <t>Norstella</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, Azure, Databricks, GCP, Hadoop, Spark, PySpark, Scala</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Azure, Blob Storage, GCP, PostgreSQL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a435f9b94ff5d489</t>
+          <t>https://www.indeed.com/viewjob?jk=49a129c7a487aae4</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Databricks)</t>
+          <t>Software Engineer, Data Engineering</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Infinitive Inc</t>
+          <t>Cambridge Mobile Telematics</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, S3, Azure, Databricks, Unity Catalog, GCP</t>
+          <t>AWS, Glue, Kinesis, Redshift, S3, SQS, SNS, RDS, Databricks, Spark</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aee5e62267dbbb6c</t>
+          <t>https://www.indeed.com/viewjob?jk=72e8b54f46d552d4</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Software Developer II</t>
+          <t>API Threat Intelligence Analyst</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Floor &amp; Decor</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL, Splunk, CI/CD</t>
+          <t>Azure, Google Cloud Platform, Kafka, NoSQL, Data Modeling, ETL, Talend, Tableau, Splunk, MicroStrategy</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,42 +1231,42 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a21fec712255df2</t>
+          <t>https://www.indeed.com/viewjob?jk=e918fa70b2a1920e</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Sr. Streaming Engineer</t>
+          <t>Backend (Python)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Ness Digital Engineering</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.9</v>
+        <v>15.3</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, IAM, RDS, Spark, Scala, Kafka, NoSQL, Splunk</t>
+          <t>Azure, Google Cloud Platform, Kafka, NoSQL, Data Modeling, ETL, Talend, Tableau, Splunk, MicroStrategy</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f90fa0ab3164dcd1</t>
+          <t>https://www.indeed.com/viewjob?jk=d711bd4394cb404e</t>
         </is>
       </c>
     </row>
@@ -1278,20 +1278,20 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Wavicle Data Solutions</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Oak Brook, IL, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, SQL Server, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, Lambda, Redshift, Azure, Databricks, GCP, Hadoop, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b748ea05c0bbf37</t>
+          <t>https://www.indeed.com/viewjob?jk=a435f9b94ff5d489</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Software Developer II</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>SOFTILITY INC</t>
+          <t>Floor &amp; Decor</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD</t>
+          <t>RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3faf69463891ca3f</t>
+          <t>https://www.indeed.com/viewjob?jk=4a21fec712255df2</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>SOFTILITY INC</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Oracle, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,14 +1371,14 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d61e7d7639acc074</t>
+          <t>https://www.indeed.com/viewjob?jk=3faf69463891ca3f</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>MLOps Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,34 +1396,34 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Oracle, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56f1aa48ba26ae3c</t>
+          <t>https://www.indeed.com/viewjob?jk=d61e7d7639acc074</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Business Intelligence Developer (Healthcare Data, EDI, ETL)</t>
+          <t>Sr. Streaming Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>MicroHealth LLC</t>
+          <t>Ness Digital Engineering</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Vienna, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Scala, Snowflake, SQL Server, PostgreSQL, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, Kinesis, S3, IAM, RDS, Spark, Scala, Kafka, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,59 +1441,59 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ba3d7e28ab6494c</t>
+          <t>https://www.indeed.com/viewjob?jk=f90fa0ab3164dcd1</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Software Engineer III - PySpark/AWS</t>
+          <t>MLOps Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Databricks, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e02c112e835bf775</t>
+          <t>https://www.indeed.com/viewjob?jk=56f1aa48ba26ae3c</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Data analyst</t>
+          <t>Software Engineer III - PySpark/AWS</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Brentwood, TN, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, ETL</t>
+          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Databricks, Spark, PySpark</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7ed131be5ba5e96</t>
+          <t>https://www.indeed.com/viewjob?jk=e02c112e835bf775</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Mid- Level Data Engineer</t>
+          <t>Senior Data analyst</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Vantage Data Centers</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Brentwood, TN, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Spark, PySpark, Scala, Data Modeling, Dimension Tables, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a35201e2c76024aa</t>
+          <t>https://www.indeed.com/viewjob?jk=b7ed131be5ba5e96</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer, Data &amp; Analytics</t>
+          <t>Mid- Level Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Blizzard Entertainment</t>
+          <t>Vantage Data Centers</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,69 +1571,69 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Dataflow, Kafka, dbt, CI/CD, Jenkins, GitHub Actions</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Spark, PySpark, Scala, Data Modeling, Dimension Tables, ETL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f56eabb97941a731</t>
+          <t>https://www.indeed.com/viewjob?jk=a35201e2c76024aa</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Solutions Engineer</t>
+          <t>Senior Site Reliability Engineer, Data &amp; Analytics</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Epsilon</t>
+          <t>Blizzard Entertainment</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Hadoop, HDFS, Spark, Scala, Kafka, CI/CD, Docker</t>
+          <t>AWS, RDS, GCP, BigQuery, Dataflow, Kafka, dbt, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22c6237fafdb9308</t>
+          <t>https://www.indeed.com/viewjob?jk=f56eabb97941a731</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Kafka Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>vectorsoft</t>
+          <t>Cloud Ramp</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Kafka, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3bdce3e69ca5f6c4</t>
+          <t>https://www.indeed.com/viewjob?jk=015ea5d5c6dc0865</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Data Engineer / Data Platform Engineer Internship Fall 2026 Semester at the Dow Delivery Center at UIUC (Champaign, IL)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Miami Marlins</t>
+          <t>DOW</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Kankakee, IL, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, GCP, Scala, Snowflake, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff87deef607d5450</t>
+          <t>https://www.indeed.com/viewjob?jk=38a9f118a8e8f0ac</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Data Solutions Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Paramount</t>
+          <t>Epsilon</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Fort Lauderdale, FL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,34 +1711,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Dataflow, Scala, MongoDB, NoSQL, Docker, Kubernetes</t>
+          <t>AWS, RDS, Databricks, Hadoop, HDFS, Spark, Scala, Kafka, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a12925c69dfc7bed</t>
+          <t>https://www.indeed.com/viewjob?jk=22c6237fafdb9308</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Data Engineer / Data Platform Engineer Internship Fall 2026 Semester at the Dow Delivery Center at UIUC (Champaign, IL)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>DOW</t>
+          <t>vectorsoft</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Kankakee, IL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38a9f118a8e8f0ac</t>
+          <t>https://www.indeed.com/viewjob?jk=3bdce3e69ca5f6c4</t>
         </is>
       </c>
     </row>
@@ -1798,17 +1798,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Multi-Cloud Network Architect V</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Moore</t>
+          <t>Availity, LLC.</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Westminster, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,34 +1816,34 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT, dbt</t>
+          <t>AWS, Lambda, Step Functions, SQS, SNS, API Gateway, RDS, Azure, Scala, Oracle</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8c5af154805cd95</t>
+          <t>https://www.indeed.com/viewjob?jk=9384fbb0ce6b583b</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Python/PySpark/AWS)</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Infinitive Inc</t>
+          <t>Miami Marlins</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,34 +1851,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Azure, Spark, PySpark, Scala, Spark Streaming, Data Modeling, ETL, CI/CD, Jenkins</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, GCP, Scala, Snowflake, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2025-02-18</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45083db400feff94</t>
+          <t>https://www.indeed.com/viewjob?jk=ff87deef607d5450</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Data Engineer (Python/PySpark/AWS)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Infinitive Inc</t>
+          <t>Mustang Cat</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,34 +1886,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Azure, Spark, PySpark, Scala, Spark Streaming, Data Modeling, ETL, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, Fact Tables, ETL</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2025-01-27</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e742c4bedd2037b</t>
+          <t>https://www.indeed.com/viewjob?jk=182574da3c06479e</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Mustang Cat</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, Fact Tables, ETL</t>
+          <t>IAM, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage, MySQL, Splunk, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=182574da3c06479e</t>
+          <t>https://www.indeed.com/viewjob?jk=52b0e598b9832c43</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Terra Quantum</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage, MySQL, Splunk, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52b0e598b9832c43</t>
+          <t>https://www.indeed.com/viewjob?jk=15eb90498bcba242</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Full Stack Engineer, Experienced</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Terra Quantum</t>
+          <t>Blue Shield of California</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,24 +1991,24 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15eb90498bcba242</t>
+          <t>https://www.indeed.com/viewjob?jk=93fe5a9749607800</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Full Stack Engineer, Experienced</t>
+          <t>Full Stack Engineer, Senior</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2036,14 +2036,14 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93fe5a9749607800</t>
+          <t>https://www.indeed.com/viewjob?jk=bcc6fa1baccf83e5</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Full Stack Engineer, Senior</t>
+          <t>Full Stack Engineer, Consultant</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bcc6fa1baccf83e5</t>
+          <t>https://www.indeed.com/viewjob?jk=a3a7d3c5d7336760</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Full Stack Engineer, Consultant</t>
+          <t>Artificial Intelligence/Machine Learning Data Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Blue Shield of California</t>
+          <t>Accenture</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,34 +2096,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, NoSQL, CI/CD, Terraform</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLflow</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3a7d3c5d7336760</t>
+          <t>https://www.indeed.com/viewjob?jk=b20f553bf3557e7a</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Summer Intern, Platform Engineering</t>
+          <t>Data Warehouse Developer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Outfront Media</t>
+          <t>New England Life Care</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Canton, MA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,34 +2131,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD, Docker</t>
+          <t>AWS, Azure, Data Factory, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, Fact Tables, Dimension Tables</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2aa35bb9483f10ad</t>
+          <t>https://www.indeed.com/viewjob?jk=b61fd67550df6c0b</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Artificial Intelligence/Machine Learning Data Engineer</t>
+          <t>Data Warehouse Developer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Accenture</t>
+          <t>New England Life Care</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Woburn, MA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLflow</t>
+          <t>AWS, Azure, Data Factory, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, Fact Tables, Dimension Tables</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b20f553bf3557e7a</t>
+          <t>https://www.indeed.com/viewjob?jk=59fae488bfb069d7</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Canton, MA, US USA</t>
+          <t>Scarborough, ME, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b61fd67550df6c0b</t>
+          <t>https://www.indeed.com/viewjob?jk=c511d00669b005c9</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Woburn, MA, US USA</t>
+          <t>Concord, NH, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59fae488bfb069d7</t>
+          <t>https://www.indeed.com/viewjob?jk=9e02714fa8eb1d57</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Data Warehouse Developer</t>
+          <t>Cloud Network Architect</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>New England Life Care</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Scarborough, ME, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, Fact Tables, Dimension Tables</t>
+          <t>Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c511d00669b005c9</t>
+          <t>https://www.indeed.com/viewjob?jk=e874dfda20060e92</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Data Warehouse Developer</t>
+          <t>Azure Network Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>New England Life Care</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Concord, NH, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, Fact Tables, Dimension Tables</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Event Hubs, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e02714fa8eb1d57</t>
+          <t>https://www.indeed.com/viewjob?jk=05dcb2c14af656a8</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Mid-Level Software Engineer</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>State Farm</t>
+          <t>Clayco</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Bloomington, IL, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, MongoDB, CI/CD, Terraform</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da08c5cf76c3287c</t>
+          <t>https://www.indeed.com/viewjob?jk=61cc49187bd6e01d</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Cloud Network Architect</t>
+          <t>Data Systems Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Central Health</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e874dfda20060e92</t>
+          <t>https://www.indeed.com/viewjob?jk=41eed22913274d81</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Azure Network Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Laural Parke</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Event Hubs, Spark, PySpark, Scala, ETL</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05dcb2c14af656a8</t>
+          <t>https://www.indeed.com/viewjob?jk=19dac2449c2108f4</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Mid-Level Software Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Clayco</t>
+          <t>State Farm</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Bloomington, IL, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, MongoDB, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61cc49187bd6e01d</t>
+          <t>https://www.indeed.com/viewjob?jk=da08c5cf76c3287c</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Data Systems Engineer</t>
+          <t>DevOps / AgentOps Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Central Health</t>
+          <t>Revelation Pharma</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, Lambda, Step Functions, S3, ECS, IAM, RDS, Azure, Vertex AI, CI/CD</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41eed22913274d81</t>
+          <t>https://www.indeed.com/viewjob?jk=265eee1218fa6fae</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Laural Parke</t>
+          <t>SBC</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,34 +2516,34 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, S3, API Gateway, RDS, Azure, Scala, SQL Server, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19dac2449c2108f4</t>
+          <t>https://www.indeed.com/viewjob?jk=e8ce310e3e5771dd</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>DevOps / AgentOps Engineer</t>
+          <t>Cloud Networking Consultant</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Revelation Pharma</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>KS, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, ECS, IAM, RDS, Azure, Vertex AI, CI/CD</t>
+          <t>RDS, Spark, Scala, Kafka, Snowflake, Splunk, CI/CD, Jenkins, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=265eee1218fa6fae</t>
+          <t>https://www.indeed.com/viewjob?jk=05bc8504be04f7d2</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Victory Live</t>
+          <t>Montefiore Einstein</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Yonkers, NY, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Snowflake, SQL Server, DynamoDB, ELT, dbt, Terraform</t>
+          <t>AWS, RDS, Medallion Architecture, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ELT, dbt</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1c259f0b00d1299</t>
+          <t>https://www.indeed.com/viewjob?jk=2d972b31a0cae529</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Cloud Networking Consultant</t>
+          <t>Snowflake/Tableau Developer / Dallas Texas</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>FirstNet Global</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>KS, US USA</t>
+          <t>Napa, CA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RDS, Spark, Scala, Kafka, Snowflake, Splunk, CI/CD, Jenkins, Docker, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05bc8504be04f7d2</t>
+          <t>https://www.indeed.com/viewjob?jk=a4ab4d99e440e9b4</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Montefiore Einstein</t>
+          <t>Klaxontech</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Yonkers, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Medallion Architecture, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,32 +2666,32 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d972b31a0cae529</t>
+          <t>https://www.indeed.com/viewjob?jk=193935f590ab7020</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Snowflake/Tableau Developer / Dallas Texas</t>
+          <t>Entry-Level Cloud Engineering Specialist</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>FirstNet Global</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Napa, CA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,32 +2701,32 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4ab4d99e440e9b4</t>
+          <t>https://www.indeed.com/viewjob?jk=43d9f4abcf179d24</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Data Scientist, AI Data Foundations</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Klaxontech</t>
+          <t>MeridianLink</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Event Hubs, Unity Catalog, Spark, PySpark, Azure Cosmos DB, ELT</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=193935f590ab7020</t>
+          <t>https://www.indeed.com/viewjob?jk=2390498da25e9e01</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data Engineer with Python</t>
+          <t>SSIS / Azure Data Factory Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Tardus inc</t>
+          <t>Intone Networks</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Blob Storage, Scala, SQL Server, ETL, Power BI</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80c45bbb6f084151</t>
+          <t>https://www.indeed.com/viewjob?jk=85c3cae0c83282a2</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer with Python</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Tardus inc</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Vertex AI, Scala, Data Modeling, Jenkins, Terraform, Jenkins</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bbf23a169f18dbc</t>
+          <t>https://www.indeed.com/viewjob?jk=80c45bbb6f084151</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer Biloxi 5139</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Keesler Federal Credit Union</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Biloxi, MS, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Vertex AI, Scala, Data Modeling, Jenkins, Terraform, Jenkins</t>
+          <t>RDS, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, CI/CD, Git</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b05514433681d42</t>
+          <t>https://www.indeed.com/viewjob?jk=923871eb4e708d96</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Clark Construction</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, dbt</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f199bfc2e975b58</t>
+          <t>https://www.indeed.com/viewjob?jk=c98f634775f326c6</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Data Scientist, AI Data Foundations</t>
+          <t>Sr. Professional, Software Engineering (Python)</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>MeridianLink</t>
+          <t>Cotality</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Event Hubs, Unity Catalog, Spark, PySpark, Azure Cosmos DB, ELT</t>
+          <t>RDS, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, Tableau, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2390498da25e9e01</t>
+          <t>https://www.indeed.com/viewjob?jk=83e013cc49a29087</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>SSIS / Azure Data Factory Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>Business Wire</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Blob Storage, Scala, SQL Server, ETL, Power BI</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85c3cae0c83282a2</t>
+          <t>https://www.indeed.com/viewjob?jk=282fdfffaf16a91c</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Data Engineer Biloxi 5139</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Keesler Federal Credit Union</t>
+          <t>Mesa Labs</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Biloxi, MS, US USA</t>
+          <t>Lakewood, CO, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, PostgreSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=923871eb4e708d96</t>
+          <t>https://www.indeed.com/viewjob?jk=71d54ee3197b525a</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer - DevOps Mobile</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Maven, Terraform, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c98f634775f326c6</t>
+          <t>https://www.indeed.com/viewjob?jk=537b207b8aaf9dd0</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Sr. Professional, Software Engineering (Python)</t>
+          <t>Software Engineer - Warehouse Management Systems (WMS)</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Cotality</t>
+          <t>Staples</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Framingham, MA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, Tableau, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, HBase, Scala, Kafka, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83e013cc49a29087</t>
+          <t>https://www.indeed.com/viewjob?jk=654753ccda866d62</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Platform/DevOps Engineer (Kubernetes-Linux)</t>
+          <t>Sr. Data Architect Specialist</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>ARMADA</t>
+          <t>SAMYANG AMERICA INC</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Brea, CA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b0e9b75e0f5558d</t>
+          <t>https://www.indeed.com/viewjob?jk=f2086e3e44cfc021</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Platform/DevOps Engineer (Kubernetes-Linux)</t>
+          <t>Senior IT Architect (Enterprise Applications / Clinical Platforms)</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>ARMADA</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Sammamish, WA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,34 +3111,34 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, EMR, API Gateway, RDS, Azure, Databricks, GCP, Scala, Kafka, Oracle</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=efa4e4e3099a0ae2</t>
+          <t>https://www.indeed.com/viewjob?jk=beeef27a81e2ec58</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Platform/DevOps Engineer (Kubernetes-Linux)</t>
+          <t>Data Scientist, AI Data Foundations</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>ARMADA</t>
+          <t>MeridianLink</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Kirkland, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Event Hubs, Unity Catalog, Spark, PySpark, Azure Cosmos DB, ELT</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33ae1f1f9d08c546</t>
+          <t>https://www.indeed.com/viewjob?jk=31ee3a3fe27b4bf1</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Platform/DevOps Engineer (Kubernetes-Linux)</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>ARMADA</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Renton, WA, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,34 +3181,34 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, S3, IAM, Databricks, Spark, Scala, DynamoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d25130b996402485</t>
+          <t>https://www.indeed.com/viewjob?jk=6f9ad7c8c6b989c1</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Platform/DevOps Engineer (Kubernetes-Linux)</t>
+          <t>Data Architect (Snowflake)</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>ARMADA</t>
+          <t>Mango Chamba, LLC</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Bothell, WA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,77 +3216,77 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, ECS, RDS, Scala, Snowflake, Time Travel, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6f9224460f3210c</t>
+          <t>https://www.indeed.com/viewjob?jk=76b38f99ba86c67f</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Platform/DevOps Engineer (Kubernetes-Linux)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>ARMADA</t>
+          <t>Montefiore Einstein</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Redmond, WA, US USA</t>
+          <t>Yonkers, NY, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, S3, RDS, Scala, Snowflake, Data Modeling, ELT, dbt, CI/CD, Git</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b86c940f686047d8</t>
+          <t>https://www.indeed.com/viewjob?jk=9a3ffcafc747cce2</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>FastAPI</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Mesa Labs</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Lakewood, CO, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, PostgreSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>RDS, Google Cloud Platform, BigQuery, Vertex AI, Spark, Scala, Spark Streaming, Kafka, CI/CD, Git</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,67 +3296,67 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71d54ee3197b525a</t>
+          <t>https://www.indeed.com/viewjob?jk=0bc1141188a8604a</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Software Engineer - DevOps Mobile</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Urology Centers of Alabama</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Maven, Terraform, Docker, Jenkins</t>
+          <t>AWS, EMR, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, ETL</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=537b207b8aaf9dd0</t>
+          <t>https://www.indeed.com/viewjob?jk=28cb24ea6139fcb9</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Software Engineer - Warehouse Management Systems (WMS)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Staples</t>
+          <t>Pearson</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Framingham, MA, US USA</t>
+          <t>Hoboken, NJ, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, HBase, Scala, Kafka, NoSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Scala, MongoDB, DynamoDB, Data Modeling, ETL, ELT, DataOps, CI/CD</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,32 +3366,32 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=654753ccda866d62</t>
+          <t>https://www.indeed.com/viewjob?jk=05547d65aabdfcf0</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Sr. Data Architect Specialist</t>
+          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>SAMYANG AMERICA INC</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Brea, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,164 +3401,164 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2086e3e44cfc021</t>
+          <t>https://www.indeed.com/viewjob?jk=34c37a226b547d01</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior IT Architect (Enterprise Applications / Clinical Platforms)</t>
+          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, EMR, API Gateway, RDS, Azure, Databricks, GCP, Scala, Kafka, Oracle</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=beeef27a81e2ec58</t>
+          <t>https://www.indeed.com/viewjob?jk=e7d77afce6f60e6f</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Data Scientist, AI Data Foundations</t>
+          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>MeridianLink</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Event Hubs, Unity Catalog, Spark, PySpark, Azure Cosmos DB, ELT</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31ee3a3fe27b4bf1</t>
+          <t>https://www.indeed.com/viewjob?jk=225c5a8131dc6595</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Databricks, Spark, Scala, DynamoDB, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f9ad7c8c6b989c1</t>
+          <t>https://www.indeed.com/viewjob?jk=301dbd1e2eb0bb70</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Mango Chamba, LLC</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, Snowflake, Time Travel, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76b38f99ba86c67f</t>
+          <t>https://www.indeed.com/viewjob?jk=d88e7121c2db79d6</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer - Python &amp; React JS</t>
+          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Checkmate</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,34 +3566,34 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, PostgreSQL, MySQL, CI/CD, GitHub Actions, Docker, Git, Datadog</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ba3d00c3fb0ee25</t>
+          <t>https://www.indeed.com/viewjob?jk=18d3f9fdcfa07035</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Engineer II-Software Development</t>
+          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Microchip Technology</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLOps, CI/CD</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3013681a0e1c4f81</t>
+          <t>https://www.indeed.com/viewjob?jk=9d2d16258cfd6718</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Engineer II-Software Development</t>
+          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Microchip Technology</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLOps, CI/CD</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2649d75a044fe7bd</t>
+          <t>https://www.indeed.com/viewjob?jk=5be8f9b4535b406c</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Montefiore Einstein</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Yonkers, NY, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,34 +3671,34 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, Snowflake, Data Modeling, ELT, dbt, CI/CD, Git</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a3ffcafc747cce2</t>
+          <t>https://www.indeed.com/viewjob?jk=26ef52c65261360a</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>FastAPI</t>
+          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,34 +3706,34 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, BigQuery, Vertex AI, Spark, Scala, Spark Streaming, Kafka, CI/CD, Git</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0bc1141188a8604a</t>
+          <t>https://www.indeed.com/viewjob?jk=f9240b7b96545a4d</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Urology Centers of Alabama</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, ETL</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28cb24ea6139fcb9</t>
+          <t>https://www.indeed.com/viewjob?jk=42ae72f7d4a97700</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Pearson</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Hoboken, NJ, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, MongoDB, DynamoDB, Data Modeling, ETL, ELT, DataOps, CI/CD</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05547d65aabdfcf0</t>
+          <t>https://www.indeed.com/viewjob?jk=dab5b1b68cc6402c</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34c37a226b547d01</t>
+          <t>https://www.indeed.com/viewjob?jk=fde8d1831ca7f9b7</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7d77afce6f60e6f</t>
+          <t>https://www.indeed.com/viewjob?jk=7a056659ad4aebd2</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=225c5a8131dc6595</t>
+          <t>https://www.indeed.com/viewjob?jk=e5402962c321dcba</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=301dbd1e2eb0bb70</t>
+          <t>https://www.indeed.com/viewjob?jk=f45ad39ec1fe503a</t>
         </is>
       </c>
     </row>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d88e7121c2db79d6</t>
+          <t>https://www.indeed.com/viewjob?jk=86cfc919b4ccc768</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18d3f9fdcfa07035</t>
+          <t>https://www.indeed.com/viewjob?jk=c9a866cff6a0e3bd</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d2d16258cfd6718</t>
+          <t>https://www.indeed.com/viewjob?jk=ab68f1e4ba82ad10</t>
         </is>
       </c>
     </row>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5be8f9b4535b406c</t>
+          <t>https://www.indeed.com/viewjob?jk=df163d5906a30146</t>
         </is>
       </c>
     </row>
@@ -4083,7 +4083,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26ef52c65261360a</t>
+          <t>https://www.indeed.com/viewjob?jk=2f0c32c0bdf67710</t>
         </is>
       </c>
     </row>
@@ -4118,7 +4118,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9240b7b96545a4d</t>
+          <t>https://www.indeed.com/viewjob?jk=25f63312ec2e267e</t>
         </is>
       </c>
     </row>
@@ -4153,7 +4153,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42ae72f7d4a97700</t>
+          <t>https://www.indeed.com/viewjob?jk=be379ec08f5c5e6f</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dab5b1b68cc6402c</t>
+          <t>https://www.indeed.com/viewjob?jk=8deeb1ab1ebcdccd</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fde8d1831ca7f9b7</t>
+          <t>https://www.indeed.com/viewjob?jk=92aa87419ba8e5df</t>
         </is>
       </c>
     </row>
@@ -4258,7 +4258,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a056659ad4aebd2</t>
+          <t>https://www.indeed.com/viewjob?jk=da334d3b3eda0eb4</t>
         </is>
       </c>
     </row>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5402962c321dcba</t>
+          <t>https://www.indeed.com/viewjob?jk=2c314e6df20a4157</t>
         </is>
       </c>
     </row>
@@ -4328,7 +4328,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f45ad39ec1fe503a</t>
+          <t>https://www.indeed.com/viewjob?jk=b90a165cff732e70</t>
         </is>
       </c>
     </row>
@@ -4363,7 +4363,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86cfc919b4ccc768</t>
+          <t>https://www.indeed.com/viewjob?jk=26bc98921360165c</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9a866cff6a0e3bd</t>
+          <t>https://www.indeed.com/viewjob?jk=c5359f322821abe9</t>
         </is>
       </c>
     </row>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab68f1e4ba82ad10</t>
+          <t>https://www.indeed.com/viewjob?jk=562ea8307dd5c91d</t>
         </is>
       </c>
     </row>
@@ -4468,7 +4468,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df163d5906a30146</t>
+          <t>https://www.indeed.com/viewjob?jk=70a64e543cdeb49a</t>
         </is>
       </c>
     </row>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4521,7 +4521,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f0c32c0bdf67710</t>
+          <t>https://www.indeed.com/viewjob?jk=ed3e28c9a543299a</t>
         </is>
       </c>
     </row>
@@ -4538,7 +4538,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4556,24 +4556,24 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25f63312ec2e267e</t>
+          <t>https://www.indeed.com/viewjob?jk=1735f01363643535</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
+          <t>Advisor Solution Architect</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Gainwell Technologies LLC</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,34 +4581,34 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
+          <t>AWS, RDS, Databricks, Hadoop, Spark, Scala, Data Modeling, ETL, ELT, Python</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be379ec08f5c5e6f</t>
+          <t>https://www.indeed.com/viewjob?jk=da2c9fb2e2a16e3d</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Track 25 LLC</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Mesa, AZ, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,34 +4616,34 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
+          <t>RDS, Azure, Medallion Architecture, Spark, PySpark, Scala, Snowflake, dbt, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8deeb1ab1ebcdccd</t>
+          <t>https://www.indeed.com/viewjob?jk=f07569aa8c95b694</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
+          <t>Senior Full Stack Engineer - Python &amp; React JS</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Checkmate</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,34 +4651,34 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
+          <t>AWS, RDS, Scala, PostgreSQL, MySQL, CI/CD, GitHub Actions, Docker, Git, Datadog</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92aa87419ba8e5df</t>
+          <t>https://www.indeed.com/viewjob?jk=6ba3d00c3fb0ee25</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
+          <t>Senior Data Integration Software Engineer</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,34 +4686,34 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, ETL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da334d3b3eda0eb4</t>
+          <t>https://www.indeed.com/viewjob?jk=b035b944f2ad4c37</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
+          <t>Senior Data Integration Software Engineer</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4721,34 +4721,34 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, ETL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c314e6df20a4157</t>
+          <t>https://www.indeed.com/viewjob?jk=9ba6e4aacd5b6631</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
+          <t>Data Integration Software Engineer</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Portsmouth, NH, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4756,34 +4756,34 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, ETL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b90a165cff732e70</t>
+          <t>https://www.indeed.com/viewjob?jk=c4c7e0f49df408be</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
+          <t>Senior Data Integration Software Engineer</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Portsmouth, NH, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4791,34 +4791,34 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, ETL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26bc98921360165c</t>
+          <t>https://www.indeed.com/viewjob?jk=93164fc43ac74193</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
+          <t>Data Integration Software Engineer</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,34 +4826,34 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, ETL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5359f322821abe9</t>
+          <t>https://www.indeed.com/viewjob?jk=12a4fd124772d9d2</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
+          <t>Data Integration Software Engineer</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4861,34 +4861,34 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, ETL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=562ea8307dd5c91d</t>
+          <t>https://www.indeed.com/viewjob?jk=c38e2fae9b46f905</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Litera</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4896,34 +4896,34 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
+          <t>RDS, Azure, Databricks, Spark, Scala, Snowflake, NoSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70a64e543cdeb49a</t>
+          <t>https://www.indeed.com/viewjob?jk=cdf1ca20dc48c20f</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Onspring Technologies, LLC</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Overland Park, KS, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4931,34 +4931,34 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, GCP, HBase, Scala, MongoDB, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed3e28c9a543299a</t>
+          <t>https://www.indeed.com/viewjob?jk=1d56a66deeafe00f</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>GCP Cloud Analytics Engineer - Senior Consultant</t>
+          <t>AI Applications Engineer</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>SEEQ</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4966,34 +4966,34 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake</t>
+          <t>AWS, Lambda, RDS, Azure, Databricks, Scala, Snowflake, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1735f01363643535</t>
+          <t>https://www.indeed.com/viewjob?jk=02ed320077d234a1</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Data Engineer II, Mobile Game Analytics</t>
+          <t>Data Scientist, Senior Associate – Product, Experience and Technology (PXT) Analytics Team</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Mattel, Inc.</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>El Segundo, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5001,34 +5001,34 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>RDS, Medallion Architecture, GCP, BigQuery, Dimensional Modeling, ETL, dbt, Tableau, CI/CD, Airflow</t>
+          <t>Redshift, RDS, Databricks, Scala, Snowflake, dbt, Tableau, CI/CD, Airflow, Git</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=087868e735e87a06</t>
+          <t>https://www.indeed.com/viewjob?jk=4b0bfe4f7e93a067</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Senior Data Integration Software Engineer</t>
+          <t>Enterprise AI Architect</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>Radwell International</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Willingboro, NJ, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5036,34 +5036,34 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, ETL, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, PostgreSQL, MySQL, NoSQL, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b035b944f2ad4c37</t>
+          <t>https://www.indeed.com/viewjob?jk=56c80236c3727026</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Senior Data Integration Software Engineer</t>
+          <t>Senior Engineer, AI</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>Harman</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Novi, MI, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5071,365 +5071,15 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, ETL, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9ba6e4aacd5b6631</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>Data Integration Software Engineer</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>Liberty Mutual Insurance</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>Portsmouth, NH, US USA</t>
-        </is>
-      </c>
-      <c r="D134" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, ETL, CI/CD, Git</t>
-        </is>
-      </c>
-      <c r="F134" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="G134" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c4c7e0f49df408be</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>Senior Data Integration Software Engineer</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>Liberty Mutual Insurance</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>Portsmouth, NH, US USA</t>
-        </is>
-      </c>
-      <c r="D135" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E135" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, ETL, CI/CD, Git</t>
-        </is>
-      </c>
-      <c r="F135" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="G135" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=93164fc43ac74193</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>Data Integration Software Engineer</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>Liberty Mutual Insurance</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>Boston, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D136" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E136" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, ETL, CI/CD, Git</t>
-        </is>
-      </c>
-      <c r="F136" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="G136" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=12a4fd124772d9d2</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>Data Integration Software Engineer</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>Liberty Mutual Insurance</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>Plano, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D137" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E137" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, ETL, CI/CD, Git</t>
-        </is>
-      </c>
-      <c r="F137" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="G137" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c38e2fae9b46f905</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>Senior Data Architect</t>
-        </is>
-      </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>Litera</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>Denver, CO, US USA</t>
-        </is>
-      </c>
-      <c r="D138" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, Spark, Scala, Snowflake, NoSQL, Data Modeling, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F138" t="inlineStr">
-        <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="G138" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=cdf1ca20dc48c20f</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>Onspring Technologies, LLC</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>Overland Park, KS, US USA</t>
-        </is>
-      </c>
-      <c r="D139" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E139" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, HBase, Scala, MongoDB, NoSQL, CI/CD, Docker</t>
-        </is>
-      </c>
-      <c r="F139" t="inlineStr">
-        <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="G139" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1d56a66deeafe00f</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>AI Applications Engineer</t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>SEEQ</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D140" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E140" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, RDS, Azure, Databricks, Scala, Snowflake, Power BI, Tableau, CI/CD</t>
-        </is>
-      </c>
-      <c r="F140" t="inlineStr">
-        <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="G140" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=02ed320077d234a1</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>Data Scientist, Senior Associate – Product, Experience and Technology (PXT) Analytics Team</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D141" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E141" t="inlineStr">
-        <is>
-          <t>Redshift, RDS, Databricks, Scala, Snowflake, dbt, Tableau, CI/CD, Airflow, Git</t>
-        </is>
-      </c>
-      <c r="F141" t="inlineStr">
-        <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="G141" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4b0bfe4f7e93a067</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>Enterprise AI Architect</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>Radwell International</t>
-        </is>
-      </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>Willingboro, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D142" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, PostgreSQL, MySQL, NoSQL, MLOps, CI/CD</t>
-        </is>
-      </c>
-      <c r="F142" t="inlineStr">
-        <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="G142" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=56c80236c3727026</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>Senior Engineer, AI</t>
-        </is>
-      </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>Harman</t>
-        </is>
-      </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>Novi, MI, US USA</t>
-        </is>
-      </c>
-      <c r="D143" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E143" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F143" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="G143" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=4a91d05d9ba98a3a</t>
         </is>
